--- a/docs/control/data.xlsx
+++ b/docs/control/data.xlsx
@@ -239,8 +239,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="TodoChecklist" displayName="TodoChecklist" ref="A1:D111" headerRowCount="1">
-  <autoFilter ref="A1:D111"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="TodoChecklist" displayName="TodoChecklist" ref="A1:D114" headerRowCount="1">
+  <autoFilter ref="A1:D114"/>
   <tableColumns count="4">
     <tableColumn id="1" name="Phase"/>
     <tableColumn id="2" name="Status"/>
@@ -252,8 +252,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Modules" displayName="Modules" ref="A1:F24" headerRowCount="1">
-  <autoFilter ref="A1:F24"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Modules" displayName="Modules" ref="A1:F25" headerRowCount="1">
+  <autoFilter ref="A1:F25"/>
   <tableColumns count="6">
     <tableColumn id="1" name="Module"/>
     <tableColumn id="2" name="Service"/>
@@ -267,8 +267,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="APIEndpoints" displayName="APIEndpoints" ref="A1:E111" headerRowCount="1">
-  <autoFilter ref="A1:E111"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="APIEndpoints" displayName="APIEndpoints" ref="A1:E132" headerRowCount="1">
+  <autoFilter ref="A1:E132"/>
   <tableColumns count="5">
     <tableColumn id="1" name="Method"/>
     <tableColumn id="2" name="Path"/>
@@ -633,12 +633,12 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>20 / 30</t>
+          <t>21 / 30</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>70%</t>
         </is>
       </c>
     </row>
@@ -684,7 +684,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>131</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>data/migrations/0001-0018</t>
+          <t>data/migrations/0001-0019</t>
         </is>
       </c>
     </row>
@@ -752,7 +752,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
@@ -1371,9 +1371,9 @@
       <c r="A22" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="12" t="inlineStr">
-        <is>
-          <t>Next up</t>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
@@ -1383,12 +1383,12 @@
       </c>
       <c r="D22" s="11" t="inlineStr">
         <is>
-          <t>Reusable Block/Mute/Report/ModerationCase/Suspension/Ban/Appeal, plus rate limiting, spam protection, abuse signals. Product-specific report reasons pluggable.</t>
+          <t>Mute/Report-&gt;ModerationCase (deduplicated)/Suspension/Ban/Appeal - Block reuses Phase 8's relationships, not duplicated. A new requireActive middleware makes Suspension/Ban actually restrict access platform-wide from one place. New shared ratelimit package (Valkey-backed) gates report spam; a critical AbuseSignal auto-opens a case.</t>
         </is>
       </c>
       <c r="E22" s="11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7af4c58</t>
         </is>
       </c>
     </row>
@@ -1396,9 +1396,9 @@
       <c r="A23" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>Next up</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
@@ -1631,7 +1631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D111"/>
+  <dimension ref="A1:D114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1984,7 +1984,7 @@
     </row>
     <row r="22">
       <c r="A22" s="9" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
@@ -1993,14 +1993,14 @@
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>Repo health baseline (make doctor / validate-all / go test / go build) run and passed</t>
+          <t>Phase 21: Trust &amp; Safety implemented, unit-tested, live-validated, documented, committed</t>
         </is>
       </c>
       <c r="D22" s="11" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
@@ -2009,18 +2009,14 @@
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>Environment / ApplicationVersion / ApplicationConfiguration</t>
-        </is>
-      </c>
-      <c r="D23" s="11" t="inlineStr">
-        <is>
-          <t>Deferred - no consumer needs them yet, documented as intentional in applications/README.md</t>
-        </is>
-      </c>
+          <t>Repo health baseline (make doctor / validate-all / go test / go build) run and passed</t>
+        </is>
+      </c>
+      <c r="D23" s="11" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
@@ -2029,32 +2025,32 @@
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>Separate Session table</t>
+          <t>Environment / ApplicationVersion / ApplicationConfiguration</t>
         </is>
       </c>
       <c r="D24" s="11" t="inlineStr">
         <is>
-          <t>Deferred - Device.SessionStatus covers today's single-session-per-device need, documented in devices/README.md</t>
+          <t>Deferred - no consumer needs them yet, documented as intentional in applications/README.md</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="B25" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+        <v>5</v>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>UserPreferences (named in Phase 4, no fields ever specified)</t>
+          <t>Separate Session table</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>Deferred to Phase 12+; notification preferences shipped, a generic preferences bag did not</t>
+          <t>Deferred - Device.SessionStatus covers today's single-session-per-device need, documented in devices/README.md</t>
         </is>
       </c>
     </row>
@@ -2069,12 +2065,12 @@
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>apps/mobile test/ directory (make flutter-test currently fails)</t>
+          <t>UserPreferences (named in Phase 4, no fields ever specified)</t>
         </is>
       </c>
       <c r="D26" s="11" t="inlineStr">
         <is>
-          <t>Known gap since Phase 9's audit, not yet picked up</t>
+          <t>Deferred to Phase 12+; notification preferences shipped, a generic preferences bag did not</t>
         </is>
       </c>
     </row>
@@ -2089,30 +2085,34 @@
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>apps/admin next@15 / sharp transitive advisories</t>
+          <t>apps/mobile test/ directory (make flutter-test currently fails)</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>Fix is a Next.js major-version bump - separate, reviewable change</t>
+          <t>Known gap since Phase 9's audit, not yet picked up</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="9" t="n">
-        <v>20</v>
-      </c>
-      <c r="B28" s="10" t="inlineStr">
-        <is>
-          <t>Done</t>
+        <v>9</v>
+      </c>
+      <c r="B28" s="13" t="inlineStr">
+        <is>
+          <t>Pending</t>
         </is>
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>Privacy: consent (append-only history)</t>
-        </is>
-      </c>
-      <c r="D28" s="11" t="inlineStr"/>
+          <t>apps/admin next@15 / sharp transitive advisories</t>
+        </is>
+      </c>
+      <c r="D28" s="11" t="inlineStr">
+        <is>
+          <t>Fix is a Next.js major-version bump - separate, reviewable change</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="9" t="n">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>Privacy: user data export (ExportUserData registry - users/devices/files/audit)</t>
+          <t>Privacy: consent (append-only history)</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr"/>
@@ -2141,7 +2141,7 @@
       </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t>Privacy: user deletion (DeleteUserData registry - users/devices/files; audit deliberately excluded)</t>
+          <t>Privacy: user data export (ExportUserData registry - users/devices/files/audit)</t>
         </is>
       </c>
       <c r="D30" s="11" t="inlineStr"/>
@@ -2157,7 +2157,7 @@
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>Privacy: retention policy (declared, not scheduled - same documented gap as Phase 13's PurgeExpired)</t>
+          <t>Privacy: user deletion (DeleteUserData registry - users/devices/files; audit deliberately excluded)</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr"/>
@@ -2173,7 +2173,7 @@
       </c>
       <c r="C32" s="11" t="inlineStr">
         <is>
-          <t>Privacy: privacy preferences</t>
+          <t>Privacy: retention policy (declared, not scheduled - same documented gap as Phase 13's PurgeExpired)</t>
         </is>
       </c>
       <c r="D32" s="11" t="inlineStr"/>
@@ -2189,7 +2189,7 @@
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>Privacy: coordinate deletion through workflows/events - core-api's own embedded Temporal worker</t>
+          <t>Privacy: privacy preferences</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr"/>
@@ -2198,21 +2198,17 @@
       <c r="A34" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="B34" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B34" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C34" s="11" t="inlineStr">
         <is>
-          <t>Privacy: notifications module as an Export/Delete participant</t>
-        </is>
-      </c>
-      <c r="D34" s="11" t="inlineStr">
-        <is>
-          <t>Deliberately deferred to prove the registry makes this a 2-line addition later, not a framework change</t>
-        </is>
-      </c>
+          <t>Privacy: coordinate deletion through workflows/events - core-api's own embedded Temporal worker</t>
+        </is>
+      </c>
+      <c r="D34" s="11" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="9" t="n">
@@ -2225,18 +2221,18 @@
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>Privacy: relationships/groups/messaging as participants</t>
+          <t>Privacy: notifications module as an Export/Delete participant</t>
         </is>
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>Deferred - shared multi-user data needs a redaction strategy this phase's per-user-in-isolation registry doesn't fit</t>
+          <t>Deliberately deferred to prove the registry makes this a 2-line addition later, not a framework change</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B36" s="13" t="inlineStr">
         <is>
@@ -2245,39 +2241,47 @@
       </c>
       <c r="C36" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: Block</t>
-        </is>
-      </c>
-      <c r="D36" s="11" t="inlineStr"/>
+          <t>Privacy: relationships/groups/messaging as participants</t>
+        </is>
+      </c>
+      <c r="D36" s="11" t="inlineStr">
+        <is>
+          <t>Deferred - shared multi-user data needs a redaction strategy this phase's per-user-in-isolation registry doesn't fit</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="B37" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B37" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: Mute</t>
-        </is>
-      </c>
-      <c r="D37" s="11" t="inlineStr"/>
+          <t>Trust &amp; Safety: Block</t>
+        </is>
+      </c>
+      <c r="D37" s="11" t="inlineStr">
+        <is>
+          <t>Reused Phase 8's relationships (Status='blocked'), deliberately not duplicated</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="B38" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B38" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C38" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: Report</t>
+          <t>Trust &amp; Safety: Mute</t>
         </is>
       </c>
       <c r="D38" s="11" t="inlineStr"/>
@@ -2286,14 +2290,14 @@
       <c r="A39" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="B39" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B39" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: ModerationCase</t>
+          <t>Trust &amp; Safety: Report -&gt; ModerationCase (deduplicated via partial unique index)</t>
         </is>
       </c>
       <c r="D39" s="11" t="inlineStr"/>
@@ -2302,9 +2306,9 @@
       <c r="A40" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="B40" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B40" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C40" s="11" t="inlineStr">
@@ -2318,9 +2322,9 @@
       <c r="A41" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="B41" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B41" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C41" s="11" t="inlineStr">
@@ -2334,14 +2338,14 @@
       <c r="A42" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="B42" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B42" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C42" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: Appeal</t>
+          <t>Trust &amp; Safety: Appeal (approving lifts the target restriction)</t>
         </is>
       </c>
       <c r="D42" s="11" t="inlineStr"/>
@@ -2350,14 +2354,14 @@
       <c r="A43" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="B43" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B43" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C43" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: rate limiting</t>
+          <t>Trust &amp; Safety: rate limiting (new platformkit/ratelimit, Valkey-backed)</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr"/>
@@ -2366,14 +2370,14 @@
       <c r="A44" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="B44" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B44" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C44" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: spam protection</t>
+          <t>Trust &amp; Safety: spam protection (5 reports/hour per reporter)</t>
         </is>
       </c>
       <c r="D44" s="11" t="inlineStr"/>
@@ -2382,14 +2386,14 @@
       <c r="A45" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="B45" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B45" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C45" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: abuse signals</t>
+          <t>Trust &amp; Safety: abuse signals (critical severity auto-opens a case)</t>
         </is>
       </c>
       <c r="D45" s="11" t="inlineStr"/>
@@ -2398,37 +2402,37 @@
       <c r="A46" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="B46" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B46" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C46" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: pluggable product-specific report reasons</t>
+          <t>Trust &amp; Safety: pluggable product-specific report reasons (free-form Reason field)</t>
         </is>
       </c>
       <c r="D46" s="11" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="9" t="n">
-        <v>22</v>
-      </c>
-      <c r="B47" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+        <v>21</v>
+      </c>
+      <c r="B47" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C47" s="11" t="inlineStr">
         <is>
-          <t>Billing / Entitlements: Payment model</t>
+          <t>Trust &amp; Safety: Suspension/Ban actually restrict access (new requireActive middleware, one entry point)</t>
         </is>
       </c>
       <c r="D47" s="11" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B48" s="13" t="inlineStr">
         <is>
@@ -2437,14 +2441,18 @@
       </c>
       <c r="C48" s="11" t="inlineStr">
         <is>
-          <t>Billing / Entitlements: Entitlement model (kept separate from Payment)</t>
-        </is>
-      </c>
-      <c r="D48" s="11" t="inlineStr"/>
+          <t>Trust &amp; Safety: WebSocket disconnect on suspension/ban</t>
+        </is>
+      </c>
+      <c r="D48" s="11" t="inlineStr">
+        <is>
+          <t>Deferred - only HTTP access is gated; an existing realtime-gateway connection isn't forcibly closed</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B49" s="13" t="inlineStr">
         <is>
@@ -2453,10 +2461,14 @@
       </c>
       <c r="C49" s="11" t="inlineStr">
         <is>
-          <t>Billing / Entitlements: provider abstraction (implement first)</t>
-        </is>
-      </c>
-      <c r="D49" s="11" t="inlineStr"/>
+          <t>Trust &amp; Safety: aggregating lower-severity signals over a time window</t>
+        </is>
+      </c>
+      <c r="D49" s="11" t="inlineStr">
+        <is>
+          <t>Deferred - a real abuse-detection engine is out of this phase's scope; only single-critical-signal escalation is implemented</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="9" t="n">
@@ -2469,7 +2481,7 @@
       </c>
       <c r="C50" s="11" t="inlineStr">
         <is>
-          <t>Billing / Entitlements: Stripe adapter</t>
+          <t>Billing / Entitlements: Payment model</t>
         </is>
       </c>
       <c r="D50" s="11" t="inlineStr"/>
@@ -2485,7 +2497,7 @@
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>Billing / Entitlements: Apple IAP adapter</t>
+          <t>Billing / Entitlements: Entitlement model (kept separate from Payment)</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr"/>
@@ -2501,14 +2513,14 @@
       </c>
       <c r="C52" s="11" t="inlineStr">
         <is>
-          <t>Billing / Entitlements: Google Play adapter</t>
+          <t>Billing / Entitlements: provider abstraction (implement first)</t>
         </is>
       </c>
       <c r="D52" s="11" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B53" s="13" t="inlineStr">
         <is>
@@ -2517,14 +2529,14 @@
       </c>
       <c r="C53" s="11" t="inlineStr">
         <is>
-          <t>Analytics: generic analytics event envelope (event_name/user_id/anonymous_id/app_id/session_id/timestamp/properties/context)</t>
+          <t>Billing / Entitlements: Stripe adapter</t>
         </is>
       </c>
       <c r="D53" s="11" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B54" s="13" t="inlineStr">
         <is>
@@ -2533,14 +2545,14 @@
       </c>
       <c r="C54" s="11" t="inlineStr">
         <is>
-          <t>Analytics: keep operational DBs out of the analytics path</t>
+          <t>Billing / Entitlements: Apple IAP adapter</t>
         </is>
       </c>
       <c r="D54" s="11" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B55" s="13" t="inlineStr">
         <is>
@@ -2549,14 +2561,14 @@
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t>Analytics: pipeline foundation for ClickHouse/warehouse/data lake</t>
+          <t>Billing / Entitlements: Google Play adapter</t>
         </is>
       </c>
       <c r="D55" s="11" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B56" s="13" t="inlineStr">
         <is>
@@ -2565,14 +2577,14 @@
       </c>
       <c r="C56" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: provider-neutral interface (OpenAI/Anthropic/Google/local/Ollama/vLLM)</t>
+          <t>Analytics: generic analytics event envelope (event_name/user_id/anonymous_id/app_id/session_id/timestamp/properties/context)</t>
         </is>
       </c>
       <c r="D56" s="11" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B57" s="13" t="inlineStr">
         <is>
@@ -2581,14 +2593,14 @@
       </c>
       <c r="C57" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: model routing</t>
+          <t>Analytics: keep operational DBs out of the analytics path</t>
         </is>
       </c>
       <c r="D57" s="11" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B58" s="13" t="inlineStr">
         <is>
@@ -2597,7 +2609,7 @@
       </c>
       <c r="C58" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: quotas</t>
+          <t>Analytics: pipeline foundation for ClickHouse/warehouse/data lake</t>
         </is>
       </c>
       <c r="D58" s="11" t="inlineStr"/>
@@ -2613,7 +2625,7 @@
       </c>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: token usage tracking</t>
+          <t>AI Gateway: provider-neutral interface (OpenAI/Anthropic/Google/local/Ollama/vLLM)</t>
         </is>
       </c>
       <c r="D59" s="11" t="inlineStr"/>
@@ -2629,7 +2641,7 @@
       </c>
       <c r="C60" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: cost tracking</t>
+          <t>AI Gateway: model routing</t>
         </is>
       </c>
       <c r="D60" s="11" t="inlineStr"/>
@@ -2645,7 +2657,7 @@
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: audit integration</t>
+          <t>AI Gateway: quotas</t>
         </is>
       </c>
       <c r="D61" s="11" t="inlineStr"/>
@@ -2661,7 +2673,7 @@
       </c>
       <c r="C62" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: prompt/version metadata</t>
+          <t>AI Gateway: token usage tracking</t>
         </is>
       </c>
       <c r="D62" s="11" t="inlineStr"/>
@@ -2677,7 +2689,7 @@
       </c>
       <c r="C63" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: timeouts</t>
+          <t>AI Gateway: cost tracking</t>
         </is>
       </c>
       <c r="D63" s="11" t="inlineStr"/>
@@ -2693,14 +2705,14 @@
       </c>
       <c r="C64" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: fallback</t>
+          <t>AI Gateway: audit integration</t>
         </is>
       </c>
       <c r="D64" s="11" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B65" s="13" t="inlineStr">
         <is>
@@ -2709,14 +2721,14 @@
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
-          <t>Admin Portal: control-plane UI in apps/admin</t>
+          <t>AI Gateway: prompt/version metadata</t>
         </is>
       </c>
       <c r="D65" s="11" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B66" s="13" t="inlineStr">
         <is>
@@ -2725,14 +2737,14 @@
       </c>
       <c r="C66" s="11" t="inlineStr">
         <is>
-          <t>Admin Portal: visibility: Applications</t>
+          <t>AI Gateway: timeouts</t>
         </is>
       </c>
       <c r="D66" s="11" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B67" s="13" t="inlineStr">
         <is>
@@ -2741,7 +2753,7 @@
       </c>
       <c r="C67" s="11" t="inlineStr">
         <is>
-          <t>Admin Portal: visibility: Users/Sessions/Devices</t>
+          <t>AI Gateway: fallback</t>
         </is>
       </c>
       <c r="D67" s="11" t="inlineStr"/>
@@ -2757,7 +2769,7 @@
       </c>
       <c r="C68" s="11" t="inlineStr">
         <is>
-          <t>Admin Portal: visibility: Roles/Permissions</t>
+          <t>Admin Portal: control-plane UI in apps/admin</t>
         </is>
       </c>
       <c r="D68" s="11" t="inlineStr"/>
@@ -2773,7 +2785,7 @@
       </c>
       <c r="C69" s="11" t="inlineStr">
         <is>
-          <t>Admin Portal: visibility: Tenants/Relationships</t>
+          <t>Admin Portal: visibility: Applications</t>
         </is>
       </c>
       <c r="D69" s="11" t="inlineStr"/>
@@ -2789,7 +2801,7 @@
       </c>
       <c r="C70" s="11" t="inlineStr">
         <is>
-          <t>Admin Portal: visibility: Messages/Notifications</t>
+          <t>Admin Portal: visibility: Users/Sessions/Devices</t>
         </is>
       </c>
       <c r="D70" s="11" t="inlineStr"/>
@@ -2805,7 +2817,7 @@
       </c>
       <c r="C71" s="11" t="inlineStr">
         <is>
-          <t>Admin Portal: visibility: Files/Jobs</t>
+          <t>Admin Portal: visibility: Roles/Permissions</t>
         </is>
       </c>
       <c r="D71" s="11" t="inlineStr"/>
@@ -2821,7 +2833,7 @@
       </c>
       <c r="C72" s="11" t="inlineStr">
         <is>
-          <t>Admin Portal: visibility: Feature flags/Configuration</t>
+          <t>Admin Portal: visibility: Tenants/Relationships</t>
         </is>
       </c>
       <c r="D72" s="11" t="inlineStr"/>
@@ -2837,7 +2849,7 @@
       </c>
       <c r="C73" s="11" t="inlineStr">
         <is>
-          <t>Admin Portal: visibility: Moderation/Audit</t>
+          <t>Admin Portal: visibility: Messages/Notifications</t>
         </is>
       </c>
       <c r="D73" s="11" t="inlineStr"/>
@@ -2853,7 +2865,7 @@
       </c>
       <c r="C74" s="11" t="inlineStr">
         <is>
-          <t>Admin Portal: visibility: System health/Deployments</t>
+          <t>Admin Portal: visibility: Files/Jobs</t>
         </is>
       </c>
       <c r="D74" s="11" t="inlineStr"/>
@@ -2869,14 +2881,14 @@
       </c>
       <c r="C75" s="11" t="inlineStr">
         <is>
-          <t>Admin Portal: must go through service APIs, never direct DB queries</t>
+          <t>Admin Portal: visibility: Feature flags/Configuration</t>
         </is>
       </c>
       <c r="D75" s="11" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B76" s="13" t="inlineStr">
         <is>
@@ -2885,14 +2897,14 @@
       </c>
       <c r="C76" s="11" t="inlineStr">
         <is>
-          <t>Backstage: integrate Backstage as developer portal</t>
+          <t>Admin Portal: visibility: Moderation/Audit</t>
         </is>
       </c>
       <c r="D76" s="11" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B77" s="13" t="inlineStr">
         <is>
@@ -2901,14 +2913,14 @@
       </c>
       <c r="C77" s="11" t="inlineStr">
         <is>
-          <t>Backstage: per-module metadata: name/description/owner/lifecycle</t>
+          <t>Admin Portal: visibility: System health/Deployments</t>
         </is>
       </c>
       <c r="D77" s="11" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B78" s="13" t="inlineStr">
         <is>
@@ -2917,7 +2929,7 @@
       </c>
       <c r="C78" s="11" t="inlineStr">
         <is>
-          <t>Backstage: per-module metadata: repository/documentation/dependencies</t>
+          <t>Admin Portal: must go through service APIs, never direct DB queries</t>
         </is>
       </c>
       <c r="D78" s="11" t="inlineStr"/>
@@ -2933,14 +2945,14 @@
       </c>
       <c r="C79" s="11" t="inlineStr">
         <is>
-          <t>Backstage: per-module metadata: APIs/events/DB ownership/dashboards/runbooks</t>
+          <t>Backstage: integrate Backstage as developer portal</t>
         </is>
       </c>
       <c r="D79" s="11" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B80" s="13" t="inlineStr">
         <is>
@@ -2949,14 +2961,14 @@
       </c>
       <c r="C80" s="11" t="inlineStr">
         <is>
-          <t>SDKs: Flutter SDK</t>
+          <t>Backstage: per-module metadata: name/description/owner/lifecycle</t>
         </is>
       </c>
       <c r="D80" s="11" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B81" s="13" t="inlineStr">
         <is>
@@ -2965,14 +2977,14 @@
       </c>
       <c r="C81" s="11" t="inlineStr">
         <is>
-          <t>SDKs: TypeScript SDK</t>
+          <t>Backstage: per-module metadata: repository/documentation/dependencies</t>
         </is>
       </c>
       <c r="D81" s="11" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B82" s="13" t="inlineStr">
         <is>
@@ -2981,7 +2993,7 @@
       </c>
       <c r="C82" s="11" t="inlineStr">
         <is>
-          <t>SDKs: Go SDK</t>
+          <t>Backstage: per-module metadata: APIs/events/DB ownership/dashboards/runbooks</t>
         </is>
       </c>
       <c r="D82" s="11" t="inlineStr"/>
@@ -2997,7 +3009,7 @@
       </c>
       <c r="C83" s="11" t="inlineStr">
         <is>
-          <t>SDKs: auth + token refresh in each SDK</t>
+          <t>SDKs: Flutter SDK</t>
         </is>
       </c>
       <c r="D83" s="11" t="inlineStr"/>
@@ -3013,7 +3025,7 @@
       </c>
       <c r="C84" s="11" t="inlineStr">
         <is>
-          <t>SDKs: pagination + safe retries</t>
+          <t>SDKs: TypeScript SDK</t>
         </is>
       </c>
       <c r="D84" s="11" t="inlineStr"/>
@@ -3029,7 +3041,7 @@
       </c>
       <c r="C85" s="11" t="inlineStr">
         <is>
-          <t>SDKs: realtime connection helper</t>
+          <t>SDKs: Go SDK</t>
         </is>
       </c>
       <c r="D85" s="11" t="inlineStr"/>
@@ -3045,7 +3057,7 @@
       </c>
       <c r="C86" s="11" t="inlineStr">
         <is>
-          <t>SDKs: correlation ID propagation</t>
+          <t>SDKs: auth + token refresh in each SDK</t>
         </is>
       </c>
       <c r="D86" s="11" t="inlineStr"/>
@@ -3061,14 +3073,14 @@
       </c>
       <c r="C87" s="11" t="inlineStr">
         <is>
-          <t>SDKs: device registration helper</t>
+          <t>SDKs: pagination + safe retries</t>
         </is>
       </c>
       <c r="D87" s="11" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B88" s="13" t="inlineStr">
         <is>
@@ -3077,14 +3089,14 @@
       </c>
       <c r="C88" s="11" t="inlineStr">
         <is>
-          <t>Observability Completion: structured logs everywhere</t>
+          <t>SDKs: realtime connection helper</t>
         </is>
       </c>
       <c r="D88" s="11" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B89" s="13" t="inlineStr">
         <is>
@@ -3093,14 +3105,14 @@
       </c>
       <c r="C89" s="11" t="inlineStr">
         <is>
-          <t>Observability Completion: metrics everywhere</t>
+          <t>SDKs: correlation ID propagation</t>
         </is>
       </c>
       <c r="D89" s="11" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B90" s="13" t="inlineStr">
         <is>
@@ -3109,7 +3121,7 @@
       </c>
       <c r="C90" s="11" t="inlineStr">
         <is>
-          <t>Observability Completion: distributed traces everywhere</t>
+          <t>SDKs: device registration helper</t>
         </is>
       </c>
       <c r="D90" s="11" t="inlineStr"/>
@@ -3125,7 +3137,7 @@
       </c>
       <c r="C91" s="11" t="inlineStr">
         <is>
-          <t>Observability Completion: health checks everywhere</t>
+          <t>Observability Completion: structured logs everywhere</t>
         </is>
       </c>
       <c r="D91" s="11" t="inlineStr"/>
@@ -3141,7 +3153,7 @@
       </c>
       <c r="C92" s="11" t="inlineStr">
         <is>
-          <t>Observability Completion: dashboard: API latency</t>
+          <t>Observability Completion: metrics everywhere</t>
         </is>
       </c>
       <c r="D92" s="11" t="inlineStr"/>
@@ -3157,7 +3169,7 @@
       </c>
       <c r="C93" s="11" t="inlineStr">
         <is>
-          <t>Observability Completion: dashboard: error rate</t>
+          <t>Observability Completion: distributed traces everywhere</t>
         </is>
       </c>
       <c r="D93" s="11" t="inlineStr"/>
@@ -3173,7 +3185,7 @@
       </c>
       <c r="C94" s="11" t="inlineStr">
         <is>
-          <t>Observability Completion: dashboard: requests/sec</t>
+          <t>Observability Completion: health checks everywhere</t>
         </is>
       </c>
       <c r="D94" s="11" t="inlineStr"/>
@@ -3189,7 +3201,7 @@
       </c>
       <c r="C95" s="11" t="inlineStr">
         <is>
-          <t>Observability Completion: dashboard: DB connections</t>
+          <t>Observability Completion: dashboard: API latency</t>
         </is>
       </c>
       <c r="D95" s="11" t="inlineStr"/>
@@ -3205,7 +3217,7 @@
       </c>
       <c r="C96" s="11" t="inlineStr">
         <is>
-          <t>Observability Completion: dashboard: Kafka lag</t>
+          <t>Observability Completion: dashboard: error rate</t>
         </is>
       </c>
       <c r="D96" s="11" t="inlineStr"/>
@@ -3221,7 +3233,7 @@
       </c>
       <c r="C97" s="11" t="inlineStr">
         <is>
-          <t>Observability Completion: dashboard: WebSocket connections</t>
+          <t>Observability Completion: dashboard: requests/sec</t>
         </is>
       </c>
       <c r="D97" s="11" t="inlineStr"/>
@@ -3237,7 +3249,7 @@
       </c>
       <c r="C98" s="11" t="inlineStr">
         <is>
-          <t>Observability Completion: dashboard: Redis latency</t>
+          <t>Observability Completion: dashboard: DB connections</t>
         </is>
       </c>
       <c r="D98" s="11" t="inlineStr"/>
@@ -3253,7 +3265,7 @@
       </c>
       <c r="C99" s="11" t="inlineStr">
         <is>
-          <t>Observability Completion: dashboard: notification failures</t>
+          <t>Observability Completion: dashboard: Kafka lag</t>
         </is>
       </c>
       <c r="D99" s="11" t="inlineStr"/>
@@ -3269,7 +3281,7 @@
       </c>
       <c r="C100" s="11" t="inlineStr">
         <is>
-          <t>Observability Completion: dashboard: background job failures</t>
+          <t>Observability Completion: dashboard: WebSocket connections</t>
         </is>
       </c>
       <c r="D100" s="11" t="inlineStr"/>
@@ -3285,14 +3297,14 @@
       </c>
       <c r="C101" s="11" t="inlineStr">
         <is>
-          <t>Observability Completion: alerting rules</t>
+          <t>Observability Completion: dashboard: Redis latency</t>
         </is>
       </c>
       <c r="D101" s="11" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B102" s="13" t="inlineStr">
         <is>
@@ -3301,14 +3313,14 @@
       </c>
       <c r="C102" s="11" t="inlineStr">
         <is>
-          <t>Platform Control Plane: one view: applications/services/versions</t>
+          <t>Observability Completion: dashboard: notification failures</t>
         </is>
       </c>
       <c r="D102" s="11" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B103" s="13" t="inlineStr">
         <is>
@@ -3317,14 +3329,14 @@
       </c>
       <c r="C103" s="11" t="inlineStr">
         <is>
-          <t>Platform Control Plane: one view: environments/dependencies/deployments</t>
+          <t>Observability Completion: dashboard: background job failures</t>
         </is>
       </c>
       <c r="D103" s="11" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B104" s="13" t="inlineStr">
         <is>
@@ -3333,7 +3345,7 @@
       </c>
       <c r="C104" s="11" t="inlineStr">
         <is>
-          <t>Platform Control Plane: one view: DB ownership/events/API contracts</t>
+          <t>Observability Completion: alerting rules</t>
         </is>
       </c>
       <c r="D104" s="11" t="inlineStr"/>
@@ -3349,14 +3361,14 @@
       </c>
       <c r="C105" s="11" t="inlineStr">
         <is>
-          <t>Platform Control Plane: one view: health/alerts/recent changes</t>
+          <t>Platform Control Plane: one view: applications/services/versions</t>
         </is>
       </c>
       <c r="D105" s="11" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="9" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B106" s="13" t="inlineStr">
         <is>
@@ -3365,14 +3377,14 @@
       </c>
       <c r="C106" s="11" t="inlineStr">
         <is>
-          <t>AI Development Context: every module: README</t>
+          <t>Platform Control Plane: one view: environments/dependencies/deployments</t>
         </is>
       </c>
       <c r="D106" s="11" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="9" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B107" s="13" t="inlineStr">
         <is>
@@ -3381,14 +3393,14 @@
       </c>
       <c r="C107" s="11" t="inlineStr">
         <is>
-          <t>AI Development Context: every module: ownership metadata</t>
+          <t>Platform Control Plane: one view: DB ownership/events/API contracts</t>
         </is>
       </c>
       <c r="D107" s="11" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="9" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B108" s="13" t="inlineStr">
         <is>
@@ -3397,7 +3409,7 @@
       </c>
       <c r="C108" s="11" t="inlineStr">
         <is>
-          <t>AI Development Context: every module: dependencies</t>
+          <t>Platform Control Plane: one view: health/alerts/recent changes</t>
         </is>
       </c>
       <c r="D108" s="11" t="inlineStr"/>
@@ -3413,7 +3425,7 @@
       </c>
       <c r="C109" s="11" t="inlineStr">
         <is>
-          <t>AI Development Context: every module: API contract</t>
+          <t>AI Development Context: every module: README</t>
         </is>
       </c>
       <c r="D109" s="11" t="inlineStr"/>
@@ -3429,7 +3441,7 @@
       </c>
       <c r="C110" s="11" t="inlineStr">
         <is>
-          <t>AI Development Context: every module: event contracts</t>
+          <t>AI Development Context: every module: ownership metadata</t>
         </is>
       </c>
       <c r="D110" s="11" t="inlineStr"/>
@@ -3445,10 +3457,58 @@
       </c>
       <c r="C111" s="11" t="inlineStr">
         <is>
+          <t>AI Development Context: every module: dependencies</t>
+        </is>
+      </c>
+      <c r="D111" s="11" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="B112" s="13" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="C112" s="11" t="inlineStr">
+        <is>
+          <t>AI Development Context: every module: API contract</t>
+        </is>
+      </c>
+      <c r="D112" s="11" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="B113" s="13" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="C113" s="11" t="inlineStr">
+        <is>
+          <t>AI Development Context: every module: event contracts</t>
+        </is>
+      </c>
+      <c r="D113" s="11" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="B114" s="13" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="C114" s="11" t="inlineStr">
+        <is>
           <t>AI Development Context: every module: DB ownership</t>
         </is>
       </c>
-      <c r="D111" s="11" t="inlineStr"/>
+      <c r="D114" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3464,7 +3524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4240,6 +4300,38 @@
       <c r="F24" s="11" t="inlineStr">
         <is>
           <t>Phase 20</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="32" customHeight="1">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>trustsafety</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t>core-api</t>
+        </is>
+      </c>
+      <c r="C25" s="11" t="inlineStr">
+        <is>
+          <t>Mute/Report/ModerationCase/Suspension/Ban/Appeal/AbuseSignal - Block reuses Phase 8's relationships</t>
+        </is>
+      </c>
+      <c r="D25" s="11" t="inlineStr">
+        <is>
+          <t>mutes, moderation_cases, reports, suspensions, bans, appeals, abuse_signals</t>
+        </is>
+      </c>
+      <c r="E25" s="11" t="inlineStr">
+        <is>
+          <t>Self for own mutes/appeals; moderator-or-admin for case/suspension/ban management</t>
+        </is>
+      </c>
+      <c r="F25" s="11" t="inlineStr">
+        <is>
+          <t>Phase 21</t>
         </is>
       </c>
     </row>
@@ -4257,7 +4349,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E111"/>
+  <dimension ref="A1:E132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -6981,6 +7073,545 @@
       <c r="E111" s="11" t="inlineStr">
         <is>
           <t>a self-deleted user must use an admin to check this</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="11" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="B112" s="11" t="inlineStr">
+        <is>
+          <t>/v1/trustsafety/mutes</t>
+        </is>
+      </c>
+      <c r="C112" s="11" t="inlineStr">
+        <is>
+          <t>trustsafety</t>
+        </is>
+      </c>
+      <c r="D112" s="11" t="inlineStr">
+        <is>
+          <t>Authenticated (self)</t>
+        </is>
+      </c>
+      <c r="E112" s="11" t="inlineStr">
+        <is>
+          <t>one-directional, silent</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="11" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="B113" s="11" t="inlineStr">
+        <is>
+          <t>/v1/trustsafety/mutes</t>
+        </is>
+      </c>
+      <c r="C113" s="11" t="inlineStr">
+        <is>
+          <t>trustsafety</t>
+        </is>
+      </c>
+      <c r="D113" s="11" t="inlineStr">
+        <is>
+          <t>Authenticated (self)</t>
+        </is>
+      </c>
+      <c r="E113" s="11" t="inlineStr">
+        <is>
+          <t>exempt from requireActive - always reachable</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="11" t="inlineStr">
+        <is>
+          <t>DELETE</t>
+        </is>
+      </c>
+      <c r="B114" s="11" t="inlineStr">
+        <is>
+          <t>/v1/trustsafety/mutes/{userId}</t>
+        </is>
+      </c>
+      <c r="C114" s="11" t="inlineStr">
+        <is>
+          <t>trustsafety</t>
+        </is>
+      </c>
+      <c r="D114" s="11" t="inlineStr">
+        <is>
+          <t>Authenticated (self)</t>
+        </is>
+      </c>
+      <c r="E114" s="11" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="11" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="B115" s="11" t="inlineStr">
+        <is>
+          <t>/v1/trustsafety/reports</t>
+        </is>
+      </c>
+      <c r="C115" s="11" t="inlineStr">
+        <is>
+          <t>trustsafety</t>
+        </is>
+      </c>
+      <c r="D115" s="11" t="inlineStr">
+        <is>
+          <t>Authenticated (self)</t>
+        </is>
+      </c>
+      <c r="E115" s="11" t="inlineStr">
+        <is>
+          <t>rate-limited 5/hour; dedupes onto one case</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="11" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="B116" s="11" t="inlineStr">
+        <is>
+          <t>/v1/trustsafety/reports/{id}</t>
+        </is>
+      </c>
+      <c r="C116" s="11" t="inlineStr">
+        <is>
+          <t>trustsafety</t>
+        </is>
+      </c>
+      <c r="D116" s="11" t="inlineStr">
+        <is>
+          <t>Reporter or moderator/admin</t>
+        </is>
+      </c>
+      <c r="E116" s="11" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="11" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="B117" s="11" t="inlineStr">
+        <is>
+          <t>/v1/trustsafety/cases</t>
+        </is>
+      </c>
+      <c r="C117" s="11" t="inlineStr">
+        <is>
+          <t>trustsafety</t>
+        </is>
+      </c>
+      <c r="D117" s="11" t="inlineStr">
+        <is>
+          <t>Moderator or platform.admin</t>
+        </is>
+      </c>
+      <c r="E117" s="11" t="inlineStr">
+        <is>
+          <t>?status=</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="11" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="B118" s="11" t="inlineStr">
+        <is>
+          <t>/v1/trustsafety/cases/{id}</t>
+        </is>
+      </c>
+      <c r="C118" s="11" t="inlineStr">
+        <is>
+          <t>trustsafety</t>
+        </is>
+      </c>
+      <c r="D118" s="11" t="inlineStr">
+        <is>
+          <t>Moderator or platform.admin</t>
+        </is>
+      </c>
+      <c r="E118" s="11" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="11" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="B119" s="11" t="inlineStr">
+        <is>
+          <t>/v1/trustsafety/cases/{id}/reports</t>
+        </is>
+      </c>
+      <c r="C119" s="11" t="inlineStr">
+        <is>
+          <t>trustsafety</t>
+        </is>
+      </c>
+      <c r="D119" s="11" t="inlineStr">
+        <is>
+          <t>Moderator or platform.admin</t>
+        </is>
+      </c>
+      <c r="E119" s="11" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="11" t="inlineStr">
+        <is>
+          <t>PATCH</t>
+        </is>
+      </c>
+      <c r="B120" s="11" t="inlineStr">
+        <is>
+          <t>/v1/trustsafety/cases/{id}/assign</t>
+        </is>
+      </c>
+      <c r="C120" s="11" t="inlineStr">
+        <is>
+          <t>trustsafety</t>
+        </is>
+      </c>
+      <c r="D120" s="11" t="inlineStr">
+        <is>
+          <t>Moderator or platform.admin</t>
+        </is>
+      </c>
+      <c r="E120" s="11" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="11" t="inlineStr">
+        <is>
+          <t>PATCH</t>
+        </is>
+      </c>
+      <c r="B121" s="11" t="inlineStr">
+        <is>
+          <t>/v1/trustsafety/cases/{id}</t>
+        </is>
+      </c>
+      <c r="C121" s="11" t="inlineStr">
+        <is>
+          <t>trustsafety</t>
+        </is>
+      </c>
+      <c r="D121" s="11" t="inlineStr">
+        <is>
+          <t>Moderator or platform.admin</t>
+        </is>
+      </c>
+      <c r="E121" s="11" t="inlineStr">
+        <is>
+          <t>resolve/dismiss</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="11" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="B122" s="11" t="inlineStr">
+        <is>
+          <t>/v1/trustsafety/suspensions</t>
+        </is>
+      </c>
+      <c r="C122" s="11" t="inlineStr">
+        <is>
+          <t>trustsafety</t>
+        </is>
+      </c>
+      <c r="D122" s="11" t="inlineStr">
+        <is>
+          <t>Moderator or platform.admin</t>
+        </is>
+      </c>
+      <c r="E122" s="11" t="inlineStr">
+        <is>
+          <t>temporary, EndsAt required</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="11" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="B123" s="11" t="inlineStr">
+        <is>
+          <t>/v1/trustsafety/suspensions</t>
+        </is>
+      </c>
+      <c r="C123" s="11" t="inlineStr">
+        <is>
+          <t>trustsafety</t>
+        </is>
+      </c>
+      <c r="D123" s="11" t="inlineStr">
+        <is>
+          <t>Self or moderator/admin</t>
+        </is>
+      </c>
+      <c r="E123" s="11" t="inlineStr">
+        <is>
+          <t>?userId=</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="11" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="B124" s="11" t="inlineStr">
+        <is>
+          <t>/v1/trustsafety/suspensions/{id}/lift</t>
+        </is>
+      </c>
+      <c r="C124" s="11" t="inlineStr">
+        <is>
+          <t>trustsafety</t>
+        </is>
+      </c>
+      <c r="D124" s="11" t="inlineStr">
+        <is>
+          <t>Moderator or platform.admin</t>
+        </is>
+      </c>
+      <c r="E124" s="11" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="11" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="B125" s="11" t="inlineStr">
+        <is>
+          <t>/v1/trustsafety/bans</t>
+        </is>
+      </c>
+      <c r="C125" s="11" t="inlineStr">
+        <is>
+          <t>trustsafety</t>
+        </is>
+      </c>
+      <c r="D125" s="11" t="inlineStr">
+        <is>
+          <t>Moderator or platform.admin</t>
+        </is>
+      </c>
+      <c r="E125" s="11" t="inlineStr">
+        <is>
+          <t>permanent until lifted</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="11" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="B126" s="11" t="inlineStr">
+        <is>
+          <t>/v1/trustsafety/bans</t>
+        </is>
+      </c>
+      <c r="C126" s="11" t="inlineStr">
+        <is>
+          <t>trustsafety</t>
+        </is>
+      </c>
+      <c r="D126" s="11" t="inlineStr">
+        <is>
+          <t>Self or moderator/admin</t>
+        </is>
+      </c>
+      <c r="E126" s="11" t="inlineStr">
+        <is>
+          <t>?userId=</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="11" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="B127" s="11" t="inlineStr">
+        <is>
+          <t>/v1/trustsafety/bans/{id}/lift</t>
+        </is>
+      </c>
+      <c r="C127" s="11" t="inlineStr">
+        <is>
+          <t>trustsafety</t>
+        </is>
+      </c>
+      <c r="D127" s="11" t="inlineStr">
+        <is>
+          <t>Moderator or platform.admin</t>
+        </is>
+      </c>
+      <c r="E127" s="11" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="11" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="B128" s="11" t="inlineStr">
+        <is>
+          <t>/v1/trustsafety/appeals</t>
+        </is>
+      </c>
+      <c r="C128" s="11" t="inlineStr">
+        <is>
+          <t>trustsafety</t>
+        </is>
+      </c>
+      <c r="D128" s="11" t="inlineStr">
+        <is>
+          <t>Authenticated (self, must own target)</t>
+        </is>
+      </c>
+      <c r="E128" s="11" t="inlineStr">
+        <is>
+          <t>exempt from requireActive - always reachable</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="11" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="B129" s="11" t="inlineStr">
+        <is>
+          <t>/v1/trustsafety/appeals</t>
+        </is>
+      </c>
+      <c r="C129" s="11" t="inlineStr">
+        <is>
+          <t>trustsafety</t>
+        </is>
+      </c>
+      <c r="D129" s="11" t="inlineStr">
+        <is>
+          <t>Self or moderator/admin</t>
+        </is>
+      </c>
+      <c r="E129" s="11" t="inlineStr">
+        <is>
+          <t>exempt from requireActive - always reachable</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="11" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="B130" s="11" t="inlineStr">
+        <is>
+          <t>/v1/trustsafety/appeals/{id}/review</t>
+        </is>
+      </c>
+      <c r="C130" s="11" t="inlineStr">
+        <is>
+          <t>trustsafety</t>
+        </is>
+      </c>
+      <c r="D130" s="11" t="inlineStr">
+        <is>
+          <t>Moderator or platform.admin</t>
+        </is>
+      </c>
+      <c r="E130" s="11" t="inlineStr">
+        <is>
+          <t>approving lifts the target restriction</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="11" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="B131" s="11" t="inlineStr">
+        <is>
+          <t>/v1/trustsafety/signals</t>
+        </is>
+      </c>
+      <c r="C131" s="11" t="inlineStr">
+        <is>
+          <t>trustsafety</t>
+        </is>
+      </c>
+      <c r="D131" s="11" t="inlineStr">
+        <is>
+          <t>Authenticated</t>
+        </is>
+      </c>
+      <c r="E131" s="11" t="inlineStr">
+        <is>
+          <t>critical severity auto-opens a case</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="11" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="B132" s="11" t="inlineStr">
+        <is>
+          <t>/v1/trustsafety/signals</t>
+        </is>
+      </c>
+      <c r="C132" s="11" t="inlineStr">
+        <is>
+          <t>trustsafety</t>
+        </is>
+      </c>
+      <c r="D132" s="11" t="inlineStr">
+        <is>
+          <t>Moderator or platform.admin</t>
+        </is>
+      </c>
+      <c r="E132" s="11" t="inlineStr">
+        <is>
+          <t>?resourceType=&amp;resourceId=</t>
         </is>
       </c>
     </row>

--- a/docs/control/data.xlsx
+++ b/docs/control/data.xlsx
@@ -281,8 +281,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="HowToTest" displayName="HowToTest" ref="A1:D18" headerRowCount="1">
-  <autoFilter ref="A1:D18"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="HowToTest" displayName="HowToTest" ref="A1:D19" headerRowCount="1">
+  <autoFilter ref="A1:D19"/>
   <tableColumns count="4">
     <tableColumn id="1" name="Step"/>
     <tableColumn id="2" name="What"/>
@@ -7629,7 +7629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -8031,6 +8031,28 @@
       <c r="D18" s="11" t="inlineStr">
         <is>
           <t>A scripted end-to-end pass (scripts/smoke.sh) against the real running services - the fastest single command to confirm the whole stack still works after a change.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="48" customHeight="1">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>Skip the curl entirely</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>Open this dashboard's API Console tab</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="inlineStr">
+        <is>
+          <t>Pick an endpoint, fetch a token via the built-in Keycloak password-grant form (or paste one you already have), and send the request - the real response comes back right in the page. core-api's CORS middleware (internal/api/cors.go) is what makes this possible; it must be running a build from Phase 21 or later.</t>
         </is>
       </c>
     </row>

--- a/docs/control/data.xlsx
+++ b/docs/control/data.xlsx
@@ -239,8 +239,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="TodoChecklist" displayName="TodoChecklist" ref="A1:D114" headerRowCount="1">
-  <autoFilter ref="A1:D114"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="TodoChecklist" displayName="TodoChecklist" ref="A1:D115" headerRowCount="1">
+  <autoFilter ref="A1:D115"/>
   <tableColumns count="4">
     <tableColumn id="1" name="Phase"/>
     <tableColumn id="2" name="Status"/>
@@ -252,8 +252,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Modules" displayName="Modules" ref="A1:F25" headerRowCount="1">
-  <autoFilter ref="A1:F25"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Modules" displayName="Modules" ref="A1:F27" headerRowCount="1">
+  <autoFilter ref="A1:F27"/>
   <tableColumns count="6">
     <tableColumn id="1" name="Module"/>
     <tableColumn id="2" name="Service"/>
@@ -267,8 +267,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="APIEndpoints" displayName="APIEndpoints" ref="A1:E132" headerRowCount="1">
-  <autoFilter ref="A1:E132"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="APIEndpoints" displayName="APIEndpoints" ref="A1:E138" headerRowCount="1">
+  <autoFilter ref="A1:E138"/>
   <tableColumns count="5">
     <tableColumn id="1" name="Method"/>
     <tableColumn id="2" name="Path"/>
@@ -633,12 +633,12 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>21 / 30</t>
+          <t>22 / 30</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>70%</t>
+          <t>73%</t>
         </is>
       </c>
     </row>
@@ -684,7 +684,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>137</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>data/migrations/0001-0019</t>
+          <t>data/migrations/0001-0020</t>
         </is>
       </c>
     </row>
@@ -752,7 +752,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
@@ -1396,9 +1396,9 @@
       <c r="A23" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="12" t="inlineStr">
-        <is>
-          <t>Next up</t>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>Separate Payment from Entitlement - products ask 'has entitlement X', never 'is the Stripe subscription active'. Provider abstraction first (Stripe, Apple IAP, Google Play).</t>
+          <t>Entitlement (platform truth, HasEntitlement) kept separate from Payment (provider transaction record). PaymentProvider abstraction + registry; billing/stripe implements Stripe's real webhook HMAC signature scheme, live-validated without a Stripe account via self-signed test payloads. Apple IAP/Google Play deliberately deferred - no sandbox credentials available.</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>8fcc87f</t>
         </is>
       </c>
     </row>
@@ -1421,9 +1421,9 @@
       <c r="A24" s="9" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B24" s="12" t="inlineStr">
+        <is>
+          <t>Next up</t>
         </is>
       </c>
       <c r="C24" s="11" t="inlineStr">
@@ -1631,7 +1631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D114"/>
+  <dimension ref="A1:D115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2000,7 +2000,7 @@
     </row>
     <row r="23">
       <c r="A23" s="9" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
@@ -2009,14 +2009,14 @@
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>Repo health baseline (make doctor / validate-all / go test / go build) run and passed</t>
+          <t>Phase 22: Billing / Entitlements implemented, unit-tested, live-validated, documented, committed</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
@@ -2025,18 +2025,14 @@
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>Environment / ApplicationVersion / ApplicationConfiguration</t>
-        </is>
-      </c>
-      <c r="D24" s="11" t="inlineStr">
-        <is>
-          <t>Deferred - no consumer needs them yet, documented as intentional in applications/README.md</t>
-        </is>
-      </c>
+          <t>Repo health baseline (make doctor / validate-all / go test / go build) run and passed</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
@@ -2045,32 +2041,32 @@
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>Separate Session table</t>
+          <t>Environment / ApplicationVersion / ApplicationConfiguration</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>Deferred - Device.SessionStatus covers today's single-session-per-device need, documented in devices/README.md</t>
+          <t>Deferred - no consumer needs them yet, documented as intentional in applications/README.md</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="B26" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+        <v>5</v>
+      </c>
+      <c r="B26" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>UserPreferences (named in Phase 4, no fields ever specified)</t>
+          <t>Separate Session table</t>
         </is>
       </c>
       <c r="D26" s="11" t="inlineStr">
         <is>
-          <t>Deferred to Phase 12+; notification preferences shipped, a generic preferences bag did not</t>
+          <t>Deferred - Device.SessionStatus covers today's single-session-per-device need, documented in devices/README.md</t>
         </is>
       </c>
     </row>
@@ -2085,12 +2081,12 @@
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>apps/mobile test/ directory (make flutter-test currently fails)</t>
+          <t>UserPreferences (named in Phase 4, no fields ever specified)</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>Known gap since Phase 9's audit, not yet picked up</t>
+          <t>Deferred to Phase 12+; notification preferences shipped, a generic preferences bag did not</t>
         </is>
       </c>
     </row>
@@ -2105,30 +2101,34 @@
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>apps/admin next@15 / sharp transitive advisories</t>
+          <t>apps/mobile test/ directory (make flutter-test currently fails)</t>
         </is>
       </c>
       <c r="D28" s="11" t="inlineStr">
         <is>
-          <t>Fix is a Next.js major-version bump - separate, reviewable change</t>
+          <t>Known gap since Phase 9's audit, not yet picked up</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="9" t="n">
-        <v>20</v>
-      </c>
-      <c r="B29" s="10" t="inlineStr">
-        <is>
-          <t>Done</t>
+        <v>9</v>
+      </c>
+      <c r="B29" s="13" t="inlineStr">
+        <is>
+          <t>Pending</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>Privacy: consent (append-only history)</t>
-        </is>
-      </c>
-      <c r="D29" s="11" t="inlineStr"/>
+          <t>apps/admin next@15 / sharp transitive advisories</t>
+        </is>
+      </c>
+      <c r="D29" s="11" t="inlineStr">
+        <is>
+          <t>Fix is a Next.js major-version bump - separate, reviewable change</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="9" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t>Privacy: user data export (ExportUserData registry - users/devices/files/audit)</t>
+          <t>Privacy: consent (append-only history)</t>
         </is>
       </c>
       <c r="D30" s="11" t="inlineStr"/>
@@ -2157,7 +2157,7 @@
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>Privacy: user deletion (DeleteUserData registry - users/devices/files; audit deliberately excluded)</t>
+          <t>Privacy: user data export (ExportUserData registry - users/devices/files/audit)</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr"/>
@@ -2173,7 +2173,7 @@
       </c>
       <c r="C32" s="11" t="inlineStr">
         <is>
-          <t>Privacy: retention policy (declared, not scheduled - same documented gap as Phase 13's PurgeExpired)</t>
+          <t>Privacy: user deletion (DeleteUserData registry - users/devices/files; audit deliberately excluded)</t>
         </is>
       </c>
       <c r="D32" s="11" t="inlineStr"/>
@@ -2189,7 +2189,7 @@
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>Privacy: privacy preferences</t>
+          <t>Privacy: retention policy (declared, not scheduled - same documented gap as Phase 13's PurgeExpired)</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr"/>
@@ -2205,7 +2205,7 @@
       </c>
       <c r="C34" s="11" t="inlineStr">
         <is>
-          <t>Privacy: coordinate deletion through workflows/events - core-api's own embedded Temporal worker</t>
+          <t>Privacy: privacy preferences</t>
         </is>
       </c>
       <c r="D34" s="11" t="inlineStr"/>
@@ -2214,21 +2214,17 @@
       <c r="A35" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="B35" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B35" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>Privacy: notifications module as an Export/Delete participant</t>
-        </is>
-      </c>
-      <c r="D35" s="11" t="inlineStr">
-        <is>
-          <t>Deliberately deferred to prove the registry makes this a 2-line addition later, not a framework change</t>
-        </is>
-      </c>
+          <t>Privacy: coordinate deletion through workflows/events - core-api's own embedded Temporal worker</t>
+        </is>
+      </c>
+      <c r="D35" s="11" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="9" t="n">
@@ -2241,32 +2237,32 @@
       </c>
       <c r="C36" s="11" t="inlineStr">
         <is>
-          <t>Privacy: relationships/groups/messaging as participants</t>
+          <t>Privacy: notifications module as an Export/Delete participant</t>
         </is>
       </c>
       <c r="D36" s="11" t="inlineStr">
         <is>
-          <t>Deferred - shared multi-user data needs a redaction strategy this phase's per-user-in-isolation registry doesn't fit</t>
+          <t>Deliberately deferred to prove the registry makes this a 2-line addition later, not a framework change</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="9" t="n">
-        <v>21</v>
-      </c>
-      <c r="B37" s="10" t="inlineStr">
-        <is>
-          <t>Done</t>
+        <v>20</v>
+      </c>
+      <c r="B37" s="13" t="inlineStr">
+        <is>
+          <t>Pending</t>
         </is>
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: Block</t>
+          <t>Privacy: relationships/groups/messaging as participants</t>
         </is>
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>Reused Phase 8's relationships (Status='blocked'), deliberately not duplicated</t>
+          <t>Deferred - shared multi-user data needs a redaction strategy this phase's per-user-in-isolation registry doesn't fit</t>
         </is>
       </c>
     </row>
@@ -2281,10 +2277,14 @@
       </c>
       <c r="C38" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: Mute</t>
-        </is>
-      </c>
-      <c r="D38" s="11" t="inlineStr"/>
+          <t>Trust &amp; Safety: Block</t>
+        </is>
+      </c>
+      <c r="D38" s="11" t="inlineStr">
+        <is>
+          <t>Reused Phase 8's relationships (Status='blocked'), deliberately not duplicated</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="9" t="n">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: Report -&gt; ModerationCase (deduplicated via partial unique index)</t>
+          <t>Trust &amp; Safety: Mute</t>
         </is>
       </c>
       <c r="D39" s="11" t="inlineStr"/>
@@ -2313,7 +2313,7 @@
       </c>
       <c r="C40" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: Suspension</t>
+          <t>Trust &amp; Safety: Report -&gt; ModerationCase (deduplicated via partial unique index)</t>
         </is>
       </c>
       <c r="D40" s="11" t="inlineStr"/>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: Ban</t>
+          <t>Trust &amp; Safety: Suspension</t>
         </is>
       </c>
       <c r="D41" s="11" t="inlineStr"/>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="C42" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: Appeal (approving lifts the target restriction)</t>
+          <t>Trust &amp; Safety: Ban</t>
         </is>
       </c>
       <c r="D42" s="11" t="inlineStr"/>
@@ -2361,7 +2361,7 @@
       </c>
       <c r="C43" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: rate limiting (new platformkit/ratelimit, Valkey-backed)</t>
+          <t>Trust &amp; Safety: Appeal (approving lifts the target restriction)</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr"/>
@@ -2377,7 +2377,7 @@
       </c>
       <c r="C44" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: spam protection (5 reports/hour per reporter)</t>
+          <t>Trust &amp; Safety: rate limiting (new platformkit/ratelimit, Valkey-backed)</t>
         </is>
       </c>
       <c r="D44" s="11" t="inlineStr"/>
@@ -2393,7 +2393,7 @@
       </c>
       <c r="C45" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: abuse signals (critical severity auto-opens a case)</t>
+          <t>Trust &amp; Safety: spam protection (5 reports/hour per reporter)</t>
         </is>
       </c>
       <c r="D45" s="11" t="inlineStr"/>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="C46" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: pluggable product-specific report reasons (free-form Reason field)</t>
+          <t>Trust &amp; Safety: abuse signals (critical severity auto-opens a case)</t>
         </is>
       </c>
       <c r="D46" s="11" t="inlineStr"/>
@@ -2425,7 +2425,7 @@
       </c>
       <c r="C47" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: Suspension/Ban actually restrict access (new requireActive middleware, one entry point)</t>
+          <t>Trust &amp; Safety: pluggable product-specific report reasons (free-form Reason field)</t>
         </is>
       </c>
       <c r="D47" s="11" t="inlineStr"/>
@@ -2434,21 +2434,17 @@
       <c r="A48" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="B48" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B48" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C48" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: WebSocket disconnect on suspension/ban</t>
-        </is>
-      </c>
-      <c r="D48" s="11" t="inlineStr">
-        <is>
-          <t>Deferred - only HTTP access is gated; an existing realtime-gateway connection isn't forcibly closed</t>
-        </is>
-      </c>
+          <t>Trust &amp; Safety: Suspension/Ban actually restrict access (new requireActive middleware, one entry point)</t>
+        </is>
+      </c>
+      <c r="D48" s="11" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="9" t="n">
@@ -2461,18 +2457,18 @@
       </c>
       <c r="C49" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: aggregating lower-severity signals over a time window</t>
+          <t>Trust &amp; Safety: WebSocket disconnect on suspension/ban</t>
         </is>
       </c>
       <c r="D49" s="11" t="inlineStr">
         <is>
-          <t>Deferred - a real abuse-detection engine is out of this phase's scope; only single-critical-signal escalation is implemented</t>
+          <t>Deferred - only HTTP access is gated; an existing realtime-gateway connection isn't forcibly closed</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B50" s="13" t="inlineStr">
         <is>
@@ -2481,23 +2477,27 @@
       </c>
       <c r="C50" s="11" t="inlineStr">
         <is>
-          <t>Billing / Entitlements: Payment model</t>
-        </is>
-      </c>
-      <c r="D50" s="11" t="inlineStr"/>
+          <t>Trust &amp; Safety: aggregating lower-severity signals over a time window</t>
+        </is>
+      </c>
+      <c r="D50" s="11" t="inlineStr">
+        <is>
+          <t>Deferred - a real abuse-detection engine is out of this phase's scope; only single-critical-signal escalation is implemented</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="B51" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B51" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>Billing / Entitlements: Entitlement model (kept separate from Payment)</t>
+          <t>Billing: Payment model (provider-specific transaction record)</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr"/>
@@ -2506,14 +2506,14 @@
       <c r="A52" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="B52" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B52" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C52" s="11" t="inlineStr">
         <is>
-          <t>Billing / Entitlements: provider abstraction (implement first)</t>
+          <t>Billing: Entitlement model (platform-facing truth, kept separate from Payment)</t>
         </is>
       </c>
       <c r="D52" s="11" t="inlineStr"/>
@@ -2522,14 +2522,14 @@
       <c r="A53" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="B53" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B53" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C53" s="11" t="inlineStr">
         <is>
-          <t>Billing / Entitlements: Stripe adapter</t>
+          <t>Billing: provider abstraction (PaymentProvider interface + registry, implemented first)</t>
         </is>
       </c>
       <c r="D53" s="11" t="inlineStr"/>
@@ -2538,17 +2538,21 @@
       <c r="A54" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="B54" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B54" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C54" s="11" t="inlineStr">
         <is>
-          <t>Billing / Entitlements: Apple IAP adapter</t>
-        </is>
-      </c>
-      <c r="D54" s="11" t="inlineStr"/>
+          <t>Billing: Stripe adapter</t>
+        </is>
+      </c>
+      <c r="D54" s="11" t="inlineStr">
+        <is>
+          <t>Real HMAC-SHA256 webhook signature verification, live-validated without a Stripe account via self-signed test payloads</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="9" t="n">
@@ -2561,14 +2565,18 @@
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t>Billing / Entitlements: Google Play adapter</t>
-        </is>
-      </c>
-      <c r="D55" s="11" t="inlineStr"/>
+          <t>Billing: Apple IAP adapter</t>
+        </is>
+      </c>
+      <c r="D55" s="11" t="inlineStr">
+        <is>
+          <t>Deferred - needs real App Store Server API credentials this environment doesn't have</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B56" s="13" t="inlineStr">
         <is>
@@ -2577,10 +2585,14 @@
       </c>
       <c r="C56" s="11" t="inlineStr">
         <is>
-          <t>Analytics: generic analytics event envelope (event_name/user_id/anonymous_id/app_id/session_id/timestamp/properties/context)</t>
-        </is>
-      </c>
-      <c r="D56" s="11" t="inlineStr"/>
+          <t>Billing: Google Play adapter</t>
+        </is>
+      </c>
+      <c r="D56" s="11" t="inlineStr">
+        <is>
+          <t>Deferred - needs real Play Developer API credentials this environment doesn't have</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="9" t="n">
@@ -2593,7 +2605,7 @@
       </c>
       <c r="C57" s="11" t="inlineStr">
         <is>
-          <t>Analytics: keep operational DBs out of the analytics path</t>
+          <t>Analytics: generic analytics event envelope (event_name/user_id/anonymous_id/app_id/session_id/timestamp/properties/context)</t>
         </is>
       </c>
       <c r="D57" s="11" t="inlineStr"/>
@@ -2609,14 +2621,14 @@
       </c>
       <c r="C58" s="11" t="inlineStr">
         <is>
-          <t>Analytics: pipeline foundation for ClickHouse/warehouse/data lake</t>
+          <t>Analytics: keep operational DBs out of the analytics path</t>
         </is>
       </c>
       <c r="D58" s="11" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B59" s="13" t="inlineStr">
         <is>
@@ -2625,7 +2637,7 @@
       </c>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: provider-neutral interface (OpenAI/Anthropic/Google/local/Ollama/vLLM)</t>
+          <t>Analytics: pipeline foundation for ClickHouse/warehouse/data lake</t>
         </is>
       </c>
       <c r="D59" s="11" t="inlineStr"/>
@@ -2641,7 +2653,7 @@
       </c>
       <c r="C60" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: model routing</t>
+          <t>AI Gateway: provider-neutral interface (OpenAI/Anthropic/Google/local/Ollama/vLLM)</t>
         </is>
       </c>
       <c r="D60" s="11" t="inlineStr"/>
@@ -2657,7 +2669,7 @@
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: quotas</t>
+          <t>AI Gateway: model routing</t>
         </is>
       </c>
       <c r="D61" s="11" t="inlineStr"/>
@@ -2673,7 +2685,7 @@
       </c>
       <c r="C62" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: token usage tracking</t>
+          <t>AI Gateway: quotas</t>
         </is>
       </c>
       <c r="D62" s="11" t="inlineStr"/>
@@ -2689,7 +2701,7 @@
       </c>
       <c r="C63" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: cost tracking</t>
+          <t>AI Gateway: token usage tracking</t>
         </is>
       </c>
       <c r="D63" s="11" t="inlineStr"/>
@@ -2705,7 +2717,7 @@
       </c>
       <c r="C64" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: audit integration</t>
+          <t>AI Gateway: cost tracking</t>
         </is>
       </c>
       <c r="D64" s="11" t="inlineStr"/>
@@ -2721,7 +2733,7 @@
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: prompt/version metadata</t>
+          <t>AI Gateway: audit integration</t>
         </is>
       </c>
       <c r="D65" s="11" t="inlineStr"/>
@@ -2737,7 +2749,7 @@
       </c>
       <c r="C66" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: timeouts</t>
+          <t>AI Gateway: prompt/version metadata</t>
         </is>
       </c>
       <c r="D66" s="11" t="inlineStr"/>
@@ -2753,14 +2765,14 @@
       </c>
       <c r="C67" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: fallback</t>
+          <t>AI Gateway: timeouts</t>
         </is>
       </c>
       <c r="D67" s="11" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B68" s="13" t="inlineStr">
         <is>
@@ -2769,7 +2781,7 @@
       </c>
       <c r="C68" s="11" t="inlineStr">
         <is>
-          <t>Admin Portal: control-plane UI in apps/admin</t>
+          <t>AI Gateway: fallback</t>
         </is>
       </c>
       <c r="D68" s="11" t="inlineStr"/>
@@ -2785,7 +2797,7 @@
       </c>
       <c r="C69" s="11" t="inlineStr">
         <is>
-          <t>Admin Portal: visibility: Applications</t>
+          <t>Admin Portal: control-plane UI in apps/admin</t>
         </is>
       </c>
       <c r="D69" s="11" t="inlineStr"/>
@@ -2801,7 +2813,7 @@
       </c>
       <c r="C70" s="11" t="inlineStr">
         <is>
-          <t>Admin Portal: visibility: Users/Sessions/Devices</t>
+          <t>Admin Portal: visibility: Applications</t>
         </is>
       </c>
       <c r="D70" s="11" t="inlineStr"/>
@@ -2817,7 +2829,7 @@
       </c>
       <c r="C71" s="11" t="inlineStr">
         <is>
-          <t>Admin Portal: visibility: Roles/Permissions</t>
+          <t>Admin Portal: visibility: Users/Sessions/Devices</t>
         </is>
       </c>
       <c r="D71" s="11" t="inlineStr"/>
@@ -2833,7 +2845,7 @@
       </c>
       <c r="C72" s="11" t="inlineStr">
         <is>
-          <t>Admin Portal: visibility: Tenants/Relationships</t>
+          <t>Admin Portal: visibility: Roles/Permissions</t>
         </is>
       </c>
       <c r="D72" s="11" t="inlineStr"/>
@@ -2849,7 +2861,7 @@
       </c>
       <c r="C73" s="11" t="inlineStr">
         <is>
-          <t>Admin Portal: visibility: Messages/Notifications</t>
+          <t>Admin Portal: visibility: Tenants/Relationships</t>
         </is>
       </c>
       <c r="D73" s="11" t="inlineStr"/>
@@ -2865,7 +2877,7 @@
       </c>
       <c r="C74" s="11" t="inlineStr">
         <is>
-          <t>Admin Portal: visibility: Files/Jobs</t>
+          <t>Admin Portal: visibility: Messages/Notifications</t>
         </is>
       </c>
       <c r="D74" s="11" t="inlineStr"/>
@@ -2881,7 +2893,7 @@
       </c>
       <c r="C75" s="11" t="inlineStr">
         <is>
-          <t>Admin Portal: visibility: Feature flags/Configuration</t>
+          <t>Admin Portal: visibility: Files/Jobs</t>
         </is>
       </c>
       <c r="D75" s="11" t="inlineStr"/>
@@ -2897,7 +2909,7 @@
       </c>
       <c r="C76" s="11" t="inlineStr">
         <is>
-          <t>Admin Portal: visibility: Moderation/Audit</t>
+          <t>Admin Portal: visibility: Feature flags/Configuration</t>
         </is>
       </c>
       <c r="D76" s="11" t="inlineStr"/>
@@ -2913,7 +2925,7 @@
       </c>
       <c r="C77" s="11" t="inlineStr">
         <is>
-          <t>Admin Portal: visibility: System health/Deployments</t>
+          <t>Admin Portal: visibility: Moderation/Audit</t>
         </is>
       </c>
       <c r="D77" s="11" t="inlineStr"/>
@@ -2929,14 +2941,14 @@
       </c>
       <c r="C78" s="11" t="inlineStr">
         <is>
-          <t>Admin Portal: must go through service APIs, never direct DB queries</t>
+          <t>Admin Portal: visibility: System health/Deployments</t>
         </is>
       </c>
       <c r="D78" s="11" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B79" s="13" t="inlineStr">
         <is>
@@ -2945,7 +2957,7 @@
       </c>
       <c r="C79" s="11" t="inlineStr">
         <is>
-          <t>Backstage: integrate Backstage as developer portal</t>
+          <t>Admin Portal: must go through service APIs, never direct DB queries</t>
         </is>
       </c>
       <c r="D79" s="11" t="inlineStr"/>
@@ -2961,7 +2973,7 @@
       </c>
       <c r="C80" s="11" t="inlineStr">
         <is>
-          <t>Backstage: per-module metadata: name/description/owner/lifecycle</t>
+          <t>Backstage: integrate Backstage as developer portal</t>
         </is>
       </c>
       <c r="D80" s="11" t="inlineStr"/>
@@ -2977,7 +2989,7 @@
       </c>
       <c r="C81" s="11" t="inlineStr">
         <is>
-          <t>Backstage: per-module metadata: repository/documentation/dependencies</t>
+          <t>Backstage: per-module metadata: name/description/owner/lifecycle</t>
         </is>
       </c>
       <c r="D81" s="11" t="inlineStr"/>
@@ -2993,14 +3005,14 @@
       </c>
       <c r="C82" s="11" t="inlineStr">
         <is>
-          <t>Backstage: per-module metadata: APIs/events/DB ownership/dashboards/runbooks</t>
+          <t>Backstage: per-module metadata: repository/documentation/dependencies</t>
         </is>
       </c>
       <c r="D82" s="11" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B83" s="13" t="inlineStr">
         <is>
@@ -3009,7 +3021,7 @@
       </c>
       <c r="C83" s="11" t="inlineStr">
         <is>
-          <t>SDKs: Flutter SDK</t>
+          <t>Backstage: per-module metadata: APIs/events/DB ownership/dashboards/runbooks</t>
         </is>
       </c>
       <c r="D83" s="11" t="inlineStr"/>
@@ -3025,7 +3037,7 @@
       </c>
       <c r="C84" s="11" t="inlineStr">
         <is>
-          <t>SDKs: TypeScript SDK</t>
+          <t>SDKs: Flutter SDK</t>
         </is>
       </c>
       <c r="D84" s="11" t="inlineStr"/>
@@ -3041,7 +3053,7 @@
       </c>
       <c r="C85" s="11" t="inlineStr">
         <is>
-          <t>SDKs: Go SDK</t>
+          <t>SDKs: TypeScript SDK</t>
         </is>
       </c>
       <c r="D85" s="11" t="inlineStr"/>
@@ -3057,7 +3069,7 @@
       </c>
       <c r="C86" s="11" t="inlineStr">
         <is>
-          <t>SDKs: auth + token refresh in each SDK</t>
+          <t>SDKs: Go SDK</t>
         </is>
       </c>
       <c r="D86" s="11" t="inlineStr"/>
@@ -3073,7 +3085,7 @@
       </c>
       <c r="C87" s="11" t="inlineStr">
         <is>
-          <t>SDKs: pagination + safe retries</t>
+          <t>SDKs: auth + token refresh in each SDK</t>
         </is>
       </c>
       <c r="D87" s="11" t="inlineStr"/>
@@ -3089,7 +3101,7 @@
       </c>
       <c r="C88" s="11" t="inlineStr">
         <is>
-          <t>SDKs: realtime connection helper</t>
+          <t>SDKs: pagination + safe retries</t>
         </is>
       </c>
       <c r="D88" s="11" t="inlineStr"/>
@@ -3105,7 +3117,7 @@
       </c>
       <c r="C89" s="11" t="inlineStr">
         <is>
-          <t>SDKs: correlation ID propagation</t>
+          <t>SDKs: realtime connection helper</t>
         </is>
       </c>
       <c r="D89" s="11" t="inlineStr"/>
@@ -3121,14 +3133,14 @@
       </c>
       <c r="C90" s="11" t="inlineStr">
         <is>
-          <t>SDKs: device registration helper</t>
+          <t>SDKs: correlation ID propagation</t>
         </is>
       </c>
       <c r="D90" s="11" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B91" s="13" t="inlineStr">
         <is>
@@ -3137,7 +3149,7 @@
       </c>
       <c r="C91" s="11" t="inlineStr">
         <is>
-          <t>Observability Completion: structured logs everywhere</t>
+          <t>SDKs: device registration helper</t>
         </is>
       </c>
       <c r="D91" s="11" t="inlineStr"/>
@@ -3153,7 +3165,7 @@
       </c>
       <c r="C92" s="11" t="inlineStr">
         <is>
-          <t>Observability Completion: metrics everywhere</t>
+          <t>Observability Completion: structured logs everywhere</t>
         </is>
       </c>
       <c r="D92" s="11" t="inlineStr"/>
@@ -3169,7 +3181,7 @@
       </c>
       <c r="C93" s="11" t="inlineStr">
         <is>
-          <t>Observability Completion: distributed traces everywhere</t>
+          <t>Observability Completion: metrics everywhere</t>
         </is>
       </c>
       <c r="D93" s="11" t="inlineStr"/>
@@ -3185,7 +3197,7 @@
       </c>
       <c r="C94" s="11" t="inlineStr">
         <is>
-          <t>Observability Completion: health checks everywhere</t>
+          <t>Observability Completion: distributed traces everywhere</t>
         </is>
       </c>
       <c r="D94" s="11" t="inlineStr"/>
@@ -3201,7 +3213,7 @@
       </c>
       <c r="C95" s="11" t="inlineStr">
         <is>
-          <t>Observability Completion: dashboard: API latency</t>
+          <t>Observability Completion: health checks everywhere</t>
         </is>
       </c>
       <c r="D95" s="11" t="inlineStr"/>
@@ -3217,7 +3229,7 @@
       </c>
       <c r="C96" s="11" t="inlineStr">
         <is>
-          <t>Observability Completion: dashboard: error rate</t>
+          <t>Observability Completion: dashboard: API latency</t>
         </is>
       </c>
       <c r="D96" s="11" t="inlineStr"/>
@@ -3233,7 +3245,7 @@
       </c>
       <c r="C97" s="11" t="inlineStr">
         <is>
-          <t>Observability Completion: dashboard: requests/sec</t>
+          <t>Observability Completion: dashboard: error rate</t>
         </is>
       </c>
       <c r="D97" s="11" t="inlineStr"/>
@@ -3249,7 +3261,7 @@
       </c>
       <c r="C98" s="11" t="inlineStr">
         <is>
-          <t>Observability Completion: dashboard: DB connections</t>
+          <t>Observability Completion: dashboard: requests/sec</t>
         </is>
       </c>
       <c r="D98" s="11" t="inlineStr"/>
@@ -3265,7 +3277,7 @@
       </c>
       <c r="C99" s="11" t="inlineStr">
         <is>
-          <t>Observability Completion: dashboard: Kafka lag</t>
+          <t>Observability Completion: dashboard: DB connections</t>
         </is>
       </c>
       <c r="D99" s="11" t="inlineStr"/>
@@ -3281,7 +3293,7 @@
       </c>
       <c r="C100" s="11" t="inlineStr">
         <is>
-          <t>Observability Completion: dashboard: WebSocket connections</t>
+          <t>Observability Completion: dashboard: Kafka lag</t>
         </is>
       </c>
       <c r="D100" s="11" t="inlineStr"/>
@@ -3297,7 +3309,7 @@
       </c>
       <c r="C101" s="11" t="inlineStr">
         <is>
-          <t>Observability Completion: dashboard: Redis latency</t>
+          <t>Observability Completion: dashboard: WebSocket connections</t>
         </is>
       </c>
       <c r="D101" s="11" t="inlineStr"/>
@@ -3313,7 +3325,7 @@
       </c>
       <c r="C102" s="11" t="inlineStr">
         <is>
-          <t>Observability Completion: dashboard: notification failures</t>
+          <t>Observability Completion: dashboard: Redis latency</t>
         </is>
       </c>
       <c r="D102" s="11" t="inlineStr"/>
@@ -3329,7 +3341,7 @@
       </c>
       <c r="C103" s="11" t="inlineStr">
         <is>
-          <t>Observability Completion: dashboard: background job failures</t>
+          <t>Observability Completion: dashboard: notification failures</t>
         </is>
       </c>
       <c r="D103" s="11" t="inlineStr"/>
@@ -3345,14 +3357,14 @@
       </c>
       <c r="C104" s="11" t="inlineStr">
         <is>
-          <t>Observability Completion: alerting rules</t>
+          <t>Observability Completion: dashboard: background job failures</t>
         </is>
       </c>
       <c r="D104" s="11" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B105" s="13" t="inlineStr">
         <is>
@@ -3361,7 +3373,7 @@
       </c>
       <c r="C105" s="11" t="inlineStr">
         <is>
-          <t>Platform Control Plane: one view: applications/services/versions</t>
+          <t>Observability Completion: alerting rules</t>
         </is>
       </c>
       <c r="D105" s="11" t="inlineStr"/>
@@ -3377,7 +3389,7 @@
       </c>
       <c r="C106" s="11" t="inlineStr">
         <is>
-          <t>Platform Control Plane: one view: environments/dependencies/deployments</t>
+          <t>Platform Control Plane: one view: applications/services/versions</t>
         </is>
       </c>
       <c r="D106" s="11" t="inlineStr"/>
@@ -3393,7 +3405,7 @@
       </c>
       <c r="C107" s="11" t="inlineStr">
         <is>
-          <t>Platform Control Plane: one view: DB ownership/events/API contracts</t>
+          <t>Platform Control Plane: one view: environments/dependencies/deployments</t>
         </is>
       </c>
       <c r="D107" s="11" t="inlineStr"/>
@@ -3409,14 +3421,14 @@
       </c>
       <c r="C108" s="11" t="inlineStr">
         <is>
-          <t>Platform Control Plane: one view: health/alerts/recent changes</t>
+          <t>Platform Control Plane: one view: DB ownership/events/API contracts</t>
         </is>
       </c>
       <c r="D108" s="11" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="9" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B109" s="13" t="inlineStr">
         <is>
@@ -3425,7 +3437,7 @@
       </c>
       <c r="C109" s="11" t="inlineStr">
         <is>
-          <t>AI Development Context: every module: README</t>
+          <t>Platform Control Plane: one view: health/alerts/recent changes</t>
         </is>
       </c>
       <c r="D109" s="11" t="inlineStr"/>
@@ -3441,7 +3453,7 @@
       </c>
       <c r="C110" s="11" t="inlineStr">
         <is>
-          <t>AI Development Context: every module: ownership metadata</t>
+          <t>AI Development Context: every module: README</t>
         </is>
       </c>
       <c r="D110" s="11" t="inlineStr"/>
@@ -3457,7 +3469,7 @@
       </c>
       <c r="C111" s="11" t="inlineStr">
         <is>
-          <t>AI Development Context: every module: dependencies</t>
+          <t>AI Development Context: every module: ownership metadata</t>
         </is>
       </c>
       <c r="D111" s="11" t="inlineStr"/>
@@ -3473,7 +3485,7 @@
       </c>
       <c r="C112" s="11" t="inlineStr">
         <is>
-          <t>AI Development Context: every module: API contract</t>
+          <t>AI Development Context: every module: dependencies</t>
         </is>
       </c>
       <c r="D112" s="11" t="inlineStr"/>
@@ -3489,7 +3501,7 @@
       </c>
       <c r="C113" s="11" t="inlineStr">
         <is>
-          <t>AI Development Context: every module: event contracts</t>
+          <t>AI Development Context: every module: API contract</t>
         </is>
       </c>
       <c r="D113" s="11" t="inlineStr"/>
@@ -3505,10 +3517,26 @@
       </c>
       <c r="C114" s="11" t="inlineStr">
         <is>
+          <t>AI Development Context: every module: event contracts</t>
+        </is>
+      </c>
+      <c r="D114" s="11" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="B115" s="13" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="C115" s="11" t="inlineStr">
+        <is>
           <t>AI Development Context: every module: DB ownership</t>
         </is>
       </c>
-      <c r="D114" s="11" t="inlineStr"/>
+      <c r="D115" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3524,7 +3552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4332,6 +4360,70 @@
       <c r="F25" s="11" t="inlineStr">
         <is>
           <t>Phase 21</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="32" customHeight="1">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>billing</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="inlineStr">
+        <is>
+          <t>core-api</t>
+        </is>
+      </c>
+      <c r="C26" s="11" t="inlineStr">
+        <is>
+          <t>Entitlement (platform truth) kept separate from Payment (provider transaction record); PaymentProvider abstraction + registry</t>
+        </is>
+      </c>
+      <c r="D26" s="11" t="inlineStr">
+        <is>
+          <t>entitlements, payments</t>
+        </is>
+      </c>
+      <c r="E26" s="11" t="inlineStr">
+        <is>
+          <t>Self for own entitlements/payments; platform.admin for manual grants</t>
+        </is>
+      </c>
+      <c r="F26" s="11" t="inlineStr">
+        <is>
+          <t>Phase 22</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="32" customHeight="1">
+      <c r="A27" s="11" t="inlineStr">
+        <is>
+          <t>billing/stripe</t>
+        </is>
+      </c>
+      <c r="B27" s="11" t="inlineStr">
+        <is>
+          <t>core-api</t>
+        </is>
+      </c>
+      <c r="C27" s="11" t="inlineStr">
+        <is>
+          <t>Real Stripe webhook HMAC-SHA256 signature verification - the one live-testable PaymentProvider this phase ships</t>
+        </is>
+      </c>
+      <c r="D27" s="11" t="inlineStr">
+        <is>
+          <t>none (stateless verification)</t>
+        </is>
+      </c>
+      <c r="E27" s="11" t="inlineStr">
+        <is>
+          <t>n/a (provider-signature-authenticated, not a Bearer route)</t>
+        </is>
+      </c>
+      <c r="F27" s="11" t="inlineStr">
+        <is>
+          <t>Phase 22</t>
         </is>
       </c>
     </row>
@@ -4349,7 +4441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E132"/>
+  <dimension ref="A1:E138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -7612,6 +7704,164 @@
       <c r="E132" s="11" t="inlineStr">
         <is>
           <t>?resourceType=&amp;resourceId=</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="11" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="B133" s="11" t="inlineStr">
+        <is>
+          <t>/v1/billing/entitlements</t>
+        </is>
+      </c>
+      <c r="C133" s="11" t="inlineStr">
+        <is>
+          <t>billing</t>
+        </is>
+      </c>
+      <c r="D133" s="11" t="inlineStr">
+        <is>
+          <t>Self or platform.admin</t>
+        </is>
+      </c>
+      <c r="E133" s="11" t="inlineStr">
+        <is>
+          <t>?userId=</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="11" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="B134" s="11" t="inlineStr">
+        <is>
+          <t>/v1/billing/entitlements/check/{key}</t>
+        </is>
+      </c>
+      <c r="C134" s="11" t="inlineStr">
+        <is>
+          <t>billing</t>
+        </is>
+      </c>
+      <c r="D134" s="11" t="inlineStr">
+        <is>
+          <t>Authenticated (self)</t>
+        </is>
+      </c>
+      <c r="E134" s="11" t="inlineStr">
+        <is>
+          <t>the literal 'do I have entitlement X' check</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="11" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="B135" s="11" t="inlineStr">
+        <is>
+          <t>/v1/billing/entitlements</t>
+        </is>
+      </c>
+      <c r="C135" s="11" t="inlineStr">
+        <is>
+          <t>billing</t>
+        </is>
+      </c>
+      <c r="D135" s="11" t="inlineStr">
+        <is>
+          <t>platform.admin</t>
+        </is>
+      </c>
+      <c r="E135" s="11" t="inlineStr">
+        <is>
+          <t>manual grant; source always "manual:&lt;adminId&gt;"</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="11" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="B136" s="11" t="inlineStr">
+        <is>
+          <t>/v1/billing/entitlements/{id}/revoke</t>
+        </is>
+      </c>
+      <c r="C136" s="11" t="inlineStr">
+        <is>
+          <t>billing</t>
+        </is>
+      </c>
+      <c r="D136" s="11" t="inlineStr">
+        <is>
+          <t>platform.admin</t>
+        </is>
+      </c>
+      <c r="E136" s="11" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="11" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="B137" s="11" t="inlineStr">
+        <is>
+          <t>/v1/billing/payments</t>
+        </is>
+      </c>
+      <c r="C137" s="11" t="inlineStr">
+        <is>
+          <t>billing</t>
+        </is>
+      </c>
+      <c r="D137" s="11" t="inlineStr">
+        <is>
+          <t>Self or platform.admin</t>
+        </is>
+      </c>
+      <c r="E137" s="11" t="inlineStr">
+        <is>
+          <t>?userId=</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="11" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="B138" s="11" t="inlineStr">
+        <is>
+          <t>/v1/billing/webhooks/{provider}</t>
+        </is>
+      </c>
+      <c r="C138" s="11" t="inlineStr">
+        <is>
+          <t>billing</t>
+        </is>
+      </c>
+      <c r="D138" s="11" t="inlineStr">
+        <is>
+          <t>Provider webhook signature (no Bearer token)</t>
+        </is>
+      </c>
+      <c r="E138" s="11" t="inlineStr">
+        <is>
+          <t>the one route on this platform with no requireUser/requireActive</t>
         </is>
       </c>
     </row>

--- a/docs/control/data.xlsx
+++ b/docs/control/data.xlsx
@@ -239,8 +239,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="TodoChecklist" displayName="TodoChecklist" ref="A1:D115" headerRowCount="1">
-  <autoFilter ref="A1:D115"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="TodoChecklist" displayName="TodoChecklist" ref="A1:D117" headerRowCount="1">
+  <autoFilter ref="A1:D117"/>
   <tableColumns count="4">
     <tableColumn id="1" name="Phase"/>
     <tableColumn id="2" name="Status"/>
@@ -252,8 +252,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Modules" displayName="Modules" ref="A1:F27" headerRowCount="1">
-  <autoFilter ref="A1:F27"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Modules" displayName="Modules" ref="A1:F29" headerRowCount="1">
+  <autoFilter ref="A1:F29"/>
   <tableColumns count="6">
     <tableColumn id="1" name="Module"/>
     <tableColumn id="2" name="Service"/>
@@ -267,8 +267,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="APIEndpoints" displayName="APIEndpoints" ref="A1:E138" headerRowCount="1">
-  <autoFilter ref="A1:E138"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="APIEndpoints" displayName="APIEndpoints" ref="A1:E140" headerRowCount="1">
+  <autoFilter ref="A1:E140"/>
   <tableColumns count="5">
     <tableColumn id="1" name="Method"/>
     <tableColumn id="2" name="Path"/>
@@ -633,12 +633,12 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>22 / 30</t>
+          <t>23 / 30</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>73%</t>
+          <t>77%</t>
         </is>
       </c>
     </row>
@@ -684,7 +684,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>139</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>data/migrations/0001-0020</t>
+          <t>data/migrations/0001-0021</t>
         </is>
       </c>
     </row>
@@ -752,7 +752,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
@@ -1421,9 +1421,9 @@
       <c r="A24" s="9" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="12" t="inlineStr">
-        <is>
-          <t>Next up</t>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C24" s="11" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="D24" s="11" t="inlineStr">
         <is>
-          <t>Generic analytics event envelope (event_name/user_id/anonymous_id/app_id/session_id/timestamp/properties/context). Operational DBs must not become analytics DBs - pipeline foundation for ClickHouse/warehouse/data lake.</t>
+          <t>Generic event envelope, matching the roadmap's own field names verbatim. analytics_events is a landing buffer, never queried for analytics - a new worker pipeline batches unflushed rows as NDJSON into MinIO/S3 (a real data-lake landing pattern). Track is this platform's one open, unauthenticated write endpoint, IP-rate-limited instead of Bearer-gated.</t>
         </is>
       </c>
       <c r="E24" s="11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>aa207ae</t>
         </is>
       </c>
     </row>
@@ -1446,9 +1446,9 @@
       <c r="A25" s="9" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>Next up</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
@@ -1631,7 +1631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D115"/>
+  <dimension ref="A1:D117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2016,7 +2016,7 @@
     </row>
     <row r="24">
       <c r="A24" s="9" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
@@ -2025,14 +2025,14 @@
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>Repo health baseline (make doctor / validate-all / go test / go build) run and passed</t>
+          <t>Phase 23: Analytics implemented, unit-tested, live-validated, documented, committed</t>
         </is>
       </c>
       <c r="D24" s="11" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
@@ -2041,18 +2041,14 @@
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>Environment / ApplicationVersion / ApplicationConfiguration</t>
-        </is>
-      </c>
-      <c r="D25" s="11" t="inlineStr">
-        <is>
-          <t>Deferred - no consumer needs them yet, documented as intentional in applications/README.md</t>
-        </is>
-      </c>
+          <t>Repo health baseline (make doctor / validate-all / go test / go build) run and passed</t>
+        </is>
+      </c>
+      <c r="D25" s="11" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
@@ -2061,32 +2057,32 @@
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>Separate Session table</t>
+          <t>Environment / ApplicationVersion / ApplicationConfiguration</t>
         </is>
       </c>
       <c r="D26" s="11" t="inlineStr">
         <is>
-          <t>Deferred - Device.SessionStatus covers today's single-session-per-device need, documented in devices/README.md</t>
+          <t>Deferred - no consumer needs them yet, documented as intentional in applications/README.md</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="B27" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+        <v>5</v>
+      </c>
+      <c r="B27" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>UserPreferences (named in Phase 4, no fields ever specified)</t>
+          <t>Separate Session table</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>Deferred to Phase 12+; notification preferences shipped, a generic preferences bag did not</t>
+          <t>Deferred - Device.SessionStatus covers today's single-session-per-device need, documented in devices/README.md</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2097,12 @@
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>apps/mobile test/ directory (make flutter-test currently fails)</t>
+          <t>UserPreferences (named in Phase 4, no fields ever specified)</t>
         </is>
       </c>
       <c r="D28" s="11" t="inlineStr">
         <is>
-          <t>Known gap since Phase 9's audit, not yet picked up</t>
+          <t>Deferred to Phase 12+; notification preferences shipped, a generic preferences bag did not</t>
         </is>
       </c>
     </row>
@@ -2121,30 +2117,34 @@
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>apps/admin next@15 / sharp transitive advisories</t>
+          <t>apps/mobile test/ directory (make flutter-test currently fails)</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>Fix is a Next.js major-version bump - separate, reviewable change</t>
+          <t>Known gap since Phase 9's audit, not yet picked up</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="9" t="n">
-        <v>20</v>
-      </c>
-      <c r="B30" s="10" t="inlineStr">
-        <is>
-          <t>Done</t>
+        <v>9</v>
+      </c>
+      <c r="B30" s="13" t="inlineStr">
+        <is>
+          <t>Pending</t>
         </is>
       </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t>Privacy: consent (append-only history)</t>
-        </is>
-      </c>
-      <c r="D30" s="11" t="inlineStr"/>
+          <t>apps/admin next@15 / sharp transitive advisories</t>
+        </is>
+      </c>
+      <c r="D30" s="11" t="inlineStr">
+        <is>
+          <t>Fix is a Next.js major-version bump - separate, reviewable change</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="9" t="n">
@@ -2157,7 +2157,7 @@
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>Privacy: user data export (ExportUserData registry - users/devices/files/audit)</t>
+          <t>Privacy: consent (append-only history)</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr"/>
@@ -2173,7 +2173,7 @@
       </c>
       <c r="C32" s="11" t="inlineStr">
         <is>
-          <t>Privacy: user deletion (DeleteUserData registry - users/devices/files; audit deliberately excluded)</t>
+          <t>Privacy: user data export (ExportUserData registry - users/devices/files/audit)</t>
         </is>
       </c>
       <c r="D32" s="11" t="inlineStr"/>
@@ -2189,7 +2189,7 @@
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>Privacy: retention policy (declared, not scheduled - same documented gap as Phase 13's PurgeExpired)</t>
+          <t>Privacy: user deletion (DeleteUserData registry - users/devices/files; audit deliberately excluded)</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr"/>
@@ -2205,7 +2205,7 @@
       </c>
       <c r="C34" s="11" t="inlineStr">
         <is>
-          <t>Privacy: privacy preferences</t>
+          <t>Privacy: retention policy (declared, not scheduled - same documented gap as Phase 13's PurgeExpired)</t>
         </is>
       </c>
       <c r="D34" s="11" t="inlineStr"/>
@@ -2221,7 +2221,7 @@
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>Privacy: coordinate deletion through workflows/events - core-api's own embedded Temporal worker</t>
+          <t>Privacy: privacy preferences</t>
         </is>
       </c>
       <c r="D35" s="11" t="inlineStr"/>
@@ -2230,21 +2230,17 @@
       <c r="A36" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="B36" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B36" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C36" s="11" t="inlineStr">
         <is>
-          <t>Privacy: notifications module as an Export/Delete participant</t>
-        </is>
-      </c>
-      <c r="D36" s="11" t="inlineStr">
-        <is>
-          <t>Deliberately deferred to prove the registry makes this a 2-line addition later, not a framework change</t>
-        </is>
-      </c>
+          <t>Privacy: coordinate deletion through workflows/events - core-api's own embedded Temporal worker</t>
+        </is>
+      </c>
+      <c r="D36" s="11" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="9" t="n">
@@ -2257,32 +2253,32 @@
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>Privacy: relationships/groups/messaging as participants</t>
+          <t>Privacy: notifications module as an Export/Delete participant</t>
         </is>
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>Deferred - shared multi-user data needs a redaction strategy this phase's per-user-in-isolation registry doesn't fit</t>
+          <t>Deliberately deferred to prove the registry makes this a 2-line addition later, not a framework change</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="9" t="n">
-        <v>21</v>
-      </c>
-      <c r="B38" s="10" t="inlineStr">
-        <is>
-          <t>Done</t>
+        <v>20</v>
+      </c>
+      <c r="B38" s="13" t="inlineStr">
+        <is>
+          <t>Pending</t>
         </is>
       </c>
       <c r="C38" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: Block</t>
+          <t>Privacy: relationships/groups/messaging as participants</t>
         </is>
       </c>
       <c r="D38" s="11" t="inlineStr">
         <is>
-          <t>Reused Phase 8's relationships (Status='blocked'), deliberately not duplicated</t>
+          <t>Deferred - shared multi-user data needs a redaction strategy this phase's per-user-in-isolation registry doesn't fit</t>
         </is>
       </c>
     </row>
@@ -2297,10 +2293,14 @@
       </c>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: Mute</t>
-        </is>
-      </c>
-      <c r="D39" s="11" t="inlineStr"/>
+          <t>Trust &amp; Safety: Block</t>
+        </is>
+      </c>
+      <c r="D39" s="11" t="inlineStr">
+        <is>
+          <t>Reused Phase 8's relationships (Status='blocked'), deliberately not duplicated</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="9" t="n">
@@ -2313,7 +2313,7 @@
       </c>
       <c r="C40" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: Report -&gt; ModerationCase (deduplicated via partial unique index)</t>
+          <t>Trust &amp; Safety: Mute</t>
         </is>
       </c>
       <c r="D40" s="11" t="inlineStr"/>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: Suspension</t>
+          <t>Trust &amp; Safety: Report -&gt; ModerationCase (deduplicated via partial unique index)</t>
         </is>
       </c>
       <c r="D41" s="11" t="inlineStr"/>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="C42" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: Ban</t>
+          <t>Trust &amp; Safety: Suspension</t>
         </is>
       </c>
       <c r="D42" s="11" t="inlineStr"/>
@@ -2361,7 +2361,7 @@
       </c>
       <c r="C43" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: Appeal (approving lifts the target restriction)</t>
+          <t>Trust &amp; Safety: Ban</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr"/>
@@ -2377,7 +2377,7 @@
       </c>
       <c r="C44" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: rate limiting (new platformkit/ratelimit, Valkey-backed)</t>
+          <t>Trust &amp; Safety: Appeal (approving lifts the target restriction)</t>
         </is>
       </c>
       <c r="D44" s="11" t="inlineStr"/>
@@ -2393,7 +2393,7 @@
       </c>
       <c r="C45" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: spam protection (5 reports/hour per reporter)</t>
+          <t>Trust &amp; Safety: rate limiting (new platformkit/ratelimit, Valkey-backed)</t>
         </is>
       </c>
       <c r="D45" s="11" t="inlineStr"/>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="C46" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: abuse signals (critical severity auto-opens a case)</t>
+          <t>Trust &amp; Safety: spam protection (5 reports/hour per reporter)</t>
         </is>
       </c>
       <c r="D46" s="11" t="inlineStr"/>
@@ -2425,7 +2425,7 @@
       </c>
       <c r="C47" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: pluggable product-specific report reasons (free-form Reason field)</t>
+          <t>Trust &amp; Safety: abuse signals (critical severity auto-opens a case)</t>
         </is>
       </c>
       <c r="D47" s="11" t="inlineStr"/>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="C48" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: Suspension/Ban actually restrict access (new requireActive middleware, one entry point)</t>
+          <t>Trust &amp; Safety: pluggable product-specific report reasons (free-form Reason field)</t>
         </is>
       </c>
       <c r="D48" s="11" t="inlineStr"/>
@@ -2450,21 +2450,17 @@
       <c r="A49" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="B49" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B49" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C49" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: WebSocket disconnect on suspension/ban</t>
-        </is>
-      </c>
-      <c r="D49" s="11" t="inlineStr">
-        <is>
-          <t>Deferred - only HTTP access is gated; an existing realtime-gateway connection isn't forcibly closed</t>
-        </is>
-      </c>
+          <t>Trust &amp; Safety: Suspension/Ban actually restrict access (new requireActive middleware, one entry point)</t>
+        </is>
+      </c>
+      <c r="D49" s="11" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="9" t="n">
@@ -2477,30 +2473,34 @@
       </c>
       <c r="C50" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: aggregating lower-severity signals over a time window</t>
+          <t>Trust &amp; Safety: WebSocket disconnect on suspension/ban</t>
         </is>
       </c>
       <c r="D50" s="11" t="inlineStr">
         <is>
-          <t>Deferred - a real abuse-detection engine is out of this phase's scope; only single-critical-signal escalation is implemented</t>
+          <t>Deferred - only HTTP access is gated; an existing realtime-gateway connection isn't forcibly closed</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="9" t="n">
-        <v>22</v>
-      </c>
-      <c r="B51" s="10" t="inlineStr">
-        <is>
-          <t>Done</t>
+        <v>21</v>
+      </c>
+      <c r="B51" s="13" t="inlineStr">
+        <is>
+          <t>Pending</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>Billing: Payment model (provider-specific transaction record)</t>
-        </is>
-      </c>
-      <c r="D51" s="11" t="inlineStr"/>
+          <t>Trust &amp; Safety: aggregating lower-severity signals over a time window</t>
+        </is>
+      </c>
+      <c r="D51" s="11" t="inlineStr">
+        <is>
+          <t>Deferred - a real abuse-detection engine is out of this phase's scope; only single-critical-signal escalation is implemented</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="9" t="n">
@@ -2513,7 +2513,7 @@
       </c>
       <c r="C52" s="11" t="inlineStr">
         <is>
-          <t>Billing: Entitlement model (platform-facing truth, kept separate from Payment)</t>
+          <t>Billing: Payment model (provider-specific transaction record)</t>
         </is>
       </c>
       <c r="D52" s="11" t="inlineStr"/>
@@ -2529,7 +2529,7 @@
       </c>
       <c r="C53" s="11" t="inlineStr">
         <is>
-          <t>Billing: provider abstraction (PaymentProvider interface + registry, implemented first)</t>
+          <t>Billing: Entitlement model (platform-facing truth, kept separate from Payment)</t>
         </is>
       </c>
       <c r="D53" s="11" t="inlineStr"/>
@@ -2545,32 +2545,28 @@
       </c>
       <c r="C54" s="11" t="inlineStr">
         <is>
-          <t>Billing: Stripe adapter</t>
-        </is>
-      </c>
-      <c r="D54" s="11" t="inlineStr">
-        <is>
-          <t>Real HMAC-SHA256 webhook signature verification, live-validated without a Stripe account via self-signed test payloads</t>
-        </is>
-      </c>
+          <t>Billing: provider abstraction (PaymentProvider interface + registry, implemented first)</t>
+        </is>
+      </c>
+      <c r="D54" s="11" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="B55" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B55" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t>Billing: Apple IAP adapter</t>
+          <t>Billing: Stripe adapter</t>
         </is>
       </c>
       <c r="D55" s="11" t="inlineStr">
         <is>
-          <t>Deferred - needs real App Store Server API credentials this environment doesn't have</t>
+          <t>Real HMAC-SHA256 webhook signature verification, live-validated without a Stripe account via self-signed test payloads</t>
         </is>
       </c>
     </row>
@@ -2585,18 +2581,18 @@
       </c>
       <c r="C56" s="11" t="inlineStr">
         <is>
-          <t>Billing: Google Play adapter</t>
+          <t>Billing: Apple IAP adapter</t>
         </is>
       </c>
       <c r="D56" s="11" t="inlineStr">
         <is>
-          <t>Deferred - needs real Play Developer API credentials this environment doesn't have</t>
+          <t>Deferred - needs real App Store Server API credentials this environment doesn't have</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B57" s="13" t="inlineStr">
         <is>
@@ -2605,23 +2601,27 @@
       </c>
       <c r="C57" s="11" t="inlineStr">
         <is>
-          <t>Analytics: generic analytics event envelope (event_name/user_id/anonymous_id/app_id/session_id/timestamp/properties/context)</t>
-        </is>
-      </c>
-      <c r="D57" s="11" t="inlineStr"/>
+          <t>Billing: Google Play adapter</t>
+        </is>
+      </c>
+      <c r="D57" s="11" t="inlineStr">
+        <is>
+          <t>Deferred - needs real Play Developer API credentials this environment doesn't have</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="9" t="n">
         <v>23</v>
       </c>
-      <c r="B58" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B58" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C58" s="11" t="inlineStr">
         <is>
-          <t>Analytics: keep operational DBs out of the analytics path</t>
+          <t>Analytics: generic event envelope (event_name/user_id/anonymous_id/app_id/session_id/timestamp/properties/context)</t>
         </is>
       </c>
       <c r="D58" s="11" t="inlineStr"/>
@@ -2630,37 +2630,37 @@
       <c r="A59" s="9" t="n">
         <v>23</v>
       </c>
-      <c r="B59" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B59" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>Analytics: pipeline foundation for ClickHouse/warehouse/data lake</t>
+          <t>Analytics: keep operational DBs out of the analytics path (analytics_events is a landing buffer, never queried for analytics)</t>
         </is>
       </c>
       <c r="D59" s="11" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="9" t="n">
-        <v>24</v>
-      </c>
-      <c r="B60" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+        <v>23</v>
+      </c>
+      <c r="B60" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C60" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: provider-neutral interface (OpenAI/Anthropic/Google/local/Ollama/vLLM)</t>
+          <t>Analytics: pipeline foundation for ClickHouse/warehouse/data lake (worker batches NDJSON into MinIO/S3)</t>
         </is>
       </c>
       <c r="D60" s="11" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B61" s="13" t="inlineStr">
         <is>
@@ -2669,10 +2669,14 @@
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: model routing</t>
-        </is>
-      </c>
-      <c r="D61" s="11" t="inlineStr"/>
+          <t>Analytics: an actual ClickHouse/warehouse/data-lake query layer</t>
+        </is>
+      </c>
+      <c r="D61" s="11" t="inlineStr">
+        <is>
+          <t>Out of scope - this phase builds the landing pipeline only; no real destination system exists in this environment to integrate against honestly</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="9" t="n">
@@ -2685,7 +2689,7 @@
       </c>
       <c r="C62" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: quotas</t>
+          <t>AI Gateway: provider-neutral interface (OpenAI/Anthropic/Google/local/Ollama/vLLM)</t>
         </is>
       </c>
       <c r="D62" s="11" t="inlineStr"/>
@@ -2701,7 +2705,7 @@
       </c>
       <c r="C63" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: token usage tracking</t>
+          <t>AI Gateway: model routing</t>
         </is>
       </c>
       <c r="D63" s="11" t="inlineStr"/>
@@ -2717,7 +2721,7 @@
       </c>
       <c r="C64" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: cost tracking</t>
+          <t>AI Gateway: quotas</t>
         </is>
       </c>
       <c r="D64" s="11" t="inlineStr"/>
@@ -2733,7 +2737,7 @@
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: audit integration</t>
+          <t>AI Gateway: token usage tracking</t>
         </is>
       </c>
       <c r="D65" s="11" t="inlineStr"/>
@@ -2749,7 +2753,7 @@
       </c>
       <c r="C66" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: prompt/version metadata</t>
+          <t>AI Gateway: cost tracking</t>
         </is>
       </c>
       <c r="D66" s="11" t="inlineStr"/>
@@ -2765,7 +2769,7 @@
       </c>
       <c r="C67" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: timeouts</t>
+          <t>AI Gateway: audit integration</t>
         </is>
       </c>
       <c r="D67" s="11" t="inlineStr"/>
@@ -2781,14 +2785,14 @@
       </c>
       <c r="C68" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: fallback</t>
+          <t>AI Gateway: prompt/version metadata</t>
         </is>
       </c>
       <c r="D68" s="11" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B69" s="13" t="inlineStr">
         <is>
@@ -2797,14 +2801,14 @@
       </c>
       <c r="C69" s="11" t="inlineStr">
         <is>
-          <t>Admin Portal: control-plane UI in apps/admin</t>
+          <t>AI Gateway: timeouts</t>
         </is>
       </c>
       <c r="D69" s="11" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B70" s="13" t="inlineStr">
         <is>
@@ -2813,7 +2817,7 @@
       </c>
       <c r="C70" s="11" t="inlineStr">
         <is>
-          <t>Admin Portal: visibility: Applications</t>
+          <t>AI Gateway: fallback</t>
         </is>
       </c>
       <c r="D70" s="11" t="inlineStr"/>
@@ -2829,7 +2833,7 @@
       </c>
       <c r="C71" s="11" t="inlineStr">
         <is>
-          <t>Admin Portal: visibility: Users/Sessions/Devices</t>
+          <t>Admin Portal: control-plane UI in apps/admin</t>
         </is>
       </c>
       <c r="D71" s="11" t="inlineStr"/>
@@ -2845,7 +2849,7 @@
       </c>
       <c r="C72" s="11" t="inlineStr">
         <is>
-          <t>Admin Portal: visibility: Roles/Permissions</t>
+          <t>Admin Portal: visibility: Applications</t>
         </is>
       </c>
       <c r="D72" s="11" t="inlineStr"/>
@@ -2861,7 +2865,7 @@
       </c>
       <c r="C73" s="11" t="inlineStr">
         <is>
-          <t>Admin Portal: visibility: Tenants/Relationships</t>
+          <t>Admin Portal: visibility: Users/Sessions/Devices</t>
         </is>
       </c>
       <c r="D73" s="11" t="inlineStr"/>
@@ -2877,7 +2881,7 @@
       </c>
       <c r="C74" s="11" t="inlineStr">
         <is>
-          <t>Admin Portal: visibility: Messages/Notifications</t>
+          <t>Admin Portal: visibility: Roles/Permissions</t>
         </is>
       </c>
       <c r="D74" s="11" t="inlineStr"/>
@@ -2893,7 +2897,7 @@
       </c>
       <c r="C75" s="11" t="inlineStr">
         <is>
-          <t>Admin Portal: visibility: Files/Jobs</t>
+          <t>Admin Portal: visibility: Tenants/Relationships</t>
         </is>
       </c>
       <c r="D75" s="11" t="inlineStr"/>
@@ -2909,7 +2913,7 @@
       </c>
       <c r="C76" s="11" t="inlineStr">
         <is>
-          <t>Admin Portal: visibility: Feature flags/Configuration</t>
+          <t>Admin Portal: visibility: Messages/Notifications</t>
         </is>
       </c>
       <c r="D76" s="11" t="inlineStr"/>
@@ -2925,7 +2929,7 @@
       </c>
       <c r="C77" s="11" t="inlineStr">
         <is>
-          <t>Admin Portal: visibility: Moderation/Audit</t>
+          <t>Admin Portal: visibility: Files/Jobs</t>
         </is>
       </c>
       <c r="D77" s="11" t="inlineStr"/>
@@ -2941,7 +2945,7 @@
       </c>
       <c r="C78" s="11" t="inlineStr">
         <is>
-          <t>Admin Portal: visibility: System health/Deployments</t>
+          <t>Admin Portal: visibility: Feature flags/Configuration</t>
         </is>
       </c>
       <c r="D78" s="11" t="inlineStr"/>
@@ -2957,14 +2961,14 @@
       </c>
       <c r="C79" s="11" t="inlineStr">
         <is>
-          <t>Admin Portal: must go through service APIs, never direct DB queries</t>
+          <t>Admin Portal: visibility: Moderation/Audit</t>
         </is>
       </c>
       <c r="D79" s="11" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B80" s="13" t="inlineStr">
         <is>
@@ -2973,14 +2977,14 @@
       </c>
       <c r="C80" s="11" t="inlineStr">
         <is>
-          <t>Backstage: integrate Backstage as developer portal</t>
+          <t>Admin Portal: visibility: System health/Deployments</t>
         </is>
       </c>
       <c r="D80" s="11" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B81" s="13" t="inlineStr">
         <is>
@@ -2989,7 +2993,7 @@
       </c>
       <c r="C81" s="11" t="inlineStr">
         <is>
-          <t>Backstage: per-module metadata: name/description/owner/lifecycle</t>
+          <t>Admin Portal: must go through service APIs, never direct DB queries</t>
         </is>
       </c>
       <c r="D81" s="11" t="inlineStr"/>
@@ -3005,7 +3009,7 @@
       </c>
       <c r="C82" s="11" t="inlineStr">
         <is>
-          <t>Backstage: per-module metadata: repository/documentation/dependencies</t>
+          <t>Backstage: integrate Backstage as developer portal</t>
         </is>
       </c>
       <c r="D82" s="11" t="inlineStr"/>
@@ -3021,14 +3025,14 @@
       </c>
       <c r="C83" s="11" t="inlineStr">
         <is>
-          <t>Backstage: per-module metadata: APIs/events/DB ownership/dashboards/runbooks</t>
+          <t>Backstage: per-module metadata: name/description/owner/lifecycle</t>
         </is>
       </c>
       <c r="D83" s="11" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B84" s="13" t="inlineStr">
         <is>
@@ -3037,14 +3041,14 @@
       </c>
       <c r="C84" s="11" t="inlineStr">
         <is>
-          <t>SDKs: Flutter SDK</t>
+          <t>Backstage: per-module metadata: repository/documentation/dependencies</t>
         </is>
       </c>
       <c r="D84" s="11" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B85" s="13" t="inlineStr">
         <is>
@@ -3053,7 +3057,7 @@
       </c>
       <c r="C85" s="11" t="inlineStr">
         <is>
-          <t>SDKs: TypeScript SDK</t>
+          <t>Backstage: per-module metadata: APIs/events/DB ownership/dashboards/runbooks</t>
         </is>
       </c>
       <c r="D85" s="11" t="inlineStr"/>
@@ -3069,7 +3073,7 @@
       </c>
       <c r="C86" s="11" t="inlineStr">
         <is>
-          <t>SDKs: Go SDK</t>
+          <t>SDKs: Flutter SDK</t>
         </is>
       </c>
       <c r="D86" s="11" t="inlineStr"/>
@@ -3085,7 +3089,7 @@
       </c>
       <c r="C87" s="11" t="inlineStr">
         <is>
-          <t>SDKs: auth + token refresh in each SDK</t>
+          <t>SDKs: TypeScript SDK</t>
         </is>
       </c>
       <c r="D87" s="11" t="inlineStr"/>
@@ -3101,7 +3105,7 @@
       </c>
       <c r="C88" s="11" t="inlineStr">
         <is>
-          <t>SDKs: pagination + safe retries</t>
+          <t>SDKs: Go SDK</t>
         </is>
       </c>
       <c r="D88" s="11" t="inlineStr"/>
@@ -3117,7 +3121,7 @@
       </c>
       <c r="C89" s="11" t="inlineStr">
         <is>
-          <t>SDKs: realtime connection helper</t>
+          <t>SDKs: auth + token refresh in each SDK</t>
         </is>
       </c>
       <c r="D89" s="11" t="inlineStr"/>
@@ -3133,7 +3137,7 @@
       </c>
       <c r="C90" s="11" t="inlineStr">
         <is>
-          <t>SDKs: correlation ID propagation</t>
+          <t>SDKs: pagination + safe retries</t>
         </is>
       </c>
       <c r="D90" s="11" t="inlineStr"/>
@@ -3149,14 +3153,14 @@
       </c>
       <c r="C91" s="11" t="inlineStr">
         <is>
-          <t>SDKs: device registration helper</t>
+          <t>SDKs: realtime connection helper</t>
         </is>
       </c>
       <c r="D91" s="11" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B92" s="13" t="inlineStr">
         <is>
@@ -3165,14 +3169,14 @@
       </c>
       <c r="C92" s="11" t="inlineStr">
         <is>
-          <t>Observability Completion: structured logs everywhere</t>
+          <t>SDKs: correlation ID propagation</t>
         </is>
       </c>
       <c r="D92" s="11" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B93" s="13" t="inlineStr">
         <is>
@@ -3181,7 +3185,7 @@
       </c>
       <c r="C93" s="11" t="inlineStr">
         <is>
-          <t>Observability Completion: metrics everywhere</t>
+          <t>SDKs: device registration helper</t>
         </is>
       </c>
       <c r="D93" s="11" t="inlineStr"/>
@@ -3197,7 +3201,7 @@
       </c>
       <c r="C94" s="11" t="inlineStr">
         <is>
-          <t>Observability Completion: distributed traces everywhere</t>
+          <t>Observability Completion: structured logs everywhere</t>
         </is>
       </c>
       <c r="D94" s="11" t="inlineStr"/>
@@ -3213,7 +3217,7 @@
       </c>
       <c r="C95" s="11" t="inlineStr">
         <is>
-          <t>Observability Completion: health checks everywhere</t>
+          <t>Observability Completion: metrics everywhere</t>
         </is>
       </c>
       <c r="D95" s="11" t="inlineStr"/>
@@ -3229,7 +3233,7 @@
       </c>
       <c r="C96" s="11" t="inlineStr">
         <is>
-          <t>Observability Completion: dashboard: API latency</t>
+          <t>Observability Completion: distributed traces everywhere</t>
         </is>
       </c>
       <c r="D96" s="11" t="inlineStr"/>
@@ -3245,7 +3249,7 @@
       </c>
       <c r="C97" s="11" t="inlineStr">
         <is>
-          <t>Observability Completion: dashboard: error rate</t>
+          <t>Observability Completion: health checks everywhere</t>
         </is>
       </c>
       <c r="D97" s="11" t="inlineStr"/>
@@ -3261,7 +3265,7 @@
       </c>
       <c r="C98" s="11" t="inlineStr">
         <is>
-          <t>Observability Completion: dashboard: requests/sec</t>
+          <t>Observability Completion: dashboard: API latency</t>
         </is>
       </c>
       <c r="D98" s="11" t="inlineStr"/>
@@ -3277,7 +3281,7 @@
       </c>
       <c r="C99" s="11" t="inlineStr">
         <is>
-          <t>Observability Completion: dashboard: DB connections</t>
+          <t>Observability Completion: dashboard: error rate</t>
         </is>
       </c>
       <c r="D99" s="11" t="inlineStr"/>
@@ -3293,7 +3297,7 @@
       </c>
       <c r="C100" s="11" t="inlineStr">
         <is>
-          <t>Observability Completion: dashboard: Kafka lag</t>
+          <t>Observability Completion: dashboard: requests/sec</t>
         </is>
       </c>
       <c r="D100" s="11" t="inlineStr"/>
@@ -3309,7 +3313,7 @@
       </c>
       <c r="C101" s="11" t="inlineStr">
         <is>
-          <t>Observability Completion: dashboard: WebSocket connections</t>
+          <t>Observability Completion: dashboard: DB connections</t>
         </is>
       </c>
       <c r="D101" s="11" t="inlineStr"/>
@@ -3325,7 +3329,7 @@
       </c>
       <c r="C102" s="11" t="inlineStr">
         <is>
-          <t>Observability Completion: dashboard: Redis latency</t>
+          <t>Observability Completion: dashboard: Kafka lag</t>
         </is>
       </c>
       <c r="D102" s="11" t="inlineStr"/>
@@ -3341,7 +3345,7 @@
       </c>
       <c r="C103" s="11" t="inlineStr">
         <is>
-          <t>Observability Completion: dashboard: notification failures</t>
+          <t>Observability Completion: dashboard: WebSocket connections</t>
         </is>
       </c>
       <c r="D103" s="11" t="inlineStr"/>
@@ -3357,7 +3361,7 @@
       </c>
       <c r="C104" s="11" t="inlineStr">
         <is>
-          <t>Observability Completion: dashboard: background job failures</t>
+          <t>Observability Completion: dashboard: Redis latency</t>
         </is>
       </c>
       <c r="D104" s="11" t="inlineStr"/>
@@ -3373,14 +3377,14 @@
       </c>
       <c r="C105" s="11" t="inlineStr">
         <is>
-          <t>Observability Completion: alerting rules</t>
+          <t>Observability Completion: dashboard: notification failures</t>
         </is>
       </c>
       <c r="D105" s="11" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B106" s="13" t="inlineStr">
         <is>
@@ -3389,14 +3393,14 @@
       </c>
       <c r="C106" s="11" t="inlineStr">
         <is>
-          <t>Platform Control Plane: one view: applications/services/versions</t>
+          <t>Observability Completion: dashboard: background job failures</t>
         </is>
       </c>
       <c r="D106" s="11" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B107" s="13" t="inlineStr">
         <is>
@@ -3405,7 +3409,7 @@
       </c>
       <c r="C107" s="11" t="inlineStr">
         <is>
-          <t>Platform Control Plane: one view: environments/dependencies/deployments</t>
+          <t>Observability Completion: alerting rules</t>
         </is>
       </c>
       <c r="D107" s="11" t="inlineStr"/>
@@ -3421,7 +3425,7 @@
       </c>
       <c r="C108" s="11" t="inlineStr">
         <is>
-          <t>Platform Control Plane: one view: DB ownership/events/API contracts</t>
+          <t>Platform Control Plane: one view: applications/services/versions</t>
         </is>
       </c>
       <c r="D108" s="11" t="inlineStr"/>
@@ -3437,14 +3441,14 @@
       </c>
       <c r="C109" s="11" t="inlineStr">
         <is>
-          <t>Platform Control Plane: one view: health/alerts/recent changes</t>
+          <t>Platform Control Plane: one view: environments/dependencies/deployments</t>
         </is>
       </c>
       <c r="D109" s="11" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="9" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B110" s="13" t="inlineStr">
         <is>
@@ -3453,14 +3457,14 @@
       </c>
       <c r="C110" s="11" t="inlineStr">
         <is>
-          <t>AI Development Context: every module: README</t>
+          <t>Platform Control Plane: one view: DB ownership/events/API contracts</t>
         </is>
       </c>
       <c r="D110" s="11" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="9" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B111" s="13" t="inlineStr">
         <is>
@@ -3469,7 +3473,7 @@
       </c>
       <c r="C111" s="11" t="inlineStr">
         <is>
-          <t>AI Development Context: every module: ownership metadata</t>
+          <t>Platform Control Plane: one view: health/alerts/recent changes</t>
         </is>
       </c>
       <c r="D111" s="11" t="inlineStr"/>
@@ -3485,7 +3489,7 @@
       </c>
       <c r="C112" s="11" t="inlineStr">
         <is>
-          <t>AI Development Context: every module: dependencies</t>
+          <t>AI Development Context: every module: README</t>
         </is>
       </c>
       <c r="D112" s="11" t="inlineStr"/>
@@ -3501,7 +3505,7 @@
       </c>
       <c r="C113" s="11" t="inlineStr">
         <is>
-          <t>AI Development Context: every module: API contract</t>
+          <t>AI Development Context: every module: ownership metadata</t>
         </is>
       </c>
       <c r="D113" s="11" t="inlineStr"/>
@@ -3517,7 +3521,7 @@
       </c>
       <c r="C114" s="11" t="inlineStr">
         <is>
-          <t>AI Development Context: every module: event contracts</t>
+          <t>AI Development Context: every module: dependencies</t>
         </is>
       </c>
       <c r="D114" s="11" t="inlineStr"/>
@@ -3533,10 +3537,42 @@
       </c>
       <c r="C115" s="11" t="inlineStr">
         <is>
+          <t>AI Development Context: every module: API contract</t>
+        </is>
+      </c>
+      <c r="D115" s="11" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="B116" s="13" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="C116" s="11" t="inlineStr">
+        <is>
+          <t>AI Development Context: every module: event contracts</t>
+        </is>
+      </c>
+      <c r="D116" s="11" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="B117" s="13" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="C117" s="11" t="inlineStr">
+        <is>
           <t>AI Development Context: every module: DB ownership</t>
         </is>
       </c>
-      <c r="D115" s="11" t="inlineStr"/>
+      <c r="D117" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3552,7 +3588,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4424,6 +4460,70 @@
       <c r="F27" s="11" t="inlineStr">
         <is>
           <t>Phase 22</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="32" customHeight="1">
+      <c r="A28" s="11" t="inlineStr">
+        <is>
+          <t>analytics</t>
+        </is>
+      </c>
+      <c r="B28" s="11" t="inlineStr">
+        <is>
+          <t>core-api</t>
+        </is>
+      </c>
+      <c r="C28" s="11" t="inlineStr">
+        <is>
+          <t>Generic event envelope ingestion; analytics_events is a landing buffer, never a query surface</t>
+        </is>
+      </c>
+      <c r="D28" s="11" t="inlineStr">
+        <is>
+          <t>analytics_events</t>
+        </is>
+      </c>
+      <c r="E28" s="11" t="inlineStr">
+        <is>
+          <t>Open (IP-rate-limited) to track; platform.admin-only debug listing</t>
+        </is>
+      </c>
+      <c r="F28" s="11" t="inlineStr">
+        <is>
+          <t>Phase 23</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="32" customHeight="1">
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t>worker: analyticspipeline</t>
+        </is>
+      </c>
+      <c r="B29" s="11" t="inlineStr">
+        <is>
+          <t>worker</t>
+        </is>
+      </c>
+      <c r="C29" s="11" t="inlineStr">
+        <is>
+          <t>Claims unflushed events, batches as NDJSON, writes to MinIO/S3 - the ClickHouse/warehouse/data-lake landing pattern</t>
+        </is>
+      </c>
+      <c r="D29" s="11" t="inlineStr">
+        <is>
+          <t>reads/writes analytics_events; writes MinIO/S3</t>
+        </is>
+      </c>
+      <c r="E29" s="11" t="inlineStr">
+        <is>
+          <t>n/a (background)</t>
+        </is>
+      </c>
+      <c r="F29" s="11" t="inlineStr">
+        <is>
+          <t>Phase 23</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E138"/>
+  <dimension ref="A1:E140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -7862,6 +7962,60 @@
       <c r="E138" s="11" t="inlineStr">
         <is>
           <t>the one route on this platform with no requireUser/requireActive</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="11" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="B139" s="11" t="inlineStr">
+        <is>
+          <t>/v1/analytics/events</t>
+        </is>
+      </c>
+      <c r="C139" s="11" t="inlineStr">
+        <is>
+          <t>analytics</t>
+        </is>
+      </c>
+      <c r="D139" s="11" t="inlineStr">
+        <is>
+          <t>Open (IP-rate-limited, no Bearer token)</t>
+        </is>
+      </c>
+      <c r="E139" s="11" t="inlineStr">
+        <is>
+          <t>the platform's one deliberately unauthenticated write endpoint</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="11" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="B140" s="11" t="inlineStr">
+        <is>
+          <t>/v1/analytics/events</t>
+        </is>
+      </c>
+      <c r="C140" s="11" t="inlineStr">
+        <is>
+          <t>analytics</t>
+        </is>
+      </c>
+      <c r="D140" s="11" t="inlineStr">
+        <is>
+          <t>platform.admin</t>
+        </is>
+      </c>
+      <c r="E140" s="11" t="inlineStr">
+        <is>
+          <t>operational debug view only, not for analytical queries</t>
         </is>
       </c>
     </row>

--- a/docs/control/data.xlsx
+++ b/docs/control/data.xlsx
@@ -239,8 +239,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="TodoChecklist" displayName="TodoChecklist" ref="A1:D117" headerRowCount="1">
-  <autoFilter ref="A1:D117"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="TodoChecklist" displayName="TodoChecklist" ref="A1:D123" headerRowCount="1">
+  <autoFilter ref="A1:D123"/>
   <tableColumns count="4">
     <tableColumn id="1" name="Phase"/>
     <tableColumn id="2" name="Status"/>
@@ -252,8 +252,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Modules" displayName="Modules" ref="A1:F29" headerRowCount="1">
-  <autoFilter ref="A1:F29"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Modules" displayName="Modules" ref="A1:F31" headerRowCount="1">
+  <autoFilter ref="A1:F31"/>
   <tableColumns count="6">
     <tableColumn id="1" name="Module"/>
     <tableColumn id="2" name="Service"/>
@@ -267,8 +267,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="APIEndpoints" displayName="APIEndpoints" ref="A1:E140" headerRowCount="1">
-  <autoFilter ref="A1:E140"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="APIEndpoints" displayName="APIEndpoints" ref="A1:E143" headerRowCount="1">
+  <autoFilter ref="A1:E143"/>
   <tableColumns count="5">
     <tableColumn id="1" name="Method"/>
     <tableColumn id="2" name="Path"/>
@@ -294,8 +294,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="InfraCredentials" displayName="InfraCredentials" ref="A1:E13" headerRowCount="1">
-  <autoFilter ref="A1:E13"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="InfraCredentials" displayName="InfraCredentials" ref="A1:E14" headerRowCount="1">
+  <autoFilter ref="A1:E14"/>
   <tableColumns count="5">
     <tableColumn id="1" name="Service"/>
     <tableColumn id="2" name="Type"/>
@@ -633,12 +633,12 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>23 / 30</t>
+          <t>24 / 30</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>80%</t>
         </is>
       </c>
     </row>
@@ -684,7 +684,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>142</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>data/migrations/0001-0021</t>
+          <t>data/migrations/0001-0022</t>
         </is>
       </c>
     </row>
@@ -735,12 +735,12 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Postgres, Valkey, Keycloak, OpenFGA, MinIO, OpenSearch, Temporal, Kafka/Redpanda, OTel</t>
+          <t>Postgres, Valkey, Keycloak, OpenFGA, MinIO, OpenSearch, Temporal, Kafka/Redpanda, Ollama, OTel</t>
         </is>
       </c>
     </row>
@@ -752,7 +752,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
@@ -1446,9 +1446,9 @@
       <c r="A25" s="9" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="12" t="inlineStr">
-        <is>
-          <t>Next up</t>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
@@ -1458,12 +1458,12 @@
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>Provider-neutral interface (OpenAI/Anthropic/Google/local models/Ollama/vLLM) with model routing, quotas, token/cost tracking, audit, timeouts, fallback. Products never call AI vendors directly.</t>
+          <t>Provider-neutral interface; real local inference via a new Ollama container (auto-pulled model, no vendor API key) - the one live-testable provider. Model routing, quotas (ratelimit reused again), real token/cost tracking, a genuine audit.Record per call, prompt/version metadata, timeouts, fallback. OpenAI/Anthropic/Google structurally supported, not implemented (no real credentials).</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>d7324b9</t>
         </is>
       </c>
     </row>
@@ -1471,9 +1471,9 @@
       <c r="A26" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B26" s="12" t="inlineStr">
+        <is>
+          <t>Next up</t>
         </is>
       </c>
       <c r="C26" s="11" t="inlineStr">
@@ -1631,7 +1631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D117"/>
+  <dimension ref="A1:D123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2032,7 +2032,7 @@
     </row>
     <row r="25">
       <c r="A25" s="9" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
@@ -2041,14 +2041,14 @@
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>Repo health baseline (make doctor / validate-all / go test / go build) run and passed</t>
+          <t>Phase 24: AI Gateway implemented, unit-tested, live-validated, documented, committed</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
@@ -2057,18 +2057,14 @@
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>Environment / ApplicationVersion / ApplicationConfiguration</t>
-        </is>
-      </c>
-      <c r="D26" s="11" t="inlineStr">
-        <is>
-          <t>Deferred - no consumer needs them yet, documented as intentional in applications/README.md</t>
-        </is>
-      </c>
+          <t>Repo health baseline (make doctor / validate-all / go test / go build) run and passed</t>
+        </is>
+      </c>
+      <c r="D26" s="11" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
@@ -2077,32 +2073,32 @@
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>Separate Session table</t>
+          <t>Environment / ApplicationVersion / ApplicationConfiguration</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>Deferred - Device.SessionStatus covers today's single-session-per-device need, documented in devices/README.md</t>
+          <t>Deferred - no consumer needs them yet, documented as intentional in applications/README.md</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="B28" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+        <v>5</v>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>UserPreferences (named in Phase 4, no fields ever specified)</t>
+          <t>Separate Session table</t>
         </is>
       </c>
       <c r="D28" s="11" t="inlineStr">
         <is>
-          <t>Deferred to Phase 12+; notification preferences shipped, a generic preferences bag did not</t>
+          <t>Deferred - Device.SessionStatus covers today's single-session-per-device need, documented in devices/README.md</t>
         </is>
       </c>
     </row>
@@ -2117,12 +2113,12 @@
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>apps/mobile test/ directory (make flutter-test currently fails)</t>
+          <t>UserPreferences (named in Phase 4, no fields ever specified)</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>Known gap since Phase 9's audit, not yet picked up</t>
+          <t>Deferred to Phase 12+; notification preferences shipped, a generic preferences bag did not</t>
         </is>
       </c>
     </row>
@@ -2137,30 +2133,34 @@
       </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t>apps/admin next@15 / sharp transitive advisories</t>
+          <t>apps/mobile test/ directory (make flutter-test currently fails)</t>
         </is>
       </c>
       <c r="D30" s="11" t="inlineStr">
         <is>
-          <t>Fix is a Next.js major-version bump - separate, reviewable change</t>
+          <t>Known gap since Phase 9's audit, not yet picked up</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="9" t="n">
-        <v>20</v>
-      </c>
-      <c r="B31" s="10" t="inlineStr">
-        <is>
-          <t>Done</t>
+        <v>9</v>
+      </c>
+      <c r="B31" s="13" t="inlineStr">
+        <is>
+          <t>Pending</t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>Privacy: consent (append-only history)</t>
-        </is>
-      </c>
-      <c r="D31" s="11" t="inlineStr"/>
+          <t>apps/admin next@15 / sharp transitive advisories</t>
+        </is>
+      </c>
+      <c r="D31" s="11" t="inlineStr">
+        <is>
+          <t>Fix is a Next.js major-version bump - separate, reviewable change</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="9" t="n">
@@ -2173,7 +2173,7 @@
       </c>
       <c r="C32" s="11" t="inlineStr">
         <is>
-          <t>Privacy: user data export (ExportUserData registry - users/devices/files/audit)</t>
+          <t>Privacy: consent (append-only history)</t>
         </is>
       </c>
       <c r="D32" s="11" t="inlineStr"/>
@@ -2189,7 +2189,7 @@
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>Privacy: user deletion (DeleteUserData registry - users/devices/files; audit deliberately excluded)</t>
+          <t>Privacy: user data export (ExportUserData registry - users/devices/files/audit)</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr"/>
@@ -2205,7 +2205,7 @@
       </c>
       <c r="C34" s="11" t="inlineStr">
         <is>
-          <t>Privacy: retention policy (declared, not scheduled - same documented gap as Phase 13's PurgeExpired)</t>
+          <t>Privacy: user deletion (DeleteUserData registry - users/devices/files; audit deliberately excluded)</t>
         </is>
       </c>
       <c r="D34" s="11" t="inlineStr"/>
@@ -2221,7 +2221,7 @@
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>Privacy: privacy preferences</t>
+          <t>Privacy: retention policy (declared, not scheduled - same documented gap as Phase 13's PurgeExpired)</t>
         </is>
       </c>
       <c r="D35" s="11" t="inlineStr"/>
@@ -2237,7 +2237,7 @@
       </c>
       <c r="C36" s="11" t="inlineStr">
         <is>
-          <t>Privacy: coordinate deletion through workflows/events - core-api's own embedded Temporal worker</t>
+          <t>Privacy: privacy preferences</t>
         </is>
       </c>
       <c r="D36" s="11" t="inlineStr"/>
@@ -2246,21 +2246,17 @@
       <c r="A37" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="B37" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B37" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>Privacy: notifications module as an Export/Delete participant</t>
-        </is>
-      </c>
-      <c r="D37" s="11" t="inlineStr">
-        <is>
-          <t>Deliberately deferred to prove the registry makes this a 2-line addition later, not a framework change</t>
-        </is>
-      </c>
+          <t>Privacy: coordinate deletion through workflows/events - core-api's own embedded Temporal worker</t>
+        </is>
+      </c>
+      <c r="D37" s="11" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="9" t="n">
@@ -2273,32 +2269,32 @@
       </c>
       <c r="C38" s="11" t="inlineStr">
         <is>
-          <t>Privacy: relationships/groups/messaging as participants</t>
+          <t>Privacy: notifications module as an Export/Delete participant</t>
         </is>
       </c>
       <c r="D38" s="11" t="inlineStr">
         <is>
-          <t>Deferred - shared multi-user data needs a redaction strategy this phase's per-user-in-isolation registry doesn't fit</t>
+          <t>Deliberately deferred to prove the registry makes this a 2-line addition later, not a framework change</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="9" t="n">
-        <v>21</v>
-      </c>
-      <c r="B39" s="10" t="inlineStr">
-        <is>
-          <t>Done</t>
+        <v>20</v>
+      </c>
+      <c r="B39" s="13" t="inlineStr">
+        <is>
+          <t>Pending</t>
         </is>
       </c>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: Block</t>
+          <t>Privacy: relationships/groups/messaging as participants</t>
         </is>
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>Reused Phase 8's relationships (Status='blocked'), deliberately not duplicated</t>
+          <t>Deferred - shared multi-user data needs a redaction strategy this phase's per-user-in-isolation registry doesn't fit</t>
         </is>
       </c>
     </row>
@@ -2313,10 +2309,14 @@
       </c>
       <c r="C40" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: Mute</t>
-        </is>
-      </c>
-      <c r="D40" s="11" t="inlineStr"/>
+          <t>Trust &amp; Safety: Block</t>
+        </is>
+      </c>
+      <c r="D40" s="11" t="inlineStr">
+        <is>
+          <t>Reused Phase 8's relationships (Status='blocked'), deliberately not duplicated</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: Report -&gt; ModerationCase (deduplicated via partial unique index)</t>
+          <t>Trust &amp; Safety: Mute</t>
         </is>
       </c>
       <c r="D41" s="11" t="inlineStr"/>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="C42" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: Suspension</t>
+          <t>Trust &amp; Safety: Report -&gt; ModerationCase (deduplicated via partial unique index)</t>
         </is>
       </c>
       <c r="D42" s="11" t="inlineStr"/>
@@ -2361,7 +2361,7 @@
       </c>
       <c r="C43" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: Ban</t>
+          <t>Trust &amp; Safety: Suspension</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr"/>
@@ -2377,7 +2377,7 @@
       </c>
       <c r="C44" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: Appeal (approving lifts the target restriction)</t>
+          <t>Trust &amp; Safety: Ban</t>
         </is>
       </c>
       <c r="D44" s="11" t="inlineStr"/>
@@ -2393,7 +2393,7 @@
       </c>
       <c r="C45" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: rate limiting (new platformkit/ratelimit, Valkey-backed)</t>
+          <t>Trust &amp; Safety: Appeal (approving lifts the target restriction)</t>
         </is>
       </c>
       <c r="D45" s="11" t="inlineStr"/>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="C46" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: spam protection (5 reports/hour per reporter)</t>
+          <t>Trust &amp; Safety: rate limiting (new platformkit/ratelimit, Valkey-backed)</t>
         </is>
       </c>
       <c r="D46" s="11" t="inlineStr"/>
@@ -2425,7 +2425,7 @@
       </c>
       <c r="C47" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: abuse signals (critical severity auto-opens a case)</t>
+          <t>Trust &amp; Safety: spam protection (5 reports/hour per reporter)</t>
         </is>
       </c>
       <c r="D47" s="11" t="inlineStr"/>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="C48" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: pluggable product-specific report reasons (free-form Reason field)</t>
+          <t>Trust &amp; Safety: abuse signals (critical severity auto-opens a case)</t>
         </is>
       </c>
       <c r="D48" s="11" t="inlineStr"/>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="C49" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: Suspension/Ban actually restrict access (new requireActive middleware, one entry point)</t>
+          <t>Trust &amp; Safety: pluggable product-specific report reasons (free-form Reason field)</t>
         </is>
       </c>
       <c r="D49" s="11" t="inlineStr"/>
@@ -2466,21 +2466,17 @@
       <c r="A50" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="B50" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B50" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C50" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: WebSocket disconnect on suspension/ban</t>
-        </is>
-      </c>
-      <c r="D50" s="11" t="inlineStr">
-        <is>
-          <t>Deferred - only HTTP access is gated; an existing realtime-gateway connection isn't forcibly closed</t>
-        </is>
-      </c>
+          <t>Trust &amp; Safety: Suspension/Ban actually restrict access (new requireActive middleware, one entry point)</t>
+        </is>
+      </c>
+      <c r="D50" s="11" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="9" t="n">
@@ -2493,30 +2489,34 @@
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: aggregating lower-severity signals over a time window</t>
+          <t>Trust &amp; Safety: WebSocket disconnect on suspension/ban</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>Deferred - a real abuse-detection engine is out of this phase's scope; only single-critical-signal escalation is implemented</t>
+          <t>Deferred - only HTTP access is gated; an existing realtime-gateway connection isn't forcibly closed</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="9" t="n">
-        <v>22</v>
-      </c>
-      <c r="B52" s="10" t="inlineStr">
-        <is>
-          <t>Done</t>
+        <v>21</v>
+      </c>
+      <c r="B52" s="13" t="inlineStr">
+        <is>
+          <t>Pending</t>
         </is>
       </c>
       <c r="C52" s="11" t="inlineStr">
         <is>
-          <t>Billing: Payment model (provider-specific transaction record)</t>
-        </is>
-      </c>
-      <c r="D52" s="11" t="inlineStr"/>
+          <t>Trust &amp; Safety: aggregating lower-severity signals over a time window</t>
+        </is>
+      </c>
+      <c r="D52" s="11" t="inlineStr">
+        <is>
+          <t>Deferred - a real abuse-detection engine is out of this phase's scope; only single-critical-signal escalation is implemented</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="9" t="n">
@@ -2529,7 +2529,7 @@
       </c>
       <c r="C53" s="11" t="inlineStr">
         <is>
-          <t>Billing: Entitlement model (platform-facing truth, kept separate from Payment)</t>
+          <t>Billing: Payment model (provider-specific transaction record)</t>
         </is>
       </c>
       <c r="D53" s="11" t="inlineStr"/>
@@ -2545,7 +2545,7 @@
       </c>
       <c r="C54" s="11" t="inlineStr">
         <is>
-          <t>Billing: provider abstraction (PaymentProvider interface + registry, implemented first)</t>
+          <t>Billing: Entitlement model (platform-facing truth, kept separate from Payment)</t>
         </is>
       </c>
       <c r="D54" s="11" t="inlineStr"/>
@@ -2561,32 +2561,28 @@
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t>Billing: Stripe adapter</t>
-        </is>
-      </c>
-      <c r="D55" s="11" t="inlineStr">
-        <is>
-          <t>Real HMAC-SHA256 webhook signature verification, live-validated without a Stripe account via self-signed test payloads</t>
-        </is>
-      </c>
+          <t>Billing: provider abstraction (PaymentProvider interface + registry, implemented first)</t>
+        </is>
+      </c>
+      <c r="D55" s="11" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="B56" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B56" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C56" s="11" t="inlineStr">
         <is>
-          <t>Billing: Apple IAP adapter</t>
+          <t>Billing: Stripe adapter</t>
         </is>
       </c>
       <c r="D56" s="11" t="inlineStr">
         <is>
-          <t>Deferred - needs real App Store Server API credentials this environment doesn't have</t>
+          <t>Real HMAC-SHA256 webhook signature verification, live-validated without a Stripe account via self-signed test payloads</t>
         </is>
       </c>
     </row>
@@ -2601,30 +2597,34 @@
       </c>
       <c r="C57" s="11" t="inlineStr">
         <is>
-          <t>Billing: Google Play adapter</t>
+          <t>Billing: Apple IAP adapter</t>
         </is>
       </c>
       <c r="D57" s="11" t="inlineStr">
         <is>
-          <t>Deferred - needs real Play Developer API credentials this environment doesn't have</t>
+          <t>Deferred - needs real App Store Server API credentials this environment doesn't have</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="9" t="n">
-        <v>23</v>
-      </c>
-      <c r="B58" s="10" t="inlineStr">
-        <is>
-          <t>Done</t>
+        <v>22</v>
+      </c>
+      <c r="B58" s="13" t="inlineStr">
+        <is>
+          <t>Pending</t>
         </is>
       </c>
       <c r="C58" s="11" t="inlineStr">
         <is>
-          <t>Analytics: generic event envelope (event_name/user_id/anonymous_id/app_id/session_id/timestamp/properties/context)</t>
-        </is>
-      </c>
-      <c r="D58" s="11" t="inlineStr"/>
+          <t>Billing: Google Play adapter</t>
+        </is>
+      </c>
+      <c r="D58" s="11" t="inlineStr">
+        <is>
+          <t>Deferred - needs real Play Developer API credentials this environment doesn't have</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="9" t="n">
@@ -2637,7 +2637,7 @@
       </c>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>Analytics: keep operational DBs out of the analytics path (analytics_events is a landing buffer, never queried for analytics)</t>
+          <t>Analytics: generic event envelope (event_name/user_id/anonymous_id/app_id/session_id/timestamp/properties/context)</t>
         </is>
       </c>
       <c r="D59" s="11" t="inlineStr"/>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="C60" s="11" t="inlineStr">
         <is>
-          <t>Analytics: pipeline foundation for ClickHouse/warehouse/data lake (worker batches NDJSON into MinIO/S3)</t>
+          <t>Analytics: keep operational DBs out of the analytics path (analytics_events is a landing buffer, never queried for analytics)</t>
         </is>
       </c>
       <c r="D60" s="11" t="inlineStr"/>
@@ -2662,25 +2662,21 @@
       <c r="A61" s="9" t="n">
         <v>23</v>
       </c>
-      <c r="B61" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B61" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>Analytics: an actual ClickHouse/warehouse/data-lake query layer</t>
-        </is>
-      </c>
-      <c r="D61" s="11" t="inlineStr">
-        <is>
-          <t>Out of scope - this phase builds the landing pipeline only; no real destination system exists in this environment to integrate against honestly</t>
-        </is>
-      </c>
+          <t>Analytics: pipeline foundation for ClickHouse/warehouse/data lake (worker batches NDJSON into MinIO/S3)</t>
+        </is>
+      </c>
+      <c r="D61" s="11" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B62" s="13" t="inlineStr">
         <is>
@@ -2689,23 +2685,27 @@
       </c>
       <c r="C62" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: provider-neutral interface (OpenAI/Anthropic/Google/local/Ollama/vLLM)</t>
-        </is>
-      </c>
-      <c r="D62" s="11" t="inlineStr"/>
+          <t>Analytics: an actual ClickHouse/warehouse/data-lake query layer</t>
+        </is>
+      </c>
+      <c r="D62" s="11" t="inlineStr">
+        <is>
+          <t>Out of scope - this phase builds the landing pipeline only; no real destination system exists in this environment to integrate against honestly</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="9" t="n">
         <v>24</v>
       </c>
-      <c r="B63" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B63" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C63" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: model routing</t>
+          <t>AI Gateway: provider-neutral interface (Provider: Name + Complete)</t>
         </is>
       </c>
       <c r="D63" s="11" t="inlineStr"/>
@@ -2714,17 +2714,21 @@
       <c r="A64" s="9" t="n">
         <v>24</v>
       </c>
-      <c r="B64" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B64" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C64" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: quotas</t>
-        </is>
-      </c>
-      <c r="D64" s="11" t="inlineStr"/>
+          <t>AI Gateway: local models / Ollama adapter</t>
+        </is>
+      </c>
+      <c r="D64" s="11" t="inlineStr">
+        <is>
+          <t>Real local inference via a new Ollama container, auto-pulled model, no vendor API key - the one live-testable provider</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="9" t="n">
@@ -2737,10 +2741,14 @@
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: token usage tracking</t>
-        </is>
-      </c>
-      <c r="D65" s="11" t="inlineStr"/>
+          <t>AI Gateway: OpenAI adapter</t>
+        </is>
+      </c>
+      <c r="D65" s="11" t="inlineStr">
+        <is>
+          <t>Deferred - no real API key in this environment to validate against honestly</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="9" t="n">
@@ -2753,10 +2761,14 @@
       </c>
       <c r="C66" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: cost tracking</t>
-        </is>
-      </c>
-      <c r="D66" s="11" t="inlineStr"/>
+          <t>AI Gateway: Anthropic adapter</t>
+        </is>
+      </c>
+      <c r="D66" s="11" t="inlineStr">
+        <is>
+          <t>Deferred - no real API key in this environment to validate against honestly</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="9" t="n">
@@ -2769,23 +2781,27 @@
       </c>
       <c r="C67" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: audit integration</t>
-        </is>
-      </c>
-      <c r="D67" s="11" t="inlineStr"/>
+          <t>AI Gateway: Google adapter</t>
+        </is>
+      </c>
+      <c r="D67" s="11" t="inlineStr">
+        <is>
+          <t>Deferred - no real API key in this environment to validate against honestly</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="9" t="n">
         <v>24</v>
       </c>
-      <c r="B68" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B68" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C68" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: prompt/version metadata</t>
+          <t>AI Gateway: model routing (product-facing ModelAlias, never a vendor model name)</t>
         </is>
       </c>
       <c r="D68" s="11" t="inlineStr"/>
@@ -2794,14 +2810,14 @@
       <c r="A69" s="9" t="n">
         <v>24</v>
       </c>
-      <c r="B69" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B69" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C69" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: timeouts</t>
+          <t>AI Gateway: quotas (ratelimit.Limiter reused a third time, 60/min/caller)</t>
         </is>
       </c>
       <c r="D69" s="11" t="inlineStr"/>
@@ -2810,101 +2826,101 @@
       <c r="A70" s="9" t="n">
         <v>24</v>
       </c>
-      <c r="B70" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B70" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C70" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: fallback</t>
+          <t>AI Gateway: token usage tracking</t>
         </is>
       </c>
       <c r="D70" s="11" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="9" t="n">
-        <v>25</v>
-      </c>
-      <c r="B71" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+        <v>24</v>
+      </c>
+      <c r="B71" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C71" s="11" t="inlineStr">
         <is>
-          <t>Admin Portal: control-plane UI in apps/admin</t>
+          <t>AI Gateway: cost tracking (real per-route price table; Ollama honestly priced at 0)</t>
         </is>
       </c>
       <c r="D71" s="11" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="9" t="n">
-        <v>25</v>
-      </c>
-      <c r="B72" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+        <v>24</v>
+      </c>
+      <c r="B72" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C72" s="11" t="inlineStr">
         <is>
-          <t>Admin Portal: visibility: Applications</t>
+          <t>AI Gateway: audit integration (new AIGatewayAuditRecorder, a genuine audit.Record per call)</t>
         </is>
       </c>
       <c r="D72" s="11" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="9" t="n">
-        <v>25</v>
-      </c>
-      <c r="B73" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+        <v>24</v>
+      </c>
+      <c r="B73" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C73" s="11" t="inlineStr">
         <is>
-          <t>Admin Portal: visibility: Users/Sessions/Devices</t>
+          <t>AI Gateway: prompt/version metadata (free-form PromptKey/PromptVersion)</t>
         </is>
       </c>
       <c r="D73" s="11" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="9" t="n">
-        <v>25</v>
-      </c>
-      <c r="B74" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+        <v>24</v>
+      </c>
+      <c r="B74" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C74" s="11" t="inlineStr">
         <is>
-          <t>Admin Portal: visibility: Roles/Permissions</t>
+          <t>AI Gateway: timeouts (context.WithTimeout per provider call)</t>
         </is>
       </c>
       <c r="D74" s="11" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="9" t="n">
-        <v>25</v>
-      </c>
-      <c r="B75" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+        <v>24</v>
+      </c>
+      <c r="B75" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C75" s="11" t="inlineStr">
         <is>
-          <t>Admin Portal: visibility: Tenants/Relationships</t>
+          <t>AI Gateway: fallback (ordered provider/model chain, first success wins)</t>
         </is>
       </c>
       <c r="D75" s="11" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B76" s="13" t="inlineStr">
         <is>
@@ -2913,10 +2929,14 @@
       </c>
       <c r="C76" s="11" t="inlineStr">
         <is>
-          <t>Admin Portal: visibility: Messages/Notifications</t>
-        </is>
-      </c>
-      <c r="D76" s="11" t="inlineStr"/>
+          <t>AI Gateway: live token-quantity quota (as opposed to today's call-count quota)</t>
+        </is>
+      </c>
+      <c r="D76" s="11" t="inlineStr">
+        <is>
+          <t>Deferred - Repository already has the data (Completion.TotalTokens); not wired as a live gate yet</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="9" t="n">
@@ -2929,7 +2949,7 @@
       </c>
       <c r="C77" s="11" t="inlineStr">
         <is>
-          <t>Admin Portal: visibility: Files/Jobs</t>
+          <t>Admin Portal: control-plane UI in apps/admin</t>
         </is>
       </c>
       <c r="D77" s="11" t="inlineStr"/>
@@ -2945,7 +2965,7 @@
       </c>
       <c r="C78" s="11" t="inlineStr">
         <is>
-          <t>Admin Portal: visibility: Feature flags/Configuration</t>
+          <t>Admin Portal: visibility: Applications</t>
         </is>
       </c>
       <c r="D78" s="11" t="inlineStr"/>
@@ -2961,7 +2981,7 @@
       </c>
       <c r="C79" s="11" t="inlineStr">
         <is>
-          <t>Admin Portal: visibility: Moderation/Audit</t>
+          <t>Admin Portal: visibility: Users/Sessions/Devices</t>
         </is>
       </c>
       <c r="D79" s="11" t="inlineStr"/>
@@ -2977,7 +2997,7 @@
       </c>
       <c r="C80" s="11" t="inlineStr">
         <is>
-          <t>Admin Portal: visibility: System health/Deployments</t>
+          <t>Admin Portal: visibility: Roles/Permissions</t>
         </is>
       </c>
       <c r="D80" s="11" t="inlineStr"/>
@@ -2993,14 +3013,14 @@
       </c>
       <c r="C81" s="11" t="inlineStr">
         <is>
-          <t>Admin Portal: must go through service APIs, never direct DB queries</t>
+          <t>Admin Portal: visibility: Tenants/Relationships</t>
         </is>
       </c>
       <c r="D81" s="11" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B82" s="13" t="inlineStr">
         <is>
@@ -3009,14 +3029,14 @@
       </c>
       <c r="C82" s="11" t="inlineStr">
         <is>
-          <t>Backstage: integrate Backstage as developer portal</t>
+          <t>Admin Portal: visibility: Messages/Notifications</t>
         </is>
       </c>
       <c r="D82" s="11" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B83" s="13" t="inlineStr">
         <is>
@@ -3025,14 +3045,14 @@
       </c>
       <c r="C83" s="11" t="inlineStr">
         <is>
-          <t>Backstage: per-module metadata: name/description/owner/lifecycle</t>
+          <t>Admin Portal: visibility: Files/Jobs</t>
         </is>
       </c>
       <c r="D83" s="11" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B84" s="13" t="inlineStr">
         <is>
@@ -3041,14 +3061,14 @@
       </c>
       <c r="C84" s="11" t="inlineStr">
         <is>
-          <t>Backstage: per-module metadata: repository/documentation/dependencies</t>
+          <t>Admin Portal: visibility: Feature flags/Configuration</t>
         </is>
       </c>
       <c r="D84" s="11" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B85" s="13" t="inlineStr">
         <is>
@@ -3057,14 +3077,14 @@
       </c>
       <c r="C85" s="11" t="inlineStr">
         <is>
-          <t>Backstage: per-module metadata: APIs/events/DB ownership/dashboards/runbooks</t>
+          <t>Admin Portal: visibility: Moderation/Audit</t>
         </is>
       </c>
       <c r="D85" s="11" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="9" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B86" s="13" t="inlineStr">
         <is>
@@ -3073,14 +3093,14 @@
       </c>
       <c r="C86" s="11" t="inlineStr">
         <is>
-          <t>SDKs: Flutter SDK</t>
+          <t>Admin Portal: visibility: System health/Deployments</t>
         </is>
       </c>
       <c r="D86" s="11" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="9" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B87" s="13" t="inlineStr">
         <is>
@@ -3089,14 +3109,14 @@
       </c>
       <c r="C87" s="11" t="inlineStr">
         <is>
-          <t>SDKs: TypeScript SDK</t>
+          <t>Admin Portal: must go through service APIs, never direct DB queries</t>
         </is>
       </c>
       <c r="D87" s="11" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B88" s="13" t="inlineStr">
         <is>
@@ -3105,14 +3125,14 @@
       </c>
       <c r="C88" s="11" t="inlineStr">
         <is>
-          <t>SDKs: Go SDK</t>
+          <t>Backstage: integrate Backstage as developer portal</t>
         </is>
       </c>
       <c r="D88" s="11" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B89" s="13" t="inlineStr">
         <is>
@@ -3121,14 +3141,14 @@
       </c>
       <c r="C89" s="11" t="inlineStr">
         <is>
-          <t>SDKs: auth + token refresh in each SDK</t>
+          <t>Backstage: per-module metadata: name/description/owner/lifecycle</t>
         </is>
       </c>
       <c r="D89" s="11" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B90" s="13" t="inlineStr">
         <is>
@@ -3137,14 +3157,14 @@
       </c>
       <c r="C90" s="11" t="inlineStr">
         <is>
-          <t>SDKs: pagination + safe retries</t>
+          <t>Backstage: per-module metadata: repository/documentation/dependencies</t>
         </is>
       </c>
       <c r="D90" s="11" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B91" s="13" t="inlineStr">
         <is>
@@ -3153,7 +3173,7 @@
       </c>
       <c r="C91" s="11" t="inlineStr">
         <is>
-          <t>SDKs: realtime connection helper</t>
+          <t>Backstage: per-module metadata: APIs/events/DB ownership/dashboards/runbooks</t>
         </is>
       </c>
       <c r="D91" s="11" t="inlineStr"/>
@@ -3169,7 +3189,7 @@
       </c>
       <c r="C92" s="11" t="inlineStr">
         <is>
-          <t>SDKs: correlation ID propagation</t>
+          <t>SDKs: Flutter SDK</t>
         </is>
       </c>
       <c r="D92" s="11" t="inlineStr"/>
@@ -3185,14 +3205,14 @@
       </c>
       <c r="C93" s="11" t="inlineStr">
         <is>
-          <t>SDKs: device registration helper</t>
+          <t>SDKs: TypeScript SDK</t>
         </is>
       </c>
       <c r="D93" s="11" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B94" s="13" t="inlineStr">
         <is>
@@ -3201,14 +3221,14 @@
       </c>
       <c r="C94" s="11" t="inlineStr">
         <is>
-          <t>Observability Completion: structured logs everywhere</t>
+          <t>SDKs: Go SDK</t>
         </is>
       </c>
       <c r="D94" s="11" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B95" s="13" t="inlineStr">
         <is>
@@ -3217,14 +3237,14 @@
       </c>
       <c r="C95" s="11" t="inlineStr">
         <is>
-          <t>Observability Completion: metrics everywhere</t>
+          <t>SDKs: auth + token refresh in each SDK</t>
         </is>
       </c>
       <c r="D95" s="11" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B96" s="13" t="inlineStr">
         <is>
@@ -3233,14 +3253,14 @@
       </c>
       <c r="C96" s="11" t="inlineStr">
         <is>
-          <t>Observability Completion: distributed traces everywhere</t>
+          <t>SDKs: pagination + safe retries</t>
         </is>
       </c>
       <c r="D96" s="11" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B97" s="13" t="inlineStr">
         <is>
@@ -3249,14 +3269,14 @@
       </c>
       <c r="C97" s="11" t="inlineStr">
         <is>
-          <t>Observability Completion: health checks everywhere</t>
+          <t>SDKs: realtime connection helper</t>
         </is>
       </c>
       <c r="D97" s="11" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B98" s="13" t="inlineStr">
         <is>
@@ -3265,14 +3285,14 @@
       </c>
       <c r="C98" s="11" t="inlineStr">
         <is>
-          <t>Observability Completion: dashboard: API latency</t>
+          <t>SDKs: correlation ID propagation</t>
         </is>
       </c>
       <c r="D98" s="11" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B99" s="13" t="inlineStr">
         <is>
@@ -3281,7 +3301,7 @@
       </c>
       <c r="C99" s="11" t="inlineStr">
         <is>
-          <t>Observability Completion: dashboard: error rate</t>
+          <t>SDKs: device registration helper</t>
         </is>
       </c>
       <c r="D99" s="11" t="inlineStr"/>
@@ -3297,7 +3317,7 @@
       </c>
       <c r="C100" s="11" t="inlineStr">
         <is>
-          <t>Observability Completion: dashboard: requests/sec</t>
+          <t>Observability Completion: structured logs everywhere</t>
         </is>
       </c>
       <c r="D100" s="11" t="inlineStr"/>
@@ -3313,7 +3333,7 @@
       </c>
       <c r="C101" s="11" t="inlineStr">
         <is>
-          <t>Observability Completion: dashboard: DB connections</t>
+          <t>Observability Completion: metrics everywhere</t>
         </is>
       </c>
       <c r="D101" s="11" t="inlineStr"/>
@@ -3329,7 +3349,7 @@
       </c>
       <c r="C102" s="11" t="inlineStr">
         <is>
-          <t>Observability Completion: dashboard: Kafka lag</t>
+          <t>Observability Completion: distributed traces everywhere</t>
         </is>
       </c>
       <c r="D102" s="11" t="inlineStr"/>
@@ -3345,7 +3365,7 @@
       </c>
       <c r="C103" s="11" t="inlineStr">
         <is>
-          <t>Observability Completion: dashboard: WebSocket connections</t>
+          <t>Observability Completion: health checks everywhere</t>
         </is>
       </c>
       <c r="D103" s="11" t="inlineStr"/>
@@ -3361,7 +3381,7 @@
       </c>
       <c r="C104" s="11" t="inlineStr">
         <is>
-          <t>Observability Completion: dashboard: Redis latency</t>
+          <t>Observability Completion: dashboard: API latency</t>
         </is>
       </c>
       <c r="D104" s="11" t="inlineStr"/>
@@ -3377,7 +3397,7 @@
       </c>
       <c r="C105" s="11" t="inlineStr">
         <is>
-          <t>Observability Completion: dashboard: notification failures</t>
+          <t>Observability Completion: dashboard: error rate</t>
         </is>
       </c>
       <c r="D105" s="11" t="inlineStr"/>
@@ -3393,7 +3413,7 @@
       </c>
       <c r="C106" s="11" t="inlineStr">
         <is>
-          <t>Observability Completion: dashboard: background job failures</t>
+          <t>Observability Completion: dashboard: requests/sec</t>
         </is>
       </c>
       <c r="D106" s="11" t="inlineStr"/>
@@ -3409,14 +3429,14 @@
       </c>
       <c r="C107" s="11" t="inlineStr">
         <is>
-          <t>Observability Completion: alerting rules</t>
+          <t>Observability Completion: dashboard: DB connections</t>
         </is>
       </c>
       <c r="D107" s="11" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B108" s="13" t="inlineStr">
         <is>
@@ -3425,14 +3445,14 @@
       </c>
       <c r="C108" s="11" t="inlineStr">
         <is>
-          <t>Platform Control Plane: one view: applications/services/versions</t>
+          <t>Observability Completion: dashboard: Kafka lag</t>
         </is>
       </c>
       <c r="D108" s="11" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B109" s="13" t="inlineStr">
         <is>
@@ -3441,14 +3461,14 @@
       </c>
       <c r="C109" s="11" t="inlineStr">
         <is>
-          <t>Platform Control Plane: one view: environments/dependencies/deployments</t>
+          <t>Observability Completion: dashboard: WebSocket connections</t>
         </is>
       </c>
       <c r="D109" s="11" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B110" s="13" t="inlineStr">
         <is>
@@ -3457,14 +3477,14 @@
       </c>
       <c r="C110" s="11" t="inlineStr">
         <is>
-          <t>Platform Control Plane: one view: DB ownership/events/API contracts</t>
+          <t>Observability Completion: dashboard: Redis latency</t>
         </is>
       </c>
       <c r="D110" s="11" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B111" s="13" t="inlineStr">
         <is>
@@ -3473,14 +3493,14 @@
       </c>
       <c r="C111" s="11" t="inlineStr">
         <is>
-          <t>Platform Control Plane: one view: health/alerts/recent changes</t>
+          <t>Observability Completion: dashboard: notification failures</t>
         </is>
       </c>
       <c r="D111" s="11" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="9" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B112" s="13" t="inlineStr">
         <is>
@@ -3489,14 +3509,14 @@
       </c>
       <c r="C112" s="11" t="inlineStr">
         <is>
-          <t>AI Development Context: every module: README</t>
+          <t>Observability Completion: dashboard: background job failures</t>
         </is>
       </c>
       <c r="D112" s="11" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="9" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B113" s="13" t="inlineStr">
         <is>
@@ -3505,14 +3525,14 @@
       </c>
       <c r="C113" s="11" t="inlineStr">
         <is>
-          <t>AI Development Context: every module: ownership metadata</t>
+          <t>Observability Completion: alerting rules</t>
         </is>
       </c>
       <c r="D113" s="11" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="9" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B114" s="13" t="inlineStr">
         <is>
@@ -3521,14 +3541,14 @@
       </c>
       <c r="C114" s="11" t="inlineStr">
         <is>
-          <t>AI Development Context: every module: dependencies</t>
+          <t>Platform Control Plane: one view: applications/services/versions</t>
         </is>
       </c>
       <c r="D114" s="11" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="9" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B115" s="13" t="inlineStr">
         <is>
@@ -3537,14 +3557,14 @@
       </c>
       <c r="C115" s="11" t="inlineStr">
         <is>
-          <t>AI Development Context: every module: API contract</t>
+          <t>Platform Control Plane: one view: environments/dependencies/deployments</t>
         </is>
       </c>
       <c r="D115" s="11" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="9" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B116" s="13" t="inlineStr">
         <is>
@@ -3553,26 +3573,122 @@
       </c>
       <c r="C116" s="11" t="inlineStr">
         <is>
-          <t>AI Development Context: every module: event contracts</t>
+          <t>Platform Control Plane: one view: DB ownership/events/API contracts</t>
         </is>
       </c>
       <c r="D116" s="11" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="9" t="n">
+        <v>29</v>
+      </c>
+      <c r="B117" s="13" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="C117" s="11" t="inlineStr">
+        <is>
+          <t>Platform Control Plane: one view: health/alerts/recent changes</t>
+        </is>
+      </c>
+      <c r="D117" s="11" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="B117" s="13" t="inlineStr">
+      <c r="B118" s="13" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="C117" s="11" t="inlineStr">
+      <c r="C118" s="11" t="inlineStr">
+        <is>
+          <t>AI Development Context: every module: README</t>
+        </is>
+      </c>
+      <c r="D118" s="11" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="B119" s="13" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="C119" s="11" t="inlineStr">
+        <is>
+          <t>AI Development Context: every module: ownership metadata</t>
+        </is>
+      </c>
+      <c r="D119" s="11" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="B120" s="13" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="C120" s="11" t="inlineStr">
+        <is>
+          <t>AI Development Context: every module: dependencies</t>
+        </is>
+      </c>
+      <c r="D120" s="11" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="B121" s="13" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="C121" s="11" t="inlineStr">
+        <is>
+          <t>AI Development Context: every module: API contract</t>
+        </is>
+      </c>
+      <c r="D121" s="11" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="B122" s="13" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="C122" s="11" t="inlineStr">
+        <is>
+          <t>AI Development Context: every module: event contracts</t>
+        </is>
+      </c>
+      <c r="D122" s="11" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="B123" s="13" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="C123" s="11" t="inlineStr">
         <is>
           <t>AI Development Context: every module: DB ownership</t>
         </is>
       </c>
-      <c r="D117" s="11" t="inlineStr"/>
+      <c r="D123" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3588,7 +3704,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4524,6 +4640,70 @@
       <c r="F29" s="11" t="inlineStr">
         <is>
           <t>Phase 23</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="32" customHeight="1">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>aigateway</t>
+        </is>
+      </c>
+      <c r="B30" s="11" t="inlineStr">
+        <is>
+          <t>core-api</t>
+        </is>
+      </c>
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t>Provider-neutral completions API - model routing, quotas, cost tracking, audit, timeouts, fallback</t>
+        </is>
+      </c>
+      <c r="D30" s="11" t="inlineStr">
+        <is>
+          <t>ai_completions</t>
+        </is>
+      </c>
+      <c r="E30" s="11" t="inlineStr">
+        <is>
+          <t>Self for own usage; open (quota-limited) to complete</t>
+        </is>
+      </c>
+      <c r="F30" s="11" t="inlineStr">
+        <is>
+          <t>Phase 24</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="32" customHeight="1">
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>aigateway/ollama</t>
+        </is>
+      </c>
+      <c r="B31" s="11" t="inlineStr">
+        <is>
+          <t>core-api</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>Real local-inference Provider adapter - the one live-testable Provider this phase ships</t>
+        </is>
+      </c>
+      <c r="D31" s="11" t="inlineStr">
+        <is>
+          <t>none (stateless HTTP client to a real Ollama container)</t>
+        </is>
+      </c>
+      <c r="E31" s="11" t="inlineStr">
+        <is>
+          <t>n/a (internal provider adapter, not a route)</t>
+        </is>
+      </c>
+      <c r="F31" s="11" t="inlineStr">
+        <is>
+          <t>Phase 24</t>
         </is>
       </c>
     </row>
@@ -4541,7 +4721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E140"/>
+  <dimension ref="A1:E143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -8016,6 +8196,87 @@
       <c r="E140" s="11" t="inlineStr">
         <is>
           <t>operational debug view only, not for analytical queries</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="11" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="B141" s="11" t="inlineStr">
+        <is>
+          <t>/v1/ai/completions</t>
+        </is>
+      </c>
+      <c r="C141" s="11" t="inlineStr">
+        <is>
+          <t>aigateway</t>
+        </is>
+      </c>
+      <c r="D141" s="11" t="inlineStr">
+        <is>
+          <t>Authenticated (quota-limited)</t>
+        </is>
+      </c>
+      <c r="E141" s="11" t="inlineStr">
+        <is>
+          <t>real local inference via Ollama; never call a vendor model name directly</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="11" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="B142" s="11" t="inlineStr">
+        <is>
+          <t>/v1/ai/usage</t>
+        </is>
+      </c>
+      <c r="C142" s="11" t="inlineStr">
+        <is>
+          <t>aigateway</t>
+        </is>
+      </c>
+      <c r="D142" s="11" t="inlineStr">
+        <is>
+          <t>Self or platform.admin</t>
+        </is>
+      </c>
+      <c r="E142" s="11" t="inlineStr">
+        <is>
+          <t>?userId=; tokens/cost/latency, never prompt or response text</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="11" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="B143" s="11" t="inlineStr">
+        <is>
+          <t>/v1/ai/models</t>
+        </is>
+      </c>
+      <c r="C143" s="11" t="inlineStr">
+        <is>
+          <t>aigateway</t>
+        </is>
+      </c>
+      <c r="D143" s="11" t="inlineStr">
+        <is>
+          <t>Authenticated</t>
+        </is>
+      </c>
+      <c r="E143" s="11" t="inlineStr">
+        <is>
+          <t>lists registered model aliases, never vendor model names</t>
         </is>
       </c>
     </row>
@@ -8474,7 +8735,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -8583,7 +8844,7 @@
       </c>
       <c r="D4" s="11" t="inlineStr">
         <is>
-          <t>Background job runner, search indexer, Temporal workflow worker.</t>
+          <t>Background job runner, search indexer, Temporal workflow worker, analytics NDJSON pipeline.</t>
         </is>
       </c>
       <c r="E4" s="11" t="inlineStr">
@@ -8811,25 +9072,52 @@
     <row r="13" ht="32" customHeight="1">
       <c r="A13" s="11" t="inlineStr">
         <is>
+          <t>Ollama</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>Docker container</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>http://localhost:11434</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>Real local LLM inference behind the AI Gateway - model qwen2.5:0.5b auto-pulled on every start, no vendor API key needed.</t>
+        </is>
+      </c>
+      <c r="E13" s="11" t="inlineStr">
+        <is>
+          <t>no auth locally</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="32" customHeight="1">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
           <t>OTel Collector / Tempo / Prometheus / Grafana / Loki</t>
         </is>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B14" s="11" t="inlineStr">
         <is>
           <t>Docker containers</t>
         </is>
       </c>
-      <c r="C13" s="11" t="inlineStr">
+      <c r="C14" s="11" t="inlineStr">
         <is>
           <t>see infra/docker/docker-compose.yml</t>
         </is>
       </c>
-      <c r="D13" s="11" t="inlineStr">
+      <c r="D14" s="11" t="inlineStr">
         <is>
           <t>Full observability stack - traces, metrics, logs, dashboards.</t>
         </is>
       </c>
-      <c r="E13" s="11" t="inlineStr">
+      <c r="E14" s="11" t="inlineStr">
         <is>
           <t>no auth locally</t>
         </is>

--- a/docs/control/data.xlsx
+++ b/docs/control/data.xlsx
@@ -267,8 +267,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="APIEndpoints" displayName="APIEndpoints" ref="A1:E143" headerRowCount="1">
-  <autoFilter ref="A1:E143"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="APIEndpoints" displayName="APIEndpoints" ref="A1:E147" headerRowCount="1">
+  <autoFilter ref="A1:E147"/>
   <tableColumns count="5">
     <tableColumn id="1" name="Method"/>
     <tableColumn id="2" name="Path"/>
@@ -281,8 +281,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="HowToTest" displayName="HowToTest" ref="A1:D19" headerRowCount="1">
-  <autoFilter ref="A1:D19"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="HowToTest" displayName="HowToTest" ref="A1:D20" headerRowCount="1">
+  <autoFilter ref="A1:D20"/>
   <tableColumns count="4">
     <tableColumn id="1" name="Step"/>
     <tableColumn id="2" name="What"/>
@@ -294,8 +294,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="InfraCredentials" displayName="InfraCredentials" ref="A1:E14" headerRowCount="1">
-  <autoFilter ref="A1:E14"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="InfraCredentials" displayName="InfraCredentials" ref="A1:E15" headerRowCount="1">
+  <autoFilter ref="A1:E15"/>
   <tableColumns count="5">
     <tableColumn id="1" name="Service"/>
     <tableColumn id="2" name="Type"/>
@@ -596,7 +596,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -633,12 +633,12 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>24 / 30</t>
+          <t>25 / 30</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>83%</t>
         </is>
       </c>
     </row>
@@ -662,7 +662,7 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Shared Go packages</t>
+          <t>Frontend apps</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -672,139 +672,156 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>packages/go/platformkit</t>
+          <t>apps/admin (Next.js 15 App Router)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Domain modules (core-api)</t>
+          <t>Shared Go packages</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>one per completed phase</t>
+          <t>packages/go/platformkit</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Live HTTP endpoints</t>
+          <t>Domain modules (core-api)</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>see 'API Endpoints' sheet</t>
+          <t>one per completed backend phase</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>DB migrations</t>
+          <t>Live HTTP endpoints</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>146</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>data/migrations/0001-0022</t>
+          <t>see 'API Endpoints' sheet</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Real infra dependencies</t>
+          <t>DB migrations</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Postgres, Valkey, Keycloak, OpenFGA, MinIO, OpenSearch, Temporal, Kafka/Redpanda, Ollama, OTel</t>
+          <t>data/migrations/0001-0022</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
+          <t>Real infra dependencies</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>Postgres, Valkey, Keycloak, OpenFGA, MinIO, OpenSearch, Temporal, Kafka/Redpanda, Ollama, OTel</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
           <t>Commits so far</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>see git log</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>How to read this workbook</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>• Roadmap - all 30 phases, one row each, status + what it delivers.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>• Todo Checklist - granular task list (completed sub-items and still-to-do sub-items) so progress is trackable at a finer grain than 'phase done or not'.</t>
+          <t>• Roadmap - all 30 phases, one row each, status + what it delivers.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>• Modules - every backend/core-api/internal module: what it owns, its storage, its access rule.</t>
+          <t>• Todo Checklist - granular task list (completed sub-items and still-to-do sub-items) so progress is trackable at a finer grain than 'phase done or not'.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>• API Endpoints - every live HTTP route across all three services, with auth level.</t>
+          <t>• Modules - every backend/core-api/internal module: what it owns, its storage, its access rule.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>• How To Test - copy-paste steps to bring the stack up locally and exercise it for real (mint a token, call endpoints, open a WebSocket).</t>
+          <t>• API Endpoints - every live HTTP route across all three services, with auth level.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>• How To Test - copy-paste steps to bring the stack up locally and exercise it for real (mint a token, call endpoints, open a WebSocket).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>• Infra &amp; Credentials - every local service, its port, and its local-only credentials.</t>
         </is>
@@ -818,7 +835,7 @@
     <mergeCell ref="A17:F17"/>
     <mergeCell ref="A18:F18"/>
     <mergeCell ref="A20:F20"/>
-    <mergeCell ref="A15:F15"/>
+    <mergeCell ref="A21:F21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1471,9 +1488,9 @@
       <c r="A26" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="12" t="inlineStr">
-        <is>
-          <t>Next up</t>
+      <c r="B26" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C26" s="11" t="inlineStr">
@@ -1483,12 +1500,12 @@
       </c>
       <c r="D26" s="11" t="inlineStr">
         <is>
-          <t>The control-plane UI (apps/admin, Next.js) - visibility into apps/users/sessions/devices/roles/tenants/relationships/messages/notifications/files/jobs/flags/config/moderation/audit/health/deployments, always through service APIs, never direct DB queries.</t>
+          <t>The control-plane UI (apps/admin, Next.js 15 App Router), always through service APIs, never direct DB queries - real Keycloak-authenticated session, live data on Users/Roles/Applications/Audit/Moderation/Feature Flags/Jobs/Configuration/System Health/Billing/AI Gateway, honest ComingSoon reasoning for every area whose backend endpoint is still self-scoped-only. Added authz's first HTTP surface and GET /v1/users (admin-wide listing) to close real gaps. Live-validated end to end with a real headless browser: login, dashboard, a full role grant/revoke round trip, logout.</t>
         </is>
       </c>
       <c r="E26" s="11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>97091a7</t>
         </is>
       </c>
     </row>
@@ -1496,9 +1513,9 @@
       <c r="A27" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B27" s="12" t="inlineStr">
+        <is>
+          <t>Next up</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
@@ -2048,7 +2065,7 @@
     </row>
     <row r="26">
       <c r="A26" s="9" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
@@ -2057,14 +2074,14 @@
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>Repo health baseline (make doctor / validate-all / go test / go build) run and passed</t>
+          <t>Phase 25: Admin Portal implemented, unit-tested, live-validated, documented, committed</t>
         </is>
       </c>
       <c r="D26" s="11" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
@@ -2073,18 +2090,14 @@
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>Environment / ApplicationVersion / ApplicationConfiguration</t>
-        </is>
-      </c>
-      <c r="D27" s="11" t="inlineStr">
-        <is>
-          <t>Deferred - no consumer needs them yet, documented as intentional in applications/README.md</t>
-        </is>
-      </c>
+          <t>Repo health baseline (make doctor / validate-all / go test / go build) run and passed</t>
+        </is>
+      </c>
+      <c r="D27" s="11" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
@@ -2093,32 +2106,32 @@
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>Separate Session table</t>
+          <t>Environment / ApplicationVersion / ApplicationConfiguration</t>
         </is>
       </c>
       <c r="D28" s="11" t="inlineStr">
         <is>
-          <t>Deferred - Device.SessionStatus covers today's single-session-per-device need, documented in devices/README.md</t>
+          <t>Deferred - no consumer needs them yet, documented as intentional in applications/README.md</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="B29" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+        <v>5</v>
+      </c>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>UserPreferences (named in Phase 4, no fields ever specified)</t>
+          <t>Separate Session table</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>Deferred to Phase 12+; notification preferences shipped, a generic preferences bag did not</t>
+          <t>Deferred - Device.SessionStatus covers today's single-session-per-device need, documented in devices/README.md</t>
         </is>
       </c>
     </row>
@@ -2133,12 +2146,12 @@
       </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t>apps/mobile test/ directory (make flutter-test currently fails)</t>
+          <t>UserPreferences (named in Phase 4, no fields ever specified)</t>
         </is>
       </c>
       <c r="D30" s="11" t="inlineStr">
         <is>
-          <t>Known gap since Phase 9's audit, not yet picked up</t>
+          <t>Deferred to Phase 12+; notification preferences shipped, a generic preferences bag did not</t>
         </is>
       </c>
     </row>
@@ -2153,30 +2166,34 @@
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>apps/admin next@15 / sharp transitive advisories</t>
+          <t>apps/mobile test/ directory (make flutter-test currently fails)</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>Fix is a Next.js major-version bump - separate, reviewable change</t>
+          <t>Known gap since Phase 9's audit, not yet picked up</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="9" t="n">
-        <v>20</v>
-      </c>
-      <c r="B32" s="10" t="inlineStr">
-        <is>
-          <t>Done</t>
+        <v>9</v>
+      </c>
+      <c r="B32" s="13" t="inlineStr">
+        <is>
+          <t>Pending</t>
         </is>
       </c>
       <c r="C32" s="11" t="inlineStr">
         <is>
-          <t>Privacy: consent (append-only history)</t>
-        </is>
-      </c>
-      <c r="D32" s="11" t="inlineStr"/>
+          <t>apps/admin next@15 / sharp transitive advisories</t>
+        </is>
+      </c>
+      <c r="D32" s="11" t="inlineStr">
+        <is>
+          <t>Fix is a Next.js major-version bump - separate, reviewable change</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="9" t="n">
@@ -2189,7 +2206,7 @@
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>Privacy: user data export (ExportUserData registry - users/devices/files/audit)</t>
+          <t>Privacy: consent (append-only history)</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr"/>
@@ -2205,7 +2222,7 @@
       </c>
       <c r="C34" s="11" t="inlineStr">
         <is>
-          <t>Privacy: user deletion (DeleteUserData registry - users/devices/files; audit deliberately excluded)</t>
+          <t>Privacy: user data export (ExportUserData registry - users/devices/files/audit)</t>
         </is>
       </c>
       <c r="D34" s="11" t="inlineStr"/>
@@ -2221,7 +2238,7 @@
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>Privacy: retention policy (declared, not scheduled - same documented gap as Phase 13's PurgeExpired)</t>
+          <t>Privacy: user deletion (DeleteUserData registry - users/devices/files; audit deliberately excluded)</t>
         </is>
       </c>
       <c r="D35" s="11" t="inlineStr"/>
@@ -2237,7 +2254,7 @@
       </c>
       <c r="C36" s="11" t="inlineStr">
         <is>
-          <t>Privacy: privacy preferences</t>
+          <t>Privacy: retention policy (declared, not scheduled - same documented gap as Phase 13's PurgeExpired)</t>
         </is>
       </c>
       <c r="D36" s="11" t="inlineStr"/>
@@ -2253,7 +2270,7 @@
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>Privacy: coordinate deletion through workflows/events - core-api's own embedded Temporal worker</t>
+          <t>Privacy: privacy preferences</t>
         </is>
       </c>
       <c r="D37" s="11" t="inlineStr"/>
@@ -2262,21 +2279,17 @@
       <c r="A38" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="B38" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B38" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C38" s="11" t="inlineStr">
         <is>
-          <t>Privacy: notifications module as an Export/Delete participant</t>
-        </is>
-      </c>
-      <c r="D38" s="11" t="inlineStr">
-        <is>
-          <t>Deliberately deferred to prove the registry makes this a 2-line addition later, not a framework change</t>
-        </is>
-      </c>
+          <t>Privacy: coordinate deletion through workflows/events - core-api's own embedded Temporal worker</t>
+        </is>
+      </c>
+      <c r="D38" s="11" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="9" t="n">
@@ -2289,32 +2302,32 @@
       </c>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>Privacy: relationships/groups/messaging as participants</t>
+          <t>Privacy: notifications module as an Export/Delete participant</t>
         </is>
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>Deferred - shared multi-user data needs a redaction strategy this phase's per-user-in-isolation registry doesn't fit</t>
+          <t>Deliberately deferred to prove the registry makes this a 2-line addition later, not a framework change</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="9" t="n">
-        <v>21</v>
-      </c>
-      <c r="B40" s="10" t="inlineStr">
-        <is>
-          <t>Done</t>
+        <v>20</v>
+      </c>
+      <c r="B40" s="13" t="inlineStr">
+        <is>
+          <t>Pending</t>
         </is>
       </c>
       <c r="C40" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: Block</t>
+          <t>Privacy: relationships/groups/messaging as participants</t>
         </is>
       </c>
       <c r="D40" s="11" t="inlineStr">
         <is>
-          <t>Reused Phase 8's relationships (Status='blocked'), deliberately not duplicated</t>
+          <t>Deferred - shared multi-user data needs a redaction strategy this phase's per-user-in-isolation registry doesn't fit</t>
         </is>
       </c>
     </row>
@@ -2329,10 +2342,14 @@
       </c>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: Mute</t>
-        </is>
-      </c>
-      <c r="D41" s="11" t="inlineStr"/>
+          <t>Trust &amp; Safety: Block</t>
+        </is>
+      </c>
+      <c r="D41" s="11" t="inlineStr">
+        <is>
+          <t>Reused Phase 8's relationships (Status='blocked'), deliberately not duplicated</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="9" t="n">
@@ -2345,7 +2362,7 @@
       </c>
       <c r="C42" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: Report -&gt; ModerationCase (deduplicated via partial unique index)</t>
+          <t>Trust &amp; Safety: Mute</t>
         </is>
       </c>
       <c r="D42" s="11" t="inlineStr"/>
@@ -2361,7 +2378,7 @@
       </c>
       <c r="C43" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: Suspension</t>
+          <t>Trust &amp; Safety: Report -&gt; ModerationCase (deduplicated via partial unique index)</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr"/>
@@ -2377,7 +2394,7 @@
       </c>
       <c r="C44" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: Ban</t>
+          <t>Trust &amp; Safety: Suspension</t>
         </is>
       </c>
       <c r="D44" s="11" t="inlineStr"/>
@@ -2393,7 +2410,7 @@
       </c>
       <c r="C45" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: Appeal (approving lifts the target restriction)</t>
+          <t>Trust &amp; Safety: Ban</t>
         </is>
       </c>
       <c r="D45" s="11" t="inlineStr"/>
@@ -2409,7 +2426,7 @@
       </c>
       <c r="C46" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: rate limiting (new platformkit/ratelimit, Valkey-backed)</t>
+          <t>Trust &amp; Safety: Appeal (approving lifts the target restriction)</t>
         </is>
       </c>
       <c r="D46" s="11" t="inlineStr"/>
@@ -2425,7 +2442,7 @@
       </c>
       <c r="C47" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: spam protection (5 reports/hour per reporter)</t>
+          <t>Trust &amp; Safety: rate limiting (new platformkit/ratelimit, Valkey-backed)</t>
         </is>
       </c>
       <c r="D47" s="11" t="inlineStr"/>
@@ -2441,7 +2458,7 @@
       </c>
       <c r="C48" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: abuse signals (critical severity auto-opens a case)</t>
+          <t>Trust &amp; Safety: spam protection (5 reports/hour per reporter)</t>
         </is>
       </c>
       <c r="D48" s="11" t="inlineStr"/>
@@ -2457,7 +2474,7 @@
       </c>
       <c r="C49" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: pluggable product-specific report reasons (free-form Reason field)</t>
+          <t>Trust &amp; Safety: abuse signals (critical severity auto-opens a case)</t>
         </is>
       </c>
       <c r="D49" s="11" t="inlineStr"/>
@@ -2473,7 +2490,7 @@
       </c>
       <c r="C50" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: Suspension/Ban actually restrict access (new requireActive middleware, one entry point)</t>
+          <t>Trust &amp; Safety: pluggable product-specific report reasons (free-form Reason field)</t>
         </is>
       </c>
       <c r="D50" s="11" t="inlineStr"/>
@@ -2482,21 +2499,17 @@
       <c r="A51" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="B51" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B51" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: WebSocket disconnect on suspension/ban</t>
-        </is>
-      </c>
-      <c r="D51" s="11" t="inlineStr">
-        <is>
-          <t>Deferred - only HTTP access is gated; an existing realtime-gateway connection isn't forcibly closed</t>
-        </is>
-      </c>
+          <t>Trust &amp; Safety: Suspension/Ban actually restrict access (new requireActive middleware, one entry point)</t>
+        </is>
+      </c>
+      <c r="D51" s="11" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="9" t="n">
@@ -2509,30 +2522,34 @@
       </c>
       <c r="C52" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: aggregating lower-severity signals over a time window</t>
+          <t>Trust &amp; Safety: WebSocket disconnect on suspension/ban</t>
         </is>
       </c>
       <c r="D52" s="11" t="inlineStr">
         <is>
-          <t>Deferred - a real abuse-detection engine is out of this phase's scope; only single-critical-signal escalation is implemented</t>
+          <t>Deferred - only HTTP access is gated; an existing realtime-gateway connection isn't forcibly closed</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="9" t="n">
-        <v>22</v>
-      </c>
-      <c r="B53" s="10" t="inlineStr">
-        <is>
-          <t>Done</t>
+        <v>21</v>
+      </c>
+      <c r="B53" s="13" t="inlineStr">
+        <is>
+          <t>Pending</t>
         </is>
       </c>
       <c r="C53" s="11" t="inlineStr">
         <is>
-          <t>Billing: Payment model (provider-specific transaction record)</t>
-        </is>
-      </c>
-      <c r="D53" s="11" t="inlineStr"/>
+          <t>Trust &amp; Safety: aggregating lower-severity signals over a time window</t>
+        </is>
+      </c>
+      <c r="D53" s="11" t="inlineStr">
+        <is>
+          <t>Deferred - a real abuse-detection engine is out of this phase's scope; only single-critical-signal escalation is implemented</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="9" t="n">
@@ -2545,7 +2562,7 @@
       </c>
       <c r="C54" s="11" t="inlineStr">
         <is>
-          <t>Billing: Entitlement model (platform-facing truth, kept separate from Payment)</t>
+          <t>Billing: Payment model (provider-specific transaction record)</t>
         </is>
       </c>
       <c r="D54" s="11" t="inlineStr"/>
@@ -2561,7 +2578,7 @@
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t>Billing: provider abstraction (PaymentProvider interface + registry, implemented first)</t>
+          <t>Billing: Entitlement model (platform-facing truth, kept separate from Payment)</t>
         </is>
       </c>
       <c r="D55" s="11" t="inlineStr"/>
@@ -2577,32 +2594,28 @@
       </c>
       <c r="C56" s="11" t="inlineStr">
         <is>
-          <t>Billing: Stripe adapter</t>
-        </is>
-      </c>
-      <c r="D56" s="11" t="inlineStr">
-        <is>
-          <t>Real HMAC-SHA256 webhook signature verification, live-validated without a Stripe account via self-signed test payloads</t>
-        </is>
-      </c>
+          <t>Billing: provider abstraction (PaymentProvider interface + registry, implemented first)</t>
+        </is>
+      </c>
+      <c r="D56" s="11" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="B57" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B57" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C57" s="11" t="inlineStr">
         <is>
-          <t>Billing: Apple IAP adapter</t>
+          <t>Billing: Stripe adapter</t>
         </is>
       </c>
       <c r="D57" s="11" t="inlineStr">
         <is>
-          <t>Deferred - needs real App Store Server API credentials this environment doesn't have</t>
+          <t>Real HMAC-SHA256 webhook signature verification, live-validated without a Stripe account via self-signed test payloads</t>
         </is>
       </c>
     </row>
@@ -2617,30 +2630,34 @@
       </c>
       <c r="C58" s="11" t="inlineStr">
         <is>
-          <t>Billing: Google Play adapter</t>
+          <t>Billing: Apple IAP adapter</t>
         </is>
       </c>
       <c r="D58" s="11" t="inlineStr">
         <is>
-          <t>Deferred - needs real Play Developer API credentials this environment doesn't have</t>
+          <t>Deferred - needs real App Store Server API credentials this environment doesn't have</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="9" t="n">
-        <v>23</v>
-      </c>
-      <c r="B59" s="10" t="inlineStr">
-        <is>
-          <t>Done</t>
+        <v>22</v>
+      </c>
+      <c r="B59" s="13" t="inlineStr">
+        <is>
+          <t>Pending</t>
         </is>
       </c>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>Analytics: generic event envelope (event_name/user_id/anonymous_id/app_id/session_id/timestamp/properties/context)</t>
-        </is>
-      </c>
-      <c r="D59" s="11" t="inlineStr"/>
+          <t>Billing: Google Play adapter</t>
+        </is>
+      </c>
+      <c r="D59" s="11" t="inlineStr">
+        <is>
+          <t>Deferred - needs real Play Developer API credentials this environment doesn't have</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="9" t="n">
@@ -2653,7 +2670,7 @@
       </c>
       <c r="C60" s="11" t="inlineStr">
         <is>
-          <t>Analytics: keep operational DBs out of the analytics path (analytics_events is a landing buffer, never queried for analytics)</t>
+          <t>Analytics: generic event envelope (event_name/user_id/anonymous_id/app_id/session_id/timestamp/properties/context)</t>
         </is>
       </c>
       <c r="D60" s="11" t="inlineStr"/>
@@ -2669,7 +2686,7 @@
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>Analytics: pipeline foundation for ClickHouse/warehouse/data lake (worker batches NDJSON into MinIO/S3)</t>
+          <t>Analytics: keep operational DBs out of the analytics path (analytics_events is a landing buffer, never queried for analytics)</t>
         </is>
       </c>
       <c r="D61" s="11" t="inlineStr"/>
@@ -2678,37 +2695,37 @@
       <c r="A62" s="9" t="n">
         <v>23</v>
       </c>
-      <c r="B62" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B62" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C62" s="11" t="inlineStr">
         <is>
-          <t>Analytics: an actual ClickHouse/warehouse/data-lake query layer</t>
-        </is>
-      </c>
-      <c r="D62" s="11" t="inlineStr">
-        <is>
-          <t>Out of scope - this phase builds the landing pipeline only; no real destination system exists in this environment to integrate against honestly</t>
-        </is>
-      </c>
+          <t>Analytics: pipeline foundation for ClickHouse/warehouse/data lake (worker batches NDJSON into MinIO/S3)</t>
+        </is>
+      </c>
+      <c r="D62" s="11" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="9" t="n">
-        <v>24</v>
-      </c>
-      <c r="B63" s="10" t="inlineStr">
-        <is>
-          <t>Done</t>
+        <v>23</v>
+      </c>
+      <c r="B63" s="13" t="inlineStr">
+        <is>
+          <t>Pending</t>
         </is>
       </c>
       <c r="C63" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: provider-neutral interface (Provider: Name + Complete)</t>
-        </is>
-      </c>
-      <c r="D63" s="11" t="inlineStr"/>
+          <t>Analytics: an actual ClickHouse/warehouse/data-lake query layer</t>
+        </is>
+      </c>
+      <c r="D63" s="11" t="inlineStr">
+        <is>
+          <t>Out of scope - this phase builds the landing pipeline only; no real destination system exists in this environment to integrate against honestly</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="9" t="n">
@@ -2721,32 +2738,28 @@
       </c>
       <c r="C64" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: local models / Ollama adapter</t>
-        </is>
-      </c>
-      <c r="D64" s="11" t="inlineStr">
-        <is>
-          <t>Real local inference via a new Ollama container, auto-pulled model, no vendor API key - the one live-testable provider</t>
-        </is>
-      </c>
+          <t>AI Gateway: provider-neutral interface (Provider: Name + Complete)</t>
+        </is>
+      </c>
+      <c r="D64" s="11" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="9" t="n">
         <v>24</v>
       </c>
-      <c r="B65" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B65" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: OpenAI adapter</t>
+          <t>AI Gateway: local models / Ollama adapter</t>
         </is>
       </c>
       <c r="D65" s="11" t="inlineStr">
         <is>
-          <t>Deferred - no real API key in this environment to validate against honestly</t>
+          <t>Real local inference via a new Ollama container, auto-pulled model, no vendor API key - the one live-testable provider</t>
         </is>
       </c>
     </row>
@@ -2761,7 +2774,7 @@
       </c>
       <c r="C66" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: Anthropic adapter</t>
+          <t>AI Gateway: OpenAI adapter</t>
         </is>
       </c>
       <c r="D66" s="11" t="inlineStr">
@@ -2781,7 +2794,7 @@
       </c>
       <c r="C67" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: Google adapter</t>
+          <t>AI Gateway: Anthropic adapter</t>
         </is>
       </c>
       <c r="D67" s="11" t="inlineStr">
@@ -2794,17 +2807,21 @@
       <c r="A68" s="9" t="n">
         <v>24</v>
       </c>
-      <c r="B68" s="10" t="inlineStr">
-        <is>
-          <t>Done</t>
+      <c r="B68" s="13" t="inlineStr">
+        <is>
+          <t>Pending</t>
         </is>
       </c>
       <c r="C68" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: model routing (product-facing ModelAlias, never a vendor model name)</t>
-        </is>
-      </c>
-      <c r="D68" s="11" t="inlineStr"/>
+          <t>AI Gateway: Google adapter</t>
+        </is>
+      </c>
+      <c r="D68" s="11" t="inlineStr">
+        <is>
+          <t>Deferred - no real API key in this environment to validate against honestly</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="9" t="n">
@@ -2817,7 +2834,7 @@
       </c>
       <c r="C69" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: quotas (ratelimit.Limiter reused a third time, 60/min/caller)</t>
+          <t>AI Gateway: model routing (product-facing ModelAlias, never a vendor model name)</t>
         </is>
       </c>
       <c r="D69" s="11" t="inlineStr"/>
@@ -2833,7 +2850,7 @@
       </c>
       <c r="C70" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: token usage tracking</t>
+          <t>AI Gateway: quotas (ratelimit.Limiter reused a third time, 60/min/caller)</t>
         </is>
       </c>
       <c r="D70" s="11" t="inlineStr"/>
@@ -2849,7 +2866,7 @@
       </c>
       <c r="C71" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: cost tracking (real per-route price table; Ollama honestly priced at 0)</t>
+          <t>AI Gateway: token usage tracking</t>
         </is>
       </c>
       <c r="D71" s="11" t="inlineStr"/>
@@ -2865,7 +2882,7 @@
       </c>
       <c r="C72" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: audit integration (new AIGatewayAuditRecorder, a genuine audit.Record per call)</t>
+          <t>AI Gateway: cost tracking (real per-route price table; Ollama honestly priced at 0)</t>
         </is>
       </c>
       <c r="D72" s="11" t="inlineStr"/>
@@ -2881,7 +2898,7 @@
       </c>
       <c r="C73" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: prompt/version metadata (free-form PromptKey/PromptVersion)</t>
+          <t>AI Gateway: audit integration (new AIGatewayAuditRecorder, a genuine audit.Record per call)</t>
         </is>
       </c>
       <c r="D73" s="11" t="inlineStr"/>
@@ -2897,7 +2914,7 @@
       </c>
       <c r="C74" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: timeouts (context.WithTimeout per provider call)</t>
+          <t>AI Gateway: prompt/version metadata (free-form PromptKey/PromptVersion)</t>
         </is>
       </c>
       <c r="D74" s="11" t="inlineStr"/>
@@ -2913,7 +2930,7 @@
       </c>
       <c r="C75" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: fallback (ordered provider/model chain, first success wins)</t>
+          <t>AI Gateway: timeouts (context.WithTimeout per provider call)</t>
         </is>
       </c>
       <c r="D75" s="11" t="inlineStr"/>
@@ -2922,25 +2939,21 @@
       <c r="A76" s="9" t="n">
         <v>24</v>
       </c>
-      <c r="B76" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B76" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C76" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: live token-quantity quota (as opposed to today's call-count quota)</t>
-        </is>
-      </c>
-      <c r="D76" s="11" t="inlineStr">
-        <is>
-          <t>Deferred - Repository already has the data (Completion.TotalTokens); not wired as a live gate yet</t>
-        </is>
-      </c>
+          <t>AI Gateway: fallback (ordered provider/model chain, first success wins)</t>
+        </is>
+      </c>
+      <c r="D76" s="11" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B77" s="13" t="inlineStr">
         <is>
@@ -2949,23 +2962,27 @@
       </c>
       <c r="C77" s="11" t="inlineStr">
         <is>
-          <t>Admin Portal: control-plane UI in apps/admin</t>
-        </is>
-      </c>
-      <c r="D77" s="11" t="inlineStr"/>
+          <t>AI Gateway: live token-quantity quota (as opposed to today's call-count quota)</t>
+        </is>
+      </c>
+      <c r="D77" s="11" t="inlineStr">
+        <is>
+          <t>Deferred - Repository already has the data (Completion.TotalTokens); not wired as a live gate yet</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="B78" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B78" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C78" s="11" t="inlineStr">
         <is>
-          <t>Admin Portal: visibility: Applications</t>
+          <t>Admin Portal: real Keycloak-authenticated session (Resource Owner Password Credentials grant), httpOnly session cookie</t>
         </is>
       </c>
       <c r="D78" s="11" t="inlineStr"/>
@@ -2974,62 +2991,74 @@
       <c r="A79" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="B79" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B79" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C79" s="11" t="inlineStr">
         <is>
-          <t>Admin Portal: visibility: Users/Sessions/Devices</t>
-        </is>
-      </c>
-      <c r="D79" s="11" t="inlineStr"/>
+          <t>Admin Portal: visibility - Applications</t>
+        </is>
+      </c>
+      <c r="D79" s="11" t="inlineStr">
+        <is>
+          <t>Real GET /v1/apps table</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="B80" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B80" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C80" s="11" t="inlineStr">
         <is>
-          <t>Admin Portal: visibility: Roles/Permissions</t>
-        </is>
-      </c>
-      <c r="D80" s="11" t="inlineStr"/>
+          <t>Admin Portal: visibility - Users (list + detail)</t>
+        </is>
+      </c>
+      <c r="D80" s="11" t="inlineStr">
+        <is>
+          <t>New admin-wide GET /v1/users (cursor-paginated, platform.admin-gated)</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="B81" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B81" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C81" s="11" t="inlineStr">
         <is>
-          <t>Admin Portal: visibility: Tenants/Relationships</t>
-        </is>
-      </c>
-      <c r="D81" s="11" t="inlineStr"/>
+          <t>Admin Portal: visibility - Roles/Permissions</t>
+        </is>
+      </c>
+      <c r="D81" s="11" t="inlineStr">
+        <is>
+          <t>New authz HTTP surface (GET/POST /v1/authz/roles, POST /v1/authz/roles/revoke) with a full grant/revoke UI</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="B82" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B82" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C82" s="11" t="inlineStr">
         <is>
-          <t>Admin Portal: visibility: Messages/Notifications</t>
+          <t>Admin Portal: visibility - Feature Flags, Configuration, Jobs</t>
         </is>
       </c>
       <c r="D82" s="11" t="inlineStr"/>
@@ -3038,14 +3067,14 @@
       <c r="A83" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="B83" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B83" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C83" s="11" t="inlineStr">
         <is>
-          <t>Admin Portal: visibility: Files/Jobs</t>
+          <t>Admin Portal: visibility - Moderation, Audit</t>
         </is>
       </c>
       <c r="D83" s="11" t="inlineStr"/>
@@ -3054,30 +3083,34 @@
       <c r="A84" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="B84" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B84" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C84" s="11" t="inlineStr">
         <is>
-          <t>Admin Portal: visibility: Feature flags/Configuration</t>
-        </is>
-      </c>
-      <c r="D84" s="11" t="inlineStr"/>
+          <t>Admin Portal: visibility - System Health</t>
+        </is>
+      </c>
+      <c r="D84" s="11" t="inlineStr">
+        <is>
+          <t>Live GET /healthz against core-api/realtime-gateway/worker</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="B85" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B85" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C85" s="11" t="inlineStr">
         <is>
-          <t>Admin Portal: visibility: Moderation/Audit</t>
+          <t>Admin Portal: visibility - Billing, AI Gateway usage (bonus, not roadmap-named)</t>
         </is>
       </c>
       <c r="D85" s="11" t="inlineStr"/>
@@ -3093,10 +3126,14 @@
       </c>
       <c r="C86" s="11" t="inlineStr">
         <is>
-          <t>Admin Portal: visibility: System health/Deployments</t>
-        </is>
-      </c>
-      <c r="D86" s="11" t="inlineStr"/>
+          <t>Admin Portal: visibility - Sessions/Devices, Tenants, Relationships, Messages, Notifications, Files</t>
+        </is>
+      </c>
+      <c r="D86" s="11" t="inlineStr">
+        <is>
+          <t>Deferred - each backing module only exposes a listMine-style self-scoped endpoint, not an admin-wide one; honest ComingSoon reasoning shown per area instead of fake rows</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="9" t="n">
@@ -3109,10 +3146,14 @@
       </c>
       <c r="C87" s="11" t="inlineStr">
         <is>
-          <t>Admin Portal: must go through service APIs, never direct DB queries</t>
-        </is>
-      </c>
-      <c r="D87" s="11" t="inlineStr"/>
+          <t>Admin Portal: visibility - Deployments</t>
+        </is>
+      </c>
+      <c r="D87" s="11" t="inlineStr">
+        <is>
+          <t>Deferred to Phase 29 - nothing in the platform tracks deployments as data yet</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="9" t="n">
@@ -4721,7 +4762,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E143"/>
+  <dimension ref="A1:E147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5066,174 +5107,182 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>/v1/users/me/devices</t>
+          <t>/v1/users</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>devices</t>
+          <t>users</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>Authenticated (self)</t>
-        </is>
-      </c>
-      <c r="E14" s="11" t="inlineStr"/>
+          <t>platform.admin</t>
+        </is>
+      </c>
+      <c r="E14" s="11" t="inlineStr">
+        <is>
+          <t>Phase 25: cursor-paginated admin-wide listing, new to close a real Admin Portal gap</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>/v1/users/me/devices</t>
+          <t>/v1/authz/roles</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>devices</t>
+          <t>authz</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>Authenticated (self)</t>
+          <t>Self or platform.admin</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>register/upsert</t>
+          <t>Phase 25: authz's first-ever HTTP surface</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>/v1/users/me/devices/{id}</t>
+          <t>/v1/authz/roles</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>devices</t>
+          <t>authz</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>Authenticated (self)</t>
+          <t>platform.admin</t>
         </is>
       </c>
       <c r="E16" s="11" t="inlineStr">
         <is>
-          <t>soft-revoke</t>
+          <t>assign a role to a user</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>/v1/tenants</t>
+          <t>/v1/authz/roles/revoke</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>tenants</t>
+          <t>authz</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>Authenticated</t>
+          <t>platform.admin</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>scoped to caller's own tenants</t>
+          <t>revoke a role from a user</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>/v1/tenants</t>
+          <t>/v1/users/me/devices</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>tenants</t>
+          <t>devices</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
         <is>
-          <t>Authenticated</t>
-        </is>
-      </c>
-      <c r="E18" s="11" t="inlineStr">
-        <is>
-          <t>creator becomes owner</t>
-        </is>
-      </c>
+          <t>Authenticated (self)</t>
+        </is>
+      </c>
+      <c r="E18" s="11" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>/v1/tenants/{id}</t>
+          <t>/v1/users/me/devices</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>tenants</t>
+          <t>devices</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>Member</t>
-        </is>
-      </c>
-      <c r="E19" s="11" t="inlineStr"/>
+          <t>Authenticated (self)</t>
+        </is>
+      </c>
+      <c r="E19" s="11" t="inlineStr">
+        <is>
+          <t>register/upsert</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>/v1/tenants/{id}</t>
+          <t>/v1/users/me/devices/{id}</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>tenants</t>
+          <t>devices</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
         <is>
-          <t>Owner or admin</t>
-        </is>
-      </c>
-      <c r="E20" s="11" t="inlineStr"/>
+          <t>Authenticated (self)</t>
+        </is>
+      </c>
+      <c r="E20" s="11" t="inlineStr">
+        <is>
+          <t>soft-revoke</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
@@ -5243,7 +5292,7 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>/v1/tenants/{id}/members</t>
+          <t>/v1/tenants</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
@@ -5253,10 +5302,14 @@
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>Member</t>
-        </is>
-      </c>
-      <c r="E21" s="11" t="inlineStr"/>
+          <t>Authenticated</t>
+        </is>
+      </c>
+      <c r="E21" s="11" t="inlineStr">
+        <is>
+          <t>scoped to caller's own tenants</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
@@ -5266,7 +5319,7 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>/v1/tenants/{id}/members</t>
+          <t>/v1/tenants</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
@@ -5276,20 +5329,24 @@
       </c>
       <c r="D22" s="11" t="inlineStr">
         <is>
-          <t>Owner or admin</t>
-        </is>
-      </c>
-      <c r="E22" s="11" t="inlineStr"/>
+          <t>Authenticated</t>
+        </is>
+      </c>
+      <c r="E22" s="11" t="inlineStr">
+        <is>
+          <t>creator becomes owner</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>/v1/tenants/{id}/members/{userId}</t>
+          <t>/v1/tenants/{id}</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
@@ -5299,7 +5356,7 @@
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>Owner/admin, or self (leave)</t>
+          <t>Member</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr"/>
@@ -5307,22 +5364,22 @@
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>/v1/relationships</t>
+          <t>/v1/tenants/{id}</t>
         </is>
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>relationships</t>
+          <t>tenants</t>
         </is>
       </c>
       <c r="D24" s="11" t="inlineStr">
         <is>
-          <t>Participant</t>
+          <t>Owner or admin</t>
         </is>
       </c>
       <c r="E24" s="11" t="inlineStr"/>
@@ -5335,17 +5392,17 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>/v1/relationships/{id}</t>
+          <t>/v1/tenants/{id}/members</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>relationships</t>
+          <t>tenants</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>Participant</t>
+          <t>Member</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr"/>
@@ -5358,44 +5415,40 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>/v1/relationships</t>
+          <t>/v1/tenants/{id}/members</t>
         </is>
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>relationships</t>
+          <t>tenants</t>
         </is>
       </c>
       <c r="D26" s="11" t="inlineStr">
         <is>
-          <t>Authenticated</t>
-        </is>
-      </c>
-      <c r="E26" s="11" t="inlineStr">
-        <is>
-          <t>request</t>
-        </is>
-      </c>
+          <t>Owner or admin</t>
+        </is>
+      </c>
+      <c r="E26" s="11" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>/v1/relationships/block</t>
+          <t>/v1/tenants/{id}/members/{userId}</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>relationships</t>
+          <t>tenants</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>Authenticated</t>
+          <t>Owner/admin, or self (leave)</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr"/>
@@ -5403,12 +5456,12 @@
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>/v1/relationships/{id}/accept</t>
+          <t>/v1/relationships</t>
         </is>
       </c>
       <c r="C28" s="11" t="inlineStr">
@@ -5418,7 +5471,7 @@
       </c>
       <c r="D28" s="11" t="inlineStr">
         <is>
-          <t>Target only</t>
+          <t>Participant</t>
         </is>
       </c>
       <c r="E28" s="11" t="inlineStr"/>
@@ -5426,12 +5479,12 @@
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>/v1/relationships/{id}/decline</t>
+          <t>/v1/relationships/{id}</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
@@ -5441,7 +5494,7 @@
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>Target only</t>
+          <t>Participant</t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr"/>
@@ -5449,12 +5502,12 @@
     <row r="30">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>/v1/relationships/{id}</t>
+          <t>/v1/relationships</t>
         </is>
       </c>
       <c r="C30" s="11" t="inlineStr">
@@ -5464,34 +5517,34 @@
       </c>
       <c r="D30" s="11" t="inlineStr">
         <is>
-          <t>Participant</t>
+          <t>Authenticated</t>
         </is>
       </c>
       <c r="E30" s="11" t="inlineStr">
         <is>
-          <t>remove/unfriend</t>
+          <t>request</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>/v1/groups</t>
+          <t>/v1/relationships/block</t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>groups</t>
+          <t>relationships</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>Member</t>
+          <t>Authenticated</t>
         </is>
       </c>
       <c r="E31" s="11" t="inlineStr"/>
@@ -5504,44 +5557,40 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>/v1/groups</t>
+          <t>/v1/relationships/{id}/accept</t>
         </is>
       </c>
       <c r="C32" s="11" t="inlineStr">
         <is>
-          <t>groups</t>
+          <t>relationships</t>
         </is>
       </c>
       <c r="D32" s="11" t="inlineStr">
         <is>
-          <t>Authenticated</t>
-        </is>
-      </c>
-      <c r="E32" s="11" t="inlineStr">
-        <is>
-          <t>creator becomes manager</t>
-        </is>
-      </c>
+          <t>Target only</t>
+        </is>
+      </c>
+      <c r="E32" s="11" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="11" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>/v1/groups/{id}</t>
+          <t>/v1/relationships/{id}/decline</t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>groups</t>
+          <t>relationships</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>Member</t>
+          <t>Target only</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr"/>
@@ -5549,25 +5598,29 @@
     <row r="34">
       <c r="A34" s="11" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>/v1/groups/{id}</t>
+          <t>/v1/relationships/{id}</t>
         </is>
       </c>
       <c r="C34" s="11" t="inlineStr">
         <is>
-          <t>groups</t>
+          <t>relationships</t>
         </is>
       </c>
       <c r="D34" s="11" t="inlineStr">
         <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E34" s="11" t="inlineStr"/>
+          <t>Participant</t>
+        </is>
+      </c>
+      <c r="E34" s="11" t="inlineStr">
+        <is>
+          <t>remove/unfriend</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="11" t="inlineStr">
@@ -5577,7 +5630,7 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>/v1/groups/{id}/members</t>
+          <t>/v1/groups</t>
         </is>
       </c>
       <c r="C35" s="11" t="inlineStr">
@@ -5600,7 +5653,7 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>/v1/groups/{id}/members</t>
+          <t>/v1/groups</t>
         </is>
       </c>
       <c r="C36" s="11" t="inlineStr">
@@ -5610,20 +5663,24 @@
       </c>
       <c r="D36" s="11" t="inlineStr">
         <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E36" s="11" t="inlineStr"/>
+          <t>Authenticated</t>
+        </is>
+      </c>
+      <c r="E36" s="11" t="inlineStr">
+        <is>
+          <t>creator becomes manager</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="11" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>/v1/groups/{id}/members/{userId}</t>
+          <t>/v1/groups/{id}</t>
         </is>
       </c>
       <c r="C37" s="11" t="inlineStr">
@@ -5633,24 +5690,20 @@
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E37" s="11" t="inlineStr">
-        <is>
-          <t>promote/demote IsManager</t>
-        </is>
-      </c>
+          <t>Member</t>
+        </is>
+      </c>
+      <c r="E37" s="11" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="11" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>/v1/groups/{id}/members/{userId}</t>
+          <t>/v1/groups/{id}</t>
         </is>
       </c>
       <c r="C38" s="11" t="inlineStr">
@@ -5660,7 +5713,7 @@
       </c>
       <c r="D38" s="11" t="inlineStr">
         <is>
-          <t>Manager, or self (leave)</t>
+          <t>Manager</t>
         </is>
       </c>
       <c r="E38" s="11" t="inlineStr"/>
@@ -5668,49 +5721,45 @@
     <row r="39">
       <c r="A39" s="11" t="inlineStr">
         <is>
-          <t>WS</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>/ws (realtime-gateway)</t>
+          <t>/v1/groups/{id}/members</t>
         </is>
       </c>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>realtime-gateway</t>
+          <t>groups</t>
         </is>
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>Bearer token at handshake</t>
-        </is>
-      </c>
-      <c r="E39" s="11" t="inlineStr">
-        <is>
-          <t>subscribe/publish/broadcast/direct message</t>
-        </is>
-      </c>
+          <t>Member</t>
+        </is>
+      </c>
+      <c r="E39" s="11" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="11" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>/v1/conversations</t>
+          <t>/v1/groups/{id}/members</t>
         </is>
       </c>
       <c r="C40" s="11" t="inlineStr">
         <is>
-          <t>messaging</t>
+          <t>groups</t>
         </is>
       </c>
       <c r="D40" s="11" t="inlineStr">
         <is>
-          <t>Member</t>
+          <t>Manager</t>
         </is>
       </c>
       <c r="E40" s="11" t="inlineStr"/>
@@ -5718,49 +5767,49 @@
     <row r="41">
       <c r="A41" s="11" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>/v1/conversations</t>
+          <t>/v1/groups/{id}/members/{userId}</t>
         </is>
       </c>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>messaging</t>
+          <t>groups</t>
         </is>
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t>Authenticated</t>
+          <t>Manager</t>
         </is>
       </c>
       <c r="E41" s="11" t="inlineStr">
         <is>
-          <t>direct convos dedup automatically</t>
+          <t>promote/demote IsManager</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="11" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>/v1/conversations/{id}</t>
+          <t>/v1/groups/{id}/members/{userId}</t>
         </is>
       </c>
       <c r="C42" s="11" t="inlineStr">
         <is>
-          <t>messaging</t>
+          <t>groups</t>
         </is>
       </c>
       <c r="D42" s="11" t="inlineStr">
         <is>
-          <t>Member</t>
+          <t>Manager, or self (leave)</t>
         </is>
       </c>
       <c r="E42" s="11" t="inlineStr"/>
@@ -5768,35 +5817,39 @@
     <row r="43">
       <c r="A43" s="11" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>WS</t>
         </is>
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>/v1/conversations/{id}/members</t>
+          <t>/ws (realtime-gateway)</t>
         </is>
       </c>
       <c r="C43" s="11" t="inlineStr">
         <is>
-          <t>messaging</t>
+          <t>realtime-gateway</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>Member</t>
-        </is>
-      </c>
-      <c r="E43" s="11" t="inlineStr"/>
+          <t>Bearer token at handshake</t>
+        </is>
+      </c>
+      <c r="E43" s="11" t="inlineStr">
+        <is>
+          <t>subscribe/publish/broadcast/direct message</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="11" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>/v1/conversations/{id}/members</t>
+          <t>/v1/conversations</t>
         </is>
       </c>
       <c r="C44" s="11" t="inlineStr">
@@ -5806,7 +5859,7 @@
       </c>
       <c r="D44" s="11" t="inlineStr">
         <is>
-          <t>Member (group only)</t>
+          <t>Member</t>
         </is>
       </c>
       <c r="E44" s="11" t="inlineStr"/>
@@ -5814,12 +5867,12 @@
     <row r="45">
       <c r="A45" s="11" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>/v1/conversations/{id}/members/{userId}</t>
+          <t>/v1/conversations</t>
         </is>
       </c>
       <c r="C45" s="11" t="inlineStr">
@@ -5829,10 +5882,14 @@
       </c>
       <c r="D45" s="11" t="inlineStr">
         <is>
-          <t>Self only (leave)</t>
-        </is>
-      </c>
-      <c r="E45" s="11" t="inlineStr"/>
+          <t>Authenticated</t>
+        </is>
+      </c>
+      <c r="E45" s="11" t="inlineStr">
+        <is>
+          <t>direct convos dedup automatically</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="11" t="inlineStr">
@@ -5842,7 +5899,7 @@
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>/v1/conversations/{id}/messages</t>
+          <t>/v1/conversations/{id}</t>
         </is>
       </c>
       <c r="C46" s="11" t="inlineStr">
@@ -5855,21 +5912,17 @@
           <t>Member</t>
         </is>
       </c>
-      <c r="E46" s="11" t="inlineStr">
-        <is>
-          <t>cursor pagination</t>
-        </is>
-      </c>
+      <c r="E46" s="11" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="11" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>/v1/conversations/{id}/messages</t>
+          <t>/v1/conversations/{id}/members</t>
         </is>
       </c>
       <c r="C47" s="11" t="inlineStr">
@@ -5882,21 +5935,17 @@
           <t>Member</t>
         </is>
       </c>
-      <c r="E47" s="11" t="inlineStr">
-        <is>
-          <t>pushes over realtime too</t>
-        </is>
-      </c>
+      <c r="E47" s="11" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="11" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>/v1/conversations/{id}/messages/{messageId}</t>
+          <t>/v1/conversations/{id}/members</t>
         </is>
       </c>
       <c r="C48" s="11" t="inlineStr">
@@ -5906,7 +5955,7 @@
       </c>
       <c r="D48" s="11" t="inlineStr">
         <is>
-          <t>Member</t>
+          <t>Member (group only)</t>
         </is>
       </c>
       <c r="E48" s="11" t="inlineStr"/>
@@ -5914,12 +5963,12 @@
     <row r="49">
       <c r="A49" s="11" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>/v1/conversations/{id}/messages/{messageId}/delivered</t>
+          <t>/v1/conversations/{id}/members/{userId}</t>
         </is>
       </c>
       <c r="C49" s="11" t="inlineStr">
@@ -5929,14 +5978,10 @@
       </c>
       <c r="D49" s="11" t="inlineStr">
         <is>
-          <t>Member</t>
-        </is>
-      </c>
-      <c r="E49" s="11" t="inlineStr">
-        <is>
-          <t>idempotent ack</t>
-        </is>
-      </c>
+          <t>Self only (leave)</t>
+        </is>
+      </c>
+      <c r="E49" s="11" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="11" t="inlineStr">
@@ -5946,7 +5991,7 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>/v1/conversations/{id}/messages/{messageId}/reactions</t>
+          <t>/v1/conversations/{id}/messages</t>
         </is>
       </c>
       <c r="C50" s="11" t="inlineStr">
@@ -5959,7 +6004,11 @@
           <t>Member</t>
         </is>
       </c>
-      <c r="E50" s="11" t="inlineStr"/>
+      <c r="E50" s="11" t="inlineStr">
+        <is>
+          <t>cursor pagination</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="11" t="inlineStr">
@@ -5969,7 +6018,7 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>/v1/conversations/{id}/messages/{messageId}/reactions</t>
+          <t>/v1/conversations/{id}/messages</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
@@ -5984,19 +6033,19 @@
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>idempotent add</t>
+          <t>pushes over realtime too</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="11" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>/v1/conversations/{id}/messages/{messageId}/reactions/{type}</t>
+          <t>/v1/conversations/{id}/messages/{messageId}</t>
         </is>
       </c>
       <c r="C52" s="11" t="inlineStr">
@@ -6014,12 +6063,12 @@
     <row r="53">
       <c r="A53" s="11" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>/v1/conversations/{id}/read/{userId}</t>
+          <t>/v1/conversations/{id}/messages/{messageId}/delivered</t>
         </is>
       </c>
       <c r="C53" s="11" t="inlineStr">
@@ -6032,17 +6081,21 @@
           <t>Member</t>
         </is>
       </c>
-      <c r="E53" s="11" t="inlineStr"/>
+      <c r="E53" s="11" t="inlineStr">
+        <is>
+          <t>idempotent ack</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="11" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t>/v1/conversations/{id}/read</t>
+          <t>/v1/conversations/{id}/messages/{messageId}/reactions</t>
         </is>
       </c>
       <c r="C54" s="11" t="inlineStr">
@@ -6060,52 +6113,52 @@
     <row r="55">
       <c r="A55" s="11" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>/v1/notifications</t>
+          <t>/v1/conversations/{id}/messages/{messageId}/reactions</t>
         </is>
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t>notifications</t>
+          <t>messaging</t>
         </is>
       </c>
       <c r="D55" s="11" t="inlineStr">
         <is>
-          <t>Authenticated (self)</t>
-        </is>
-      </c>
-      <c r="E55" s="11" t="inlineStr"/>
+          <t>Member</t>
+        </is>
+      </c>
+      <c r="E55" s="11" t="inlineStr">
+        <is>
+          <t>idempotent add</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="11" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t>/v1/notifications</t>
+          <t>/v1/conversations/{id}/messages/{messageId}/reactions/{type}</t>
         </is>
       </c>
       <c r="C56" s="11" t="inlineStr">
         <is>
-          <t>notifications</t>
+          <t>messaging</t>
         </is>
       </c>
       <c r="D56" s="11" t="inlineStr">
         <is>
-          <t>Self or platform.admin</t>
-        </is>
-      </c>
-      <c r="E56" s="11" t="inlineStr">
-        <is>
-          <t>send</t>
-        </is>
-      </c>
+          <t>Member</t>
+        </is>
+      </c>
+      <c r="E56" s="11" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="11" t="inlineStr">
@@ -6115,17 +6168,17 @@
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>/v1/notifications/{id}</t>
+          <t>/v1/conversations/{id}/read/{userId}</t>
         </is>
       </c>
       <c r="C57" s="11" t="inlineStr">
         <is>
-          <t>notifications</t>
+          <t>messaging</t>
         </is>
       </c>
       <c r="D57" s="11" t="inlineStr">
         <is>
-          <t>Self or platform.admin</t>
+          <t>Member</t>
         </is>
       </c>
       <c r="E57" s="11" t="inlineStr"/>
@@ -6133,22 +6186,22 @@
     <row r="58">
       <c r="A58" s="11" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t>/v1/notifications/{id}/deliveries</t>
+          <t>/v1/conversations/{id}/read</t>
         </is>
       </c>
       <c r="C58" s="11" t="inlineStr">
         <is>
-          <t>notifications</t>
+          <t>messaging</t>
         </is>
       </c>
       <c r="D58" s="11" t="inlineStr">
         <is>
-          <t>Self or platform.admin</t>
+          <t>Member</t>
         </is>
       </c>
       <c r="E58" s="11" t="inlineStr"/>
@@ -6156,12 +6209,12 @@
     <row r="59">
       <c r="A59" s="11" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>/v1/notifications/{id}/deliveries/{deliveryId}/retry</t>
+          <t>/v1/notifications</t>
         </is>
       </c>
       <c r="C59" s="11" t="inlineStr">
@@ -6171,7 +6224,7 @@
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>Self or platform.admin</t>
+          <t>Authenticated (self)</t>
         </is>
       </c>
       <c r="E59" s="11" t="inlineStr"/>
@@ -6179,12 +6232,12 @@
     <row r="60">
       <c r="A60" s="11" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t>/v1/notification-preferences</t>
+          <t>/v1/notifications</t>
         </is>
       </c>
       <c r="C60" s="11" t="inlineStr">
@@ -6194,20 +6247,24 @@
       </c>
       <c r="D60" s="11" t="inlineStr">
         <is>
-          <t>Authenticated (self)</t>
-        </is>
-      </c>
-      <c r="E60" s="11" t="inlineStr"/>
+          <t>Self or platform.admin</t>
+        </is>
+      </c>
+      <c r="E60" s="11" t="inlineStr">
+        <is>
+          <t>send</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="11" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>/v1/notification-preferences</t>
+          <t>/v1/notifications/{id}</t>
         </is>
       </c>
       <c r="C61" s="11" t="inlineStr">
@@ -6217,14 +6274,10 @@
       </c>
       <c r="D61" s="11" t="inlineStr">
         <is>
-          <t>Authenticated (self)</t>
-        </is>
-      </c>
-      <c r="E61" s="11" t="inlineStr">
-        <is>
-          <t>category opt-outs</t>
-        </is>
-      </c>
+          <t>Self or platform.admin</t>
+        </is>
+      </c>
+      <c r="E61" s="11" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="11" t="inlineStr">
@@ -6234,7 +6287,7 @@
       </c>
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t>/v1/notification-preferences/quiet-hours</t>
+          <t>/v1/notifications/{id}/deliveries</t>
         </is>
       </c>
       <c r="C62" s="11" t="inlineStr">
@@ -6244,7 +6297,7 @@
       </c>
       <c r="D62" s="11" t="inlineStr">
         <is>
-          <t>Authenticated (self)</t>
+          <t>Self or platform.admin</t>
         </is>
       </c>
       <c r="E62" s="11" t="inlineStr"/>
@@ -6252,12 +6305,12 @@
     <row r="63">
       <c r="A63" s="11" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>/v1/notification-preferences/quiet-hours</t>
+          <t>/v1/notifications/{id}/deliveries/{deliveryId}/retry</t>
         </is>
       </c>
       <c r="C63" s="11" t="inlineStr">
@@ -6267,7 +6320,7 @@
       </c>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t>Authenticated (self)</t>
+          <t>Self or platform.admin</t>
         </is>
       </c>
       <c r="E63" s="11" t="inlineStr"/>
@@ -6275,12 +6328,12 @@
     <row r="64">
       <c r="A64" s="11" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t>/v1/notification-templates</t>
+          <t>/v1/notification-preferences</t>
         </is>
       </c>
       <c r="C64" s="11" t="inlineStr">
@@ -6290,7 +6343,7 @@
       </c>
       <c r="D64" s="11" t="inlineStr">
         <is>
-          <t>platform.admin</t>
+          <t>Authenticated (self)</t>
         </is>
       </c>
       <c r="E64" s="11" t="inlineStr"/>
@@ -6298,12 +6351,12 @@
     <row r="65">
       <c r="A65" s="11" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>/v1/notification-templates/{appId}/{key}</t>
+          <t>/v1/notification-preferences</t>
         </is>
       </c>
       <c r="C65" s="11" t="inlineStr">
@@ -6313,20 +6366,24 @@
       </c>
       <c r="D65" s="11" t="inlineStr">
         <is>
-          <t>platform.admin</t>
-        </is>
-      </c>
-      <c r="E65" s="11" t="inlineStr"/>
+          <t>Authenticated (self)</t>
+        </is>
+      </c>
+      <c r="E65" s="11" t="inlineStr">
+        <is>
+          <t>category opt-outs</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="11" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B66" s="11" t="inlineStr">
         <is>
-          <t>/v1/notification-templates/{appId}/{key}</t>
+          <t>/v1/notification-preferences/quiet-hours</t>
         </is>
       </c>
       <c r="C66" s="11" t="inlineStr">
@@ -6336,7 +6393,7 @@
       </c>
       <c r="D66" s="11" t="inlineStr">
         <is>
-          <t>platform.admin</t>
+          <t>Authenticated (self)</t>
         </is>
       </c>
       <c r="E66" s="11" t="inlineStr"/>
@@ -6344,22 +6401,22 @@
     <row r="67">
       <c r="A67" s="11" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>/v1/files</t>
+          <t>/v1/notification-preferences/quiet-hours</t>
         </is>
       </c>
       <c r="C67" s="11" t="inlineStr">
         <is>
-          <t>files</t>
+          <t>notifications</t>
         </is>
       </c>
       <c r="D67" s="11" t="inlineStr">
         <is>
-          <t>Owner or platform.admin</t>
+          <t>Authenticated (self)</t>
         </is>
       </c>
       <c r="E67" s="11" t="inlineStr"/>
@@ -6372,71 +6429,63 @@
       </c>
       <c r="B68" s="11" t="inlineStr">
         <is>
-          <t>/v1/files</t>
+          <t>/v1/notification-templates</t>
         </is>
       </c>
       <c r="C68" s="11" t="inlineStr">
         <is>
-          <t>files</t>
+          <t>notifications</t>
         </is>
       </c>
       <c r="D68" s="11" t="inlineStr">
         <is>
-          <t>Authenticated</t>
-        </is>
-      </c>
-      <c r="E68" s="11" t="inlineStr">
-        <is>
-          <t>requests a presigned upload URL</t>
-        </is>
-      </c>
+          <t>platform.admin</t>
+        </is>
+      </c>
+      <c r="E68" s="11" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="11" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>/v1/files/{id}/confirm</t>
+          <t>/v1/notification-templates/{appId}/{key}</t>
         </is>
       </c>
       <c r="C69" s="11" t="inlineStr">
         <is>
-          <t>files</t>
+          <t>notifications</t>
         </is>
       </c>
       <c r="D69" s="11" t="inlineStr">
         <is>
-          <t>Owner</t>
-        </is>
-      </c>
-      <c r="E69" s="11" t="inlineStr">
-        <is>
-          <t>verifies real size + MD5 checksum</t>
-        </is>
-      </c>
+          <t>platform.admin</t>
+        </is>
+      </c>
+      <c r="E69" s="11" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="11" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t>/v1/files/{id}</t>
+          <t>/v1/notification-templates/{appId}/{key}</t>
         </is>
       </c>
       <c r="C70" s="11" t="inlineStr">
         <is>
-          <t>files</t>
+          <t>notifications</t>
         </is>
       </c>
       <c r="D70" s="11" t="inlineStr">
         <is>
-          <t>Owner, or public if visibility allows</t>
+          <t>platform.admin</t>
         </is>
       </c>
       <c r="E70" s="11" t="inlineStr"/>
@@ -6449,7 +6498,7 @@
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>/v1/files/{id}/download</t>
+          <t>/v1/files</t>
         </is>
       </c>
       <c r="C71" s="11" t="inlineStr">
@@ -6459,24 +6508,20 @@
       </c>
       <c r="D71" s="11" t="inlineStr">
         <is>
-          <t>Owner, or public if visibility allows</t>
-        </is>
-      </c>
-      <c r="E71" s="11" t="inlineStr">
-        <is>
-          <t>presigned GET</t>
-        </is>
-      </c>
+          <t>Owner or platform.admin</t>
+        </is>
+      </c>
+      <c r="E71" s="11" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="11" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B72" s="11" t="inlineStr">
         <is>
-          <t>/v1/files/{id}</t>
+          <t>/v1/files</t>
         </is>
       </c>
       <c r="C72" s="11" t="inlineStr">
@@ -6486,12 +6531,12 @@
       </c>
       <c r="D72" s="11" t="inlineStr">
         <is>
-          <t>Owner or platform.admin</t>
+          <t>Authenticated</t>
         </is>
       </c>
       <c r="E72" s="11" t="inlineStr">
         <is>
-          <t>also deletes from storage</t>
+          <t>requests a presigned upload URL</t>
         </is>
       </c>
     </row>
@@ -6503,7 +6548,7 @@
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>/v1/files/purge-expired</t>
+          <t>/v1/files/{id}/confirm</t>
         </is>
       </c>
       <c r="C73" s="11" t="inlineStr">
@@ -6513,10 +6558,14 @@
       </c>
       <c r="D73" s="11" t="inlineStr">
         <is>
-          <t>platform.admin</t>
-        </is>
-      </c>
-      <c r="E73" s="11" t="inlineStr"/>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="E73" s="11" t="inlineStr">
+        <is>
+          <t>verifies real size + MD5 checksum</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="11" t="inlineStr">
@@ -6526,17 +6575,17 @@
       </c>
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t>/v1/search</t>
+          <t>/v1/files/{id}</t>
         </is>
       </c>
       <c r="C74" s="11" t="inlineStr">
         <is>
-          <t>search</t>
+          <t>files</t>
         </is>
       </c>
       <c r="D74" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Owner, or public if visibility allows</t>
         </is>
       </c>
       <c r="E74" s="11" t="inlineStr"/>
@@ -6544,27 +6593,27 @@
     <row r="75">
       <c r="A75" s="11" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>/v1/search/index</t>
+          <t>/v1/files/{id}/download</t>
         </is>
       </c>
       <c r="C75" s="11" t="inlineStr">
         <is>
-          <t>search</t>
+          <t>files</t>
         </is>
       </c>
       <c r="D75" s="11" t="inlineStr">
         <is>
-          <t>platform.admin</t>
+          <t>Owner, or public if visibility allows</t>
         </is>
       </c>
       <c r="E75" s="11" t="inlineStr">
         <is>
-          <t>manual index (normally event-driven)</t>
+          <t>presigned GET</t>
         </is>
       </c>
     </row>
@@ -6576,40 +6625,44 @@
       </c>
       <c r="B76" s="11" t="inlineStr">
         <is>
-          <t>/v1/search/index/{type}/{id}</t>
+          <t>/v1/files/{id}</t>
         </is>
       </c>
       <c r="C76" s="11" t="inlineStr">
         <is>
-          <t>search</t>
+          <t>files</t>
         </is>
       </c>
       <c r="D76" s="11" t="inlineStr">
         <is>
-          <t>platform.admin</t>
-        </is>
-      </c>
-      <c r="E76" s="11" t="inlineStr"/>
+          <t>Owner or platform.admin</t>
+        </is>
+      </c>
+      <c r="E76" s="11" t="inlineStr">
+        <is>
+          <t>also deletes from storage</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="11" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t>/v1/jobs</t>
+          <t>/v1/files/purge-expired</t>
         </is>
       </c>
       <c r="C77" s="11" t="inlineStr">
         <is>
-          <t>jobs</t>
+          <t>files</t>
         </is>
       </c>
       <c r="D77" s="11" t="inlineStr">
         <is>
-          <t>Owner or platform.admin</t>
+          <t>platform.admin</t>
         </is>
       </c>
       <c r="E77" s="11" t="inlineStr"/>
@@ -6617,72 +6670,72 @@
     <row r="78">
       <c r="A78" s="11" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B78" s="11" t="inlineStr">
         <is>
-          <t>/v1/jobs</t>
+          <t>/v1/search</t>
         </is>
       </c>
       <c r="C78" s="11" t="inlineStr">
         <is>
-          <t>jobs</t>
+          <t>search</t>
         </is>
       </c>
       <c r="D78" s="11" t="inlineStr">
         <is>
-          <t>Authenticated</t>
-        </is>
-      </c>
-      <c r="E78" s="11" t="inlineStr">
-        <is>
-          <t>enqueue only - never runs inline</t>
-        </is>
-      </c>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E78" s="11" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="11" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>/v1/jobs/{id}</t>
+          <t>/v1/search/index</t>
         </is>
       </c>
       <c r="C79" s="11" t="inlineStr">
         <is>
-          <t>jobs</t>
+          <t>search</t>
         </is>
       </c>
       <c r="D79" s="11" t="inlineStr">
         <is>
-          <t>Owner or platform.admin</t>
-        </is>
-      </c>
-      <c r="E79" s="11" t="inlineStr"/>
+          <t>platform.admin</t>
+        </is>
+      </c>
+      <c r="E79" s="11" t="inlineStr">
+        <is>
+          <t>manual index (normally event-driven)</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="11" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B80" s="11" t="inlineStr">
         <is>
-          <t>/v1/jobs/{id}/attempts</t>
+          <t>/v1/search/index/{type}/{id}</t>
         </is>
       </c>
       <c r="C80" s="11" t="inlineStr">
         <is>
-          <t>jobs</t>
+          <t>search</t>
         </is>
       </c>
       <c r="D80" s="11" t="inlineStr">
         <is>
-          <t>Owner or platform.admin</t>
+          <t>platform.admin</t>
         </is>
       </c>
       <c r="E80" s="11" t="inlineStr"/>
@@ -6690,71 +6743,67 @@
     <row r="81">
       <c r="A81" s="11" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t>/v1/workflows</t>
+          <t>/v1/jobs</t>
         </is>
       </c>
       <c r="C81" s="11" t="inlineStr">
         <is>
-          <t>workflows</t>
+          <t>jobs</t>
         </is>
       </c>
       <c r="D81" s="11" t="inlineStr">
         <is>
-          <t>Authenticated</t>
-        </is>
-      </c>
-      <c r="E81" s="11" t="inlineStr">
-        <is>
-          <t>starts a Temporal workflow</t>
-        </is>
-      </c>
+          <t>Owner or platform.admin</t>
+        </is>
+      </c>
+      <c r="E81" s="11" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="11" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B82" s="11" t="inlineStr">
         <is>
-          <t>/v1/workflows/{id}</t>
+          <t>/v1/jobs</t>
         </is>
       </c>
       <c r="C82" s="11" t="inlineStr">
         <is>
-          <t>workflows</t>
+          <t>jobs</t>
         </is>
       </c>
       <c r="D82" s="11" t="inlineStr">
         <is>
-          <t>Owner or platform.admin</t>
+          <t>Authenticated</t>
         </is>
       </c>
       <c r="E82" s="11" t="inlineStr">
         <is>
-          <t>live-queried from Temporal</t>
+          <t>enqueue only - never runs inline</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="11" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t>/v1/workflows/{id}/signal</t>
+          <t>/v1/jobs/{id}</t>
         </is>
       </c>
       <c r="C83" s="11" t="inlineStr">
         <is>
-          <t>workflows</t>
+          <t>jobs</t>
         </is>
       </c>
       <c r="D83" s="11" t="inlineStr">
@@ -6772,17 +6821,17 @@
       </c>
       <c r="B84" s="11" t="inlineStr">
         <is>
-          <t>/v1/features</t>
+          <t>/v1/jobs/{id}/attempts</t>
         </is>
       </c>
       <c r="C84" s="11" t="inlineStr">
         <is>
-          <t>features</t>
+          <t>jobs</t>
         </is>
       </c>
       <c r="D84" s="11" t="inlineStr">
         <is>
-          <t>platform.admin</t>
+          <t>Owner or platform.admin</t>
         </is>
       </c>
       <c r="E84" s="11" t="inlineStr"/>
@@ -6795,20 +6844,24 @@
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>/v1/features</t>
+          <t>/v1/workflows</t>
         </is>
       </c>
       <c r="C85" s="11" t="inlineStr">
         <is>
-          <t>features</t>
+          <t>workflows</t>
         </is>
       </c>
       <c r="D85" s="11" t="inlineStr">
         <is>
-          <t>platform.admin</t>
-        </is>
-      </c>
-      <c r="E85" s="11" t="inlineStr"/>
+          <t>Authenticated</t>
+        </is>
+      </c>
+      <c r="E85" s="11" t="inlineStr">
+        <is>
+          <t>starts a Temporal workflow</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="11" t="inlineStr">
@@ -6818,57 +6871,57 @@
       </c>
       <c r="B86" s="11" t="inlineStr">
         <is>
-          <t>/v1/features/{appId}/{key}</t>
+          <t>/v1/workflows/{id}</t>
         </is>
       </c>
       <c r="C86" s="11" t="inlineStr">
         <is>
-          <t>features</t>
+          <t>workflows</t>
         </is>
       </c>
       <c r="D86" s="11" t="inlineStr">
         <is>
-          <t>platform.admin</t>
-        </is>
-      </c>
-      <c r="E86" s="11" t="inlineStr"/>
+          <t>Owner or platform.admin</t>
+        </is>
+      </c>
+      <c r="E86" s="11" t="inlineStr">
+        <is>
+          <t>live-queried from Temporal</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="11" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>/v1/features/{appId}/{key}</t>
+          <t>/v1/workflows/{id}/signal</t>
         </is>
       </c>
       <c r="C87" s="11" t="inlineStr">
         <is>
-          <t>features</t>
+          <t>workflows</t>
         </is>
       </c>
       <c r="D87" s="11" t="inlineStr">
         <is>
-          <t>platform.admin</t>
-        </is>
-      </c>
-      <c r="E87" s="11" t="inlineStr">
-        <is>
-          <t>kill switch etc</t>
-        </is>
-      </c>
+          <t>Owner or platform.admin</t>
+        </is>
+      </c>
+      <c r="E87" s="11" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="11" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t>/v1/features/{appId}/{key}/evaluate</t>
+          <t>/v1/features</t>
         </is>
       </c>
       <c r="C88" s="11" t="inlineStr">
@@ -6878,24 +6931,20 @@
       </c>
       <c r="D88" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="E88" s="11" t="inlineStr">
-        <is>
-          <t>isEnabled(feature, context)</t>
-        </is>
-      </c>
+          <t>platform.admin</t>
+        </is>
+      </c>
+      <c r="E88" s="11" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="11" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>/v1/features/{appId}/{key}/rules</t>
+          <t>/v1/features</t>
         </is>
       </c>
       <c r="C89" s="11" t="inlineStr">
@@ -6913,12 +6962,12 @@
     <row r="90">
       <c r="A90" s="11" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B90" s="11" t="inlineStr">
         <is>
-          <t>/v1/features/{appId}/{key}/rules</t>
+          <t>/v1/features/{appId}/{key}</t>
         </is>
       </c>
       <c r="C90" s="11" t="inlineStr">
@@ -6941,7 +6990,7 @@
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>/v1/features/{appId}/{key}/rules/{ruleId}</t>
+          <t>/v1/features/{appId}/{key}</t>
         </is>
       </c>
       <c r="C91" s="11" t="inlineStr">
@@ -6954,17 +7003,21 @@
           <t>platform.admin</t>
         </is>
       </c>
-      <c r="E91" s="11" t="inlineStr"/>
+      <c r="E91" s="11" t="inlineStr">
+        <is>
+          <t>kill switch etc</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="11" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B92" s="11" t="inlineStr">
         <is>
-          <t>/v1/features/{appId}/{key}/rules/{ruleId}</t>
+          <t>/v1/features/{appId}/{key}/evaluate</t>
         </is>
       </c>
       <c r="C92" s="11" t="inlineStr">
@@ -6974,10 +7027,14 @@
       </c>
       <c r="D92" s="11" t="inlineStr">
         <is>
-          <t>platform.admin</t>
-        </is>
-      </c>
-      <c r="E92" s="11" t="inlineStr"/>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E92" s="11" t="inlineStr">
+        <is>
+          <t>isEnabled(feature, context)</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="11" t="inlineStr">
@@ -6987,44 +7044,40 @@
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t>/v1/config</t>
+          <t>/v1/features/{appId}/{key}/rules</t>
         </is>
       </c>
       <c r="C93" s="11" t="inlineStr">
         <is>
-          <t>remoteconfig</t>
+          <t>features</t>
         </is>
       </c>
       <c r="D93" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="E93" s="11" t="inlineStr">
-        <is>
-          <t>list entries</t>
-        </is>
-      </c>
+          <t>platform.admin</t>
+        </is>
+      </c>
+      <c r="E93" s="11" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="11" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B94" s="11" t="inlineStr">
         <is>
-          <t>/v1/config/{appId}/{environment}/{key}</t>
+          <t>/v1/features/{appId}/{key}/rules</t>
         </is>
       </c>
       <c r="C94" s="11" t="inlineStr">
         <is>
-          <t>remoteconfig</t>
+          <t>features</t>
         </is>
       </c>
       <c r="D94" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>platform.admin</t>
         </is>
       </c>
       <c r="E94" s="11" t="inlineStr"/>
@@ -7032,17 +7085,17 @@
     <row r="95">
       <c r="A95" s="11" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>/v1/config/{appId}/{environment}/{key}</t>
+          <t>/v1/features/{appId}/{key}/rules/{ruleId}</t>
         </is>
       </c>
       <c r="C95" s="11" t="inlineStr">
         <is>
-          <t>remoteconfig</t>
+          <t>features</t>
         </is>
       </c>
       <c r="D95" s="11" t="inlineStr">
@@ -7050,11 +7103,7 @@
           <t>platform.admin</t>
         </is>
       </c>
-      <c r="E95" s="11" t="inlineStr">
-        <is>
-          <t>writes an audited Change row</t>
-        </is>
-      </c>
+      <c r="E95" s="11" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="11" t="inlineStr">
@@ -7064,12 +7113,12 @@
       </c>
       <c r="B96" s="11" t="inlineStr">
         <is>
-          <t>/v1/config/{appId}/{environment}/{key}</t>
+          <t>/v1/features/{appId}/{key}/rules/{ruleId}</t>
         </is>
       </c>
       <c r="C96" s="11" t="inlineStr">
         <is>
-          <t>remoteconfig</t>
+          <t>features</t>
         </is>
       </c>
       <c r="D96" s="11" t="inlineStr">
@@ -7087,7 +7136,7 @@
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t>/v1/config/{appId}/{environment}/{key}/history</t>
+          <t>/v1/config</t>
         </is>
       </c>
       <c r="C97" s="11" t="inlineStr">
@@ -7097,30 +7146,34 @@
       </c>
       <c r="D97" s="11" t="inlineStr">
         <is>
-          <t>platform.admin</t>
-        </is>
-      </c>
-      <c r="E97" s="11" t="inlineStr"/>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E97" s="11" t="inlineStr">
+        <is>
+          <t>list entries</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="11" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B98" s="11" t="inlineStr">
         <is>
-          <t>/v1/audit</t>
+          <t>/v1/config/{appId}/{environment}/{key}</t>
         </is>
       </c>
       <c r="C98" s="11" t="inlineStr">
         <is>
-          <t>audit</t>
+          <t>remoteconfig</t>
         </is>
       </c>
       <c r="D98" s="11" t="inlineStr">
         <is>
-          <t>Authenticated (actor forced server-side)</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="E98" s="11" t="inlineStr"/>
@@ -7128,17 +7181,17 @@
     <row r="99">
       <c r="A99" s="11" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t>/v1/audit</t>
+          <t>/v1/config/{appId}/{environment}/{key}</t>
         </is>
       </c>
       <c r="C99" s="11" t="inlineStr">
         <is>
-          <t>audit</t>
+          <t>remoteconfig</t>
         </is>
       </c>
       <c r="D99" s="11" t="inlineStr">
@@ -7146,22 +7199,26 @@
           <t>platform.admin</t>
         </is>
       </c>
-      <c r="E99" s="11" t="inlineStr"/>
+      <c r="E99" s="11" t="inlineStr">
+        <is>
+          <t>writes an audited Change row</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="11" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B100" s="11" t="inlineStr">
         <is>
-          <t>/v1/audit/{id}</t>
+          <t>/v1/config/{appId}/{environment}/{key}</t>
         </is>
       </c>
       <c r="C100" s="11" t="inlineStr">
         <is>
-          <t>audit</t>
+          <t>remoteconfig</t>
         </is>
       </c>
       <c r="D100" s="11" t="inlineStr">
@@ -7174,49 +7231,45 @@
     <row r="101">
       <c r="A101" s="11" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
-          <t>/v1/privacy/consent</t>
+          <t>/v1/config/{appId}/{environment}/{key}/history</t>
         </is>
       </c>
       <c r="C101" s="11" t="inlineStr">
         <is>
-          <t>privacy</t>
+          <t>remoteconfig</t>
         </is>
       </c>
       <c r="D101" s="11" t="inlineStr">
         <is>
-          <t>Authenticated (self)</t>
-        </is>
-      </c>
-      <c r="E101" s="11" t="inlineStr">
-        <is>
-          <t>append-only history</t>
-        </is>
-      </c>
+          <t>platform.admin</t>
+        </is>
+      </c>
+      <c r="E101" s="11" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="11" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B102" s="11" t="inlineStr">
         <is>
-          <t>/v1/privacy/consent</t>
+          <t>/v1/audit</t>
         </is>
       </c>
       <c r="C102" s="11" t="inlineStr">
         <is>
-          <t>privacy</t>
+          <t>audit</t>
         </is>
       </c>
       <c r="D102" s="11" t="inlineStr">
         <is>
-          <t>Authenticated (self)</t>
+          <t>Authenticated (actor forced server-side)</t>
         </is>
       </c>
       <c r="E102" s="11" t="inlineStr"/>
@@ -7229,17 +7282,17 @@
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t>/v1/privacy/preferences</t>
+          <t>/v1/audit</t>
         </is>
       </c>
       <c r="C103" s="11" t="inlineStr">
         <is>
-          <t>privacy</t>
+          <t>audit</t>
         </is>
       </c>
       <c r="D103" s="11" t="inlineStr">
         <is>
-          <t>Authenticated (self)</t>
+          <t>platform.admin</t>
         </is>
       </c>
       <c r="E103" s="11" t="inlineStr"/>
@@ -7247,22 +7300,22 @@
     <row r="104">
       <c r="A104" s="11" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B104" s="11" t="inlineStr">
         <is>
-          <t>/v1/privacy/preferences</t>
+          <t>/v1/audit/{id}</t>
         </is>
       </c>
       <c r="C104" s="11" t="inlineStr">
         <is>
-          <t>privacy</t>
+          <t>audit</t>
         </is>
       </c>
       <c r="D104" s="11" t="inlineStr">
         <is>
-          <t>Authenticated (self)</t>
+          <t>platform.admin</t>
         </is>
       </c>
       <c r="E104" s="11" t="inlineStr"/>
@@ -7275,7 +7328,7 @@
       </c>
       <c r="B105" s="11" t="inlineStr">
         <is>
-          <t>/v1/privacy/retention-policies</t>
+          <t>/v1/privacy/consent</t>
         </is>
       </c>
       <c r="C105" s="11" t="inlineStr">
@@ -7285,10 +7338,14 @@
       </c>
       <c r="D105" s="11" t="inlineStr">
         <is>
-          <t>platform.admin</t>
-        </is>
-      </c>
-      <c r="E105" s="11" t="inlineStr"/>
+          <t>Authenticated (self)</t>
+        </is>
+      </c>
+      <c r="E105" s="11" t="inlineStr">
+        <is>
+          <t>append-only history</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="11" t="inlineStr">
@@ -7298,7 +7355,7 @@
       </c>
       <c r="B106" s="11" t="inlineStr">
         <is>
-          <t>/v1/privacy/retention-policies</t>
+          <t>/v1/privacy/consent</t>
         </is>
       </c>
       <c r="C106" s="11" t="inlineStr">
@@ -7308,7 +7365,7 @@
       </c>
       <c r="D106" s="11" t="inlineStr">
         <is>
-          <t>platform.admin</t>
+          <t>Authenticated (self)</t>
         </is>
       </c>
       <c r="E106" s="11" t="inlineStr"/>
@@ -7316,12 +7373,12 @@
     <row r="107">
       <c r="A107" s="11" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B107" s="11" t="inlineStr">
         <is>
-          <t>/v1/privacy/export</t>
+          <t>/v1/privacy/preferences</t>
         </is>
       </c>
       <c r="C107" s="11" t="inlineStr">
@@ -7334,21 +7391,17 @@
           <t>Authenticated (self)</t>
         </is>
       </c>
-      <c r="E107" s="11" t="inlineStr">
-        <is>
-          <t>starts a Temporal workflow</t>
-        </is>
-      </c>
+      <c r="E107" s="11" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="11" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B108" s="11" t="inlineStr">
         <is>
-          <t>/v1/privacy/export/{id}</t>
+          <t>/v1/privacy/preferences</t>
         </is>
       </c>
       <c r="C108" s="11" t="inlineStr">
@@ -7358,24 +7411,20 @@
       </c>
       <c r="D108" s="11" t="inlineStr">
         <is>
-          <t>Self or platform.admin</t>
-        </is>
-      </c>
-      <c r="E108" s="11" t="inlineStr">
-        <is>
-          <t>status is read from Postgres, not Temporal</t>
-        </is>
-      </c>
+          <t>Authenticated (self)</t>
+        </is>
+      </c>
+      <c r="E108" s="11" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="11" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B109" s="11" t="inlineStr">
         <is>
-          <t>/v1/privacy/export/{id}/download</t>
+          <t>/v1/privacy/retention-policies</t>
         </is>
       </c>
       <c r="C109" s="11" t="inlineStr">
@@ -7385,24 +7434,20 @@
       </c>
       <c r="D109" s="11" t="inlineStr">
         <is>
-          <t>Self or platform.admin</t>
-        </is>
-      </c>
-      <c r="E109" s="11" t="inlineStr">
-        <is>
-          <t>presigned MinIO/S3 GET</t>
-        </is>
-      </c>
+          <t>platform.admin</t>
+        </is>
+      </c>
+      <c r="E109" s="11" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="11" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B110" s="11" t="inlineStr">
         <is>
-          <t>/v1/privacy/delete</t>
+          <t>/v1/privacy/retention-policies</t>
         </is>
       </c>
       <c r="C110" s="11" t="inlineStr">
@@ -7412,24 +7457,20 @@
       </c>
       <c r="D110" s="11" t="inlineStr">
         <is>
-          <t>Authenticated (self)</t>
-        </is>
-      </c>
-      <c r="E110" s="11" t="inlineStr">
-        <is>
-          <t>starts a Temporal workflow</t>
-        </is>
-      </c>
+          <t>platform.admin</t>
+        </is>
+      </c>
+      <c r="E110" s="11" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="11" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B111" s="11" t="inlineStr">
         <is>
-          <t>/v1/privacy/delete/{id}</t>
+          <t>/v1/privacy/export</t>
         </is>
       </c>
       <c r="C111" s="11" t="inlineStr">
@@ -7439,39 +7480,39 @@
       </c>
       <c r="D111" s="11" t="inlineStr">
         <is>
-          <t>Self or platform.admin</t>
+          <t>Authenticated (self)</t>
         </is>
       </c>
       <c r="E111" s="11" t="inlineStr">
         <is>
-          <t>a self-deleted user must use an admin to check this</t>
+          <t>starts a Temporal workflow</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="11" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B112" s="11" t="inlineStr">
         <is>
-          <t>/v1/trustsafety/mutes</t>
+          <t>/v1/privacy/export/{id}</t>
         </is>
       </c>
       <c r="C112" s="11" t="inlineStr">
         <is>
-          <t>trustsafety</t>
+          <t>privacy</t>
         </is>
       </c>
       <c r="D112" s="11" t="inlineStr">
         <is>
-          <t>Authenticated (self)</t>
+          <t>Self or platform.admin</t>
         </is>
       </c>
       <c r="E112" s="11" t="inlineStr">
         <is>
-          <t>one-directional, silent</t>
+          <t>status is read from Postgres, not Temporal</t>
         </is>
       </c>
     </row>
@@ -7483,39 +7524,39 @@
       </c>
       <c r="B113" s="11" t="inlineStr">
         <is>
-          <t>/v1/trustsafety/mutes</t>
+          <t>/v1/privacy/export/{id}/download</t>
         </is>
       </c>
       <c r="C113" s="11" t="inlineStr">
         <is>
-          <t>trustsafety</t>
+          <t>privacy</t>
         </is>
       </c>
       <c r="D113" s="11" t="inlineStr">
         <is>
-          <t>Authenticated (self)</t>
+          <t>Self or platform.admin</t>
         </is>
       </c>
       <c r="E113" s="11" t="inlineStr">
         <is>
-          <t>exempt from requireActive - always reachable</t>
+          <t>presigned MinIO/S3 GET</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="11" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B114" s="11" t="inlineStr">
         <is>
-          <t>/v1/trustsafety/mutes/{userId}</t>
+          <t>/v1/privacy/delete</t>
         </is>
       </c>
       <c r="C114" s="11" t="inlineStr">
         <is>
-          <t>trustsafety</t>
+          <t>privacy</t>
         </is>
       </c>
       <c r="D114" s="11" t="inlineStr">
@@ -7523,44 +7564,48 @@
           <t>Authenticated (self)</t>
         </is>
       </c>
-      <c r="E114" s="11" t="inlineStr"/>
+      <c r="E114" s="11" t="inlineStr">
+        <is>
+          <t>starts a Temporal workflow</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="11" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B115" s="11" t="inlineStr">
         <is>
-          <t>/v1/trustsafety/reports</t>
+          <t>/v1/privacy/delete/{id}</t>
         </is>
       </c>
       <c r="C115" s="11" t="inlineStr">
         <is>
-          <t>trustsafety</t>
+          <t>privacy</t>
         </is>
       </c>
       <c r="D115" s="11" t="inlineStr">
         <is>
-          <t>Authenticated (self)</t>
+          <t>Self or platform.admin</t>
         </is>
       </c>
       <c r="E115" s="11" t="inlineStr">
         <is>
-          <t>rate-limited 5/hour; dedupes onto one case</t>
+          <t>a self-deleted user must use an admin to check this</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="11" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B116" s="11" t="inlineStr">
         <is>
-          <t>/v1/trustsafety/reports/{id}</t>
+          <t>/v1/trustsafety/mutes</t>
         </is>
       </c>
       <c r="C116" s="11" t="inlineStr">
@@ -7570,10 +7615,14 @@
       </c>
       <c r="D116" s="11" t="inlineStr">
         <is>
-          <t>Reporter or moderator/admin</t>
-        </is>
-      </c>
-      <c r="E116" s="11" t="inlineStr"/>
+          <t>Authenticated (self)</t>
+        </is>
+      </c>
+      <c r="E116" s="11" t="inlineStr">
+        <is>
+          <t>one-directional, silent</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="11" t="inlineStr">
@@ -7583,7 +7632,7 @@
       </c>
       <c r="B117" s="11" t="inlineStr">
         <is>
-          <t>/v1/trustsafety/cases</t>
+          <t>/v1/trustsafety/mutes</t>
         </is>
       </c>
       <c r="C117" s="11" t="inlineStr">
@@ -7593,24 +7642,24 @@
       </c>
       <c r="D117" s="11" t="inlineStr">
         <is>
-          <t>Moderator or platform.admin</t>
+          <t>Authenticated (self)</t>
         </is>
       </c>
       <c r="E117" s="11" t="inlineStr">
         <is>
-          <t>?status=</t>
+          <t>exempt from requireActive - always reachable</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="11" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B118" s="11" t="inlineStr">
         <is>
-          <t>/v1/trustsafety/cases/{id}</t>
+          <t>/v1/trustsafety/mutes/{userId}</t>
         </is>
       </c>
       <c r="C118" s="11" t="inlineStr">
@@ -7620,7 +7669,7 @@
       </c>
       <c r="D118" s="11" t="inlineStr">
         <is>
-          <t>Moderator or platform.admin</t>
+          <t>Authenticated (self)</t>
         </is>
       </c>
       <c r="E118" s="11" t="inlineStr"/>
@@ -7628,12 +7677,12 @@
     <row r="119">
       <c r="A119" s="11" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B119" s="11" t="inlineStr">
         <is>
-          <t>/v1/trustsafety/cases/{id}/reports</t>
+          <t>/v1/trustsafety/reports</t>
         </is>
       </c>
       <c r="C119" s="11" t="inlineStr">
@@ -7643,20 +7692,24 @@
       </c>
       <c r="D119" s="11" t="inlineStr">
         <is>
-          <t>Moderator or platform.admin</t>
-        </is>
-      </c>
-      <c r="E119" s="11" t="inlineStr"/>
+          <t>Authenticated (self)</t>
+        </is>
+      </c>
+      <c r="E119" s="11" t="inlineStr">
+        <is>
+          <t>rate-limited 5/hour; dedupes onto one case</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="11" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B120" s="11" t="inlineStr">
         <is>
-          <t>/v1/trustsafety/cases/{id}/assign</t>
+          <t>/v1/trustsafety/reports/{id}</t>
         </is>
       </c>
       <c r="C120" s="11" t="inlineStr">
@@ -7666,7 +7719,7 @@
       </c>
       <c r="D120" s="11" t="inlineStr">
         <is>
-          <t>Moderator or platform.admin</t>
+          <t>Reporter or moderator/admin</t>
         </is>
       </c>
       <c r="E120" s="11" t="inlineStr"/>
@@ -7674,12 +7727,12 @@
     <row r="121">
       <c r="A121" s="11" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B121" s="11" t="inlineStr">
         <is>
-          <t>/v1/trustsafety/cases/{id}</t>
+          <t>/v1/trustsafety/cases</t>
         </is>
       </c>
       <c r="C121" s="11" t="inlineStr">
@@ -7694,19 +7747,19 @@
       </c>
       <c r="E121" s="11" t="inlineStr">
         <is>
-          <t>resolve/dismiss</t>
+          <t>?status=</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="11" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B122" s="11" t="inlineStr">
         <is>
-          <t>/v1/trustsafety/suspensions</t>
+          <t>/v1/trustsafety/cases/{id}</t>
         </is>
       </c>
       <c r="C122" s="11" t="inlineStr">
@@ -7719,11 +7772,7 @@
           <t>Moderator or platform.admin</t>
         </is>
       </c>
-      <c r="E122" s="11" t="inlineStr">
-        <is>
-          <t>temporary, EndsAt required</t>
-        </is>
-      </c>
+      <c r="E122" s="11" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="11" t="inlineStr">
@@ -7733,7 +7782,7 @@
       </c>
       <c r="B123" s="11" t="inlineStr">
         <is>
-          <t>/v1/trustsafety/suspensions</t>
+          <t>/v1/trustsafety/cases/{id}/reports</t>
         </is>
       </c>
       <c r="C123" s="11" t="inlineStr">
@@ -7743,24 +7792,20 @@
       </c>
       <c r="D123" s="11" t="inlineStr">
         <is>
-          <t>Self or moderator/admin</t>
-        </is>
-      </c>
-      <c r="E123" s="11" t="inlineStr">
-        <is>
-          <t>?userId=</t>
-        </is>
-      </c>
+          <t>Moderator or platform.admin</t>
+        </is>
+      </c>
+      <c r="E123" s="11" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="11" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B124" s="11" t="inlineStr">
         <is>
-          <t>/v1/trustsafety/suspensions/{id}/lift</t>
+          <t>/v1/trustsafety/cases/{id}/assign</t>
         </is>
       </c>
       <c r="C124" s="11" t="inlineStr">
@@ -7778,12 +7823,12 @@
     <row r="125">
       <c r="A125" s="11" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B125" s="11" t="inlineStr">
         <is>
-          <t>/v1/trustsafety/bans</t>
+          <t>/v1/trustsafety/cases/{id}</t>
         </is>
       </c>
       <c r="C125" s="11" t="inlineStr">
@@ -7798,19 +7843,19 @@
       </c>
       <c r="E125" s="11" t="inlineStr">
         <is>
-          <t>permanent until lifted</t>
+          <t>resolve/dismiss</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="11" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B126" s="11" t="inlineStr">
         <is>
-          <t>/v1/trustsafety/bans</t>
+          <t>/v1/trustsafety/suspensions</t>
         </is>
       </c>
       <c r="C126" s="11" t="inlineStr">
@@ -7820,24 +7865,24 @@
       </c>
       <c r="D126" s="11" t="inlineStr">
         <is>
-          <t>Self or moderator/admin</t>
+          <t>Moderator or platform.admin</t>
         </is>
       </c>
       <c r="E126" s="11" t="inlineStr">
         <is>
-          <t>?userId=</t>
+          <t>temporary, EndsAt required</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="11" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B127" s="11" t="inlineStr">
         <is>
-          <t>/v1/trustsafety/bans/{id}/lift</t>
+          <t>/v1/trustsafety/suspensions</t>
         </is>
       </c>
       <c r="C127" s="11" t="inlineStr">
@@ -7847,10 +7892,14 @@
       </c>
       <c r="D127" s="11" t="inlineStr">
         <is>
-          <t>Moderator or platform.admin</t>
-        </is>
-      </c>
-      <c r="E127" s="11" t="inlineStr"/>
+          <t>Self or moderator/admin</t>
+        </is>
+      </c>
+      <c r="E127" s="11" t="inlineStr">
+        <is>
+          <t>?userId=</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="11" t="inlineStr">
@@ -7860,7 +7909,7 @@
       </c>
       <c r="B128" s="11" t="inlineStr">
         <is>
-          <t>/v1/trustsafety/appeals</t>
+          <t>/v1/trustsafety/suspensions/{id}/lift</t>
         </is>
       </c>
       <c r="C128" s="11" t="inlineStr">
@@ -7870,24 +7919,20 @@
       </c>
       <c r="D128" s="11" t="inlineStr">
         <is>
-          <t>Authenticated (self, must own target)</t>
-        </is>
-      </c>
-      <c r="E128" s="11" t="inlineStr">
-        <is>
-          <t>exempt from requireActive - always reachable</t>
-        </is>
-      </c>
+          <t>Moderator or platform.admin</t>
+        </is>
+      </c>
+      <c r="E128" s="11" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="11" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B129" s="11" t="inlineStr">
         <is>
-          <t>/v1/trustsafety/appeals</t>
+          <t>/v1/trustsafety/bans</t>
         </is>
       </c>
       <c r="C129" s="11" t="inlineStr">
@@ -7897,24 +7942,24 @@
       </c>
       <c r="D129" s="11" t="inlineStr">
         <is>
-          <t>Self or moderator/admin</t>
+          <t>Moderator or platform.admin</t>
         </is>
       </c>
       <c r="E129" s="11" t="inlineStr">
         <is>
-          <t>exempt from requireActive - always reachable</t>
+          <t>permanent until lifted</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="11" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B130" s="11" t="inlineStr">
         <is>
-          <t>/v1/trustsafety/appeals/{id}/review</t>
+          <t>/v1/trustsafety/bans</t>
         </is>
       </c>
       <c r="C130" s="11" t="inlineStr">
@@ -7924,12 +7969,12 @@
       </c>
       <c r="D130" s="11" t="inlineStr">
         <is>
-          <t>Moderator or platform.admin</t>
+          <t>Self or moderator/admin</t>
         </is>
       </c>
       <c r="E130" s="11" t="inlineStr">
         <is>
-          <t>approving lifts the target restriction</t>
+          <t>?userId=</t>
         </is>
       </c>
     </row>
@@ -7941,7 +7986,7 @@
       </c>
       <c r="B131" s="11" t="inlineStr">
         <is>
-          <t>/v1/trustsafety/signals</t>
+          <t>/v1/trustsafety/bans/{id}/lift</t>
         </is>
       </c>
       <c r="C131" s="11" t="inlineStr">
@@ -7951,24 +7996,20 @@
       </c>
       <c r="D131" s="11" t="inlineStr">
         <is>
-          <t>Authenticated</t>
-        </is>
-      </c>
-      <c r="E131" s="11" t="inlineStr">
-        <is>
-          <t>critical severity auto-opens a case</t>
-        </is>
-      </c>
+          <t>Moderator or platform.admin</t>
+        </is>
+      </c>
+      <c r="E131" s="11" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="11" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B132" s="11" t="inlineStr">
         <is>
-          <t>/v1/trustsafety/signals</t>
+          <t>/v1/trustsafety/appeals</t>
         </is>
       </c>
       <c r="C132" s="11" t="inlineStr">
@@ -7978,12 +8019,12 @@
       </c>
       <c r="D132" s="11" t="inlineStr">
         <is>
-          <t>Moderator or platform.admin</t>
+          <t>Authenticated (self, must own target)</t>
         </is>
       </c>
       <c r="E132" s="11" t="inlineStr">
         <is>
-          <t>?resourceType=&amp;resourceId=</t>
+          <t>exempt from requireActive - always reachable</t>
         </is>
       </c>
     </row>
@@ -7995,49 +8036,49 @@
       </c>
       <c r="B133" s="11" t="inlineStr">
         <is>
-          <t>/v1/billing/entitlements</t>
+          <t>/v1/trustsafety/appeals</t>
         </is>
       </c>
       <c r="C133" s="11" t="inlineStr">
         <is>
-          <t>billing</t>
+          <t>trustsafety</t>
         </is>
       </c>
       <c r="D133" s="11" t="inlineStr">
         <is>
-          <t>Self or platform.admin</t>
+          <t>Self or moderator/admin</t>
         </is>
       </c>
       <c r="E133" s="11" t="inlineStr">
         <is>
-          <t>?userId=</t>
+          <t>exempt from requireActive - always reachable</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="11" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B134" s="11" t="inlineStr">
         <is>
-          <t>/v1/billing/entitlements/check/{key}</t>
+          <t>/v1/trustsafety/appeals/{id}/review</t>
         </is>
       </c>
       <c r="C134" s="11" t="inlineStr">
         <is>
-          <t>billing</t>
+          <t>trustsafety</t>
         </is>
       </c>
       <c r="D134" s="11" t="inlineStr">
         <is>
-          <t>Authenticated (self)</t>
+          <t>Moderator or platform.admin</t>
         </is>
       </c>
       <c r="E134" s="11" t="inlineStr">
         <is>
-          <t>the literal 'do I have entitlement X' check</t>
+          <t>approving lifts the target restriction</t>
         </is>
       </c>
     </row>
@@ -8049,47 +8090,51 @@
       </c>
       <c r="B135" s="11" t="inlineStr">
         <is>
-          <t>/v1/billing/entitlements</t>
+          <t>/v1/trustsafety/signals</t>
         </is>
       </c>
       <c r="C135" s="11" t="inlineStr">
         <is>
-          <t>billing</t>
+          <t>trustsafety</t>
         </is>
       </c>
       <c r="D135" s="11" t="inlineStr">
         <is>
-          <t>platform.admin</t>
+          <t>Authenticated</t>
         </is>
       </c>
       <c r="E135" s="11" t="inlineStr">
         <is>
-          <t>manual grant; source always "manual:&lt;adminId&gt;"</t>
+          <t>critical severity auto-opens a case</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="11" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B136" s="11" t="inlineStr">
         <is>
-          <t>/v1/billing/entitlements/{id}/revoke</t>
+          <t>/v1/trustsafety/signals</t>
         </is>
       </c>
       <c r="C136" s="11" t="inlineStr">
         <is>
-          <t>billing</t>
+          <t>trustsafety</t>
         </is>
       </c>
       <c r="D136" s="11" t="inlineStr">
         <is>
-          <t>platform.admin</t>
-        </is>
-      </c>
-      <c r="E136" s="11" t="inlineStr"/>
+          <t>Moderator or platform.admin</t>
+        </is>
+      </c>
+      <c r="E136" s="11" t="inlineStr">
+        <is>
+          <t>?resourceType=&amp;resourceId=</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="11" t="inlineStr">
@@ -8099,7 +8144,7 @@
       </c>
       <c r="B137" s="11" t="inlineStr">
         <is>
-          <t>/v1/billing/payments</t>
+          <t>/v1/billing/entitlements</t>
         </is>
       </c>
       <c r="C137" s="11" t="inlineStr">
@@ -8121,12 +8166,12 @@
     <row r="138">
       <c r="A138" s="11" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B138" s="11" t="inlineStr">
         <is>
-          <t>/v1/billing/webhooks/{provider}</t>
+          <t>/v1/billing/entitlements/check/{key}</t>
         </is>
       </c>
       <c r="C138" s="11" t="inlineStr">
@@ -8136,12 +8181,12 @@
       </c>
       <c r="D138" s="11" t="inlineStr">
         <is>
-          <t>Provider webhook signature (no Bearer token)</t>
+          <t>Authenticated (self)</t>
         </is>
       </c>
       <c r="E138" s="11" t="inlineStr">
         <is>
-          <t>the one route on this platform with no requireUser/requireActive</t>
+          <t>the literal 'do I have entitlement X' check</t>
         </is>
       </c>
     </row>
@@ -8153,39 +8198,39 @@
       </c>
       <c r="B139" s="11" t="inlineStr">
         <is>
-          <t>/v1/analytics/events</t>
+          <t>/v1/billing/entitlements</t>
         </is>
       </c>
       <c r="C139" s="11" t="inlineStr">
         <is>
-          <t>analytics</t>
+          <t>billing</t>
         </is>
       </c>
       <c r="D139" s="11" t="inlineStr">
         <is>
-          <t>Open (IP-rate-limited, no Bearer token)</t>
+          <t>platform.admin</t>
         </is>
       </c>
       <c r="E139" s="11" t="inlineStr">
         <is>
-          <t>the platform's one deliberately unauthenticated write endpoint</t>
+          <t>manual grant; source always "manual:&lt;adminId&gt;"</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="11" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B140" s="11" t="inlineStr">
         <is>
-          <t>/v1/analytics/events</t>
+          <t>/v1/billing/entitlements/{id}/revoke</t>
         </is>
       </c>
       <c r="C140" s="11" t="inlineStr">
         <is>
-          <t>analytics</t>
+          <t>billing</t>
         </is>
       </c>
       <c r="D140" s="11" t="inlineStr">
@@ -8193,88 +8238,192 @@
           <t>platform.admin</t>
         </is>
       </c>
-      <c r="E140" s="11" t="inlineStr">
-        <is>
-          <t>operational debug view only, not for analytical queries</t>
-        </is>
-      </c>
+      <c r="E140" s="11" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="11" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B141" s="11" t="inlineStr">
         <is>
-          <t>/v1/ai/completions</t>
+          <t>/v1/billing/payments</t>
         </is>
       </c>
       <c r="C141" s="11" t="inlineStr">
         <is>
-          <t>aigateway</t>
+          <t>billing</t>
         </is>
       </c>
       <c r="D141" s="11" t="inlineStr">
         <is>
-          <t>Authenticated (quota-limited)</t>
+          <t>Self or platform.admin</t>
         </is>
       </c>
       <c r="E141" s="11" t="inlineStr">
         <is>
-          <t>real local inference via Ollama; never call a vendor model name directly</t>
+          <t>?userId=</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="11" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B142" s="11" t="inlineStr">
         <is>
-          <t>/v1/ai/usage</t>
+          <t>/v1/billing/webhooks/{provider}</t>
         </is>
       </c>
       <c r="C142" s="11" t="inlineStr">
         <is>
-          <t>aigateway</t>
+          <t>billing</t>
         </is>
       </c>
       <c r="D142" s="11" t="inlineStr">
         <is>
-          <t>Self or platform.admin</t>
+          <t>Provider webhook signature (no Bearer token)</t>
         </is>
       </c>
       <c r="E142" s="11" t="inlineStr">
         <is>
-          <t>?userId=; tokens/cost/latency, never prompt or response text</t>
+          <t>the one route on this platform with no requireUser/requireActive</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="11" t="inlineStr">
         <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="B143" s="11" t="inlineStr">
+        <is>
+          <t>/v1/analytics/events</t>
+        </is>
+      </c>
+      <c r="C143" s="11" t="inlineStr">
+        <is>
+          <t>analytics</t>
+        </is>
+      </c>
+      <c r="D143" s="11" t="inlineStr">
+        <is>
+          <t>Open (IP-rate-limited, no Bearer token)</t>
+        </is>
+      </c>
+      <c r="E143" s="11" t="inlineStr">
+        <is>
+          <t>the platform's one deliberately unauthenticated write endpoint</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="11" t="inlineStr">
+        <is>
           <t>GET</t>
         </is>
       </c>
-      <c r="B143" s="11" t="inlineStr">
+      <c r="B144" s="11" t="inlineStr">
+        <is>
+          <t>/v1/analytics/events</t>
+        </is>
+      </c>
+      <c r="C144" s="11" t="inlineStr">
+        <is>
+          <t>analytics</t>
+        </is>
+      </c>
+      <c r="D144" s="11" t="inlineStr">
+        <is>
+          <t>platform.admin</t>
+        </is>
+      </c>
+      <c r="E144" s="11" t="inlineStr">
+        <is>
+          <t>operational debug view only, not for analytical queries</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="11" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="B145" s="11" t="inlineStr">
+        <is>
+          <t>/v1/ai/completions</t>
+        </is>
+      </c>
+      <c r="C145" s="11" t="inlineStr">
+        <is>
+          <t>aigateway</t>
+        </is>
+      </c>
+      <c r="D145" s="11" t="inlineStr">
+        <is>
+          <t>Authenticated (quota-limited)</t>
+        </is>
+      </c>
+      <c r="E145" s="11" t="inlineStr">
+        <is>
+          <t>real local inference via Ollama; never call a vendor model name directly</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="11" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="B146" s="11" t="inlineStr">
+        <is>
+          <t>/v1/ai/usage</t>
+        </is>
+      </c>
+      <c r="C146" s="11" t="inlineStr">
+        <is>
+          <t>aigateway</t>
+        </is>
+      </c>
+      <c r="D146" s="11" t="inlineStr">
+        <is>
+          <t>Self or platform.admin</t>
+        </is>
+      </c>
+      <c r="E146" s="11" t="inlineStr">
+        <is>
+          <t>?userId=; tokens/cost/latency, never prompt or response text</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="11" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="B147" s="11" t="inlineStr">
         <is>
           <t>/v1/ai/models</t>
         </is>
       </c>
-      <c r="C143" s="11" t="inlineStr">
+      <c r="C147" s="11" t="inlineStr">
         <is>
           <t>aigateway</t>
         </is>
       </c>
-      <c r="D143" s="11" t="inlineStr">
+      <c r="D147" s="11" t="inlineStr">
         <is>
           <t>Authenticated</t>
         </is>
       </c>
-      <c r="E143" s="11" t="inlineStr">
+      <c r="E147" s="11" t="inlineStr">
         <is>
           <t>lists registered model aliases, never vendor model names</t>
         </is>
@@ -8294,7 +8443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -8580,12 +8729,12 @@
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>There is no HTTP route for this by design (it's a privileged, rarely-needed action) - write a small throwaway Go program under backend/core-api/cmd/&lt;name&gt;/main.go that constructs authz.Service the same way cmd/server/main.go does and calls AssignRole, then delete it.</t>
+          <t>curl -s -X POST http://localhost:8080/v1/authz/roles -H "Authorization: Bearer $TOKEN" -H 'Content-Type: application/json' -d '{"userId":"&lt;id&gt;","role":"platform.admin"}'</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>This is the same pattern used to verify every admin-gated module during development - see any phase's entry in VALIDATION.md for a worked example.</t>
+          <t>Phase 25 gave authz a real HTTP surface - $TOKEN's own user must already be platform.admin (the seeded 'demo' user is, in this environment). Also doable from the Admin Portal's Users -&gt; role management UI. The very first admin in a brand-new environment still needs a one-time throwaway Go program (AssignRole has no caller-privilege check at the service layer, only at HTTP) - the same bootstrap problem every real RBAC system has.</t>
         </is>
       </c>
     </row>
@@ -8718,6 +8867,28 @@
       <c r="D19" s="11" t="inlineStr">
         <is>
           <t>Pick an endpoint, fetch a token via the built-in Keycloak password-grant form (or paste one you already have), and send the request - the real response comes back right in the page. core-api's CORS middleware (internal/api/cors.go) is what makes this possible; it must be running a build from Phase 21 or later.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="48" customHeight="1">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>Run the actual Admin Portal</t>
+        </is>
+      </c>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>cd apps/admin &amp;&amp; npm install &amp;&amp; npm run dev</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="inlineStr">
+        <is>
+          <t>Then open http://localhost:3000 and sign in with demo/demo. Real UI over real data (Phase 25) - Users, Roles, Audit, Moderation, Feature Flags, Jobs, Configuration, System Health, Billing, AI Gateway. Needs core-api (and ideally realtime-gateway/worker) already running per steps 5-7.</t>
         </is>
       </c>
     </row>
@@ -8735,7 +8906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -8802,34 +8973,34 @@
     <row r="3" ht="32" customHeight="1">
       <c r="A3" s="11" t="inlineStr">
         <is>
-          <t>realtime-gateway</t>
+          <t>admin (apps/admin)</t>
         </is>
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>Go service</t>
+          <t>Next.js app</t>
         </is>
       </c>
       <c r="C3" s="11" t="inlineStr">
         <is>
-          <t>ws://localhost:8090</t>
+          <t>http://localhost:3000</t>
         </is>
       </c>
       <c r="D3" s="11" t="inlineStr">
         <is>
-          <t>WebSocket connections, presence, channel fan-out.</t>
+          <t>The Admin Portal (Phase 25) - real UI over core-api, session-based auth via Keycloak.</t>
         </is>
       </c>
       <c r="E3" s="11" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>sign in with demo/demo (same as core realm)</t>
         </is>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>worker</t>
+          <t>realtime-gateway</t>
         </is>
       </c>
       <c r="B4" s="11" t="inlineStr">
@@ -8839,12 +9010,12 @@
       </c>
       <c r="C4" s="11" t="inlineStr">
         <is>
-          <t>http://localhost:8091 (health only)</t>
+          <t>ws://localhost:8090</t>
         </is>
       </c>
       <c r="D4" s="11" t="inlineStr">
         <is>
-          <t>Background job runner, search indexer, Temporal workflow worker, analytics NDJSON pipeline.</t>
+          <t>WebSocket connections, presence, channel fan-out.</t>
         </is>
       </c>
       <c r="E4" s="11" t="inlineStr">
@@ -8856,34 +9027,34 @@
     <row r="5" ht="32" customHeight="1">
       <c r="A5" s="11" t="inlineStr">
         <is>
-          <t>Postgres</t>
+          <t>worker</t>
         </is>
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Docker container</t>
+          <t>Go service</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>localhost:5432</t>
+          <t>http://localhost:8091 (health only)</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
-          <t>System of record for every domain module.</t>
+          <t>Background job runner, search indexer, Temporal workflow worker, analytics NDJSON pipeline.</t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>core / core, db 'core'</t>
+          <t>n/a</t>
         </is>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>Valkey (Redis-compatible)</t>
+          <t>Postgres</t>
         </is>
       </c>
       <c r="B6" s="11" t="inlineStr">
@@ -8893,24 +9064,24 @@
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>localhost:6379</t>
+          <t>localhost:5432</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>Realtime pub/sub fan-out, presence (TTL-based).</t>
+          <t>System of record for every domain module.</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>no auth locally</t>
+          <t>core / core, db 'core'</t>
         </is>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>Keycloak</t>
+          <t>Valkey (Redis-compatible)</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr">
@@ -8920,24 +9091,24 @@
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>http://localhost:8081</t>
+          <t>localhost:6379</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>Identity provider. Realm 'core' is re-imported on every restart (no persistent volume).</t>
+          <t>Realtime pub/sub fan-out, presence (TTL-based).</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>admin/admin (master realm); demo/demo (core realm, seeded user)</t>
+          <t>no auth locally</t>
         </is>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>OpenFGA</t>
+          <t>Keycloak</t>
         </is>
       </c>
       <c r="B8" s="11" t="inlineStr">
@@ -8947,24 +9118,24 @@
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>http://localhost:8082</t>
+          <t>http://localhost:8081</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>Fine-grained ReBAC engine behind authz.Service.Can. In-memory store, self-heals its store/model on every restart.</t>
+          <t>Identity provider. Realm 'core' is re-imported on every restart (no persistent volume).</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>no auth locally</t>
+          <t>admin/admin (master realm); demo/demo (core realm, seeded user)</t>
         </is>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1">
       <c r="A9" s="11" t="inlineStr">
         <is>
-          <t>MinIO (S3-compatible)</t>
+          <t>OpenFGA</t>
         </is>
       </c>
       <c r="B9" s="11" t="inlineStr">
@@ -8974,24 +9145,24 @@
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>http://localhost:9000</t>
+          <t>http://localhost:8082</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>Object storage backing the files module.</t>
+          <t>Fine-grained ReBAC engine behind authz.Service.Can. In-memory store, self-heals its store/model on every restart.</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>minio / minio123, bucket 'core-platform'</t>
+          <t>no auth locally</t>
         </is>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>OpenSearch</t>
+          <t>MinIO (S3-compatible)</t>
         </is>
       </c>
       <c r="B10" s="11" t="inlineStr">
@@ -9001,24 +9172,24 @@
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>http://localhost:9200</t>
+          <t>http://localhost:9000</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>Backs the search module, indexed by worker's indexer.</t>
+          <t>Object storage backing the files module.</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>no auth locally</t>
+          <t>minio / minio123, bucket 'core-platform'</t>
         </is>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1">
       <c r="A11" s="11" t="inlineStr">
         <is>
-          <t>Temporal</t>
+          <t>OpenSearch</t>
         </is>
       </c>
       <c r="B11" s="11" t="inlineStr">
@@ -9028,12 +9199,12 @@
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>localhost:7233</t>
+          <t>http://localhost:9200</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>Durable workflow execution engine behind the workflows module.</t>
+          <t>Backs the search module, indexed by worker's indexer.</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
@@ -9045,7 +9216,7 @@
     <row r="12" ht="32" customHeight="1">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>Kafka / Redpanda</t>
+          <t>Temporal</t>
         </is>
       </c>
       <c r="B12" s="11" t="inlineStr">
@@ -9055,12 +9226,12 @@
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>localhost:9092</t>
+          <t>localhost:7233</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>Health-checked today; no producer wired yet (outbox-to-Kafka relay is a documented future gap).</t>
+          <t>Durable workflow execution engine behind the workflows module.</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
@@ -9072,7 +9243,7 @@
     <row r="13" ht="32" customHeight="1">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t>Ollama</t>
+          <t>Kafka / Redpanda</t>
         </is>
       </c>
       <c r="B13" s="11" t="inlineStr">
@@ -9082,12 +9253,12 @@
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>http://localhost:11434</t>
+          <t>localhost:9092</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>Real local LLM inference behind the AI Gateway - model qwen2.5:0.5b auto-pulled on every start, no vendor API key needed.</t>
+          <t>Health-checked today; no producer wired yet (outbox-to-Kafka relay is a documented future gap).</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
@@ -9099,25 +9270,52 @@
     <row r="14" ht="32" customHeight="1">
       <c r="A14" s="11" t="inlineStr">
         <is>
+          <t>Ollama</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>Docker container</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>http://localhost:11434</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="inlineStr">
+        <is>
+          <t>Real local LLM inference behind the AI Gateway - model qwen2.5:0.5b auto-pulled on every start, no vendor API key needed.</t>
+        </is>
+      </c>
+      <c r="E14" s="11" t="inlineStr">
+        <is>
+          <t>no auth locally</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="32" customHeight="1">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
           <t>OTel Collector / Tempo / Prometheus / Grafana / Loki</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B15" s="11" t="inlineStr">
         <is>
           <t>Docker containers</t>
         </is>
       </c>
-      <c r="C14" s="11" t="inlineStr">
+      <c r="C15" s="11" t="inlineStr">
         <is>
           <t>see infra/docker/docker-compose.yml</t>
         </is>
       </c>
-      <c r="D14" s="11" t="inlineStr">
+      <c r="D15" s="11" t="inlineStr">
         <is>
           <t>Full observability stack - traces, metrics, logs, dashboards.</t>
         </is>
       </c>
-      <c r="E14" s="11" t="inlineStr">
+      <c r="E15" s="11" t="inlineStr">
         <is>
           <t>no auth locally</t>
         </is>

--- a/docs/control/data.xlsx
+++ b/docs/control/data.xlsx
@@ -239,8 +239,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="TodoChecklist" displayName="TodoChecklist" ref="A1:D123" headerRowCount="1">
-  <autoFilter ref="A1:D123"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="TodoChecklist" displayName="TodoChecklist" ref="A1:D129" headerRowCount="1">
+  <autoFilter ref="A1:D129"/>
   <tableColumns count="4">
     <tableColumn id="1" name="Phase"/>
     <tableColumn id="2" name="Status"/>
@@ -281,8 +281,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="HowToTest" displayName="HowToTest" ref="A1:D20" headerRowCount="1">
-  <autoFilter ref="A1:D20"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="HowToTest" displayName="HowToTest" ref="A1:D21" headerRowCount="1">
+  <autoFilter ref="A1:D21"/>
   <tableColumns count="4">
     <tableColumn id="1" name="Step"/>
     <tableColumn id="2" name="What"/>
@@ -294,8 +294,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="InfraCredentials" displayName="InfraCredentials" ref="A1:E15" headerRowCount="1">
-  <autoFilter ref="A1:E15"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="InfraCredentials" displayName="InfraCredentials" ref="A1:E16" headerRowCount="1">
+  <autoFilter ref="A1:E16"/>
   <tableColumns count="5">
     <tableColumn id="1" name="Service"/>
     <tableColumn id="2" name="Type"/>
@@ -596,7 +596,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -633,12 +633,12 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>25 / 30</t>
+          <t>26 / 30</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>83%</t>
+          <t>87%</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Shared Go packages</t>
+          <t>Developer portal</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
@@ -689,139 +689,156 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>packages/go/platformkit</t>
+          <t>platform/backstage (real @backstage/create-app, 24-entity catalog)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Domain modules (core-api)</t>
+          <t>Shared Go packages</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>one per completed backend phase</t>
+          <t>packages/go/platformkit</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Live HTTP endpoints</t>
+          <t>Domain modules (core-api)</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>see 'API Endpoints' sheet</t>
+          <t>one per completed backend phase</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>DB migrations</t>
+          <t>Live HTTP endpoints</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>146</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>data/migrations/0001-0022</t>
+          <t>see 'API Endpoints' sheet</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Real infra dependencies</t>
+          <t>DB migrations</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Postgres, Valkey, Keycloak, OpenFGA, MinIO, OpenSearch, Temporal, Kafka/Redpanda, Ollama, OTel</t>
+          <t>data/migrations/0001-0022</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
+          <t>Real infra dependencies</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>Postgres, Valkey, Keycloak, OpenFGA, MinIO, OpenSearch, Temporal, Kafka/Redpanda, Ollama, OTel</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
           <t>Commits so far</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>see git log</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>How to read this workbook</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>• Roadmap - all 30 phases, one row each, status + what it delivers.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>• Todo Checklist - granular task list (completed sub-items and still-to-do sub-items) so progress is trackable at a finer grain than 'phase done or not'.</t>
+          <t>• Roadmap - all 30 phases, one row each, status + what it delivers.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>• Modules - every backend/core-api/internal module: what it owns, its storage, its access rule.</t>
+          <t>• Todo Checklist - granular task list (completed sub-items and still-to-do sub-items) so progress is trackable at a finer grain than 'phase done or not'.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>• API Endpoints - every live HTTP route across all three services, with auth level.</t>
+          <t>• Modules - every backend/core-api/internal module: what it owns, its storage, its access rule.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>• How To Test - copy-paste steps to bring the stack up locally and exercise it for real (mint a token, call endpoints, open a WebSocket).</t>
+          <t>• API Endpoints - every live HTTP route across all three services, with auth level.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>• How To Test - copy-paste steps to bring the stack up locally and exercise it for real (mint a token, call endpoints, open a WebSocket).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>• Infra &amp; Credentials - every local service, its port, and its local-only credentials.</t>
         </is>
@@ -830,8 +847,8 @@
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A16:F16"/>
     <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A22:F22"/>
     <mergeCell ref="A17:F17"/>
     <mergeCell ref="A18:F18"/>
     <mergeCell ref="A20:F20"/>
@@ -1513,9 +1530,9 @@
       <c r="A27" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="12" t="inlineStr">
-        <is>
-          <t>Next up</t>
+      <c r="B27" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
@@ -1525,12 +1542,12 @@
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>Integrate Backstage as the developer portal - every service/module exposes metadata (owner, lifecycle, repo, docs, dependencies, APIs, events, DB ownership, dashboards, runbooks). Backstage becomes the map of the platform.</t>
+          <t>A real @backstage/create-app instance (platform/backstage) whose catalog (catalog/system.yaml) is 24 real entities - a Group, the System, Components for all 3 services + admin + 16 domain modules with real dependsOn/providesApis, and 2 API entities embedding the full real OpenAPI/AsyncAPI specs. Filled in 11 stub module READMEs, fixed 2 real YAML bugs in the OpenAPI spec, generated ~110 missing OpenAPI paths from the actual Go route registrations, and live-validated the whole catalog loads with zero processing errors via the real catalog API.</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>b1bf7b9</t>
         </is>
       </c>
     </row>
@@ -1538,9 +1555,9 @@
       <c r="A28" s="9" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B28" s="12" t="inlineStr">
+        <is>
+          <t>Next up</t>
         </is>
       </c>
       <c r="C28" s="11" t="inlineStr">
@@ -1648,7 +1665,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D123"/>
+  <dimension ref="A1:D129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2081,7 +2098,7 @@
     </row>
     <row r="27">
       <c r="A27" s="9" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
@@ -2090,14 +2107,14 @@
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>Repo health baseline (make doctor / validate-all / go test / go build) run and passed</t>
+          <t>Phase 26: Backstage implemented, unit-tested, live-validated, documented, committed</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
@@ -2106,18 +2123,14 @@
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>Environment / ApplicationVersion / ApplicationConfiguration</t>
-        </is>
-      </c>
-      <c r="D28" s="11" t="inlineStr">
-        <is>
-          <t>Deferred - no consumer needs them yet, documented as intentional in applications/README.md</t>
-        </is>
-      </c>
+          <t>Repo health baseline (make doctor / validate-all / go test / go build) run and passed</t>
+        </is>
+      </c>
+      <c r="D28" s="11" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
@@ -2126,32 +2139,32 @@
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>Separate Session table</t>
+          <t>Environment / ApplicationVersion / ApplicationConfiguration</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>Deferred - Device.SessionStatus covers today's single-session-per-device need, documented in devices/README.md</t>
+          <t>Deferred - no consumer needs them yet, documented as intentional in applications/README.md</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="B30" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+        <v>5</v>
+      </c>
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t>UserPreferences (named in Phase 4, no fields ever specified)</t>
+          <t>Separate Session table</t>
         </is>
       </c>
       <c r="D30" s="11" t="inlineStr">
         <is>
-          <t>Deferred to Phase 12+; notification preferences shipped, a generic preferences bag did not</t>
+          <t>Deferred - Device.SessionStatus covers today's single-session-per-device need, documented in devices/README.md</t>
         </is>
       </c>
     </row>
@@ -2166,12 +2179,12 @@
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>apps/mobile test/ directory (make flutter-test currently fails)</t>
+          <t>UserPreferences (named in Phase 4, no fields ever specified)</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>Known gap since Phase 9's audit, not yet picked up</t>
+          <t>Deferred to Phase 12+; notification preferences shipped, a generic preferences bag did not</t>
         </is>
       </c>
     </row>
@@ -2186,30 +2199,34 @@
       </c>
       <c r="C32" s="11" t="inlineStr">
         <is>
-          <t>apps/admin next@15 / sharp transitive advisories</t>
+          <t>apps/mobile test/ directory (make flutter-test currently fails)</t>
         </is>
       </c>
       <c r="D32" s="11" t="inlineStr">
         <is>
-          <t>Fix is a Next.js major-version bump - separate, reviewable change</t>
+          <t>Known gap since Phase 9's audit, not yet picked up</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="9" t="n">
-        <v>20</v>
-      </c>
-      <c r="B33" s="10" t="inlineStr">
-        <is>
-          <t>Done</t>
+        <v>9</v>
+      </c>
+      <c r="B33" s="13" t="inlineStr">
+        <is>
+          <t>Pending</t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>Privacy: consent (append-only history)</t>
-        </is>
-      </c>
-      <c r="D33" s="11" t="inlineStr"/>
+          <t>apps/admin next@15 / sharp transitive advisories</t>
+        </is>
+      </c>
+      <c r="D33" s="11" t="inlineStr">
+        <is>
+          <t>Fix is a Next.js major-version bump - separate, reviewable change</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="9" t="n">
@@ -2222,7 +2239,7 @@
       </c>
       <c r="C34" s="11" t="inlineStr">
         <is>
-          <t>Privacy: user data export (ExportUserData registry - users/devices/files/audit)</t>
+          <t>Privacy: consent (append-only history)</t>
         </is>
       </c>
       <c r="D34" s="11" t="inlineStr"/>
@@ -2238,7 +2255,7 @@
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>Privacy: user deletion (DeleteUserData registry - users/devices/files; audit deliberately excluded)</t>
+          <t>Privacy: user data export (ExportUserData registry - users/devices/files/audit)</t>
         </is>
       </c>
       <c r="D35" s="11" t="inlineStr"/>
@@ -2254,7 +2271,7 @@
       </c>
       <c r="C36" s="11" t="inlineStr">
         <is>
-          <t>Privacy: retention policy (declared, not scheduled - same documented gap as Phase 13's PurgeExpired)</t>
+          <t>Privacy: user deletion (DeleteUserData registry - users/devices/files; audit deliberately excluded)</t>
         </is>
       </c>
       <c r="D36" s="11" t="inlineStr"/>
@@ -2270,7 +2287,7 @@
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>Privacy: privacy preferences</t>
+          <t>Privacy: retention policy (declared, not scheduled - same documented gap as Phase 13's PurgeExpired)</t>
         </is>
       </c>
       <c r="D37" s="11" t="inlineStr"/>
@@ -2286,7 +2303,7 @@
       </c>
       <c r="C38" s="11" t="inlineStr">
         <is>
-          <t>Privacy: coordinate deletion through workflows/events - core-api's own embedded Temporal worker</t>
+          <t>Privacy: privacy preferences</t>
         </is>
       </c>
       <c r="D38" s="11" t="inlineStr"/>
@@ -2295,21 +2312,17 @@
       <c r="A39" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="B39" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B39" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>Privacy: notifications module as an Export/Delete participant</t>
-        </is>
-      </c>
-      <c r="D39" s="11" t="inlineStr">
-        <is>
-          <t>Deliberately deferred to prove the registry makes this a 2-line addition later, not a framework change</t>
-        </is>
-      </c>
+          <t>Privacy: coordinate deletion through workflows/events - core-api's own embedded Temporal worker</t>
+        </is>
+      </c>
+      <c r="D39" s="11" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="9" t="n">
@@ -2322,32 +2335,32 @@
       </c>
       <c r="C40" s="11" t="inlineStr">
         <is>
-          <t>Privacy: relationships/groups/messaging as participants</t>
+          <t>Privacy: notifications module as an Export/Delete participant</t>
         </is>
       </c>
       <c r="D40" s="11" t="inlineStr">
         <is>
-          <t>Deferred - shared multi-user data needs a redaction strategy this phase's per-user-in-isolation registry doesn't fit</t>
+          <t>Deliberately deferred to prove the registry makes this a 2-line addition later, not a framework change</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="9" t="n">
-        <v>21</v>
-      </c>
-      <c r="B41" s="10" t="inlineStr">
-        <is>
-          <t>Done</t>
+        <v>20</v>
+      </c>
+      <c r="B41" s="13" t="inlineStr">
+        <is>
+          <t>Pending</t>
         </is>
       </c>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: Block</t>
+          <t>Privacy: relationships/groups/messaging as participants</t>
         </is>
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t>Reused Phase 8's relationships (Status='blocked'), deliberately not duplicated</t>
+          <t>Deferred - shared multi-user data needs a redaction strategy this phase's per-user-in-isolation registry doesn't fit</t>
         </is>
       </c>
     </row>
@@ -2362,10 +2375,14 @@
       </c>
       <c r="C42" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: Mute</t>
-        </is>
-      </c>
-      <c r="D42" s="11" t="inlineStr"/>
+          <t>Trust &amp; Safety: Block</t>
+        </is>
+      </c>
+      <c r="D42" s="11" t="inlineStr">
+        <is>
+          <t>Reused Phase 8's relationships (Status='blocked'), deliberately not duplicated</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="9" t="n">
@@ -2378,7 +2395,7 @@
       </c>
       <c r="C43" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: Report -&gt; ModerationCase (deduplicated via partial unique index)</t>
+          <t>Trust &amp; Safety: Mute</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr"/>
@@ -2394,7 +2411,7 @@
       </c>
       <c r="C44" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: Suspension</t>
+          <t>Trust &amp; Safety: Report -&gt; ModerationCase (deduplicated via partial unique index)</t>
         </is>
       </c>
       <c r="D44" s="11" t="inlineStr"/>
@@ -2410,7 +2427,7 @@
       </c>
       <c r="C45" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: Ban</t>
+          <t>Trust &amp; Safety: Suspension</t>
         </is>
       </c>
       <c r="D45" s="11" t="inlineStr"/>
@@ -2426,7 +2443,7 @@
       </c>
       <c r="C46" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: Appeal (approving lifts the target restriction)</t>
+          <t>Trust &amp; Safety: Ban</t>
         </is>
       </c>
       <c r="D46" s="11" t="inlineStr"/>
@@ -2442,7 +2459,7 @@
       </c>
       <c r="C47" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: rate limiting (new platformkit/ratelimit, Valkey-backed)</t>
+          <t>Trust &amp; Safety: Appeal (approving lifts the target restriction)</t>
         </is>
       </c>
       <c r="D47" s="11" t="inlineStr"/>
@@ -2458,7 +2475,7 @@
       </c>
       <c r="C48" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: spam protection (5 reports/hour per reporter)</t>
+          <t>Trust &amp; Safety: rate limiting (new platformkit/ratelimit, Valkey-backed)</t>
         </is>
       </c>
       <c r="D48" s="11" t="inlineStr"/>
@@ -2474,7 +2491,7 @@
       </c>
       <c r="C49" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: abuse signals (critical severity auto-opens a case)</t>
+          <t>Trust &amp; Safety: spam protection (5 reports/hour per reporter)</t>
         </is>
       </c>
       <c r="D49" s="11" t="inlineStr"/>
@@ -2490,7 +2507,7 @@
       </c>
       <c r="C50" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: pluggable product-specific report reasons (free-form Reason field)</t>
+          <t>Trust &amp; Safety: abuse signals (critical severity auto-opens a case)</t>
         </is>
       </c>
       <c r="D50" s="11" t="inlineStr"/>
@@ -2506,7 +2523,7 @@
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: Suspension/Ban actually restrict access (new requireActive middleware, one entry point)</t>
+          <t>Trust &amp; Safety: pluggable product-specific report reasons (free-form Reason field)</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr"/>
@@ -2515,21 +2532,17 @@
       <c r="A52" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="B52" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B52" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C52" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: WebSocket disconnect on suspension/ban</t>
-        </is>
-      </c>
-      <c r="D52" s="11" t="inlineStr">
-        <is>
-          <t>Deferred - only HTTP access is gated; an existing realtime-gateway connection isn't forcibly closed</t>
-        </is>
-      </c>
+          <t>Trust &amp; Safety: Suspension/Ban actually restrict access (new requireActive middleware, one entry point)</t>
+        </is>
+      </c>
+      <c r="D52" s="11" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="9" t="n">
@@ -2542,30 +2555,34 @@
       </c>
       <c r="C53" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: aggregating lower-severity signals over a time window</t>
+          <t>Trust &amp; Safety: WebSocket disconnect on suspension/ban</t>
         </is>
       </c>
       <c r="D53" s="11" t="inlineStr">
         <is>
-          <t>Deferred - a real abuse-detection engine is out of this phase's scope; only single-critical-signal escalation is implemented</t>
+          <t>Deferred - only HTTP access is gated; an existing realtime-gateway connection isn't forcibly closed</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="9" t="n">
-        <v>22</v>
-      </c>
-      <c r="B54" s="10" t="inlineStr">
-        <is>
-          <t>Done</t>
+        <v>21</v>
+      </c>
+      <c r="B54" s="13" t="inlineStr">
+        <is>
+          <t>Pending</t>
         </is>
       </c>
       <c r="C54" s="11" t="inlineStr">
         <is>
-          <t>Billing: Payment model (provider-specific transaction record)</t>
-        </is>
-      </c>
-      <c r="D54" s="11" t="inlineStr"/>
+          <t>Trust &amp; Safety: aggregating lower-severity signals over a time window</t>
+        </is>
+      </c>
+      <c r="D54" s="11" t="inlineStr">
+        <is>
+          <t>Deferred - a real abuse-detection engine is out of this phase's scope; only single-critical-signal escalation is implemented</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="9" t="n">
@@ -2578,7 +2595,7 @@
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t>Billing: Entitlement model (platform-facing truth, kept separate from Payment)</t>
+          <t>Billing: Payment model (provider-specific transaction record)</t>
         </is>
       </c>
       <c r="D55" s="11" t="inlineStr"/>
@@ -2594,7 +2611,7 @@
       </c>
       <c r="C56" s="11" t="inlineStr">
         <is>
-          <t>Billing: provider abstraction (PaymentProvider interface + registry, implemented first)</t>
+          <t>Billing: Entitlement model (platform-facing truth, kept separate from Payment)</t>
         </is>
       </c>
       <c r="D56" s="11" t="inlineStr"/>
@@ -2610,32 +2627,28 @@
       </c>
       <c r="C57" s="11" t="inlineStr">
         <is>
-          <t>Billing: Stripe adapter</t>
-        </is>
-      </c>
-      <c r="D57" s="11" t="inlineStr">
-        <is>
-          <t>Real HMAC-SHA256 webhook signature verification, live-validated without a Stripe account via self-signed test payloads</t>
-        </is>
-      </c>
+          <t>Billing: provider abstraction (PaymentProvider interface + registry, implemented first)</t>
+        </is>
+      </c>
+      <c r="D57" s="11" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="B58" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B58" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C58" s="11" t="inlineStr">
         <is>
-          <t>Billing: Apple IAP adapter</t>
+          <t>Billing: Stripe adapter</t>
         </is>
       </c>
       <c r="D58" s="11" t="inlineStr">
         <is>
-          <t>Deferred - needs real App Store Server API credentials this environment doesn't have</t>
+          <t>Real HMAC-SHA256 webhook signature verification, live-validated without a Stripe account via self-signed test payloads</t>
         </is>
       </c>
     </row>
@@ -2650,30 +2663,34 @@
       </c>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>Billing: Google Play adapter</t>
+          <t>Billing: Apple IAP adapter</t>
         </is>
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>Deferred - needs real Play Developer API credentials this environment doesn't have</t>
+          <t>Deferred - needs real App Store Server API credentials this environment doesn't have</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="9" t="n">
-        <v>23</v>
-      </c>
-      <c r="B60" s="10" t="inlineStr">
-        <is>
-          <t>Done</t>
+        <v>22</v>
+      </c>
+      <c r="B60" s="13" t="inlineStr">
+        <is>
+          <t>Pending</t>
         </is>
       </c>
       <c r="C60" s="11" t="inlineStr">
         <is>
-          <t>Analytics: generic event envelope (event_name/user_id/anonymous_id/app_id/session_id/timestamp/properties/context)</t>
-        </is>
-      </c>
-      <c r="D60" s="11" t="inlineStr"/>
+          <t>Billing: Google Play adapter</t>
+        </is>
+      </c>
+      <c r="D60" s="11" t="inlineStr">
+        <is>
+          <t>Deferred - needs real Play Developer API credentials this environment doesn't have</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="9" t="n">
@@ -2686,7 +2703,7 @@
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>Analytics: keep operational DBs out of the analytics path (analytics_events is a landing buffer, never queried for analytics)</t>
+          <t>Analytics: generic event envelope (event_name/user_id/anonymous_id/app_id/session_id/timestamp/properties/context)</t>
         </is>
       </c>
       <c r="D61" s="11" t="inlineStr"/>
@@ -2702,7 +2719,7 @@
       </c>
       <c r="C62" s="11" t="inlineStr">
         <is>
-          <t>Analytics: pipeline foundation for ClickHouse/warehouse/data lake (worker batches NDJSON into MinIO/S3)</t>
+          <t>Analytics: keep operational DBs out of the analytics path (analytics_events is a landing buffer, never queried for analytics)</t>
         </is>
       </c>
       <c r="D62" s="11" t="inlineStr"/>
@@ -2711,37 +2728,37 @@
       <c r="A63" s="9" t="n">
         <v>23</v>
       </c>
-      <c r="B63" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B63" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C63" s="11" t="inlineStr">
         <is>
-          <t>Analytics: an actual ClickHouse/warehouse/data-lake query layer</t>
-        </is>
-      </c>
-      <c r="D63" s="11" t="inlineStr">
-        <is>
-          <t>Out of scope - this phase builds the landing pipeline only; no real destination system exists in this environment to integrate against honestly</t>
-        </is>
-      </c>
+          <t>Analytics: pipeline foundation for ClickHouse/warehouse/data lake (worker batches NDJSON into MinIO/S3)</t>
+        </is>
+      </c>
+      <c r="D63" s="11" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="9" t="n">
-        <v>24</v>
-      </c>
-      <c r="B64" s="10" t="inlineStr">
-        <is>
-          <t>Done</t>
+        <v>23</v>
+      </c>
+      <c r="B64" s="13" t="inlineStr">
+        <is>
+          <t>Pending</t>
         </is>
       </c>
       <c r="C64" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: provider-neutral interface (Provider: Name + Complete)</t>
-        </is>
-      </c>
-      <c r="D64" s="11" t="inlineStr"/>
+          <t>Analytics: an actual ClickHouse/warehouse/data-lake query layer</t>
+        </is>
+      </c>
+      <c r="D64" s="11" t="inlineStr">
+        <is>
+          <t>Out of scope - this phase builds the landing pipeline only; no real destination system exists in this environment to integrate against honestly</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="9" t="n">
@@ -2754,32 +2771,28 @@
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: local models / Ollama adapter</t>
-        </is>
-      </c>
-      <c r="D65" s="11" t="inlineStr">
-        <is>
-          <t>Real local inference via a new Ollama container, auto-pulled model, no vendor API key - the one live-testable provider</t>
-        </is>
-      </c>
+          <t>AI Gateway: provider-neutral interface (Provider: Name + Complete)</t>
+        </is>
+      </c>
+      <c r="D65" s="11" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="9" t="n">
         <v>24</v>
       </c>
-      <c r="B66" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B66" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C66" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: OpenAI adapter</t>
+          <t>AI Gateway: local models / Ollama adapter</t>
         </is>
       </c>
       <c r="D66" s="11" t="inlineStr">
         <is>
-          <t>Deferred - no real API key in this environment to validate against honestly</t>
+          <t>Real local inference via a new Ollama container, auto-pulled model, no vendor API key - the one live-testable provider</t>
         </is>
       </c>
     </row>
@@ -2794,7 +2807,7 @@
       </c>
       <c r="C67" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: Anthropic adapter</t>
+          <t>AI Gateway: OpenAI adapter</t>
         </is>
       </c>
       <c r="D67" s="11" t="inlineStr">
@@ -2814,7 +2827,7 @@
       </c>
       <c r="C68" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: Google adapter</t>
+          <t>AI Gateway: Anthropic adapter</t>
         </is>
       </c>
       <c r="D68" s="11" t="inlineStr">
@@ -2827,17 +2840,21 @@
       <c r="A69" s="9" t="n">
         <v>24</v>
       </c>
-      <c r="B69" s="10" t="inlineStr">
-        <is>
-          <t>Done</t>
+      <c r="B69" s="13" t="inlineStr">
+        <is>
+          <t>Pending</t>
         </is>
       </c>
       <c r="C69" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: model routing (product-facing ModelAlias, never a vendor model name)</t>
-        </is>
-      </c>
-      <c r="D69" s="11" t="inlineStr"/>
+          <t>AI Gateway: Google adapter</t>
+        </is>
+      </c>
+      <c r="D69" s="11" t="inlineStr">
+        <is>
+          <t>Deferred - no real API key in this environment to validate against honestly</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="9" t="n">
@@ -2850,7 +2867,7 @@
       </c>
       <c r="C70" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: quotas (ratelimit.Limiter reused a third time, 60/min/caller)</t>
+          <t>AI Gateway: model routing (product-facing ModelAlias, never a vendor model name)</t>
         </is>
       </c>
       <c r="D70" s="11" t="inlineStr"/>
@@ -2866,7 +2883,7 @@
       </c>
       <c r="C71" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: token usage tracking</t>
+          <t>AI Gateway: quotas (ratelimit.Limiter reused a third time, 60/min/caller)</t>
         </is>
       </c>
       <c r="D71" s="11" t="inlineStr"/>
@@ -2882,7 +2899,7 @@
       </c>
       <c r="C72" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: cost tracking (real per-route price table; Ollama honestly priced at 0)</t>
+          <t>AI Gateway: token usage tracking</t>
         </is>
       </c>
       <c r="D72" s="11" t="inlineStr"/>
@@ -2898,7 +2915,7 @@
       </c>
       <c r="C73" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: audit integration (new AIGatewayAuditRecorder, a genuine audit.Record per call)</t>
+          <t>AI Gateway: cost tracking (real per-route price table; Ollama honestly priced at 0)</t>
         </is>
       </c>
       <c r="D73" s="11" t="inlineStr"/>
@@ -2914,7 +2931,7 @@
       </c>
       <c r="C74" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: prompt/version metadata (free-form PromptKey/PromptVersion)</t>
+          <t>AI Gateway: audit integration (new AIGatewayAuditRecorder, a genuine audit.Record per call)</t>
         </is>
       </c>
       <c r="D74" s="11" t="inlineStr"/>
@@ -2930,7 +2947,7 @@
       </c>
       <c r="C75" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: timeouts (context.WithTimeout per provider call)</t>
+          <t>AI Gateway: prompt/version metadata (free-form PromptKey/PromptVersion)</t>
         </is>
       </c>
       <c r="D75" s="11" t="inlineStr"/>
@@ -2946,7 +2963,7 @@
       </c>
       <c r="C76" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: fallback (ordered provider/model chain, first success wins)</t>
+          <t>AI Gateway: timeouts (context.WithTimeout per provider call)</t>
         </is>
       </c>
       <c r="D76" s="11" t="inlineStr"/>
@@ -2955,37 +2972,37 @@
       <c r="A77" s="9" t="n">
         <v>24</v>
       </c>
-      <c r="B77" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B77" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C77" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: live token-quantity quota (as opposed to today's call-count quota)</t>
-        </is>
-      </c>
-      <c r="D77" s="11" t="inlineStr">
-        <is>
-          <t>Deferred - Repository already has the data (Completion.TotalTokens); not wired as a live gate yet</t>
-        </is>
-      </c>
+          <t>AI Gateway: fallback (ordered provider/model chain, first success wins)</t>
+        </is>
+      </c>
+      <c r="D77" s="11" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="9" t="n">
-        <v>25</v>
-      </c>
-      <c r="B78" s="10" t="inlineStr">
-        <is>
-          <t>Done</t>
+        <v>24</v>
+      </c>
+      <c r="B78" s="13" t="inlineStr">
+        <is>
+          <t>Pending</t>
         </is>
       </c>
       <c r="C78" s="11" t="inlineStr">
         <is>
-          <t>Admin Portal: real Keycloak-authenticated session (Resource Owner Password Credentials grant), httpOnly session cookie</t>
-        </is>
-      </c>
-      <c r="D78" s="11" t="inlineStr"/>
+          <t>AI Gateway: live token-quantity quota (as opposed to today's call-count quota)</t>
+        </is>
+      </c>
+      <c r="D78" s="11" t="inlineStr">
+        <is>
+          <t>Deferred - Repository already has the data (Completion.TotalTokens); not wired as a live gate yet</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="9" t="n">
@@ -2998,14 +3015,10 @@
       </c>
       <c r="C79" s="11" t="inlineStr">
         <is>
-          <t>Admin Portal: visibility - Applications</t>
-        </is>
-      </c>
-      <c r="D79" s="11" t="inlineStr">
-        <is>
-          <t>Real GET /v1/apps table</t>
-        </is>
-      </c>
+          <t>Admin Portal: real Keycloak-authenticated session (Resource Owner Password Credentials grant), httpOnly session cookie</t>
+        </is>
+      </c>
+      <c r="D79" s="11" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="9" t="n">
@@ -3018,12 +3031,12 @@
       </c>
       <c r="C80" s="11" t="inlineStr">
         <is>
-          <t>Admin Portal: visibility - Users (list + detail)</t>
+          <t>Admin Portal: visibility - Applications</t>
         </is>
       </c>
       <c r="D80" s="11" t="inlineStr">
         <is>
-          <t>New admin-wide GET /v1/users (cursor-paginated, platform.admin-gated)</t>
+          <t>Real GET /v1/apps table</t>
         </is>
       </c>
     </row>
@@ -3038,12 +3051,12 @@
       </c>
       <c r="C81" s="11" t="inlineStr">
         <is>
-          <t>Admin Portal: visibility - Roles/Permissions</t>
+          <t>Admin Portal: visibility - Users (list + detail)</t>
         </is>
       </c>
       <c r="D81" s="11" t="inlineStr">
         <is>
-          <t>New authz HTTP surface (GET/POST /v1/authz/roles, POST /v1/authz/roles/revoke) with a full grant/revoke UI</t>
+          <t>New admin-wide GET /v1/users (cursor-paginated, platform.admin-gated)</t>
         </is>
       </c>
     </row>
@@ -3058,10 +3071,14 @@
       </c>
       <c r="C82" s="11" t="inlineStr">
         <is>
-          <t>Admin Portal: visibility - Feature Flags, Configuration, Jobs</t>
-        </is>
-      </c>
-      <c r="D82" s="11" t="inlineStr"/>
+          <t>Admin Portal: visibility - Roles/Permissions</t>
+        </is>
+      </c>
+      <c r="D82" s="11" t="inlineStr">
+        <is>
+          <t>New authz HTTP surface (GET/POST /v1/authz/roles, POST /v1/authz/roles/revoke) with a full grant/revoke UI</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="9" t="n">
@@ -3074,7 +3091,7 @@
       </c>
       <c r="C83" s="11" t="inlineStr">
         <is>
-          <t>Admin Portal: visibility - Moderation, Audit</t>
+          <t>Admin Portal: visibility - Feature Flags, Configuration, Jobs</t>
         </is>
       </c>
       <c r="D83" s="11" t="inlineStr"/>
@@ -3090,14 +3107,10 @@
       </c>
       <c r="C84" s="11" t="inlineStr">
         <is>
-          <t>Admin Portal: visibility - System Health</t>
-        </is>
-      </c>
-      <c r="D84" s="11" t="inlineStr">
-        <is>
-          <t>Live GET /healthz against core-api/realtime-gateway/worker</t>
-        </is>
-      </c>
+          <t>Admin Portal: visibility - Moderation, Audit</t>
+        </is>
+      </c>
+      <c r="D84" s="11" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="9" t="n">
@@ -3110,30 +3123,30 @@
       </c>
       <c r="C85" s="11" t="inlineStr">
         <is>
-          <t>Admin Portal: visibility - Billing, AI Gateway usage (bonus, not roadmap-named)</t>
-        </is>
-      </c>
-      <c r="D85" s="11" t="inlineStr"/>
+          <t>Admin Portal: visibility - System Health</t>
+        </is>
+      </c>
+      <c r="D85" s="11" t="inlineStr">
+        <is>
+          <t>Live GET /healthz against core-api/realtime-gateway/worker</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="B86" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B86" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C86" s="11" t="inlineStr">
         <is>
-          <t>Admin Portal: visibility - Sessions/Devices, Tenants, Relationships, Messages, Notifications, Files</t>
-        </is>
-      </c>
-      <c r="D86" s="11" t="inlineStr">
-        <is>
-          <t>Deferred - each backing module only exposes a listMine-style self-scoped endpoint, not an admin-wide one; honest ComingSoon reasoning shown per area instead of fake rows</t>
-        </is>
-      </c>
+          <t>Admin Portal: visibility - Billing, AI Gateway usage (bonus, not roadmap-named)</t>
+        </is>
+      </c>
+      <c r="D86" s="11" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="9" t="n">
@@ -3146,18 +3159,18 @@
       </c>
       <c r="C87" s="11" t="inlineStr">
         <is>
-          <t>Admin Portal: visibility - Deployments</t>
+          <t>Admin Portal: visibility - Sessions/Devices, Tenants, Relationships, Messages, Notifications, Files</t>
         </is>
       </c>
       <c r="D87" s="11" t="inlineStr">
         <is>
-          <t>Deferred to Phase 29 - nothing in the platform tracks deployments as data yet</t>
+          <t>Deferred - each backing module only exposes a listMine-style self-scoped endpoint, not an admin-wide one; honest ComingSoon reasoning shown per area instead of fake rows</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B88" s="13" t="inlineStr">
         <is>
@@ -3166,110 +3179,138 @@
       </c>
       <c r="C88" s="11" t="inlineStr">
         <is>
-          <t>Backstage: integrate Backstage as developer portal</t>
-        </is>
-      </c>
-      <c r="D88" s="11" t="inlineStr"/>
+          <t>Admin Portal: visibility - Deployments</t>
+        </is>
+      </c>
+      <c r="D88" s="11" t="inlineStr">
+        <is>
+          <t>Deferred to Phase 29 - nothing in the platform tracks deployments as data yet</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="B89" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B89" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C89" s="11" t="inlineStr">
         <is>
-          <t>Backstage: per-module metadata: name/description/owner/lifecycle</t>
-        </is>
-      </c>
-      <c r="D89" s="11" t="inlineStr"/>
+          <t>Backstage: integrate Backstage as developer portal</t>
+        </is>
+      </c>
+      <c r="D89" s="11" t="inlineStr">
+        <is>
+          <t>Real @backstage/create-app instance at platform/backstage, catalog wired to real catalog/*.yaml + contracts/*/catalog-info.yaml, live-validated via the real catalog API (21 Components, 2 APIs, 1 System, 1 Group, 0 processing errors)</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="B90" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B90" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C90" s="11" t="inlineStr">
         <is>
-          <t>Backstage: per-module metadata: repository/documentation/dependencies</t>
-        </is>
-      </c>
-      <c r="D90" s="11" t="inlineStr"/>
+          <t>Backstage: per-module metadata - name/description/owner/lifecycle</t>
+        </is>
+      </c>
+      <c r="D90" s="11" t="inlineStr">
+        <is>
+          <t>All 16 modules/*/module.yaml + README.md real (11 were still stub text before this phase)</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="B91" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B91" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C91" s="11" t="inlineStr">
         <is>
-          <t>Backstage: per-module metadata: APIs/events/DB ownership/dashboards/runbooks</t>
-        </is>
-      </c>
-      <c r="D91" s="11" t="inlineStr"/>
+          <t>Backstage: per-module metadata - repository/documentation</t>
+        </is>
+      </c>
+      <c r="D91" s="11" t="inlineStr">
+        <is>
+          <t>Every Component links its module README; the System entity links VALIDATION.md and the new docs/RUNBOOKS.md</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="9" t="n">
-        <v>27</v>
-      </c>
-      <c r="B92" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+        <v>26</v>
+      </c>
+      <c r="B92" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C92" s="11" t="inlineStr">
         <is>
-          <t>SDKs: Flutter SDK</t>
-        </is>
-      </c>
-      <c r="D92" s="11" t="inlineStr"/>
+          <t>Backstage: per-module metadata - dependencies</t>
+        </is>
+      </c>
+      <c r="D92" s="11" t="inlineStr">
+        <is>
+          <t>Component dependsOn mirrors modules/*/module.yaml's real dependency graph; Backstage computes reverse dependencyOf relations automatically, confirmed live</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="9" t="n">
-        <v>27</v>
-      </c>
-      <c r="B93" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+        <v>26</v>
+      </c>
+      <c r="B93" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C93" s="11" t="inlineStr">
         <is>
-          <t>SDKs: TypeScript SDK</t>
-        </is>
-      </c>
-      <c r="D93" s="11" t="inlineStr"/>
+          <t>Backstage: per-module metadata - APIs</t>
+        </is>
+      </c>
+      <c r="D93" s="11" t="inlineStr">
+        <is>
+          <t>2 API entities (OpenAPI, AsyncAPI), both with their full real spec embedded and live-loaded</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="9" t="n">
-        <v>27</v>
-      </c>
-      <c r="B94" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+        <v>26</v>
+      </c>
+      <c r="B94" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C94" s="11" t="inlineStr">
         <is>
-          <t>SDKs: Go SDK</t>
-        </is>
-      </c>
-      <c r="D94" s="11" t="inlineStr"/>
+          <t>Backstage: per-module metadata - events</t>
+        </is>
+      </c>
+      <c r="D94" s="11" t="inlineStr">
+        <is>
+          <t>providesApis set only on the components whose code actually calls outbox.Record, cross-checked against the real Go source</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B95" s="13" t="inlineStr">
         <is>
@@ -3278,42 +3319,54 @@
       </c>
       <c r="C95" s="11" t="inlineStr">
         <is>
-          <t>SDKs: auth + token refresh in each SDK</t>
-        </is>
-      </c>
-      <c r="D95" s="11" t="inlineStr"/>
+          <t>Backstage: per-module metadata - database ownership</t>
+        </is>
+      </c>
+      <c r="D95" s="11" t="inlineStr">
+        <is>
+          <t>Deferred - no per-module DB-ownership annotation convention chosen yet; docs/control's Modules sheet tracks this today at a finer grain than catalog/system.yaml's 16 domains</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="9" t="n">
-        <v>27</v>
-      </c>
-      <c r="B96" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+        <v>26</v>
+      </c>
+      <c r="B96" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C96" s="11" t="inlineStr">
         <is>
-          <t>SDKs: pagination + safe retries</t>
-        </is>
-      </c>
-      <c r="D96" s="11" t="inlineStr"/>
+          <t>Backstage: per-module metadata - dashboards</t>
+        </is>
+      </c>
+      <c r="D96" s="11" t="inlineStr">
+        <is>
+          <t>core-platform.io/dashboard annotation on each service pointing at the real local Grafana instance - no per-service dashboard exists yet (that's Phase 28), so it points at the shared instance, documented as such</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="9" t="n">
-        <v>27</v>
-      </c>
-      <c r="B97" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+        <v>26</v>
+      </c>
+      <c r="B97" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C97" s="11" t="inlineStr">
         <is>
-          <t>SDKs: realtime connection helper</t>
-        </is>
-      </c>
-      <c r="D97" s="11" t="inlineStr"/>
+          <t>Backstage: per-module metadata - runbooks</t>
+        </is>
+      </c>
+      <c r="D97" s="11" t="inlineStr">
+        <is>
+          <t>New docs/RUNBOOKS.md, linked from the System entity</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="9" t="n">
@@ -3326,7 +3379,7 @@
       </c>
       <c r="C98" s="11" t="inlineStr">
         <is>
-          <t>SDKs: correlation ID propagation</t>
+          <t>SDKs: Flutter SDK</t>
         </is>
       </c>
       <c r="D98" s="11" t="inlineStr"/>
@@ -3342,14 +3395,14 @@
       </c>
       <c r="C99" s="11" t="inlineStr">
         <is>
-          <t>SDKs: device registration helper</t>
+          <t>SDKs: TypeScript SDK</t>
         </is>
       </c>
       <c r="D99" s="11" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B100" s="13" t="inlineStr">
         <is>
@@ -3358,14 +3411,14 @@
       </c>
       <c r="C100" s="11" t="inlineStr">
         <is>
-          <t>Observability Completion: structured logs everywhere</t>
+          <t>SDKs: Go SDK</t>
         </is>
       </c>
       <c r="D100" s="11" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B101" s="13" t="inlineStr">
         <is>
@@ -3374,14 +3427,14 @@
       </c>
       <c r="C101" s="11" t="inlineStr">
         <is>
-          <t>Observability Completion: metrics everywhere</t>
+          <t>SDKs: auth + token refresh in each SDK</t>
         </is>
       </c>
       <c r="D101" s="11" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B102" s="13" t="inlineStr">
         <is>
@@ -3390,14 +3443,14 @@
       </c>
       <c r="C102" s="11" t="inlineStr">
         <is>
-          <t>Observability Completion: distributed traces everywhere</t>
+          <t>SDKs: pagination + safe retries</t>
         </is>
       </c>
       <c r="D102" s="11" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B103" s="13" t="inlineStr">
         <is>
@@ -3406,14 +3459,14 @@
       </c>
       <c r="C103" s="11" t="inlineStr">
         <is>
-          <t>Observability Completion: health checks everywhere</t>
+          <t>SDKs: realtime connection helper</t>
         </is>
       </c>
       <c r="D103" s="11" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B104" s="13" t="inlineStr">
         <is>
@@ -3422,14 +3475,14 @@
       </c>
       <c r="C104" s="11" t="inlineStr">
         <is>
-          <t>Observability Completion: dashboard: API latency</t>
+          <t>SDKs: correlation ID propagation</t>
         </is>
       </c>
       <c r="D104" s="11" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B105" s="13" t="inlineStr">
         <is>
@@ -3438,7 +3491,7 @@
       </c>
       <c r="C105" s="11" t="inlineStr">
         <is>
-          <t>Observability Completion: dashboard: error rate</t>
+          <t>SDKs: device registration helper</t>
         </is>
       </c>
       <c r="D105" s="11" t="inlineStr"/>
@@ -3454,7 +3507,7 @@
       </c>
       <c r="C106" s="11" t="inlineStr">
         <is>
-          <t>Observability Completion: dashboard: requests/sec</t>
+          <t>Observability Completion: structured logs everywhere</t>
         </is>
       </c>
       <c r="D106" s="11" t="inlineStr"/>
@@ -3470,7 +3523,7 @@
       </c>
       <c r="C107" s="11" t="inlineStr">
         <is>
-          <t>Observability Completion: dashboard: DB connections</t>
+          <t>Observability Completion: metrics everywhere</t>
         </is>
       </c>
       <c r="D107" s="11" t="inlineStr"/>
@@ -3486,7 +3539,7 @@
       </c>
       <c r="C108" s="11" t="inlineStr">
         <is>
-          <t>Observability Completion: dashboard: Kafka lag</t>
+          <t>Observability Completion: distributed traces everywhere</t>
         </is>
       </c>
       <c r="D108" s="11" t="inlineStr"/>
@@ -3502,7 +3555,7 @@
       </c>
       <c r="C109" s="11" t="inlineStr">
         <is>
-          <t>Observability Completion: dashboard: WebSocket connections</t>
+          <t>Observability Completion: health checks everywhere</t>
         </is>
       </c>
       <c r="D109" s="11" t="inlineStr"/>
@@ -3518,7 +3571,7 @@
       </c>
       <c r="C110" s="11" t="inlineStr">
         <is>
-          <t>Observability Completion: dashboard: Redis latency</t>
+          <t>Observability Completion: dashboard: API latency</t>
         </is>
       </c>
       <c r="D110" s="11" t="inlineStr"/>
@@ -3534,7 +3587,7 @@
       </c>
       <c r="C111" s="11" t="inlineStr">
         <is>
-          <t>Observability Completion: dashboard: notification failures</t>
+          <t>Observability Completion: dashboard: error rate</t>
         </is>
       </c>
       <c r="D111" s="11" t="inlineStr"/>
@@ -3550,7 +3603,7 @@
       </c>
       <c r="C112" s="11" t="inlineStr">
         <is>
-          <t>Observability Completion: dashboard: background job failures</t>
+          <t>Observability Completion: dashboard: requests/sec</t>
         </is>
       </c>
       <c r="D112" s="11" t="inlineStr"/>
@@ -3566,14 +3619,14 @@
       </c>
       <c r="C113" s="11" t="inlineStr">
         <is>
-          <t>Observability Completion: alerting rules</t>
+          <t>Observability Completion: dashboard: DB connections</t>
         </is>
       </c>
       <c r="D113" s="11" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B114" s="13" t="inlineStr">
         <is>
@@ -3582,14 +3635,14 @@
       </c>
       <c r="C114" s="11" t="inlineStr">
         <is>
-          <t>Platform Control Plane: one view: applications/services/versions</t>
+          <t>Observability Completion: dashboard: Kafka lag</t>
         </is>
       </c>
       <c r="D114" s="11" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B115" s="13" t="inlineStr">
         <is>
@@ -3598,14 +3651,14 @@
       </c>
       <c r="C115" s="11" t="inlineStr">
         <is>
-          <t>Platform Control Plane: one view: environments/dependencies/deployments</t>
+          <t>Observability Completion: dashboard: WebSocket connections</t>
         </is>
       </c>
       <c r="D115" s="11" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B116" s="13" t="inlineStr">
         <is>
@@ -3614,14 +3667,14 @@
       </c>
       <c r="C116" s="11" t="inlineStr">
         <is>
-          <t>Platform Control Plane: one view: DB ownership/events/API contracts</t>
+          <t>Observability Completion: dashboard: Redis latency</t>
         </is>
       </c>
       <c r="D116" s="11" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B117" s="13" t="inlineStr">
         <is>
@@ -3630,14 +3683,14 @@
       </c>
       <c r="C117" s="11" t="inlineStr">
         <is>
-          <t>Platform Control Plane: one view: health/alerts/recent changes</t>
+          <t>Observability Completion: dashboard: notification failures</t>
         </is>
       </c>
       <c r="D117" s="11" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="9" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B118" s="13" t="inlineStr">
         <is>
@@ -3646,14 +3699,14 @@
       </c>
       <c r="C118" s="11" t="inlineStr">
         <is>
-          <t>AI Development Context: every module: README</t>
+          <t>Observability Completion: dashboard: background job failures</t>
         </is>
       </c>
       <c r="D118" s="11" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="9" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B119" s="13" t="inlineStr">
         <is>
@@ -3662,14 +3715,14 @@
       </c>
       <c r="C119" s="11" t="inlineStr">
         <is>
-          <t>AI Development Context: every module: ownership metadata</t>
+          <t>Observability Completion: alerting rules</t>
         </is>
       </c>
       <c r="D119" s="11" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="9" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B120" s="13" t="inlineStr">
         <is>
@@ -3678,14 +3731,14 @@
       </c>
       <c r="C120" s="11" t="inlineStr">
         <is>
-          <t>AI Development Context: every module: dependencies</t>
+          <t>Platform Control Plane: one view: applications/services/versions</t>
         </is>
       </c>
       <c r="D120" s="11" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="9" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B121" s="13" t="inlineStr">
         <is>
@@ -3694,14 +3747,14 @@
       </c>
       <c r="C121" s="11" t="inlineStr">
         <is>
-          <t>AI Development Context: every module: API contract</t>
+          <t>Platform Control Plane: one view: environments/dependencies/deployments</t>
         </is>
       </c>
       <c r="D121" s="11" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="9" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B122" s="13" t="inlineStr">
         <is>
@@ -3710,26 +3763,122 @@
       </c>
       <c r="C122" s="11" t="inlineStr">
         <is>
-          <t>AI Development Context: every module: event contracts</t>
+          <t>Platform Control Plane: one view: DB ownership/events/API contracts</t>
         </is>
       </c>
       <c r="D122" s="11" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="9" t="n">
+        <v>29</v>
+      </c>
+      <c r="B123" s="13" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="C123" s="11" t="inlineStr">
+        <is>
+          <t>Platform Control Plane: one view: health/alerts/recent changes</t>
+        </is>
+      </c>
+      <c r="D123" s="11" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="B123" s="13" t="inlineStr">
+      <c r="B124" s="13" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="C123" s="11" t="inlineStr">
+      <c r="C124" s="11" t="inlineStr">
+        <is>
+          <t>AI Development Context: every module: README</t>
+        </is>
+      </c>
+      <c r="D124" s="11" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="B125" s="13" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="C125" s="11" t="inlineStr">
+        <is>
+          <t>AI Development Context: every module: ownership metadata</t>
+        </is>
+      </c>
+      <c r="D125" s="11" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="B126" s="13" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="C126" s="11" t="inlineStr">
+        <is>
+          <t>AI Development Context: every module: dependencies</t>
+        </is>
+      </c>
+      <c r="D126" s="11" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="B127" s="13" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="C127" s="11" t="inlineStr">
+        <is>
+          <t>AI Development Context: every module: API contract</t>
+        </is>
+      </c>
+      <c r="D127" s="11" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="B128" s="13" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="C128" s="11" t="inlineStr">
+        <is>
+          <t>AI Development Context: every module: event contracts</t>
+        </is>
+      </c>
+      <c r="D128" s="11" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="B129" s="13" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="C129" s="11" t="inlineStr">
         <is>
           <t>AI Development Context: every module: DB ownership</t>
         </is>
       </c>
-      <c r="D123" s="11" t="inlineStr"/>
+      <c r="D129" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8443,7 +8592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -8889,6 +9038,28 @@
       <c r="D20" s="11" t="inlineStr">
         <is>
           <t>Then open http://localhost:3000 and sign in with demo/demo. Real UI over real data (Phase 25) - Users, Roles, Audit, Moderation, Feature Flags, Jobs, Configuration, System Health, Billing, AI Gateway. Needs core-api (and ideally realtime-gateway/worker) already running per steps 5-7.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="48" customHeight="1">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>Browse the real developer-portal catalog</t>
+        </is>
+      </c>
+      <c r="C21" s="11" t="inlineStr">
+        <is>
+          <t>cd platform/backstage &amp;&amp; yarn install &amp;&amp; yarn start</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="inlineStr">
+        <is>
+          <t>Needs Node 20/22 and a real Yarn install - see platform/backstage/README.md if the versions on $PATH don't satisfy Backstage's own prerequisite check. Then open http://localhost:3000 (stop the Admin Portal first, they share a port) and browse the Catalog - every module/service/app is a real entity (Phase 26), not example fixture data.</t>
         </is>
       </c>
     </row>
@@ -8906,7 +9077,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -9000,34 +9171,34 @@
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>realtime-gateway</t>
+          <t>backstage (platform/backstage)</t>
         </is>
       </c>
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t>Go service</t>
+          <t>Backstage app</t>
         </is>
       </c>
       <c r="C4" s="11" t="inlineStr">
         <is>
-          <t>ws://localhost:8090</t>
+          <t>http://localhost:3000 (frontend), :7007 (backend)</t>
         </is>
       </c>
       <c r="D4" s="11" t="inlineStr">
         <is>
-          <t>WebSocket connections, presence, channel fan-out.</t>
+          <t>The developer portal (Phase 26) - real catalog of every module/service/app. Shares apps/admin's default frontend port 3000, so only run one of the two at a time locally unless one's app-config.yaml is repointed at a different port.</t>
         </is>
       </c>
       <c r="E4" s="11" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>guest auth only, no credentials</t>
         </is>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1">
       <c r="A5" s="11" t="inlineStr">
         <is>
-          <t>worker</t>
+          <t>realtime-gateway</t>
         </is>
       </c>
       <c r="B5" s="11" t="inlineStr">
@@ -9037,12 +9208,12 @@
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>http://localhost:8091 (health only)</t>
+          <t>ws://localhost:8090</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
-          <t>Background job runner, search indexer, Temporal workflow worker, analytics NDJSON pipeline.</t>
+          <t>WebSocket connections, presence, channel fan-out.</t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
@@ -9054,34 +9225,34 @@
     <row r="6" ht="32" customHeight="1">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>Postgres</t>
+          <t>worker</t>
         </is>
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Docker container</t>
+          <t>Go service</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>localhost:5432</t>
+          <t>http://localhost:8091 (health only)</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>System of record for every domain module.</t>
+          <t>Background job runner, search indexer, Temporal workflow worker, analytics NDJSON pipeline.</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>core / core, db 'core'</t>
+          <t>n/a</t>
         </is>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>Valkey (Redis-compatible)</t>
+          <t>Postgres</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr">
@@ -9091,24 +9262,24 @@
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>localhost:6379</t>
+          <t>localhost:5432</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>Realtime pub/sub fan-out, presence (TTL-based).</t>
+          <t>System of record for every domain module.</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>no auth locally</t>
+          <t>core / core, db 'core'</t>
         </is>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>Keycloak</t>
+          <t>Valkey (Redis-compatible)</t>
         </is>
       </c>
       <c r="B8" s="11" t="inlineStr">
@@ -9118,24 +9289,24 @@
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>http://localhost:8081</t>
+          <t>localhost:6379</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>Identity provider. Realm 'core' is re-imported on every restart (no persistent volume).</t>
+          <t>Realtime pub/sub fan-out, presence (TTL-based).</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>admin/admin (master realm); demo/demo (core realm, seeded user)</t>
+          <t>no auth locally</t>
         </is>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1">
       <c r="A9" s="11" t="inlineStr">
         <is>
-          <t>OpenFGA</t>
+          <t>Keycloak</t>
         </is>
       </c>
       <c r="B9" s="11" t="inlineStr">
@@ -9145,24 +9316,24 @@
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>http://localhost:8082</t>
+          <t>http://localhost:8081</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>Fine-grained ReBAC engine behind authz.Service.Can. In-memory store, self-heals its store/model on every restart.</t>
+          <t>Identity provider. Realm 'core' is re-imported on every restart (no persistent volume).</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>no auth locally</t>
+          <t>admin/admin (master realm); demo/demo (core realm, seeded user)</t>
         </is>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>MinIO (S3-compatible)</t>
+          <t>OpenFGA</t>
         </is>
       </c>
       <c r="B10" s="11" t="inlineStr">
@@ -9172,24 +9343,24 @@
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>http://localhost:9000</t>
+          <t>http://localhost:8082</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>Object storage backing the files module.</t>
+          <t>Fine-grained ReBAC engine behind authz.Service.Can. In-memory store, self-heals its store/model on every restart.</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>minio / minio123, bucket 'core-platform'</t>
+          <t>no auth locally</t>
         </is>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1">
       <c r="A11" s="11" t="inlineStr">
         <is>
-          <t>OpenSearch</t>
+          <t>MinIO (S3-compatible)</t>
         </is>
       </c>
       <c r="B11" s="11" t="inlineStr">
@@ -9199,24 +9370,24 @@
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>http://localhost:9200</t>
+          <t>http://localhost:9000</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>Backs the search module, indexed by worker's indexer.</t>
+          <t>Object storage backing the files module.</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>no auth locally</t>
+          <t>minio / minio123, bucket 'core-platform'</t>
         </is>
       </c>
     </row>
     <row r="12" ht="32" customHeight="1">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>Temporal</t>
+          <t>OpenSearch</t>
         </is>
       </c>
       <c r="B12" s="11" t="inlineStr">
@@ -9226,12 +9397,12 @@
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>localhost:7233</t>
+          <t>http://localhost:9200</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>Durable workflow execution engine behind the workflows module.</t>
+          <t>Backs the search module, indexed by worker's indexer.</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
@@ -9243,7 +9414,7 @@
     <row r="13" ht="32" customHeight="1">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t>Kafka / Redpanda</t>
+          <t>Temporal</t>
         </is>
       </c>
       <c r="B13" s="11" t="inlineStr">
@@ -9253,12 +9424,12 @@
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>localhost:9092</t>
+          <t>localhost:7233</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>Health-checked today; no producer wired yet (outbox-to-Kafka relay is a documented future gap).</t>
+          <t>Durable workflow execution engine behind the workflows module.</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
@@ -9270,7 +9441,7 @@
     <row r="14" ht="32" customHeight="1">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>Ollama</t>
+          <t>Kafka / Redpanda</t>
         </is>
       </c>
       <c r="B14" s="11" t="inlineStr">
@@ -9280,12 +9451,12 @@
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>http://localhost:11434</t>
+          <t>localhost:9092</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>Real local LLM inference behind the AI Gateway - model qwen2.5:0.5b auto-pulled on every start, no vendor API key needed.</t>
+          <t>Health-checked today; no producer wired yet (outbox-to-Kafka relay is a documented future gap).</t>
         </is>
       </c>
       <c r="E14" s="11" t="inlineStr">
@@ -9297,25 +9468,52 @@
     <row r="15" ht="32" customHeight="1">
       <c r="A15" s="11" t="inlineStr">
         <is>
+          <t>Ollama</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>Docker container</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>http://localhost:11434</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>Real local LLM inference behind the AI Gateway - model qwen2.5:0.5b auto-pulled on every start, no vendor API key needed.</t>
+        </is>
+      </c>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>no auth locally</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="32" customHeight="1">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
           <t>OTel Collector / Tempo / Prometheus / Grafana / Loki</t>
         </is>
       </c>
-      <c r="B15" s="11" t="inlineStr">
+      <c r="B16" s="11" t="inlineStr">
         <is>
           <t>Docker containers</t>
         </is>
       </c>
-      <c r="C15" s="11" t="inlineStr">
+      <c r="C16" s="11" t="inlineStr">
         <is>
           <t>see infra/docker/docker-compose.yml</t>
         </is>
       </c>
-      <c r="D15" s="11" t="inlineStr">
+      <c r="D16" s="11" t="inlineStr">
         <is>
           <t>Full observability stack - traces, metrics, logs, dashboards.</t>
         </is>
       </c>
-      <c r="E15" s="11" t="inlineStr">
+      <c r="E16" s="11" t="inlineStr">
         <is>
           <t>no auth locally</t>
         </is>

--- a/docs/control/data.xlsx
+++ b/docs/control/data.xlsx
@@ -239,8 +239,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="TodoChecklist" displayName="TodoChecklist" ref="A1:D129" headerRowCount="1">
-  <autoFilter ref="A1:D129"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="TodoChecklist" displayName="TodoChecklist" ref="A1:D132" headerRowCount="1">
+  <autoFilter ref="A1:D132"/>
   <tableColumns count="4">
     <tableColumn id="1" name="Phase"/>
     <tableColumn id="2" name="Status"/>
@@ -281,8 +281,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="HowToTest" displayName="HowToTest" ref="A1:D21" headerRowCount="1">
-  <autoFilter ref="A1:D21"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="HowToTest" displayName="HowToTest" ref="A1:D24" headerRowCount="1">
+  <autoFilter ref="A1:D24"/>
   <tableColumns count="4">
     <tableColumn id="1" name="Step"/>
     <tableColumn id="2" name="What"/>
@@ -596,7 +596,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -633,12 +633,12 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>26 / 30</t>
+          <t>27 / 30</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>87%</t>
+          <t>90%</t>
         </is>
       </c>
     </row>
@@ -689,156 +689,173 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>platform/backstage (real @backstage/create-app, 24-entity catalog)</t>
+          <t>platform/backstage (real @backstage/create-app, 27-entity catalog)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Shared Go packages</t>
+          <t>Client SDKs</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>packages/go/platformkit</t>
+          <t>Go, TypeScript, Dart - packages/go/coresdk, packages/typescript/core-sdk, packages/flutter/core_sdk</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Domain modules (core-api)</t>
+          <t>Shared Go packages</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>one per completed backend phase</t>
+          <t>packages/go/platformkit</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Live HTTP endpoints</t>
+          <t>Domain modules (core-api)</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>see 'API Endpoints' sheet</t>
+          <t>one per completed backend phase</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>DB migrations</t>
+          <t>Live HTTP endpoints</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>146</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>data/migrations/0001-0022</t>
+          <t>see 'API Endpoints' sheet</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Real infra dependencies</t>
+          <t>DB migrations</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>Postgres, Valkey, Keycloak, OpenFGA, MinIO, OpenSearch, Temporal, Kafka/Redpanda, Ollama, OTel</t>
+          <t>data/migrations/0001-0022</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
+          <t>Real infra dependencies</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>Postgres, Valkey, Keycloak, OpenFGA, MinIO, OpenSearch, Temporal, Kafka/Redpanda, Ollama, OTel</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
           <t>Commits so far</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>see git log</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>How to read this workbook</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>• Roadmap - all 30 phases, one row each, status + what it delivers.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>• Todo Checklist - granular task list (completed sub-items and still-to-do sub-items) so progress is trackable at a finer grain than 'phase done or not'.</t>
+          <t>• Roadmap - all 30 phases, one row each, status + what it delivers.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>• Modules - every backend/core-api/internal module: what it owns, its storage, its access rule.</t>
+          <t>• Todo Checklist - granular task list (completed sub-items and still-to-do sub-items) so progress is trackable at a finer grain than 'phase done or not'.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>• API Endpoints - every live HTTP route across all three services, with auth level.</t>
+          <t>• Modules - every backend/core-api/internal module: what it owns, its storage, its access rule.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>• How To Test - copy-paste steps to bring the stack up locally and exercise it for real (mint a token, call endpoints, open a WebSocket).</t>
+          <t>• API Endpoints - every live HTTP route across all three services, with auth level.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>• How To Test - copy-paste steps to bring the stack up locally and exercise it for real (mint a token, call endpoints, open a WebSocket).</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>• Infra &amp; Credentials - every local service, its port, and its local-only credentials.</t>
         </is>
@@ -848,8 +865,8 @@
   <mergeCells count="7">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A23:F23"/>
     <mergeCell ref="A22:F22"/>
-    <mergeCell ref="A17:F17"/>
     <mergeCell ref="A18:F18"/>
     <mergeCell ref="A20:F20"/>
     <mergeCell ref="A21:F21"/>
@@ -1555,9 +1572,9 @@
       <c r="A28" s="9" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="12" t="inlineStr">
-        <is>
-          <t>Next up</t>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C28" s="11" t="inlineStr">
@@ -1567,12 +1584,12 @@
       </c>
       <c r="D28" s="11" t="inlineStr">
         <is>
-          <t>Flutter SDK, TypeScript SDK, Go SDK - auth, token refresh, API calls, errors, pagination, safe retries, realtime connection, correlation IDs, device registration. Future products talk to Core primarily through these.</t>
+          <t>Go (packages/go/coresdk), TypeScript (packages/typescript/core-sdk), and Dart (packages/flutter/core_sdk) - auth/token refresh, typed API calls, errors, pagination, GET-only retries, a real realtime WebSocket client, device registration, in all three. Each proven by a real consumer: apps/admin migrated its entire API layer to the TS SDK; apps/mobile's login/profile flow uses the Dart SDK (and closed a real Phase 9 gap - make flutter-test now passes). 39 unit tests total, all against real local HTTP servers, plus live validation against real Keycloak/core-api/realtime-gateway for all three.</t>
         </is>
       </c>
       <c r="E28" s="11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>12b9046</t>
         </is>
       </c>
     </row>
@@ -1580,9 +1597,9 @@
       <c r="A29" s="9" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B29" s="12" t="inlineStr">
+        <is>
+          <t>Next up</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
@@ -1665,7 +1682,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D129"/>
+  <dimension ref="A1:D132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2114,7 +2131,7 @@
     </row>
     <row r="28">
       <c r="A28" s="9" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
@@ -2123,14 +2140,14 @@
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>Repo health baseline (make doctor / validate-all / go test / go build) run and passed</t>
+          <t>Phase 27: SDKs implemented, unit-tested, live-validated, documented, committed</t>
         </is>
       </c>
       <c r="D28" s="11" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
@@ -2139,18 +2156,14 @@
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>Environment / ApplicationVersion / ApplicationConfiguration</t>
-        </is>
-      </c>
-      <c r="D29" s="11" t="inlineStr">
-        <is>
-          <t>Deferred - no consumer needs them yet, documented as intentional in applications/README.md</t>
-        </is>
-      </c>
+          <t>Repo health baseline (make doctor / validate-all / go test / go build) run and passed</t>
+        </is>
+      </c>
+      <c r="D29" s="11" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
@@ -2159,32 +2172,32 @@
       </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t>Separate Session table</t>
+          <t>Environment / ApplicationVersion / ApplicationConfiguration</t>
         </is>
       </c>
       <c r="D30" s="11" t="inlineStr">
         <is>
-          <t>Deferred - Device.SessionStatus covers today's single-session-per-device need, documented in devices/README.md</t>
+          <t>Deferred - no consumer needs them yet, documented as intentional in applications/README.md</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="B31" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+        <v>5</v>
+      </c>
+      <c r="B31" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>UserPreferences (named in Phase 4, no fields ever specified)</t>
+          <t>Separate Session table</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>Deferred to Phase 12+; notification preferences shipped, a generic preferences bag did not</t>
+          <t>Deferred - Device.SessionStatus covers today's single-session-per-device need, documented in devices/README.md</t>
         </is>
       </c>
     </row>
@@ -2199,12 +2212,12 @@
       </c>
       <c r="C32" s="11" t="inlineStr">
         <is>
-          <t>apps/mobile test/ directory (make flutter-test currently fails)</t>
+          <t>UserPreferences (named in Phase 4, no fields ever specified)</t>
         </is>
       </c>
       <c r="D32" s="11" t="inlineStr">
         <is>
-          <t>Known gap since Phase 9's audit, not yet picked up</t>
+          <t>Deferred to Phase 12+; notification preferences shipped, a generic preferences bag did not</t>
         </is>
       </c>
     </row>
@@ -2219,30 +2232,34 @@
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>apps/admin next@15 / sharp transitive advisories</t>
+          <t>apps/mobile test/ directory (make flutter-test currently fails)</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>Fix is a Next.js major-version bump - separate, reviewable change</t>
+          <t>Known gap since Phase 9's audit, not yet picked up</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="9" t="n">
-        <v>20</v>
-      </c>
-      <c r="B34" s="10" t="inlineStr">
-        <is>
-          <t>Done</t>
+        <v>9</v>
+      </c>
+      <c r="B34" s="13" t="inlineStr">
+        <is>
+          <t>Pending</t>
         </is>
       </c>
       <c r="C34" s="11" t="inlineStr">
         <is>
-          <t>Privacy: consent (append-only history)</t>
-        </is>
-      </c>
-      <c r="D34" s="11" t="inlineStr"/>
+          <t>apps/admin next@15 / sharp transitive advisories</t>
+        </is>
+      </c>
+      <c r="D34" s="11" t="inlineStr">
+        <is>
+          <t>Fix is a Next.js major-version bump - separate, reviewable change</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="9" t="n">
@@ -2255,7 +2272,7 @@
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>Privacy: user data export (ExportUserData registry - users/devices/files/audit)</t>
+          <t>Privacy: consent (append-only history)</t>
         </is>
       </c>
       <c r="D35" s="11" t="inlineStr"/>
@@ -2271,7 +2288,7 @@
       </c>
       <c r="C36" s="11" t="inlineStr">
         <is>
-          <t>Privacy: user deletion (DeleteUserData registry - users/devices/files; audit deliberately excluded)</t>
+          <t>Privacy: user data export (ExportUserData registry - users/devices/files/audit)</t>
         </is>
       </c>
       <c r="D36" s="11" t="inlineStr"/>
@@ -2287,7 +2304,7 @@
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>Privacy: retention policy (declared, not scheduled - same documented gap as Phase 13's PurgeExpired)</t>
+          <t>Privacy: user deletion (DeleteUserData registry - users/devices/files; audit deliberately excluded)</t>
         </is>
       </c>
       <c r="D37" s="11" t="inlineStr"/>
@@ -2303,7 +2320,7 @@
       </c>
       <c r="C38" s="11" t="inlineStr">
         <is>
-          <t>Privacy: privacy preferences</t>
+          <t>Privacy: retention policy (declared, not scheduled - same documented gap as Phase 13's PurgeExpired)</t>
         </is>
       </c>
       <c r="D38" s="11" t="inlineStr"/>
@@ -2319,7 +2336,7 @@
       </c>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>Privacy: coordinate deletion through workflows/events - core-api's own embedded Temporal worker</t>
+          <t>Privacy: privacy preferences</t>
         </is>
       </c>
       <c r="D39" s="11" t="inlineStr"/>
@@ -2328,21 +2345,17 @@
       <c r="A40" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="B40" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B40" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C40" s="11" t="inlineStr">
         <is>
-          <t>Privacy: notifications module as an Export/Delete participant</t>
-        </is>
-      </c>
-      <c r="D40" s="11" t="inlineStr">
-        <is>
-          <t>Deliberately deferred to prove the registry makes this a 2-line addition later, not a framework change</t>
-        </is>
-      </c>
+          <t>Privacy: coordinate deletion through workflows/events - core-api's own embedded Temporal worker</t>
+        </is>
+      </c>
+      <c r="D40" s="11" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="9" t="n">
@@ -2355,32 +2368,32 @@
       </c>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>Privacy: relationships/groups/messaging as participants</t>
+          <t>Privacy: notifications module as an Export/Delete participant</t>
         </is>
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t>Deferred - shared multi-user data needs a redaction strategy this phase's per-user-in-isolation registry doesn't fit</t>
+          <t>Deliberately deferred to prove the registry makes this a 2-line addition later, not a framework change</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="9" t="n">
-        <v>21</v>
-      </c>
-      <c r="B42" s="10" t="inlineStr">
-        <is>
-          <t>Done</t>
+        <v>20</v>
+      </c>
+      <c r="B42" s="13" t="inlineStr">
+        <is>
+          <t>Pending</t>
         </is>
       </c>
       <c r="C42" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: Block</t>
+          <t>Privacy: relationships/groups/messaging as participants</t>
         </is>
       </c>
       <c r="D42" s="11" t="inlineStr">
         <is>
-          <t>Reused Phase 8's relationships (Status='blocked'), deliberately not duplicated</t>
+          <t>Deferred - shared multi-user data needs a redaction strategy this phase's per-user-in-isolation registry doesn't fit</t>
         </is>
       </c>
     </row>
@@ -2395,10 +2408,14 @@
       </c>
       <c r="C43" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: Mute</t>
-        </is>
-      </c>
-      <c r="D43" s="11" t="inlineStr"/>
+          <t>Trust &amp; Safety: Block</t>
+        </is>
+      </c>
+      <c r="D43" s="11" t="inlineStr">
+        <is>
+          <t>Reused Phase 8's relationships (Status='blocked'), deliberately not duplicated</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="9" t="n">
@@ -2411,7 +2428,7 @@
       </c>
       <c r="C44" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: Report -&gt; ModerationCase (deduplicated via partial unique index)</t>
+          <t>Trust &amp; Safety: Mute</t>
         </is>
       </c>
       <c r="D44" s="11" t="inlineStr"/>
@@ -2427,7 +2444,7 @@
       </c>
       <c r="C45" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: Suspension</t>
+          <t>Trust &amp; Safety: Report -&gt; ModerationCase (deduplicated via partial unique index)</t>
         </is>
       </c>
       <c r="D45" s="11" t="inlineStr"/>
@@ -2443,7 +2460,7 @@
       </c>
       <c r="C46" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: Ban</t>
+          <t>Trust &amp; Safety: Suspension</t>
         </is>
       </c>
       <c r="D46" s="11" t="inlineStr"/>
@@ -2459,7 +2476,7 @@
       </c>
       <c r="C47" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: Appeal (approving lifts the target restriction)</t>
+          <t>Trust &amp; Safety: Ban</t>
         </is>
       </c>
       <c r="D47" s="11" t="inlineStr"/>
@@ -2475,7 +2492,7 @@
       </c>
       <c r="C48" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: rate limiting (new platformkit/ratelimit, Valkey-backed)</t>
+          <t>Trust &amp; Safety: Appeal (approving lifts the target restriction)</t>
         </is>
       </c>
       <c r="D48" s="11" t="inlineStr"/>
@@ -2491,7 +2508,7 @@
       </c>
       <c r="C49" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: spam protection (5 reports/hour per reporter)</t>
+          <t>Trust &amp; Safety: rate limiting (new platformkit/ratelimit, Valkey-backed)</t>
         </is>
       </c>
       <c r="D49" s="11" t="inlineStr"/>
@@ -2507,7 +2524,7 @@
       </c>
       <c r="C50" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: abuse signals (critical severity auto-opens a case)</t>
+          <t>Trust &amp; Safety: spam protection (5 reports/hour per reporter)</t>
         </is>
       </c>
       <c r="D50" s="11" t="inlineStr"/>
@@ -2523,7 +2540,7 @@
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: pluggable product-specific report reasons (free-form Reason field)</t>
+          <t>Trust &amp; Safety: abuse signals (critical severity auto-opens a case)</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr"/>
@@ -2539,7 +2556,7 @@
       </c>
       <c r="C52" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: Suspension/Ban actually restrict access (new requireActive middleware, one entry point)</t>
+          <t>Trust &amp; Safety: pluggable product-specific report reasons (free-form Reason field)</t>
         </is>
       </c>
       <c r="D52" s="11" t="inlineStr"/>
@@ -2548,21 +2565,17 @@
       <c r="A53" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="B53" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B53" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C53" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: WebSocket disconnect on suspension/ban</t>
-        </is>
-      </c>
-      <c r="D53" s="11" t="inlineStr">
-        <is>
-          <t>Deferred - only HTTP access is gated; an existing realtime-gateway connection isn't forcibly closed</t>
-        </is>
-      </c>
+          <t>Trust &amp; Safety: Suspension/Ban actually restrict access (new requireActive middleware, one entry point)</t>
+        </is>
+      </c>
+      <c r="D53" s="11" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="9" t="n">
@@ -2575,30 +2588,34 @@
       </c>
       <c r="C54" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: aggregating lower-severity signals over a time window</t>
+          <t>Trust &amp; Safety: WebSocket disconnect on suspension/ban</t>
         </is>
       </c>
       <c r="D54" s="11" t="inlineStr">
         <is>
-          <t>Deferred - a real abuse-detection engine is out of this phase's scope; only single-critical-signal escalation is implemented</t>
+          <t>Deferred - only HTTP access is gated; an existing realtime-gateway connection isn't forcibly closed</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="9" t="n">
-        <v>22</v>
-      </c>
-      <c r="B55" s="10" t="inlineStr">
-        <is>
-          <t>Done</t>
+        <v>21</v>
+      </c>
+      <c r="B55" s="13" t="inlineStr">
+        <is>
+          <t>Pending</t>
         </is>
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t>Billing: Payment model (provider-specific transaction record)</t>
-        </is>
-      </c>
-      <c r="D55" s="11" t="inlineStr"/>
+          <t>Trust &amp; Safety: aggregating lower-severity signals over a time window</t>
+        </is>
+      </c>
+      <c r="D55" s="11" t="inlineStr">
+        <is>
+          <t>Deferred - a real abuse-detection engine is out of this phase's scope; only single-critical-signal escalation is implemented</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="9" t="n">
@@ -2611,7 +2628,7 @@
       </c>
       <c r="C56" s="11" t="inlineStr">
         <is>
-          <t>Billing: Entitlement model (platform-facing truth, kept separate from Payment)</t>
+          <t>Billing: Payment model (provider-specific transaction record)</t>
         </is>
       </c>
       <c r="D56" s="11" t="inlineStr"/>
@@ -2627,7 +2644,7 @@
       </c>
       <c r="C57" s="11" t="inlineStr">
         <is>
-          <t>Billing: provider abstraction (PaymentProvider interface + registry, implemented first)</t>
+          <t>Billing: Entitlement model (platform-facing truth, kept separate from Payment)</t>
         </is>
       </c>
       <c r="D57" s="11" t="inlineStr"/>
@@ -2643,32 +2660,28 @@
       </c>
       <c r="C58" s="11" t="inlineStr">
         <is>
-          <t>Billing: Stripe adapter</t>
-        </is>
-      </c>
-      <c r="D58" s="11" t="inlineStr">
-        <is>
-          <t>Real HMAC-SHA256 webhook signature verification, live-validated without a Stripe account via self-signed test payloads</t>
-        </is>
-      </c>
+          <t>Billing: provider abstraction (PaymentProvider interface + registry, implemented first)</t>
+        </is>
+      </c>
+      <c r="D58" s="11" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="B59" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B59" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>Billing: Apple IAP adapter</t>
+          <t>Billing: Stripe adapter</t>
         </is>
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>Deferred - needs real App Store Server API credentials this environment doesn't have</t>
+          <t>Real HMAC-SHA256 webhook signature verification, live-validated without a Stripe account via self-signed test payloads</t>
         </is>
       </c>
     </row>
@@ -2683,30 +2696,34 @@
       </c>
       <c r="C60" s="11" t="inlineStr">
         <is>
-          <t>Billing: Google Play adapter</t>
+          <t>Billing: Apple IAP adapter</t>
         </is>
       </c>
       <c r="D60" s="11" t="inlineStr">
         <is>
-          <t>Deferred - needs real Play Developer API credentials this environment doesn't have</t>
+          <t>Deferred - needs real App Store Server API credentials this environment doesn't have</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="9" t="n">
-        <v>23</v>
-      </c>
-      <c r="B61" s="10" t="inlineStr">
-        <is>
-          <t>Done</t>
+        <v>22</v>
+      </c>
+      <c r="B61" s="13" t="inlineStr">
+        <is>
+          <t>Pending</t>
         </is>
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>Analytics: generic event envelope (event_name/user_id/anonymous_id/app_id/session_id/timestamp/properties/context)</t>
-        </is>
-      </c>
-      <c r="D61" s="11" t="inlineStr"/>
+          <t>Billing: Google Play adapter</t>
+        </is>
+      </c>
+      <c r="D61" s="11" t="inlineStr">
+        <is>
+          <t>Deferred - needs real Play Developer API credentials this environment doesn't have</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="9" t="n">
@@ -2719,7 +2736,7 @@
       </c>
       <c r="C62" s="11" t="inlineStr">
         <is>
-          <t>Analytics: keep operational DBs out of the analytics path (analytics_events is a landing buffer, never queried for analytics)</t>
+          <t>Analytics: generic event envelope (event_name/user_id/anonymous_id/app_id/session_id/timestamp/properties/context)</t>
         </is>
       </c>
       <c r="D62" s="11" t="inlineStr"/>
@@ -2735,7 +2752,7 @@
       </c>
       <c r="C63" s="11" t="inlineStr">
         <is>
-          <t>Analytics: pipeline foundation for ClickHouse/warehouse/data lake (worker batches NDJSON into MinIO/S3)</t>
+          <t>Analytics: keep operational DBs out of the analytics path (analytics_events is a landing buffer, never queried for analytics)</t>
         </is>
       </c>
       <c r="D63" s="11" t="inlineStr"/>
@@ -2744,37 +2761,37 @@
       <c r="A64" s="9" t="n">
         <v>23</v>
       </c>
-      <c r="B64" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B64" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C64" s="11" t="inlineStr">
         <is>
-          <t>Analytics: an actual ClickHouse/warehouse/data-lake query layer</t>
-        </is>
-      </c>
-      <c r="D64" s="11" t="inlineStr">
-        <is>
-          <t>Out of scope - this phase builds the landing pipeline only; no real destination system exists in this environment to integrate against honestly</t>
-        </is>
-      </c>
+          <t>Analytics: pipeline foundation for ClickHouse/warehouse/data lake (worker batches NDJSON into MinIO/S3)</t>
+        </is>
+      </c>
+      <c r="D64" s="11" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="9" t="n">
-        <v>24</v>
-      </c>
-      <c r="B65" s="10" t="inlineStr">
-        <is>
-          <t>Done</t>
+        <v>23</v>
+      </c>
+      <c r="B65" s="13" t="inlineStr">
+        <is>
+          <t>Pending</t>
         </is>
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: provider-neutral interface (Provider: Name + Complete)</t>
-        </is>
-      </c>
-      <c r="D65" s="11" t="inlineStr"/>
+          <t>Analytics: an actual ClickHouse/warehouse/data-lake query layer</t>
+        </is>
+      </c>
+      <c r="D65" s="11" t="inlineStr">
+        <is>
+          <t>Out of scope - this phase builds the landing pipeline only; no real destination system exists in this environment to integrate against honestly</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="9" t="n">
@@ -2787,32 +2804,28 @@
       </c>
       <c r="C66" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: local models / Ollama adapter</t>
-        </is>
-      </c>
-      <c r="D66" s="11" t="inlineStr">
-        <is>
-          <t>Real local inference via a new Ollama container, auto-pulled model, no vendor API key - the one live-testable provider</t>
-        </is>
-      </c>
+          <t>AI Gateway: provider-neutral interface (Provider: Name + Complete)</t>
+        </is>
+      </c>
+      <c r="D66" s="11" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="9" t="n">
         <v>24</v>
       </c>
-      <c r="B67" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B67" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C67" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: OpenAI adapter</t>
+          <t>AI Gateway: local models / Ollama adapter</t>
         </is>
       </c>
       <c r="D67" s="11" t="inlineStr">
         <is>
-          <t>Deferred - no real API key in this environment to validate against honestly</t>
+          <t>Real local inference via a new Ollama container, auto-pulled model, no vendor API key - the one live-testable provider</t>
         </is>
       </c>
     </row>
@@ -2827,7 +2840,7 @@
       </c>
       <c r="C68" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: Anthropic adapter</t>
+          <t>AI Gateway: OpenAI adapter</t>
         </is>
       </c>
       <c r="D68" s="11" t="inlineStr">
@@ -2847,7 +2860,7 @@
       </c>
       <c r="C69" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: Google adapter</t>
+          <t>AI Gateway: Anthropic adapter</t>
         </is>
       </c>
       <c r="D69" s="11" t="inlineStr">
@@ -2860,17 +2873,21 @@
       <c r="A70" s="9" t="n">
         <v>24</v>
       </c>
-      <c r="B70" s="10" t="inlineStr">
-        <is>
-          <t>Done</t>
+      <c r="B70" s="13" t="inlineStr">
+        <is>
+          <t>Pending</t>
         </is>
       </c>
       <c r="C70" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: model routing (product-facing ModelAlias, never a vendor model name)</t>
-        </is>
-      </c>
-      <c r="D70" s="11" t="inlineStr"/>
+          <t>AI Gateway: Google adapter</t>
+        </is>
+      </c>
+      <c r="D70" s="11" t="inlineStr">
+        <is>
+          <t>Deferred - no real API key in this environment to validate against honestly</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="9" t="n">
@@ -2883,7 +2900,7 @@
       </c>
       <c r="C71" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: quotas (ratelimit.Limiter reused a third time, 60/min/caller)</t>
+          <t>AI Gateway: model routing (product-facing ModelAlias, never a vendor model name)</t>
         </is>
       </c>
       <c r="D71" s="11" t="inlineStr"/>
@@ -2899,7 +2916,7 @@
       </c>
       <c r="C72" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: token usage tracking</t>
+          <t>AI Gateway: quotas (ratelimit.Limiter reused a third time, 60/min/caller)</t>
         </is>
       </c>
       <c r="D72" s="11" t="inlineStr"/>
@@ -2915,7 +2932,7 @@
       </c>
       <c r="C73" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: cost tracking (real per-route price table; Ollama honestly priced at 0)</t>
+          <t>AI Gateway: token usage tracking</t>
         </is>
       </c>
       <c r="D73" s="11" t="inlineStr"/>
@@ -2931,7 +2948,7 @@
       </c>
       <c r="C74" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: audit integration (new AIGatewayAuditRecorder, a genuine audit.Record per call)</t>
+          <t>AI Gateway: cost tracking (real per-route price table; Ollama honestly priced at 0)</t>
         </is>
       </c>
       <c r="D74" s="11" t="inlineStr"/>
@@ -2947,7 +2964,7 @@
       </c>
       <c r="C75" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: prompt/version metadata (free-form PromptKey/PromptVersion)</t>
+          <t>AI Gateway: audit integration (new AIGatewayAuditRecorder, a genuine audit.Record per call)</t>
         </is>
       </c>
       <c r="D75" s="11" t="inlineStr"/>
@@ -2963,7 +2980,7 @@
       </c>
       <c r="C76" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: timeouts (context.WithTimeout per provider call)</t>
+          <t>AI Gateway: prompt/version metadata (free-form PromptKey/PromptVersion)</t>
         </is>
       </c>
       <c r="D76" s="11" t="inlineStr"/>
@@ -2979,7 +2996,7 @@
       </c>
       <c r="C77" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: fallback (ordered provider/model chain, first success wins)</t>
+          <t>AI Gateway: timeouts (context.WithTimeout per provider call)</t>
         </is>
       </c>
       <c r="D77" s="11" t="inlineStr"/>
@@ -2988,37 +3005,37 @@
       <c r="A78" s="9" t="n">
         <v>24</v>
       </c>
-      <c r="B78" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B78" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C78" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: live token-quantity quota (as opposed to today's call-count quota)</t>
-        </is>
-      </c>
-      <c r="D78" s="11" t="inlineStr">
-        <is>
-          <t>Deferred - Repository already has the data (Completion.TotalTokens); not wired as a live gate yet</t>
-        </is>
-      </c>
+          <t>AI Gateway: fallback (ordered provider/model chain, first success wins)</t>
+        </is>
+      </c>
+      <c r="D78" s="11" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="9" t="n">
-        <v>25</v>
-      </c>
-      <c r="B79" s="10" t="inlineStr">
-        <is>
-          <t>Done</t>
+        <v>24</v>
+      </c>
+      <c r="B79" s="13" t="inlineStr">
+        <is>
+          <t>Pending</t>
         </is>
       </c>
       <c r="C79" s="11" t="inlineStr">
         <is>
-          <t>Admin Portal: real Keycloak-authenticated session (Resource Owner Password Credentials grant), httpOnly session cookie</t>
-        </is>
-      </c>
-      <c r="D79" s="11" t="inlineStr"/>
+          <t>AI Gateway: live token-quantity quota (as opposed to today's call-count quota)</t>
+        </is>
+      </c>
+      <c r="D79" s="11" t="inlineStr">
+        <is>
+          <t>Deferred - Repository already has the data (Completion.TotalTokens); not wired as a live gate yet</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="9" t="n">
@@ -3031,14 +3048,10 @@
       </c>
       <c r="C80" s="11" t="inlineStr">
         <is>
-          <t>Admin Portal: visibility - Applications</t>
-        </is>
-      </c>
-      <c r="D80" s="11" t="inlineStr">
-        <is>
-          <t>Real GET /v1/apps table</t>
-        </is>
-      </c>
+          <t>Admin Portal: real Keycloak-authenticated session (Resource Owner Password Credentials grant), httpOnly session cookie</t>
+        </is>
+      </c>
+      <c r="D80" s="11" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="9" t="n">
@@ -3051,12 +3064,12 @@
       </c>
       <c r="C81" s="11" t="inlineStr">
         <is>
-          <t>Admin Portal: visibility - Users (list + detail)</t>
+          <t>Admin Portal: visibility - Applications</t>
         </is>
       </c>
       <c r="D81" s="11" t="inlineStr">
         <is>
-          <t>New admin-wide GET /v1/users (cursor-paginated, platform.admin-gated)</t>
+          <t>Real GET /v1/apps table</t>
         </is>
       </c>
     </row>
@@ -3071,12 +3084,12 @@
       </c>
       <c r="C82" s="11" t="inlineStr">
         <is>
-          <t>Admin Portal: visibility - Roles/Permissions</t>
+          <t>Admin Portal: visibility - Users (list + detail)</t>
         </is>
       </c>
       <c r="D82" s="11" t="inlineStr">
         <is>
-          <t>New authz HTTP surface (GET/POST /v1/authz/roles, POST /v1/authz/roles/revoke) with a full grant/revoke UI</t>
+          <t>New admin-wide GET /v1/users (cursor-paginated, platform.admin-gated)</t>
         </is>
       </c>
     </row>
@@ -3091,10 +3104,14 @@
       </c>
       <c r="C83" s="11" t="inlineStr">
         <is>
-          <t>Admin Portal: visibility - Feature Flags, Configuration, Jobs</t>
-        </is>
-      </c>
-      <c r="D83" s="11" t="inlineStr"/>
+          <t>Admin Portal: visibility - Roles/Permissions</t>
+        </is>
+      </c>
+      <c r="D83" s="11" t="inlineStr">
+        <is>
+          <t>New authz HTTP surface (GET/POST /v1/authz/roles, POST /v1/authz/roles/revoke) with a full grant/revoke UI</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="9" t="n">
@@ -3107,7 +3124,7 @@
       </c>
       <c r="C84" s="11" t="inlineStr">
         <is>
-          <t>Admin Portal: visibility - Moderation, Audit</t>
+          <t>Admin Portal: visibility - Feature Flags, Configuration, Jobs</t>
         </is>
       </c>
       <c r="D84" s="11" t="inlineStr"/>
@@ -3123,14 +3140,10 @@
       </c>
       <c r="C85" s="11" t="inlineStr">
         <is>
-          <t>Admin Portal: visibility - System Health</t>
-        </is>
-      </c>
-      <c r="D85" s="11" t="inlineStr">
-        <is>
-          <t>Live GET /healthz against core-api/realtime-gateway/worker</t>
-        </is>
-      </c>
+          <t>Admin Portal: visibility - Moderation, Audit</t>
+        </is>
+      </c>
+      <c r="D85" s="11" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="9" t="n">
@@ -3143,30 +3156,30 @@
       </c>
       <c r="C86" s="11" t="inlineStr">
         <is>
-          <t>Admin Portal: visibility - Billing, AI Gateway usage (bonus, not roadmap-named)</t>
-        </is>
-      </c>
-      <c r="D86" s="11" t="inlineStr"/>
+          <t>Admin Portal: visibility - System Health</t>
+        </is>
+      </c>
+      <c r="D86" s="11" t="inlineStr">
+        <is>
+          <t>Live GET /healthz against core-api/realtime-gateway/worker</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="B87" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B87" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C87" s="11" t="inlineStr">
         <is>
-          <t>Admin Portal: visibility - Sessions/Devices, Tenants, Relationships, Messages, Notifications, Files</t>
-        </is>
-      </c>
-      <c r="D87" s="11" t="inlineStr">
-        <is>
-          <t>Deferred - each backing module only exposes a listMine-style self-scoped endpoint, not an admin-wide one; honest ComingSoon reasoning shown per area instead of fake rows</t>
-        </is>
-      </c>
+          <t>Admin Portal: visibility - Billing, AI Gateway usage (bonus, not roadmap-named)</t>
+        </is>
+      </c>
+      <c r="D87" s="11" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="9" t="n">
@@ -3179,32 +3192,32 @@
       </c>
       <c r="C88" s="11" t="inlineStr">
         <is>
-          <t>Admin Portal: visibility - Deployments</t>
+          <t>Admin Portal: visibility - Sessions/Devices, Tenants, Relationships, Messages, Notifications, Files</t>
         </is>
       </c>
       <c r="D88" s="11" t="inlineStr">
         <is>
-          <t>Deferred to Phase 29 - nothing in the platform tracks deployments as data yet</t>
+          <t>Deferred - each backing module only exposes a listMine-style self-scoped endpoint, not an admin-wide one; honest ComingSoon reasoning shown per area instead of fake rows</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="9" t="n">
-        <v>26</v>
-      </c>
-      <c r="B89" s="10" t="inlineStr">
-        <is>
-          <t>Done</t>
+        <v>25</v>
+      </c>
+      <c r="B89" s="13" t="inlineStr">
+        <is>
+          <t>Pending</t>
         </is>
       </c>
       <c r="C89" s="11" t="inlineStr">
         <is>
-          <t>Backstage: integrate Backstage as developer portal</t>
+          <t>Admin Portal: visibility - Deployments</t>
         </is>
       </c>
       <c r="D89" s="11" t="inlineStr">
         <is>
-          <t>Real @backstage/create-app instance at platform/backstage, catalog wired to real catalog/*.yaml + contracts/*/catalog-info.yaml, live-validated via the real catalog API (21 Components, 2 APIs, 1 System, 1 Group, 0 processing errors)</t>
+          <t>Deferred to Phase 29 - nothing in the platform tracks deployments as data yet</t>
         </is>
       </c>
     </row>
@@ -3219,12 +3232,12 @@
       </c>
       <c r="C90" s="11" t="inlineStr">
         <is>
-          <t>Backstage: per-module metadata - name/description/owner/lifecycle</t>
+          <t>Backstage: integrate Backstage as developer portal</t>
         </is>
       </c>
       <c r="D90" s="11" t="inlineStr">
         <is>
-          <t>All 16 modules/*/module.yaml + README.md real (11 were still stub text before this phase)</t>
+          <t>Real @backstage/create-app instance at platform/backstage, catalog wired to real catalog/*.yaml + contracts/*/catalog-info.yaml, live-validated via the real catalog API (21 Components, 2 APIs, 1 System, 1 Group, 0 processing errors)</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3252,12 @@
       </c>
       <c r="C91" s="11" t="inlineStr">
         <is>
-          <t>Backstage: per-module metadata - repository/documentation</t>
+          <t>Backstage: per-module metadata - name/description/owner/lifecycle</t>
         </is>
       </c>
       <c r="D91" s="11" t="inlineStr">
         <is>
-          <t>Every Component links its module README; the System entity links VALIDATION.md and the new docs/RUNBOOKS.md</t>
+          <t>All 16 modules/*/module.yaml + README.md real (11 were still stub text before this phase)</t>
         </is>
       </c>
     </row>
@@ -3259,12 +3272,12 @@
       </c>
       <c r="C92" s="11" t="inlineStr">
         <is>
-          <t>Backstage: per-module metadata - dependencies</t>
+          <t>Backstage: per-module metadata - repository/documentation</t>
         </is>
       </c>
       <c r="D92" s="11" t="inlineStr">
         <is>
-          <t>Component dependsOn mirrors modules/*/module.yaml's real dependency graph; Backstage computes reverse dependencyOf relations automatically, confirmed live</t>
+          <t>Every Component links its module README; the System entity links VALIDATION.md and the new docs/RUNBOOKS.md</t>
         </is>
       </c>
     </row>
@@ -3279,12 +3292,12 @@
       </c>
       <c r="C93" s="11" t="inlineStr">
         <is>
-          <t>Backstage: per-module metadata - APIs</t>
+          <t>Backstage: per-module metadata - dependencies</t>
         </is>
       </c>
       <c r="D93" s="11" t="inlineStr">
         <is>
-          <t>2 API entities (OpenAPI, AsyncAPI), both with their full real spec embedded and live-loaded</t>
+          <t>Component dependsOn mirrors modules/*/module.yaml's real dependency graph; Backstage computes reverse dependencyOf relations automatically, confirmed live</t>
         </is>
       </c>
     </row>
@@ -3299,12 +3312,12 @@
       </c>
       <c r="C94" s="11" t="inlineStr">
         <is>
-          <t>Backstage: per-module metadata - events</t>
+          <t>Backstage: per-module metadata - APIs</t>
         </is>
       </c>
       <c r="D94" s="11" t="inlineStr">
         <is>
-          <t>providesApis set only on the components whose code actually calls outbox.Record, cross-checked against the real Go source</t>
+          <t>2 API entities (OpenAPI, AsyncAPI), both with their full real spec embedded and live-loaded</t>
         </is>
       </c>
     </row>
@@ -3312,19 +3325,19 @@
       <c r="A95" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="B95" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B95" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C95" s="11" t="inlineStr">
         <is>
-          <t>Backstage: per-module metadata - database ownership</t>
+          <t>Backstage: per-module metadata - events</t>
         </is>
       </c>
       <c r="D95" s="11" t="inlineStr">
         <is>
-          <t>Deferred - no per-module DB-ownership annotation convention chosen yet; docs/control's Modules sheet tracks this today at a finer grain than catalog/system.yaml's 16 domains</t>
+          <t>providesApis set only on the components whose code actually calls outbox.Record, cross-checked against the real Go source</t>
         </is>
       </c>
     </row>
@@ -3332,19 +3345,19 @@
       <c r="A96" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="B96" s="10" t="inlineStr">
-        <is>
-          <t>Done</t>
+      <c r="B96" s="13" t="inlineStr">
+        <is>
+          <t>Pending</t>
         </is>
       </c>
       <c r="C96" s="11" t="inlineStr">
         <is>
-          <t>Backstage: per-module metadata - dashboards</t>
+          <t>Backstage: per-module metadata - database ownership</t>
         </is>
       </c>
       <c r="D96" s="11" t="inlineStr">
         <is>
-          <t>core-platform.io/dashboard annotation on each service pointing at the real local Grafana instance - no per-service dashboard exists yet (that's Phase 28), so it points at the shared instance, documented as such</t>
+          <t>Deferred - no per-module DB-ownership annotation convention chosen yet; docs/control's Modules sheet tracks this today at a finer grain than catalog/system.yaml's 16 domains</t>
         </is>
       </c>
     </row>
@@ -3359,178 +3372,218 @@
       </c>
       <c r="C97" s="11" t="inlineStr">
         <is>
-          <t>Backstage: per-module metadata - runbooks</t>
+          <t>Backstage: per-module metadata - dashboards</t>
         </is>
       </c>
       <c r="D97" s="11" t="inlineStr">
         <is>
-          <t>New docs/RUNBOOKS.md, linked from the System entity</t>
+          <t>core-platform.io/dashboard annotation on each service pointing at the real local Grafana instance - no per-service dashboard exists yet (that's Phase 28), so it points at the shared instance, documented as such</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="9" t="n">
-        <v>27</v>
-      </c>
-      <c r="B98" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+        <v>26</v>
+      </c>
+      <c r="B98" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C98" s="11" t="inlineStr">
         <is>
-          <t>SDKs: Flutter SDK</t>
-        </is>
-      </c>
-      <c r="D98" s="11" t="inlineStr"/>
+          <t>Backstage: per-module metadata - runbooks</t>
+        </is>
+      </c>
+      <c r="D98" s="11" t="inlineStr">
+        <is>
+          <t>New docs/RUNBOOKS.md, linked from the System entity</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="9" t="n">
         <v>27</v>
       </c>
-      <c r="B99" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B99" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C99" s="11" t="inlineStr">
         <is>
-          <t>SDKs: TypeScript SDK</t>
-        </is>
-      </c>
-      <c r="D99" s="11" t="inlineStr"/>
+          <t>SDKs: Go SDK</t>
+        </is>
+      </c>
+      <c r="D99" s="11" t="inlineStr">
+        <is>
+          <t>packages/go/coresdk - 12 unit tests (httptest.Server), live-validated against real Keycloak/core-api/realtime-gateway</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="9" t="n">
         <v>27</v>
       </c>
-      <c r="B100" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B100" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C100" s="11" t="inlineStr">
         <is>
-          <t>SDKs: Go SDK</t>
-        </is>
-      </c>
-      <c r="D100" s="11" t="inlineStr"/>
+          <t>SDKs: TypeScript SDK</t>
+        </is>
+      </c>
+      <c r="D100" s="11" t="inlineStr">
+        <is>
+          <t>packages/typescript/core-sdk - 13 unit tests (node:http), real consumer: apps/admin's entire lib/api.ts migrated to it</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="9" t="n">
         <v>27</v>
       </c>
-      <c r="B101" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B101" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C101" s="11" t="inlineStr">
         <is>
-          <t>SDKs: auth + token refresh in each SDK</t>
-        </is>
-      </c>
-      <c r="D101" s="11" t="inlineStr"/>
+          <t>SDKs: Dart SDK</t>
+        </is>
+      </c>
+      <c r="D101" s="11" t="inlineStr">
+        <is>
+          <t>packages/flutter/core_sdk (pure Dart, no Flutter dependency) - 13 unit tests (dart:io HttpServer), real consumer: apps/mobile's login/profile flow</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="9" t="n">
         <v>27</v>
       </c>
-      <c r="B102" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B102" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C102" s="11" t="inlineStr">
         <is>
-          <t>SDKs: pagination + safe retries</t>
-        </is>
-      </c>
-      <c r="D102" s="11" t="inlineStr"/>
+          <t>SDKs: auth + token refresh in each SDK</t>
+        </is>
+      </c>
+      <c r="D102" s="11" t="inlineStr">
+        <is>
+          <t>TokenSource (static + real Keycloak password-grant with skew-aware, concurrency-coalesced refresh) in all three</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="9" t="n">
         <v>27</v>
       </c>
-      <c r="B103" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B103" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C103" s="11" t="inlineStr">
         <is>
-          <t>SDKs: realtime connection helper</t>
-        </is>
-      </c>
-      <c r="D103" s="11" t="inlineStr"/>
+          <t>SDKs: pagination + safe retries</t>
+        </is>
+      </c>
+      <c r="D103" s="11" t="inlineStr">
+        <is>
+          <t>Page/paginate/collectAll over the real {items,nextCursor} shape; GET-only retries by default on transient statuses, in all three</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="9" t="n">
         <v>27</v>
       </c>
-      <c r="B104" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B104" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C104" s="11" t="inlineStr">
         <is>
-          <t>SDKs: correlation ID propagation</t>
-        </is>
-      </c>
-      <c r="D104" s="11" t="inlineStr"/>
+          <t>SDKs: realtime connection helper</t>
+        </is>
+      </c>
+      <c r="D104" s="11" t="inlineStr">
+        <is>
+          <t>Reproduces realtime-gateway's real ws://.../ws?access_token=&amp;deviceId= protocol and message shapes exactly, in all three - live-validated with real cross-connection fan-out</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="9" t="n">
         <v>27</v>
       </c>
-      <c r="B105" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B105" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C105" s="11" t="inlineStr">
         <is>
-          <t>SDKs: device registration helper</t>
-        </is>
-      </c>
-      <c r="D105" s="11" t="inlineStr"/>
+          <t>SDKs: correlation ID propagation</t>
+        </is>
+      </c>
+      <c r="D105" s="11" t="inlineStr">
+        <is>
+          <t>X-Correlation-ID on every call, matching platformkit/correlation's real header name, in all three</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="9" t="n">
-        <v>28</v>
-      </c>
-      <c r="B106" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+        <v>27</v>
+      </c>
+      <c r="B106" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C106" s="11" t="inlineStr">
         <is>
-          <t>Observability Completion: structured logs everywhere</t>
-        </is>
-      </c>
-      <c r="D106" s="11" t="inlineStr"/>
+          <t>SDKs: device registration helper</t>
+        </is>
+      </c>
+      <c r="D106" s="11" t="inlineStr">
+        <is>
+          <t>DevicesRegister/devicesRegister in all three - realtime dial requires a real registered device id</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="9" t="n">
-        <v>28</v>
-      </c>
-      <c r="B107" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+        <v>27</v>
+      </c>
+      <c r="B107" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C107" s="11" t="inlineStr">
         <is>
-          <t>Observability Completion: metrics everywhere</t>
-        </is>
-      </c>
-      <c r="D107" s="11" t="inlineStr"/>
+          <t>SDKs: apps/mobile test/ directory (make flutter-test currently fails)</t>
+        </is>
+      </c>
+      <c r="D107" s="11" t="inlineStr">
+        <is>
+          <t>Closed as a side effect - real widget tests added, discovered and worked around Flutter's TestWidgetsFlutterBinding network-mocking constraint live. Was pending since Phase 9.</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B108" s="13" t="inlineStr">
         <is>
@@ -3539,10 +3592,14 @@
       </c>
       <c r="C108" s="11" t="inlineStr">
         <is>
-          <t>Observability Completion: distributed traces everywhere</t>
-        </is>
-      </c>
-      <c r="D108" s="11" t="inlineStr"/>
+          <t>SDKs: full API coverage (all 146 endpoints typed) in each SDK</t>
+        </is>
+      </c>
+      <c r="D108" s="11" t="inlineStr">
+        <is>
+          <t>Deferred - each SDK covers a representative 'core identity' slice (platform/identity/users/devices/applications) plus what its real consumer needs; the untyped request()/Do() escape hatch reaches everything else. Broader coverage is real, additive work, not a framework limitation.</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="9" t="n">
@@ -3555,7 +3612,7 @@
       </c>
       <c r="C109" s="11" t="inlineStr">
         <is>
-          <t>Observability Completion: health checks everywhere</t>
+          <t>Observability Completion: structured logs everywhere</t>
         </is>
       </c>
       <c r="D109" s="11" t="inlineStr"/>
@@ -3571,7 +3628,7 @@
       </c>
       <c r="C110" s="11" t="inlineStr">
         <is>
-          <t>Observability Completion: dashboard: API latency</t>
+          <t>Observability Completion: metrics everywhere</t>
         </is>
       </c>
       <c r="D110" s="11" t="inlineStr"/>
@@ -3587,7 +3644,7 @@
       </c>
       <c r="C111" s="11" t="inlineStr">
         <is>
-          <t>Observability Completion: dashboard: error rate</t>
+          <t>Observability Completion: distributed traces everywhere</t>
         </is>
       </c>
       <c r="D111" s="11" t="inlineStr"/>
@@ -3603,7 +3660,7 @@
       </c>
       <c r="C112" s="11" t="inlineStr">
         <is>
-          <t>Observability Completion: dashboard: requests/sec</t>
+          <t>Observability Completion: health checks everywhere</t>
         </is>
       </c>
       <c r="D112" s="11" t="inlineStr"/>
@@ -3619,7 +3676,7 @@
       </c>
       <c r="C113" s="11" t="inlineStr">
         <is>
-          <t>Observability Completion: dashboard: DB connections</t>
+          <t>Observability Completion: dashboard: API latency</t>
         </is>
       </c>
       <c r="D113" s="11" t="inlineStr"/>
@@ -3635,7 +3692,7 @@
       </c>
       <c r="C114" s="11" t="inlineStr">
         <is>
-          <t>Observability Completion: dashboard: Kafka lag</t>
+          <t>Observability Completion: dashboard: error rate</t>
         </is>
       </c>
       <c r="D114" s="11" t="inlineStr"/>
@@ -3651,7 +3708,7 @@
       </c>
       <c r="C115" s="11" t="inlineStr">
         <is>
-          <t>Observability Completion: dashboard: WebSocket connections</t>
+          <t>Observability Completion: dashboard: requests/sec</t>
         </is>
       </c>
       <c r="D115" s="11" t="inlineStr"/>
@@ -3667,7 +3724,7 @@
       </c>
       <c r="C116" s="11" t="inlineStr">
         <is>
-          <t>Observability Completion: dashboard: Redis latency</t>
+          <t>Observability Completion: dashboard: DB connections</t>
         </is>
       </c>
       <c r="D116" s="11" t="inlineStr"/>
@@ -3683,7 +3740,7 @@
       </c>
       <c r="C117" s="11" t="inlineStr">
         <is>
-          <t>Observability Completion: dashboard: notification failures</t>
+          <t>Observability Completion: dashboard: Kafka lag</t>
         </is>
       </c>
       <c r="D117" s="11" t="inlineStr"/>
@@ -3699,7 +3756,7 @@
       </c>
       <c r="C118" s="11" t="inlineStr">
         <is>
-          <t>Observability Completion: dashboard: background job failures</t>
+          <t>Observability Completion: dashboard: WebSocket connections</t>
         </is>
       </c>
       <c r="D118" s="11" t="inlineStr"/>
@@ -3715,14 +3772,14 @@
       </c>
       <c r="C119" s="11" t="inlineStr">
         <is>
-          <t>Observability Completion: alerting rules</t>
+          <t>Observability Completion: dashboard: Redis latency</t>
         </is>
       </c>
       <c r="D119" s="11" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B120" s="13" t="inlineStr">
         <is>
@@ -3731,14 +3788,14 @@
       </c>
       <c r="C120" s="11" t="inlineStr">
         <is>
-          <t>Platform Control Plane: one view: applications/services/versions</t>
+          <t>Observability Completion: dashboard: notification failures</t>
         </is>
       </c>
       <c r="D120" s="11" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B121" s="13" t="inlineStr">
         <is>
@@ -3747,14 +3804,14 @@
       </c>
       <c r="C121" s="11" t="inlineStr">
         <is>
-          <t>Platform Control Plane: one view: environments/dependencies/deployments</t>
+          <t>Observability Completion: dashboard: background job failures</t>
         </is>
       </c>
       <c r="D121" s="11" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B122" s="13" t="inlineStr">
         <is>
@@ -3763,7 +3820,7 @@
       </c>
       <c r="C122" s="11" t="inlineStr">
         <is>
-          <t>Platform Control Plane: one view: DB ownership/events/API contracts</t>
+          <t>Observability Completion: alerting rules</t>
         </is>
       </c>
       <c r="D122" s="11" t="inlineStr"/>
@@ -3779,14 +3836,14 @@
       </c>
       <c r="C123" s="11" t="inlineStr">
         <is>
-          <t>Platform Control Plane: one view: health/alerts/recent changes</t>
+          <t>Platform Control Plane: one view: applications/services/versions</t>
         </is>
       </c>
       <c r="D123" s="11" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="9" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B124" s="13" t="inlineStr">
         <is>
@@ -3795,14 +3852,14 @@
       </c>
       <c r="C124" s="11" t="inlineStr">
         <is>
-          <t>AI Development Context: every module: README</t>
+          <t>Platform Control Plane: one view: environments/dependencies/deployments</t>
         </is>
       </c>
       <c r="D124" s="11" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="9" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B125" s="13" t="inlineStr">
         <is>
@@ -3811,14 +3868,14 @@
       </c>
       <c r="C125" s="11" t="inlineStr">
         <is>
-          <t>AI Development Context: every module: ownership metadata</t>
+          <t>Platform Control Plane: one view: DB ownership/events/API contracts</t>
         </is>
       </c>
       <c r="D125" s="11" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="9" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B126" s="13" t="inlineStr">
         <is>
@@ -3827,7 +3884,7 @@
       </c>
       <c r="C126" s="11" t="inlineStr">
         <is>
-          <t>AI Development Context: every module: dependencies</t>
+          <t>Platform Control Plane: one view: health/alerts/recent changes</t>
         </is>
       </c>
       <c r="D126" s="11" t="inlineStr"/>
@@ -3843,7 +3900,7 @@
       </c>
       <c r="C127" s="11" t="inlineStr">
         <is>
-          <t>AI Development Context: every module: API contract</t>
+          <t>AI Development Context: every module: README</t>
         </is>
       </c>
       <c r="D127" s="11" t="inlineStr"/>
@@ -3859,7 +3916,7 @@
       </c>
       <c r="C128" s="11" t="inlineStr">
         <is>
-          <t>AI Development Context: every module: event contracts</t>
+          <t>AI Development Context: every module: ownership metadata</t>
         </is>
       </c>
       <c r="D128" s="11" t="inlineStr"/>
@@ -3875,10 +3932,58 @@
       </c>
       <c r="C129" s="11" t="inlineStr">
         <is>
+          <t>AI Development Context: every module: dependencies</t>
+        </is>
+      </c>
+      <c r="D129" s="11" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="B130" s="13" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="C130" s="11" t="inlineStr">
+        <is>
+          <t>AI Development Context: every module: API contract</t>
+        </is>
+      </c>
+      <c r="D130" s="11" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="B131" s="13" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="C131" s="11" t="inlineStr">
+        <is>
+          <t>AI Development Context: every module: event contracts</t>
+        </is>
+      </c>
+      <c r="D131" s="11" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="B132" s="13" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="C132" s="11" t="inlineStr">
+        <is>
           <t>AI Development Context: every module: DB ownership</t>
         </is>
       </c>
-      <c r="D129" s="11" t="inlineStr"/>
+      <c r="D132" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8592,7 +8697,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -9060,6 +9165,72 @@
       <c r="D21" s="11" t="inlineStr">
         <is>
           <t>Needs Node 20/22 and a real Yarn install - see platform/backstage/README.md if the versions on $PATH don't satisfy Backstage's own prerequisite check. Then open http://localhost:3000 (stop the Admin Portal first, they share a port) and browse the Catalog - every module/service/app is a real entity (Phase 26), not example fixture data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="48" customHeight="1">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="inlineStr">
+        <is>
+          <t>Test the Go SDK</t>
+        </is>
+      </c>
+      <c r="C22" s="11" t="inlineStr">
+        <is>
+          <t>cd packages/go/coresdk &amp;&amp; go test ./...</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="inlineStr">
+        <is>
+          <t>12 unit tests against a real httptest.Server (Phase 27) - no mocking library.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="48" customHeight="1">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="inlineStr">
+        <is>
+          <t>Test the TypeScript SDK</t>
+        </is>
+      </c>
+      <c r="C23" s="11" t="inlineStr">
+        <is>
+          <t>cd packages/typescript/core-sdk &amp;&amp; npm install &amp;&amp; npm test</t>
+        </is>
+      </c>
+      <c r="D23" s="11" t="inlineStr">
+        <is>
+          <t>13 unit tests against a real node:http server. make sdk-ts-build must run before apps/admin can resolve @core-platform/sdk - make admin-install/admin-build already depend on it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="48" customHeight="1">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t>Test the Dart SDK</t>
+        </is>
+      </c>
+      <c r="C24" s="11" t="inlineStr">
+        <is>
+          <t>cd packages/flutter/core_sdk &amp;&amp; dart pub get &amp;&amp; dart test</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="inlineStr">
+        <is>
+          <t>13 unit tests against a real dart:io HttpServer. apps/mobile depends on this package via a path: dependency in its pubspec.yaml.</t>
         </is>
       </c>
     </row>

--- a/docs/control/data.xlsx
+++ b/docs/control/data.xlsx
@@ -239,8 +239,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="TodoChecklist" displayName="TodoChecklist" ref="A1:D132" headerRowCount="1">
-  <autoFilter ref="A1:D132"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="TodoChecklist" displayName="TodoChecklist" ref="A1:D135" headerRowCount="1">
+  <autoFilter ref="A1:D135"/>
   <tableColumns count="4">
     <tableColumn id="1" name="Phase"/>
     <tableColumn id="2" name="Status"/>
@@ -267,8 +267,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="APIEndpoints" displayName="APIEndpoints" ref="A1:E147" headerRowCount="1">
-  <autoFilter ref="A1:E147"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="APIEndpoints" displayName="APIEndpoints" ref="A1:E148" headerRowCount="1">
+  <autoFilter ref="A1:E148"/>
   <tableColumns count="5">
     <tableColumn id="1" name="Method"/>
     <tableColumn id="2" name="Path"/>
@@ -281,8 +281,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="HowToTest" displayName="HowToTest" ref="A1:D24" headerRowCount="1">
-  <autoFilter ref="A1:D24"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="HowToTest" displayName="HowToTest" ref="A1:D25" headerRowCount="1">
+  <autoFilter ref="A1:D25"/>
   <tableColumns count="4">
     <tableColumn id="1" name="Step"/>
     <tableColumn id="2" name="What"/>
@@ -294,8 +294,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="InfraCredentials" displayName="InfraCredentials" ref="A1:E16" headerRowCount="1">
-  <autoFilter ref="A1:E16"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="InfraCredentials" displayName="InfraCredentials" ref="A1:E20" headerRowCount="1">
+  <autoFilter ref="A1:E20"/>
   <tableColumns count="5">
     <tableColumn id="1" name="Service"/>
     <tableColumn id="2" name="Type"/>
@@ -633,12 +633,12 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>27 / 30</t>
+          <t>28 / 30</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>93%</t>
         </is>
       </c>
     </row>
@@ -718,12 +718,12 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>packages/go/platformkit</t>
+          <t>packages/go/platformkit, packages/go/coresdk</t>
         </is>
       </c>
     </row>
@@ -752,7 +752,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>147</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Postgres, Valkey, Keycloak, OpenFGA, MinIO, OpenSearch, Temporal, Kafka/Redpanda, Ollama, OTel</t>
+          <t>Postgres, Valkey, Keycloak, OpenFGA, MinIO, OpenSearch, Temporal, Kafka/Redpanda, Ollama, OTel/Prometheus/Grafana/Loki/Tempo</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -1597,9 +1597,9 @@
       <c r="A29" s="9" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="12" t="inlineStr">
-        <is>
-          <t>Next up</t>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
@@ -1609,12 +1609,12 @@
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>Every production component gets structured logs, metrics, traces, health checks, dashboards, alerts. Standard dashboards for API latency, error rate, req/sec, DB connections, Kafka lag, WS connections, Redis latency, notification/job failures.</t>
+          <t>New packages/go/platformkit/metrics gives every service a real /metrics endpoint and all 8 named dashboards real backing data (Kafka lag excluded - no real producer/consumer exists yet, an honest placeholder panel instead). logging.NewWithLoki ships structured logs directly to Loki's push API with real trace_id correlation. Grafana provisioning (previously mounted nowhere) now auto-loads Prometheus/Tempo/Loki datasources and a real dashboard; alerts.yml adds 6 live-evaluated Prometheus alerting rules. A real regression (broken WebSocket Hijack) was caught by the metrics middleware's own tests before ever reaching a running service.</t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>697ea4c</t>
         </is>
       </c>
     </row>
@@ -1622,9 +1622,9 @@
       <c r="A30" s="9" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B30" s="12" t="inlineStr">
+        <is>
+          <t>Next up</t>
         </is>
       </c>
       <c r="C30" s="11" t="inlineStr">
@@ -1682,7 +1682,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D132"/>
+  <dimension ref="A1:D135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2147,7 +2147,7 @@
     </row>
     <row r="29">
       <c r="A29" s="9" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
@@ -2156,14 +2156,14 @@
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>Repo health baseline (make doctor / validate-all / go test / go build) run and passed</t>
+          <t>Phase 28: Observability Completion implemented, unit-tested, live-validated, documented, committed</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
@@ -2172,18 +2172,14 @@
       </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t>Environment / ApplicationVersion / ApplicationConfiguration</t>
-        </is>
-      </c>
-      <c r="D30" s="11" t="inlineStr">
-        <is>
-          <t>Deferred - no consumer needs them yet, documented as intentional in applications/README.md</t>
-        </is>
-      </c>
+          <t>Repo health baseline (make doctor / validate-all / go test / go build) run and passed</t>
+        </is>
+      </c>
+      <c r="D30" s="11" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
@@ -2192,32 +2188,32 @@
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>Separate Session table</t>
+          <t>Environment / ApplicationVersion / ApplicationConfiguration</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>Deferred - Device.SessionStatus covers today's single-session-per-device need, documented in devices/README.md</t>
+          <t>Deferred - no consumer needs them yet, documented as intentional in applications/README.md</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="B32" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+        <v>5</v>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C32" s="11" t="inlineStr">
         <is>
-          <t>UserPreferences (named in Phase 4, no fields ever specified)</t>
+          <t>Separate Session table</t>
         </is>
       </c>
       <c r="D32" s="11" t="inlineStr">
         <is>
-          <t>Deferred to Phase 12+; notification preferences shipped, a generic preferences bag did not</t>
+          <t>Deferred - Device.SessionStatus covers today's single-session-per-device need, documented in devices/README.md</t>
         </is>
       </c>
     </row>
@@ -2232,12 +2228,12 @@
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>apps/mobile test/ directory (make flutter-test currently fails)</t>
+          <t>UserPreferences (named in Phase 4, no fields ever specified)</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>Known gap since Phase 9's audit, not yet picked up</t>
+          <t>Deferred to Phase 12+; notification preferences shipped, a generic preferences bag did not</t>
         </is>
       </c>
     </row>
@@ -2252,30 +2248,34 @@
       </c>
       <c r="C34" s="11" t="inlineStr">
         <is>
-          <t>apps/admin next@15 / sharp transitive advisories</t>
+          <t>apps/mobile test/ directory (make flutter-test currently fails)</t>
         </is>
       </c>
       <c r="D34" s="11" t="inlineStr">
         <is>
-          <t>Fix is a Next.js major-version bump - separate, reviewable change</t>
+          <t>Known gap since Phase 9's audit, not yet picked up</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="9" t="n">
-        <v>20</v>
-      </c>
-      <c r="B35" s="10" t="inlineStr">
-        <is>
-          <t>Done</t>
+        <v>9</v>
+      </c>
+      <c r="B35" s="13" t="inlineStr">
+        <is>
+          <t>Pending</t>
         </is>
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>Privacy: consent (append-only history)</t>
-        </is>
-      </c>
-      <c r="D35" s="11" t="inlineStr"/>
+          <t>apps/admin next@15 / sharp transitive advisories</t>
+        </is>
+      </c>
+      <c r="D35" s="11" t="inlineStr">
+        <is>
+          <t>Fix is a Next.js major-version bump - separate, reviewable change</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="9" t="n">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="C36" s="11" t="inlineStr">
         <is>
-          <t>Privacy: user data export (ExportUserData registry - users/devices/files/audit)</t>
+          <t>Privacy: consent (append-only history)</t>
         </is>
       </c>
       <c r="D36" s="11" t="inlineStr"/>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>Privacy: user deletion (DeleteUserData registry - users/devices/files; audit deliberately excluded)</t>
+          <t>Privacy: user data export (ExportUserData registry - users/devices/files/audit)</t>
         </is>
       </c>
       <c r="D37" s="11" t="inlineStr"/>
@@ -2320,7 +2320,7 @@
       </c>
       <c r="C38" s="11" t="inlineStr">
         <is>
-          <t>Privacy: retention policy (declared, not scheduled - same documented gap as Phase 13's PurgeExpired)</t>
+          <t>Privacy: user deletion (DeleteUserData registry - users/devices/files; audit deliberately excluded)</t>
         </is>
       </c>
       <c r="D38" s="11" t="inlineStr"/>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>Privacy: privacy preferences</t>
+          <t>Privacy: retention policy (declared, not scheduled - same documented gap as Phase 13's PurgeExpired)</t>
         </is>
       </c>
       <c r="D39" s="11" t="inlineStr"/>
@@ -2352,7 +2352,7 @@
       </c>
       <c r="C40" s="11" t="inlineStr">
         <is>
-          <t>Privacy: coordinate deletion through workflows/events - core-api's own embedded Temporal worker</t>
+          <t>Privacy: privacy preferences</t>
         </is>
       </c>
       <c r="D40" s="11" t="inlineStr"/>
@@ -2361,21 +2361,17 @@
       <c r="A41" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="B41" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B41" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>Privacy: notifications module as an Export/Delete participant</t>
-        </is>
-      </c>
-      <c r="D41" s="11" t="inlineStr">
-        <is>
-          <t>Deliberately deferred to prove the registry makes this a 2-line addition later, not a framework change</t>
-        </is>
-      </c>
+          <t>Privacy: coordinate deletion through workflows/events - core-api's own embedded Temporal worker</t>
+        </is>
+      </c>
+      <c r="D41" s="11" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="9" t="n">
@@ -2388,32 +2384,32 @@
       </c>
       <c r="C42" s="11" t="inlineStr">
         <is>
-          <t>Privacy: relationships/groups/messaging as participants</t>
+          <t>Privacy: notifications module as an Export/Delete participant</t>
         </is>
       </c>
       <c r="D42" s="11" t="inlineStr">
         <is>
-          <t>Deferred - shared multi-user data needs a redaction strategy this phase's per-user-in-isolation registry doesn't fit</t>
+          <t>Deliberately deferred to prove the registry makes this a 2-line addition later, not a framework change</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="9" t="n">
-        <v>21</v>
-      </c>
-      <c r="B43" s="10" t="inlineStr">
-        <is>
-          <t>Done</t>
+        <v>20</v>
+      </c>
+      <c r="B43" s="13" t="inlineStr">
+        <is>
+          <t>Pending</t>
         </is>
       </c>
       <c r="C43" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: Block</t>
+          <t>Privacy: relationships/groups/messaging as participants</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>Reused Phase 8's relationships (Status='blocked'), deliberately not duplicated</t>
+          <t>Deferred - shared multi-user data needs a redaction strategy this phase's per-user-in-isolation registry doesn't fit</t>
         </is>
       </c>
     </row>
@@ -2428,10 +2424,14 @@
       </c>
       <c r="C44" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: Mute</t>
-        </is>
-      </c>
-      <c r="D44" s="11" t="inlineStr"/>
+          <t>Trust &amp; Safety: Block</t>
+        </is>
+      </c>
+      <c r="D44" s="11" t="inlineStr">
+        <is>
+          <t>Reused Phase 8's relationships (Status='blocked'), deliberately not duplicated</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="9" t="n">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="C45" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: Report -&gt; ModerationCase (deduplicated via partial unique index)</t>
+          <t>Trust &amp; Safety: Mute</t>
         </is>
       </c>
       <c r="D45" s="11" t="inlineStr"/>
@@ -2460,7 +2460,7 @@
       </c>
       <c r="C46" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: Suspension</t>
+          <t>Trust &amp; Safety: Report -&gt; ModerationCase (deduplicated via partial unique index)</t>
         </is>
       </c>
       <c r="D46" s="11" t="inlineStr"/>
@@ -2476,7 +2476,7 @@
       </c>
       <c r="C47" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: Ban</t>
+          <t>Trust &amp; Safety: Suspension</t>
         </is>
       </c>
       <c r="D47" s="11" t="inlineStr"/>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="C48" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: Appeal (approving lifts the target restriction)</t>
+          <t>Trust &amp; Safety: Ban</t>
         </is>
       </c>
       <c r="D48" s="11" t="inlineStr"/>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C49" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: rate limiting (new platformkit/ratelimit, Valkey-backed)</t>
+          <t>Trust &amp; Safety: Appeal (approving lifts the target restriction)</t>
         </is>
       </c>
       <c r="D49" s="11" t="inlineStr"/>
@@ -2524,7 +2524,7 @@
       </c>
       <c r="C50" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: spam protection (5 reports/hour per reporter)</t>
+          <t>Trust &amp; Safety: rate limiting (new platformkit/ratelimit, Valkey-backed)</t>
         </is>
       </c>
       <c r="D50" s="11" t="inlineStr"/>
@@ -2540,7 +2540,7 @@
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: abuse signals (critical severity auto-opens a case)</t>
+          <t>Trust &amp; Safety: spam protection (5 reports/hour per reporter)</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr"/>
@@ -2556,7 +2556,7 @@
       </c>
       <c r="C52" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: pluggable product-specific report reasons (free-form Reason field)</t>
+          <t>Trust &amp; Safety: abuse signals (critical severity auto-opens a case)</t>
         </is>
       </c>
       <c r="D52" s="11" t="inlineStr"/>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="C53" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: Suspension/Ban actually restrict access (new requireActive middleware, one entry point)</t>
+          <t>Trust &amp; Safety: pluggable product-specific report reasons (free-form Reason field)</t>
         </is>
       </c>
       <c r="D53" s="11" t="inlineStr"/>
@@ -2581,21 +2581,17 @@
       <c r="A54" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="B54" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B54" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C54" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: WebSocket disconnect on suspension/ban</t>
-        </is>
-      </c>
-      <c r="D54" s="11" t="inlineStr">
-        <is>
-          <t>Deferred - only HTTP access is gated; an existing realtime-gateway connection isn't forcibly closed</t>
-        </is>
-      </c>
+          <t>Trust &amp; Safety: Suspension/Ban actually restrict access (new requireActive middleware, one entry point)</t>
+        </is>
+      </c>
+      <c r="D54" s="11" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="9" t="n">
@@ -2608,30 +2604,34 @@
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: aggregating lower-severity signals over a time window</t>
+          <t>Trust &amp; Safety: WebSocket disconnect on suspension/ban</t>
         </is>
       </c>
       <c r="D55" s="11" t="inlineStr">
         <is>
-          <t>Deferred - a real abuse-detection engine is out of this phase's scope; only single-critical-signal escalation is implemented</t>
+          <t>Deferred - only HTTP access is gated; an existing realtime-gateway connection isn't forcibly closed</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="9" t="n">
-        <v>22</v>
-      </c>
-      <c r="B56" s="10" t="inlineStr">
-        <is>
-          <t>Done</t>
+        <v>21</v>
+      </c>
+      <c r="B56" s="13" t="inlineStr">
+        <is>
+          <t>Pending</t>
         </is>
       </c>
       <c r="C56" s="11" t="inlineStr">
         <is>
-          <t>Billing: Payment model (provider-specific transaction record)</t>
-        </is>
-      </c>
-      <c r="D56" s="11" t="inlineStr"/>
+          <t>Trust &amp; Safety: aggregating lower-severity signals over a time window</t>
+        </is>
+      </c>
+      <c r="D56" s="11" t="inlineStr">
+        <is>
+          <t>Deferred - a real abuse-detection engine is out of this phase's scope; only single-critical-signal escalation is implemented</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="9" t="n">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="C57" s="11" t="inlineStr">
         <is>
-          <t>Billing: Entitlement model (platform-facing truth, kept separate from Payment)</t>
+          <t>Billing: Payment model (provider-specific transaction record)</t>
         </is>
       </c>
       <c r="D57" s="11" t="inlineStr"/>
@@ -2660,7 +2660,7 @@
       </c>
       <c r="C58" s="11" t="inlineStr">
         <is>
-          <t>Billing: provider abstraction (PaymentProvider interface + registry, implemented first)</t>
+          <t>Billing: Entitlement model (platform-facing truth, kept separate from Payment)</t>
         </is>
       </c>
       <c r="D58" s="11" t="inlineStr"/>
@@ -2676,32 +2676,28 @@
       </c>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>Billing: Stripe adapter</t>
-        </is>
-      </c>
-      <c r="D59" s="11" t="inlineStr">
-        <is>
-          <t>Real HMAC-SHA256 webhook signature verification, live-validated without a Stripe account via self-signed test payloads</t>
-        </is>
-      </c>
+          <t>Billing: provider abstraction (PaymentProvider interface + registry, implemented first)</t>
+        </is>
+      </c>
+      <c r="D59" s="11" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="B60" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B60" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C60" s="11" t="inlineStr">
         <is>
-          <t>Billing: Apple IAP adapter</t>
+          <t>Billing: Stripe adapter</t>
         </is>
       </c>
       <c r="D60" s="11" t="inlineStr">
         <is>
-          <t>Deferred - needs real App Store Server API credentials this environment doesn't have</t>
+          <t>Real HMAC-SHA256 webhook signature verification, live-validated without a Stripe account via self-signed test payloads</t>
         </is>
       </c>
     </row>
@@ -2716,30 +2712,34 @@
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>Billing: Google Play adapter</t>
+          <t>Billing: Apple IAP adapter</t>
         </is>
       </c>
       <c r="D61" s="11" t="inlineStr">
         <is>
-          <t>Deferred - needs real Play Developer API credentials this environment doesn't have</t>
+          <t>Deferred - needs real App Store Server API credentials this environment doesn't have</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="9" t="n">
-        <v>23</v>
-      </c>
-      <c r="B62" s="10" t="inlineStr">
-        <is>
-          <t>Done</t>
+        <v>22</v>
+      </c>
+      <c r="B62" s="13" t="inlineStr">
+        <is>
+          <t>Pending</t>
         </is>
       </c>
       <c r="C62" s="11" t="inlineStr">
         <is>
-          <t>Analytics: generic event envelope (event_name/user_id/anonymous_id/app_id/session_id/timestamp/properties/context)</t>
-        </is>
-      </c>
-      <c r="D62" s="11" t="inlineStr"/>
+          <t>Billing: Google Play adapter</t>
+        </is>
+      </c>
+      <c r="D62" s="11" t="inlineStr">
+        <is>
+          <t>Deferred - needs real Play Developer API credentials this environment doesn't have</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="9" t="n">
@@ -2752,7 +2752,7 @@
       </c>
       <c r="C63" s="11" t="inlineStr">
         <is>
-          <t>Analytics: keep operational DBs out of the analytics path (analytics_events is a landing buffer, never queried for analytics)</t>
+          <t>Analytics: generic event envelope (event_name/user_id/anonymous_id/app_id/session_id/timestamp/properties/context)</t>
         </is>
       </c>
       <c r="D63" s="11" t="inlineStr"/>
@@ -2768,7 +2768,7 @@
       </c>
       <c r="C64" s="11" t="inlineStr">
         <is>
-          <t>Analytics: pipeline foundation for ClickHouse/warehouse/data lake (worker batches NDJSON into MinIO/S3)</t>
+          <t>Analytics: keep operational DBs out of the analytics path (analytics_events is a landing buffer, never queried for analytics)</t>
         </is>
       </c>
       <c r="D64" s="11" t="inlineStr"/>
@@ -2777,37 +2777,37 @@
       <c r="A65" s="9" t="n">
         <v>23</v>
       </c>
-      <c r="B65" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B65" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
-          <t>Analytics: an actual ClickHouse/warehouse/data-lake query layer</t>
-        </is>
-      </c>
-      <c r="D65" s="11" t="inlineStr">
-        <is>
-          <t>Out of scope - this phase builds the landing pipeline only; no real destination system exists in this environment to integrate against honestly</t>
-        </is>
-      </c>
+          <t>Analytics: pipeline foundation for ClickHouse/warehouse/data lake (worker batches NDJSON into MinIO/S3)</t>
+        </is>
+      </c>
+      <c r="D65" s="11" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="9" t="n">
-        <v>24</v>
-      </c>
-      <c r="B66" s="10" t="inlineStr">
-        <is>
-          <t>Done</t>
+        <v>23</v>
+      </c>
+      <c r="B66" s="13" t="inlineStr">
+        <is>
+          <t>Pending</t>
         </is>
       </c>
       <c r="C66" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: provider-neutral interface (Provider: Name + Complete)</t>
-        </is>
-      </c>
-      <c r="D66" s="11" t="inlineStr"/>
+          <t>Analytics: an actual ClickHouse/warehouse/data-lake query layer</t>
+        </is>
+      </c>
+      <c r="D66" s="11" t="inlineStr">
+        <is>
+          <t>Out of scope - this phase builds the landing pipeline only; no real destination system exists in this environment to integrate against honestly</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="9" t="n">
@@ -2820,32 +2820,28 @@
       </c>
       <c r="C67" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: local models / Ollama adapter</t>
-        </is>
-      </c>
-      <c r="D67" s="11" t="inlineStr">
-        <is>
-          <t>Real local inference via a new Ollama container, auto-pulled model, no vendor API key - the one live-testable provider</t>
-        </is>
-      </c>
+          <t>AI Gateway: provider-neutral interface (Provider: Name + Complete)</t>
+        </is>
+      </c>
+      <c r="D67" s="11" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="9" t="n">
         <v>24</v>
       </c>
-      <c r="B68" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B68" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C68" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: OpenAI adapter</t>
+          <t>AI Gateway: local models / Ollama adapter</t>
         </is>
       </c>
       <c r="D68" s="11" t="inlineStr">
         <is>
-          <t>Deferred - no real API key in this environment to validate against honestly</t>
+          <t>Real local inference via a new Ollama container, auto-pulled model, no vendor API key - the one live-testable provider</t>
         </is>
       </c>
     </row>
@@ -2860,7 +2856,7 @@
       </c>
       <c r="C69" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: Anthropic adapter</t>
+          <t>AI Gateway: OpenAI adapter</t>
         </is>
       </c>
       <c r="D69" s="11" t="inlineStr">
@@ -2880,7 +2876,7 @@
       </c>
       <c r="C70" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: Google adapter</t>
+          <t>AI Gateway: Anthropic adapter</t>
         </is>
       </c>
       <c r="D70" s="11" t="inlineStr">
@@ -2893,17 +2889,21 @@
       <c r="A71" s="9" t="n">
         <v>24</v>
       </c>
-      <c r="B71" s="10" t="inlineStr">
-        <is>
-          <t>Done</t>
+      <c r="B71" s="13" t="inlineStr">
+        <is>
+          <t>Pending</t>
         </is>
       </c>
       <c r="C71" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: model routing (product-facing ModelAlias, never a vendor model name)</t>
-        </is>
-      </c>
-      <c r="D71" s="11" t="inlineStr"/>
+          <t>AI Gateway: Google adapter</t>
+        </is>
+      </c>
+      <c r="D71" s="11" t="inlineStr">
+        <is>
+          <t>Deferred - no real API key in this environment to validate against honestly</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="9" t="n">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="C72" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: quotas (ratelimit.Limiter reused a third time, 60/min/caller)</t>
+          <t>AI Gateway: model routing (product-facing ModelAlias, never a vendor model name)</t>
         </is>
       </c>
       <c r="D72" s="11" t="inlineStr"/>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="C73" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: token usage tracking</t>
+          <t>AI Gateway: quotas (ratelimit.Limiter reused a third time, 60/min/caller)</t>
         </is>
       </c>
       <c r="D73" s="11" t="inlineStr"/>
@@ -2948,7 +2948,7 @@
       </c>
       <c r="C74" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: cost tracking (real per-route price table; Ollama honestly priced at 0)</t>
+          <t>AI Gateway: token usage tracking</t>
         </is>
       </c>
       <c r="D74" s="11" t="inlineStr"/>
@@ -2964,7 +2964,7 @@
       </c>
       <c r="C75" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: audit integration (new AIGatewayAuditRecorder, a genuine audit.Record per call)</t>
+          <t>AI Gateway: cost tracking (real per-route price table; Ollama honestly priced at 0)</t>
         </is>
       </c>
       <c r="D75" s="11" t="inlineStr"/>
@@ -2980,7 +2980,7 @@
       </c>
       <c r="C76" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: prompt/version metadata (free-form PromptKey/PromptVersion)</t>
+          <t>AI Gateway: audit integration (new AIGatewayAuditRecorder, a genuine audit.Record per call)</t>
         </is>
       </c>
       <c r="D76" s="11" t="inlineStr"/>
@@ -2996,7 +2996,7 @@
       </c>
       <c r="C77" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: timeouts (context.WithTimeout per provider call)</t>
+          <t>AI Gateway: prompt/version metadata (free-form PromptKey/PromptVersion)</t>
         </is>
       </c>
       <c r="D77" s="11" t="inlineStr"/>
@@ -3012,7 +3012,7 @@
       </c>
       <c r="C78" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: fallback (ordered provider/model chain, first success wins)</t>
+          <t>AI Gateway: timeouts (context.WithTimeout per provider call)</t>
         </is>
       </c>
       <c r="D78" s="11" t="inlineStr"/>
@@ -3021,37 +3021,37 @@
       <c r="A79" s="9" t="n">
         <v>24</v>
       </c>
-      <c r="B79" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B79" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C79" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: live token-quantity quota (as opposed to today's call-count quota)</t>
-        </is>
-      </c>
-      <c r="D79" s="11" t="inlineStr">
-        <is>
-          <t>Deferred - Repository already has the data (Completion.TotalTokens); not wired as a live gate yet</t>
-        </is>
-      </c>
+          <t>AI Gateway: fallback (ordered provider/model chain, first success wins)</t>
+        </is>
+      </c>
+      <c r="D79" s="11" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="9" t="n">
-        <v>25</v>
-      </c>
-      <c r="B80" s="10" t="inlineStr">
-        <is>
-          <t>Done</t>
+        <v>24</v>
+      </c>
+      <c r="B80" s="13" t="inlineStr">
+        <is>
+          <t>Pending</t>
         </is>
       </c>
       <c r="C80" s="11" t="inlineStr">
         <is>
-          <t>Admin Portal: real Keycloak-authenticated session (Resource Owner Password Credentials grant), httpOnly session cookie</t>
-        </is>
-      </c>
-      <c r="D80" s="11" t="inlineStr"/>
+          <t>AI Gateway: live token-quantity quota (as opposed to today's call-count quota)</t>
+        </is>
+      </c>
+      <c r="D80" s="11" t="inlineStr">
+        <is>
+          <t>Deferred - Repository already has the data (Completion.TotalTokens); not wired as a live gate yet</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="9" t="n">
@@ -3064,14 +3064,10 @@
       </c>
       <c r="C81" s="11" t="inlineStr">
         <is>
-          <t>Admin Portal: visibility - Applications</t>
-        </is>
-      </c>
-      <c r="D81" s="11" t="inlineStr">
-        <is>
-          <t>Real GET /v1/apps table</t>
-        </is>
-      </c>
+          <t>Admin Portal: real Keycloak-authenticated session (Resource Owner Password Credentials grant), httpOnly session cookie</t>
+        </is>
+      </c>
+      <c r="D81" s="11" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="9" t="n">
@@ -3084,12 +3080,12 @@
       </c>
       <c r="C82" s="11" t="inlineStr">
         <is>
-          <t>Admin Portal: visibility - Users (list + detail)</t>
+          <t>Admin Portal: visibility - Applications</t>
         </is>
       </c>
       <c r="D82" s="11" t="inlineStr">
         <is>
-          <t>New admin-wide GET /v1/users (cursor-paginated, platform.admin-gated)</t>
+          <t>Real GET /v1/apps table</t>
         </is>
       </c>
     </row>
@@ -3104,12 +3100,12 @@
       </c>
       <c r="C83" s="11" t="inlineStr">
         <is>
-          <t>Admin Portal: visibility - Roles/Permissions</t>
+          <t>Admin Portal: visibility - Users (list + detail)</t>
         </is>
       </c>
       <c r="D83" s="11" t="inlineStr">
         <is>
-          <t>New authz HTTP surface (GET/POST /v1/authz/roles, POST /v1/authz/roles/revoke) with a full grant/revoke UI</t>
+          <t>New admin-wide GET /v1/users (cursor-paginated, platform.admin-gated)</t>
         </is>
       </c>
     </row>
@@ -3124,10 +3120,14 @@
       </c>
       <c r="C84" s="11" t="inlineStr">
         <is>
-          <t>Admin Portal: visibility - Feature Flags, Configuration, Jobs</t>
-        </is>
-      </c>
-      <c r="D84" s="11" t="inlineStr"/>
+          <t>Admin Portal: visibility - Roles/Permissions</t>
+        </is>
+      </c>
+      <c r="D84" s="11" t="inlineStr">
+        <is>
+          <t>New authz HTTP surface (GET/POST /v1/authz/roles, POST /v1/authz/roles/revoke) with a full grant/revoke UI</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="9" t="n">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="C85" s="11" t="inlineStr">
         <is>
-          <t>Admin Portal: visibility - Moderation, Audit</t>
+          <t>Admin Portal: visibility - Feature Flags, Configuration, Jobs</t>
         </is>
       </c>
       <c r="D85" s="11" t="inlineStr"/>
@@ -3156,14 +3156,10 @@
       </c>
       <c r="C86" s="11" t="inlineStr">
         <is>
-          <t>Admin Portal: visibility - System Health</t>
-        </is>
-      </c>
-      <c r="D86" s="11" t="inlineStr">
-        <is>
-          <t>Live GET /healthz against core-api/realtime-gateway/worker</t>
-        </is>
-      </c>
+          <t>Admin Portal: visibility - Moderation, Audit</t>
+        </is>
+      </c>
+      <c r="D86" s="11" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="9" t="n">
@@ -3176,30 +3172,30 @@
       </c>
       <c r="C87" s="11" t="inlineStr">
         <is>
-          <t>Admin Portal: visibility - Billing, AI Gateway usage (bonus, not roadmap-named)</t>
-        </is>
-      </c>
-      <c r="D87" s="11" t="inlineStr"/>
+          <t>Admin Portal: visibility - System Health</t>
+        </is>
+      </c>
+      <c r="D87" s="11" t="inlineStr">
+        <is>
+          <t>Live GET /healthz against core-api/realtime-gateway/worker</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="B88" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B88" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C88" s="11" t="inlineStr">
         <is>
-          <t>Admin Portal: visibility - Sessions/Devices, Tenants, Relationships, Messages, Notifications, Files</t>
-        </is>
-      </c>
-      <c r="D88" s="11" t="inlineStr">
-        <is>
-          <t>Deferred - each backing module only exposes a listMine-style self-scoped endpoint, not an admin-wide one; honest ComingSoon reasoning shown per area instead of fake rows</t>
-        </is>
-      </c>
+          <t>Admin Portal: visibility - Billing, AI Gateway usage (bonus, not roadmap-named)</t>
+        </is>
+      </c>
+      <c r="D88" s="11" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="9" t="n">
@@ -3212,32 +3208,32 @@
       </c>
       <c r="C89" s="11" t="inlineStr">
         <is>
-          <t>Admin Portal: visibility - Deployments</t>
+          <t>Admin Portal: visibility - Sessions/Devices, Tenants, Relationships, Messages, Notifications, Files</t>
         </is>
       </c>
       <c r="D89" s="11" t="inlineStr">
         <is>
-          <t>Deferred to Phase 29 - nothing in the platform tracks deployments as data yet</t>
+          <t>Deferred - each backing module only exposes a listMine-style self-scoped endpoint, not an admin-wide one; honest ComingSoon reasoning shown per area instead of fake rows</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="9" t="n">
-        <v>26</v>
-      </c>
-      <c r="B90" s="10" t="inlineStr">
-        <is>
-          <t>Done</t>
+        <v>25</v>
+      </c>
+      <c r="B90" s="13" t="inlineStr">
+        <is>
+          <t>Pending</t>
         </is>
       </c>
       <c r="C90" s="11" t="inlineStr">
         <is>
-          <t>Backstage: integrate Backstage as developer portal</t>
+          <t>Admin Portal: visibility - Deployments</t>
         </is>
       </c>
       <c r="D90" s="11" t="inlineStr">
         <is>
-          <t>Real @backstage/create-app instance at platform/backstage, catalog wired to real catalog/*.yaml + contracts/*/catalog-info.yaml, live-validated via the real catalog API (21 Components, 2 APIs, 1 System, 1 Group, 0 processing errors)</t>
+          <t>Deferred to Phase 29 - nothing in the platform tracks deployments as data yet</t>
         </is>
       </c>
     </row>
@@ -3252,12 +3248,12 @@
       </c>
       <c r="C91" s="11" t="inlineStr">
         <is>
-          <t>Backstage: per-module metadata - name/description/owner/lifecycle</t>
+          <t>Backstage: integrate Backstage as developer portal</t>
         </is>
       </c>
       <c r="D91" s="11" t="inlineStr">
         <is>
-          <t>All 16 modules/*/module.yaml + README.md real (11 were still stub text before this phase)</t>
+          <t>Real @backstage/create-app instance at platform/backstage, catalog wired to real catalog/*.yaml + contracts/*/catalog-info.yaml, live-validated via the real catalog API (21 Components, 2 APIs, 1 System, 1 Group, 0 processing errors)</t>
         </is>
       </c>
     </row>
@@ -3272,12 +3268,12 @@
       </c>
       <c r="C92" s="11" t="inlineStr">
         <is>
-          <t>Backstage: per-module metadata - repository/documentation</t>
+          <t>Backstage: per-module metadata - name/description/owner/lifecycle</t>
         </is>
       </c>
       <c r="D92" s="11" t="inlineStr">
         <is>
-          <t>Every Component links its module README; the System entity links VALIDATION.md and the new docs/RUNBOOKS.md</t>
+          <t>All 16 modules/*/module.yaml + README.md real (11 were still stub text before this phase)</t>
         </is>
       </c>
     </row>
@@ -3292,12 +3288,12 @@
       </c>
       <c r="C93" s="11" t="inlineStr">
         <is>
-          <t>Backstage: per-module metadata - dependencies</t>
+          <t>Backstage: per-module metadata - repository/documentation</t>
         </is>
       </c>
       <c r="D93" s="11" t="inlineStr">
         <is>
-          <t>Component dependsOn mirrors modules/*/module.yaml's real dependency graph; Backstage computes reverse dependencyOf relations automatically, confirmed live</t>
+          <t>Every Component links its module README; the System entity links VALIDATION.md and the new docs/RUNBOOKS.md</t>
         </is>
       </c>
     </row>
@@ -3312,12 +3308,12 @@
       </c>
       <c r="C94" s="11" t="inlineStr">
         <is>
-          <t>Backstage: per-module metadata - APIs</t>
+          <t>Backstage: per-module metadata - dependencies</t>
         </is>
       </c>
       <c r="D94" s="11" t="inlineStr">
         <is>
-          <t>2 API entities (OpenAPI, AsyncAPI), both with their full real spec embedded and live-loaded</t>
+          <t>Component dependsOn mirrors modules/*/module.yaml's real dependency graph; Backstage computes reverse dependencyOf relations automatically, confirmed live</t>
         </is>
       </c>
     </row>
@@ -3332,12 +3328,12 @@
       </c>
       <c r="C95" s="11" t="inlineStr">
         <is>
-          <t>Backstage: per-module metadata - events</t>
+          <t>Backstage: per-module metadata - APIs</t>
         </is>
       </c>
       <c r="D95" s="11" t="inlineStr">
         <is>
-          <t>providesApis set only on the components whose code actually calls outbox.Record, cross-checked against the real Go source</t>
+          <t>2 API entities (OpenAPI, AsyncAPI), both with their full real spec embedded and live-loaded</t>
         </is>
       </c>
     </row>
@@ -3345,19 +3341,19 @@
       <c r="A96" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="B96" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B96" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C96" s="11" t="inlineStr">
         <is>
-          <t>Backstage: per-module metadata - database ownership</t>
+          <t>Backstage: per-module metadata - events</t>
         </is>
       </c>
       <c r="D96" s="11" t="inlineStr">
         <is>
-          <t>Deferred - no per-module DB-ownership annotation convention chosen yet; docs/control's Modules sheet tracks this today at a finer grain than catalog/system.yaml's 16 domains</t>
+          <t>providesApis set only on the components whose code actually calls outbox.Record, cross-checked against the real Go source</t>
         </is>
       </c>
     </row>
@@ -3365,19 +3361,19 @@
       <c r="A97" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="B97" s="10" t="inlineStr">
-        <is>
-          <t>Done</t>
+      <c r="B97" s="13" t="inlineStr">
+        <is>
+          <t>Pending</t>
         </is>
       </c>
       <c r="C97" s="11" t="inlineStr">
         <is>
-          <t>Backstage: per-module metadata - dashboards</t>
+          <t>Backstage: per-module metadata - database ownership</t>
         </is>
       </c>
       <c r="D97" s="11" t="inlineStr">
         <is>
-          <t>core-platform.io/dashboard annotation on each service pointing at the real local Grafana instance - no per-service dashboard exists yet (that's Phase 28), so it points at the shared instance, documented as such</t>
+          <t>Deferred - no per-module DB-ownership annotation convention chosen yet; docs/control's Modules sheet tracks this today at a finer grain than catalog/system.yaml's 16 domains</t>
         </is>
       </c>
     </row>
@@ -3392,18 +3388,18 @@
       </c>
       <c r="C98" s="11" t="inlineStr">
         <is>
-          <t>Backstage: per-module metadata - runbooks</t>
+          <t>Backstage: per-module metadata - dashboards</t>
         </is>
       </c>
       <c r="D98" s="11" t="inlineStr">
         <is>
-          <t>New docs/RUNBOOKS.md, linked from the System entity</t>
+          <t>core-platform.io/dashboard annotation on each service pointing at the real local Grafana instance - no per-service dashboard exists yet (that's Phase 28), so it points at the shared instance, documented as such</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B99" s="10" t="inlineStr">
         <is>
@@ -3412,12 +3408,12 @@
       </c>
       <c r="C99" s="11" t="inlineStr">
         <is>
-          <t>SDKs: Go SDK</t>
+          <t>Backstage: per-module metadata - runbooks</t>
         </is>
       </c>
       <c r="D99" s="11" t="inlineStr">
         <is>
-          <t>packages/go/coresdk - 12 unit tests (httptest.Server), live-validated against real Keycloak/core-api/realtime-gateway</t>
+          <t>New docs/RUNBOOKS.md, linked from the System entity</t>
         </is>
       </c>
     </row>
@@ -3432,12 +3428,12 @@
       </c>
       <c r="C100" s="11" t="inlineStr">
         <is>
-          <t>SDKs: TypeScript SDK</t>
+          <t>SDKs: Go SDK</t>
         </is>
       </c>
       <c r="D100" s="11" t="inlineStr">
         <is>
-          <t>packages/typescript/core-sdk - 13 unit tests (node:http), real consumer: apps/admin's entire lib/api.ts migrated to it</t>
+          <t>packages/go/coresdk - 12 unit tests (httptest.Server), live-validated against real Keycloak/core-api/realtime-gateway</t>
         </is>
       </c>
     </row>
@@ -3452,12 +3448,12 @@
       </c>
       <c r="C101" s="11" t="inlineStr">
         <is>
-          <t>SDKs: Dart SDK</t>
+          <t>SDKs: TypeScript SDK</t>
         </is>
       </c>
       <c r="D101" s="11" t="inlineStr">
         <is>
-          <t>packages/flutter/core_sdk (pure Dart, no Flutter dependency) - 13 unit tests (dart:io HttpServer), real consumer: apps/mobile's login/profile flow</t>
+          <t>packages/typescript/core-sdk - 13 unit tests (node:http), real consumer: apps/admin's entire lib/api.ts migrated to it</t>
         </is>
       </c>
     </row>
@@ -3472,12 +3468,12 @@
       </c>
       <c r="C102" s="11" t="inlineStr">
         <is>
-          <t>SDKs: auth + token refresh in each SDK</t>
+          <t>SDKs: Dart SDK</t>
         </is>
       </c>
       <c r="D102" s="11" t="inlineStr">
         <is>
-          <t>TokenSource (static + real Keycloak password-grant with skew-aware, concurrency-coalesced refresh) in all three</t>
+          <t>packages/flutter/core_sdk (pure Dart, no Flutter dependency) - 13 unit tests (dart:io HttpServer), real consumer: apps/mobile's login/profile flow</t>
         </is>
       </c>
     </row>
@@ -3492,12 +3488,12 @@
       </c>
       <c r="C103" s="11" t="inlineStr">
         <is>
-          <t>SDKs: pagination + safe retries</t>
+          <t>SDKs: auth + token refresh in each SDK</t>
         </is>
       </c>
       <c r="D103" s="11" t="inlineStr">
         <is>
-          <t>Page/paginate/collectAll over the real {items,nextCursor} shape; GET-only retries by default on transient statuses, in all three</t>
+          <t>TokenSource (static + real Keycloak password-grant with skew-aware, concurrency-coalesced refresh) in all three</t>
         </is>
       </c>
     </row>
@@ -3512,12 +3508,12 @@
       </c>
       <c r="C104" s="11" t="inlineStr">
         <is>
-          <t>SDKs: realtime connection helper</t>
+          <t>SDKs: pagination + safe retries</t>
         </is>
       </c>
       <c r="D104" s="11" t="inlineStr">
         <is>
-          <t>Reproduces realtime-gateway's real ws://.../ws?access_token=&amp;deviceId= protocol and message shapes exactly, in all three - live-validated with real cross-connection fan-out</t>
+          <t>Page/paginate/collectAll over the real {items,nextCursor} shape; GET-only retries by default on transient statuses, in all three</t>
         </is>
       </c>
     </row>
@@ -3532,12 +3528,12 @@
       </c>
       <c r="C105" s="11" t="inlineStr">
         <is>
-          <t>SDKs: correlation ID propagation</t>
+          <t>SDKs: realtime connection helper</t>
         </is>
       </c>
       <c r="D105" s="11" t="inlineStr">
         <is>
-          <t>X-Correlation-ID on every call, matching platformkit/correlation's real header name, in all three</t>
+          <t>Reproduces realtime-gateway's real ws://.../ws?access_token=&amp;deviceId= protocol and message shapes exactly, in all three - live-validated with real cross-connection fan-out</t>
         </is>
       </c>
     </row>
@@ -3552,12 +3548,12 @@
       </c>
       <c r="C106" s="11" t="inlineStr">
         <is>
-          <t>SDKs: device registration helper</t>
+          <t>SDKs: correlation ID propagation</t>
         </is>
       </c>
       <c r="D106" s="11" t="inlineStr">
         <is>
-          <t>DevicesRegister/devicesRegister in all three - realtime dial requires a real registered device id</t>
+          <t>X-Correlation-ID on every call, matching platformkit/correlation's real header name, in all three</t>
         </is>
       </c>
     </row>
@@ -3572,12 +3568,12 @@
       </c>
       <c r="C107" s="11" t="inlineStr">
         <is>
-          <t>SDKs: apps/mobile test/ directory (make flutter-test currently fails)</t>
+          <t>SDKs: device registration helper</t>
         </is>
       </c>
       <c r="D107" s="11" t="inlineStr">
         <is>
-          <t>Closed as a side effect - real widget tests added, discovered and worked around Flutter's TestWidgetsFlutterBinding network-mocking constraint live. Was pending since Phase 9.</t>
+          <t>DevicesRegister/devicesRegister in all three - realtime dial requires a real registered device id</t>
         </is>
       </c>
     </row>
@@ -3585,25 +3581,25 @@
       <c r="A108" s="9" t="n">
         <v>27</v>
       </c>
-      <c r="B108" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B108" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C108" s="11" t="inlineStr">
         <is>
-          <t>SDKs: full API coverage (all 146 endpoints typed) in each SDK</t>
+          <t>SDKs: apps/mobile test/ directory (make flutter-test currently fails)</t>
         </is>
       </c>
       <c r="D108" s="11" t="inlineStr">
         <is>
-          <t>Deferred - each SDK covers a representative 'core identity' slice (platform/identity/users/devices/applications) plus what its real consumer needs; the untyped request()/Do() escape hatch reaches everything else. Broader coverage is real, additive work, not a framework limitation.</t>
+          <t>Closed as a side effect - real widget tests added, discovered and worked around Flutter's TestWidgetsFlutterBinding network-mocking constraint live. Was pending since Phase 9.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B109" s="13" t="inlineStr">
         <is>
@@ -3612,138 +3608,174 @@
       </c>
       <c r="C109" s="11" t="inlineStr">
         <is>
-          <t>Observability Completion: structured logs everywhere</t>
-        </is>
-      </c>
-      <c r="D109" s="11" t="inlineStr"/>
+          <t>SDKs: full API coverage (all 146 endpoints typed) in each SDK</t>
+        </is>
+      </c>
+      <c r="D109" s="11" t="inlineStr">
+        <is>
+          <t>Deferred - each SDK covers a representative 'core identity' slice (platform/identity/users/devices/applications) plus what its real consumer needs; the untyped request()/Do() escape hatch reaches everything else. Broader coverage is real, additive work, not a framework limitation.</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="9" t="n">
         <v>28</v>
       </c>
-      <c r="B110" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B110" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C110" s="11" t="inlineStr">
         <is>
-          <t>Observability Completion: metrics everywhere</t>
-        </is>
-      </c>
-      <c r="D110" s="11" t="inlineStr"/>
+          <t>Observability: structured logs everywhere</t>
+        </is>
+      </c>
+      <c r="D110" s="11" t="inlineStr">
+        <is>
+          <t>logging.NewWithLoki ships every record to Loki's real push API directly; on by default locally (LOKI_PUSH_URL)</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="9" t="n">
         <v>28</v>
       </c>
-      <c r="B111" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B111" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C111" s="11" t="inlineStr">
         <is>
-          <t>Observability Completion: distributed traces everywhere</t>
-        </is>
-      </c>
-      <c r="D111" s="11" t="inlineStr"/>
+          <t>Observability: metrics everywhere</t>
+        </is>
+      </c>
+      <c r="D111" s="11" t="inlineStr">
+        <is>
+          <t>New packages/go/platformkit/metrics - real GET /metrics (Prometheus exposition) on core-api, realtime-gateway, and worker</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="9" t="n">
         <v>28</v>
       </c>
-      <c r="B112" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B112" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C112" s="11" t="inlineStr">
         <is>
-          <t>Observability Completion: health checks everywhere</t>
-        </is>
-      </c>
-      <c r="D112" s="11" t="inlineStr"/>
+          <t>Observability: distributed traces everywhere</t>
+        </is>
+      </c>
+      <c r="D112" s="11" t="inlineStr">
+        <is>
+          <t>Already real since Phase 1 (otelx) - confirmed still working live this phase</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="9" t="n">
         <v>28</v>
       </c>
-      <c r="B113" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B113" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C113" s="11" t="inlineStr">
         <is>
-          <t>Observability Completion: dashboard: API latency</t>
-        </is>
-      </c>
-      <c r="D113" s="11" t="inlineStr"/>
+          <t>Observability: health checks everywhere</t>
+        </is>
+      </c>
+      <c r="D113" s="11" t="inlineStr">
+        <is>
+          <t>Already real since Phase 1 (/livez /readyz /healthz) - confirmed still working live this phase</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="9" t="n">
         <v>28</v>
       </c>
-      <c r="B114" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B114" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C114" s="11" t="inlineStr">
         <is>
-          <t>Observability Completion: dashboard: error rate</t>
-        </is>
-      </c>
-      <c r="D114" s="11" t="inlineStr"/>
+          <t>Observability: dashboard - API latency</t>
+        </is>
+      </c>
+      <c r="D114" s="11" t="inlineStr">
+        <is>
+          <t>http_request_duration_seconds, labeled by route pattern (not raw path) to keep cardinality bounded</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="9" t="n">
         <v>28</v>
       </c>
-      <c r="B115" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B115" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C115" s="11" t="inlineStr">
         <is>
-          <t>Observability Completion: dashboard: requests/sec</t>
-        </is>
-      </c>
-      <c r="D115" s="11" t="inlineStr"/>
+          <t>Observability: dashboard - error rate</t>
+        </is>
+      </c>
+      <c r="D115" s="11" t="inlineStr">
+        <is>
+          <t>http_requests_total{status=~"5.."} / http_requests_total</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="9" t="n">
         <v>28</v>
       </c>
-      <c r="B116" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B116" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C116" s="11" t="inlineStr">
         <is>
-          <t>Observability Completion: dashboard: DB connections</t>
-        </is>
-      </c>
-      <c r="D116" s="11" t="inlineStr"/>
+          <t>Observability: dashboard - requests/sec</t>
+        </is>
+      </c>
+      <c r="D116" s="11" t="inlineStr">
+        <is>
+          <t>rate(http_requests_total[5m])</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="9" t="n">
         <v>28</v>
       </c>
-      <c r="B117" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B117" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C117" s="11" t="inlineStr">
         <is>
-          <t>Observability Completion: dashboard: Kafka lag</t>
-        </is>
-      </c>
-      <c r="D117" s="11" t="inlineStr"/>
+          <t>Observability: dashboard - DB connections</t>
+        </is>
+      </c>
+      <c r="D117" s="11" t="inlineStr">
+        <is>
+          <t>db_pool_connections, real pgxpool.Stat() polled on a ticker (pg.ReportStats) on all 3 services</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="9" t="n">
@@ -3756,94 +3788,118 @@
       </c>
       <c r="C118" s="11" t="inlineStr">
         <is>
-          <t>Observability Completion: dashboard: WebSocket connections</t>
-        </is>
-      </c>
-      <c r="D118" s="11" t="inlineStr"/>
+          <t>Observability: dashboard - Kafka lag</t>
+        </is>
+      </c>
+      <c r="D118" s="11" t="inlineStr">
+        <is>
+          <t>Deliberately not implemented - no real Kafka/Redpanda producer or consumer exists in this codebase yet (documented since Phase 14); an honest placeholder panel explains this instead of a fabricated metric</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="9" t="n">
         <v>28</v>
       </c>
-      <c r="B119" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B119" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C119" s="11" t="inlineStr">
         <is>
-          <t>Observability Completion: dashboard: Redis latency</t>
-        </is>
-      </c>
-      <c r="D119" s="11" t="inlineStr"/>
+          <t>Observability: dashboard - WebSocket connections</t>
+        </is>
+      </c>
+      <c r="D119" s="11" t="inlineStr">
+        <is>
+          <t>realtime_ws_connections, live-validated going 0 -&gt; 1 -&gt; 0 across a real connect/hold/disconnect cycle against the running service</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="9" t="n">
         <v>28</v>
       </c>
-      <c r="B120" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B120" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C120" s="11" t="inlineStr">
         <is>
-          <t>Observability Completion: dashboard: notification failures</t>
-        </is>
-      </c>
-      <c r="D120" s="11" t="inlineStr"/>
+          <t>Observability: dashboard - Redis latency</t>
+        </is>
+      </c>
+      <c r="D120" s="11" t="inlineStr">
+        <is>
+          <t>redis_command_duration_seconds via a real go-redis v9 Hook, InstrumentRedis</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="9" t="n">
         <v>28</v>
       </c>
-      <c r="B121" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B121" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C121" s="11" t="inlineStr">
         <is>
-          <t>Observability Completion: dashboard: background job failures</t>
-        </is>
-      </c>
-      <c r="D121" s="11" t="inlineStr"/>
+          <t>Observability: dashboard - notification failures</t>
+        </is>
+      </c>
+      <c r="D121" s="11" t="inlineStr">
+        <is>
+          <t>notification_delivery_failures_total, incremented at notifications.Service.dispatch's two real failure paths</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="9" t="n">
         <v>28</v>
       </c>
-      <c r="B122" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B122" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C122" s="11" t="inlineStr">
         <is>
-          <t>Observability Completion: alerting rules</t>
-        </is>
-      </c>
-      <c r="D122" s="11" t="inlineStr"/>
+          <t>Observability: dashboard - background job failures</t>
+        </is>
+      </c>
+      <c r="D122" s="11" t="inlineStr">
+        <is>
+          <t>job_failures_total, incremented only on jobrunner's real dead_letter transition (not every retryable attempt)</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="9" t="n">
-        <v>29</v>
-      </c>
-      <c r="B123" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+        <v>28</v>
+      </c>
+      <c r="B123" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C123" s="11" t="inlineStr">
         <is>
-          <t>Platform Control Plane: one view: applications/services/versions</t>
-        </is>
-      </c>
-      <c r="D123" s="11" t="inlineStr"/>
+          <t>Observability: alerting rules</t>
+        </is>
+      </c>
+      <c r="D123" s="11" t="inlineStr">
+        <is>
+          <t>6 real, live-evaluated Prometheus rules (infra/observability/alerts.yml) - ServiceDown live-confirmed firing then clearing on the real service lifecycle</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B124" s="13" t="inlineStr">
         <is>
@@ -3852,14 +3908,18 @@
       </c>
       <c r="C124" s="11" t="inlineStr">
         <is>
-          <t>Platform Control Plane: one view: environments/dependencies/deployments</t>
-        </is>
-      </c>
-      <c r="D124" s="11" t="inlineStr"/>
+          <t>Observability: Alertmanager routing (Slack/PagerDuty/email)</t>
+        </is>
+      </c>
+      <c r="D124" s="11" t="inlineStr">
+        <is>
+          <t>Deferred - no real notification-channel credentials in this environment, the same reasoning Stripe/AI vendor adapters have documented; Prometheus's own rule evaluation and API are real regardless</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B125" s="13" t="inlineStr">
         <is>
@@ -3868,10 +3928,14 @@
       </c>
       <c r="C125" s="11" t="inlineStr">
         <is>
-          <t>Platform Control Plane: one view: DB ownership/events/API contracts</t>
-        </is>
-      </c>
-      <c r="D125" s="11" t="inlineStr"/>
+          <t>Observability: per-service (not shared) Grafana dashboards</t>
+        </is>
+      </c>
+      <c r="D125" s="11" t="inlineStr">
+        <is>
+          <t>Deferred - one shared 'Core Platform Overview' dashboard covers all 3 services today, not 9 separate roadmap-named dashboards</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="9" t="n">
@@ -3884,14 +3948,14 @@
       </c>
       <c r="C126" s="11" t="inlineStr">
         <is>
-          <t>Platform Control Plane: one view: health/alerts/recent changes</t>
+          <t>Platform Control Plane: one view: applications/services/versions</t>
         </is>
       </c>
       <c r="D126" s="11" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="9" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B127" s="13" t="inlineStr">
         <is>
@@ -3900,14 +3964,14 @@
       </c>
       <c r="C127" s="11" t="inlineStr">
         <is>
-          <t>AI Development Context: every module: README</t>
+          <t>Platform Control Plane: one view: environments/dependencies/deployments</t>
         </is>
       </c>
       <c r="D127" s="11" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="9" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B128" s="13" t="inlineStr">
         <is>
@@ -3916,14 +3980,14 @@
       </c>
       <c r="C128" s="11" t="inlineStr">
         <is>
-          <t>AI Development Context: every module: ownership metadata</t>
+          <t>Platform Control Plane: one view: DB ownership/events/API contracts</t>
         </is>
       </c>
       <c r="D128" s="11" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="9" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B129" s="13" t="inlineStr">
         <is>
@@ -3932,7 +3996,7 @@
       </c>
       <c r="C129" s="11" t="inlineStr">
         <is>
-          <t>AI Development Context: every module: dependencies</t>
+          <t>Platform Control Plane: one view: health/alerts/recent changes</t>
         </is>
       </c>
       <c r="D129" s="11" t="inlineStr"/>
@@ -3948,7 +4012,7 @@
       </c>
       <c r="C130" s="11" t="inlineStr">
         <is>
-          <t>AI Development Context: every module: API contract</t>
+          <t>AI Development Context: every module: README</t>
         </is>
       </c>
       <c r="D130" s="11" t="inlineStr"/>
@@ -3964,7 +4028,7 @@
       </c>
       <c r="C131" s="11" t="inlineStr">
         <is>
-          <t>AI Development Context: every module: event contracts</t>
+          <t>AI Development Context: every module: ownership metadata</t>
         </is>
       </c>
       <c r="D131" s="11" t="inlineStr"/>
@@ -3980,10 +4044,58 @@
       </c>
       <c r="C132" s="11" t="inlineStr">
         <is>
+          <t>AI Development Context: every module: dependencies</t>
+        </is>
+      </c>
+      <c r="D132" s="11" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="B133" s="13" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="C133" s="11" t="inlineStr">
+        <is>
+          <t>AI Development Context: every module: API contract</t>
+        </is>
+      </c>
+      <c r="D133" s="11" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="B134" s="13" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="C134" s="11" t="inlineStr">
+        <is>
+          <t>AI Development Context: every module: event contracts</t>
+        </is>
+      </c>
+      <c r="D134" s="11" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="B135" s="13" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="C135" s="11" t="inlineStr">
+        <is>
           <t>AI Development Context: every module: DB ownership</t>
         </is>
       </c>
-      <c r="D132" s="11" t="inlineStr"/>
+      <c r="D135" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5016,7 +5128,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E147"/>
+  <dimension ref="A1:E148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5142,7 +5254,7 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>/v1/platform</t>
+          <t>/metrics</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
@@ -5157,37 +5269,41 @@
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>platform name/env/version</t>
+          <t>Prometheus exposition (Phase 28) - real on core-api, realtime-gateway, and worker</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>/v1/apps</t>
+          <t>/v1/platform</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>applications</t>
+          <t>platform</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>Open (this phase's scope)</t>
-        </is>
-      </c>
-      <c r="E6" s="11" t="inlineStr"/>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="inlineStr">
+        <is>
+          <t>platform name/env/version</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr">
@@ -5202,14 +5318,10 @@
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="E7" s="11" t="inlineStr">
-        <is>
-          <t>cursor-paginated list</t>
-        </is>
-      </c>
+          <t>Open (this phase's scope)</t>
+        </is>
+      </c>
+      <c r="E7" s="11" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
@@ -5219,7 +5331,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>/v1/apps/{id}</t>
+          <t>/v1/apps</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
@@ -5232,12 +5344,16 @@
           <t>Open</t>
         </is>
       </c>
-      <c r="E8" s="11" t="inlineStr"/>
+      <c r="E8" s="11" t="inlineStr">
+        <is>
+          <t>cursor-paginated list</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="11" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B9" s="11" t="inlineStr">
@@ -5252,7 +5368,7 @@
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>Open (this phase's scope)</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr"/>
@@ -5260,29 +5376,25 @@
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>/v1/identity/me</t>
+          <t>/v1/apps/{id}</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>identity</t>
+          <t>applications</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>Authenticated</t>
-        </is>
-      </c>
-      <c r="E10" s="11" t="inlineStr">
-        <is>
-          <t>resolves the caller's Identity</t>
-        </is>
-      </c>
+          <t>Open (this phase's scope)</t>
+        </is>
+      </c>
+      <c r="E10" s="11" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
@@ -5292,25 +5404,29 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>/v1/users/me</t>
+          <t>/v1/identity/me</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>users</t>
+          <t>identity</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>Authenticated (self)</t>
-        </is>
-      </c>
-      <c r="E11" s="11" t="inlineStr"/>
+          <t>Authenticated</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>resolves the caller's Identity</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B12" s="11" t="inlineStr">
@@ -5333,12 +5449,12 @@
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>/v1/users/{id}</t>
+          <t>/v1/users/me</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
@@ -5348,7 +5464,7 @@
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>Self or platform.admin</t>
+          <t>Authenticated (self)</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr"/>
@@ -5361,7 +5477,7 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>/v1/users</t>
+          <t>/v1/users/{id}</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
@@ -5371,14 +5487,10 @@
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>platform.admin</t>
-        </is>
-      </c>
-      <c r="E14" s="11" t="inlineStr">
-        <is>
-          <t>Phase 25: cursor-paginated admin-wide listing, new to close a real Admin Portal gap</t>
-        </is>
-      </c>
+          <t>Self or platform.admin</t>
+        </is>
+      </c>
+      <c r="E14" s="11" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
@@ -5388,29 +5500,29 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>/v1/authz/roles</t>
+          <t>/v1/users</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>authz</t>
+          <t>users</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>Self or platform.admin</t>
+          <t>platform.admin</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>Phase 25: authz's first-ever HTTP surface</t>
+          <t>Phase 25: cursor-paginated admin-wide listing, new to close a real Admin Portal gap</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B16" s="11" t="inlineStr">
@@ -5425,12 +5537,12 @@
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>platform.admin</t>
+          <t>Self or platform.admin</t>
         </is>
       </c>
       <c r="E16" s="11" t="inlineStr">
         <is>
-          <t>assign a role to a user</t>
+          <t>Phase 25: authz's first-ever HTTP surface</t>
         </is>
       </c>
     </row>
@@ -5442,7 +5554,7 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>/v1/authz/roles/revoke</t>
+          <t>/v1/authz/roles</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
@@ -5457,37 +5569,41 @@
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>revoke a role from a user</t>
+          <t>assign a role to a user</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>/v1/users/me/devices</t>
+          <t>/v1/authz/roles/revoke</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>devices</t>
+          <t>authz</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
         <is>
-          <t>Authenticated (self)</t>
-        </is>
-      </c>
-      <c r="E18" s="11" t="inlineStr"/>
+          <t>platform.admin</t>
+        </is>
+      </c>
+      <c r="E18" s="11" t="inlineStr">
+        <is>
+          <t>revoke a role from a user</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B19" s="11" t="inlineStr">
@@ -5505,21 +5621,17 @@
           <t>Authenticated (self)</t>
         </is>
       </c>
-      <c r="E19" s="11" t="inlineStr">
-        <is>
-          <t>register/upsert</t>
-        </is>
-      </c>
+      <c r="E19" s="11" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>/v1/users/me/devices/{id}</t>
+          <t>/v1/users/me/devices</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
@@ -5534,41 +5646,41 @@
       </c>
       <c r="E20" s="11" t="inlineStr">
         <is>
-          <t>soft-revoke</t>
+          <t>register/upsert</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>/v1/tenants</t>
+          <t>/v1/users/me/devices/{id}</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>tenants</t>
+          <t>devices</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>Authenticated</t>
+          <t>Authenticated (self)</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>scoped to caller's own tenants</t>
+          <t>soft-revoke</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B22" s="11" t="inlineStr">
@@ -5588,19 +5700,19 @@
       </c>
       <c r="E22" s="11" t="inlineStr">
         <is>
-          <t>creator becomes owner</t>
+          <t>scoped to caller's own tenants</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>/v1/tenants/{id}</t>
+          <t>/v1/tenants</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
@@ -5610,15 +5722,19 @@
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>Member</t>
-        </is>
-      </c>
-      <c r="E23" s="11" t="inlineStr"/>
+          <t>Authenticated</t>
+        </is>
+      </c>
+      <c r="E23" s="11" t="inlineStr">
+        <is>
+          <t>creator becomes owner</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B24" s="11" t="inlineStr">
@@ -5633,7 +5749,7 @@
       </c>
       <c r="D24" s="11" t="inlineStr">
         <is>
-          <t>Owner or admin</t>
+          <t>Member</t>
         </is>
       </c>
       <c r="E24" s="11" t="inlineStr"/>
@@ -5641,12 +5757,12 @@
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>/v1/tenants/{id}/members</t>
+          <t>/v1/tenants/{id}</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
@@ -5656,7 +5772,7 @@
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>Member</t>
+          <t>Owner or admin</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr"/>
@@ -5664,7 +5780,7 @@
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B26" s="11" t="inlineStr">
@@ -5679,7 +5795,7 @@
       </c>
       <c r="D26" s="11" t="inlineStr">
         <is>
-          <t>Owner or admin</t>
+          <t>Member</t>
         </is>
       </c>
       <c r="E26" s="11" t="inlineStr"/>
@@ -5687,12 +5803,12 @@
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>/v1/tenants/{id}/members/{userId}</t>
+          <t>/v1/tenants/{id}/members</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
@@ -5702,7 +5818,7 @@
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>Owner/admin, or self (leave)</t>
+          <t>Owner or admin</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr"/>
@@ -5710,22 +5826,22 @@
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>/v1/relationships</t>
+          <t>/v1/tenants/{id}/members/{userId}</t>
         </is>
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>relationships</t>
+          <t>tenants</t>
         </is>
       </c>
       <c r="D28" s="11" t="inlineStr">
         <is>
-          <t>Participant</t>
+          <t>Owner/admin, or self (leave)</t>
         </is>
       </c>
       <c r="E28" s="11" t="inlineStr"/>
@@ -5738,7 +5854,7 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>/v1/relationships/{id}</t>
+          <t>/v1/relationships</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
@@ -5756,12 +5872,12 @@
     <row r="30">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>/v1/relationships</t>
+          <t>/v1/relationships/{id}</t>
         </is>
       </c>
       <c r="C30" s="11" t="inlineStr">
@@ -5771,14 +5887,10 @@
       </c>
       <c r="D30" s="11" t="inlineStr">
         <is>
-          <t>Authenticated</t>
-        </is>
-      </c>
-      <c r="E30" s="11" t="inlineStr">
-        <is>
-          <t>request</t>
-        </is>
-      </c>
+          <t>Participant</t>
+        </is>
+      </c>
+      <c r="E30" s="11" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
@@ -5788,7 +5900,7 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>/v1/relationships/block</t>
+          <t>/v1/relationships</t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr">
@@ -5801,7 +5913,11 @@
           <t>Authenticated</t>
         </is>
       </c>
-      <c r="E31" s="11" t="inlineStr"/>
+      <c r="E31" s="11" t="inlineStr">
+        <is>
+          <t>request</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="11" t="inlineStr">
@@ -5811,7 +5927,7 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>/v1/relationships/{id}/accept</t>
+          <t>/v1/relationships/block</t>
         </is>
       </c>
       <c r="C32" s="11" t="inlineStr">
@@ -5821,7 +5937,7 @@
       </c>
       <c r="D32" s="11" t="inlineStr">
         <is>
-          <t>Target only</t>
+          <t>Authenticated</t>
         </is>
       </c>
       <c r="E32" s="11" t="inlineStr"/>
@@ -5834,7 +5950,7 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>/v1/relationships/{id}/decline</t>
+          <t>/v1/relationships/{id}/accept</t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr">
@@ -5852,12 +5968,12 @@
     <row r="34">
       <c r="A34" s="11" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>/v1/relationships/{id}</t>
+          <t>/v1/relationships/{id}/decline</t>
         </is>
       </c>
       <c r="C34" s="11" t="inlineStr">
@@ -5867,42 +5983,42 @@
       </c>
       <c r="D34" s="11" t="inlineStr">
         <is>
-          <t>Participant</t>
-        </is>
-      </c>
-      <c r="E34" s="11" t="inlineStr">
-        <is>
-          <t>remove/unfriend</t>
-        </is>
-      </c>
+          <t>Target only</t>
+        </is>
+      </c>
+      <c r="E34" s="11" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="11" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>/v1/groups</t>
+          <t>/v1/relationships/{id}</t>
         </is>
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>groups</t>
+          <t>relationships</t>
         </is>
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>Member</t>
-        </is>
-      </c>
-      <c r="E35" s="11" t="inlineStr"/>
+          <t>Participant</t>
+        </is>
+      </c>
+      <c r="E35" s="11" t="inlineStr">
+        <is>
+          <t>remove/unfriend</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="11" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B36" s="11" t="inlineStr">
@@ -5917,24 +6033,20 @@
       </c>
       <c r="D36" s="11" t="inlineStr">
         <is>
-          <t>Authenticated</t>
-        </is>
-      </c>
-      <c r="E36" s="11" t="inlineStr">
-        <is>
-          <t>creator becomes manager</t>
-        </is>
-      </c>
+          <t>Member</t>
+        </is>
+      </c>
+      <c r="E36" s="11" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="11" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>/v1/groups/{id}</t>
+          <t>/v1/groups</t>
         </is>
       </c>
       <c r="C37" s="11" t="inlineStr">
@@ -5944,15 +6056,19 @@
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>Member</t>
-        </is>
-      </c>
-      <c r="E37" s="11" t="inlineStr"/>
+          <t>Authenticated</t>
+        </is>
+      </c>
+      <c r="E37" s="11" t="inlineStr">
+        <is>
+          <t>creator becomes manager</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="11" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B38" s="11" t="inlineStr">
@@ -5967,7 +6083,7 @@
       </c>
       <c r="D38" s="11" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>Member</t>
         </is>
       </c>
       <c r="E38" s="11" t="inlineStr"/>
@@ -5975,12 +6091,12 @@
     <row r="39">
       <c r="A39" s="11" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>/v1/groups/{id}/members</t>
+          <t>/v1/groups/{id}</t>
         </is>
       </c>
       <c r="C39" s="11" t="inlineStr">
@@ -5990,7 +6106,7 @@
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>Member</t>
+          <t>Manager</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr"/>
@@ -5998,7 +6114,7 @@
     <row r="40">
       <c r="A40" s="11" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B40" s="11" t="inlineStr">
@@ -6013,7 +6129,7 @@
       </c>
       <c r="D40" s="11" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>Member</t>
         </is>
       </c>
       <c r="E40" s="11" t="inlineStr"/>
@@ -6021,12 +6137,12 @@
     <row r="41">
       <c r="A41" s="11" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>/v1/groups/{id}/members/{userId}</t>
+          <t>/v1/groups/{id}/members</t>
         </is>
       </c>
       <c r="C41" s="11" t="inlineStr">
@@ -6039,16 +6155,12 @@
           <t>Manager</t>
         </is>
       </c>
-      <c r="E41" s="11" t="inlineStr">
-        <is>
-          <t>promote/demote IsManager</t>
-        </is>
-      </c>
+      <c r="E41" s="11" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="11" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B42" s="11" t="inlineStr">
@@ -6063,65 +6175,69 @@
       </c>
       <c r="D42" s="11" t="inlineStr">
         <is>
-          <t>Manager, or self (leave)</t>
-        </is>
-      </c>
-      <c r="E42" s="11" t="inlineStr"/>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E42" s="11" t="inlineStr">
+        <is>
+          <t>promote/demote IsManager</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="11" t="inlineStr">
         <is>
-          <t>WS</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>/ws (realtime-gateway)</t>
+          <t>/v1/groups/{id}/members/{userId}</t>
         </is>
       </c>
       <c r="C43" s="11" t="inlineStr">
         <is>
-          <t>realtime-gateway</t>
+          <t>groups</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>Bearer token at handshake</t>
-        </is>
-      </c>
-      <c r="E43" s="11" t="inlineStr">
-        <is>
-          <t>subscribe/publish/broadcast/direct message</t>
-        </is>
-      </c>
+          <t>Manager, or self (leave)</t>
+        </is>
+      </c>
+      <c r="E43" s="11" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="11" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>WS</t>
         </is>
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>/v1/conversations</t>
+          <t>/ws (realtime-gateway)</t>
         </is>
       </c>
       <c r="C44" s="11" t="inlineStr">
         <is>
-          <t>messaging</t>
+          <t>realtime-gateway</t>
         </is>
       </c>
       <c r="D44" s="11" t="inlineStr">
         <is>
-          <t>Member</t>
-        </is>
-      </c>
-      <c r="E44" s="11" t="inlineStr"/>
+          <t>Bearer token at handshake</t>
+        </is>
+      </c>
+      <c r="E44" s="11" t="inlineStr">
+        <is>
+          <t>subscribe/publish/broadcast/direct message</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="11" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B45" s="11" t="inlineStr">
@@ -6136,24 +6252,20 @@
       </c>
       <c r="D45" s="11" t="inlineStr">
         <is>
-          <t>Authenticated</t>
-        </is>
-      </c>
-      <c r="E45" s="11" t="inlineStr">
-        <is>
-          <t>direct convos dedup automatically</t>
-        </is>
-      </c>
+          <t>Member</t>
+        </is>
+      </c>
+      <c r="E45" s="11" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="11" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>/v1/conversations/{id}</t>
+          <t>/v1/conversations</t>
         </is>
       </c>
       <c r="C46" s="11" t="inlineStr">
@@ -6163,10 +6275,14 @@
       </c>
       <c r="D46" s="11" t="inlineStr">
         <is>
-          <t>Member</t>
-        </is>
-      </c>
-      <c r="E46" s="11" t="inlineStr"/>
+          <t>Authenticated</t>
+        </is>
+      </c>
+      <c r="E46" s="11" t="inlineStr">
+        <is>
+          <t>direct convos dedup automatically</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="11" t="inlineStr">
@@ -6176,7 +6292,7 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>/v1/conversations/{id}/members</t>
+          <t>/v1/conversations/{id}</t>
         </is>
       </c>
       <c r="C47" s="11" t="inlineStr">
@@ -6194,7 +6310,7 @@
     <row r="48">
       <c r="A48" s="11" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B48" s="11" t="inlineStr">
@@ -6209,7 +6325,7 @@
       </c>
       <c r="D48" s="11" t="inlineStr">
         <is>
-          <t>Member (group only)</t>
+          <t>Member</t>
         </is>
       </c>
       <c r="E48" s="11" t="inlineStr"/>
@@ -6217,12 +6333,12 @@
     <row r="49">
       <c r="A49" s="11" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>/v1/conversations/{id}/members/{userId}</t>
+          <t>/v1/conversations/{id}/members</t>
         </is>
       </c>
       <c r="C49" s="11" t="inlineStr">
@@ -6232,7 +6348,7 @@
       </c>
       <c r="D49" s="11" t="inlineStr">
         <is>
-          <t>Self only (leave)</t>
+          <t>Member (group only)</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr"/>
@@ -6240,12 +6356,12 @@
     <row r="50">
       <c r="A50" s="11" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>/v1/conversations/{id}/messages</t>
+          <t>/v1/conversations/{id}/members/{userId}</t>
         </is>
       </c>
       <c r="C50" s="11" t="inlineStr">
@@ -6255,19 +6371,15 @@
       </c>
       <c r="D50" s="11" t="inlineStr">
         <is>
-          <t>Member</t>
-        </is>
-      </c>
-      <c r="E50" s="11" t="inlineStr">
-        <is>
-          <t>cursor pagination</t>
-        </is>
-      </c>
+          <t>Self only (leave)</t>
+        </is>
+      </c>
+      <c r="E50" s="11" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="11" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B51" s="11" t="inlineStr">
@@ -6287,19 +6399,19 @@
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>pushes over realtime too</t>
+          <t>cursor pagination</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="11" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>/v1/conversations/{id}/messages/{messageId}</t>
+          <t>/v1/conversations/{id}/messages</t>
         </is>
       </c>
       <c r="C52" s="11" t="inlineStr">
@@ -6312,17 +6424,21 @@
           <t>Member</t>
         </is>
       </c>
-      <c r="E52" s="11" t="inlineStr"/>
+      <c r="E52" s="11" t="inlineStr">
+        <is>
+          <t>pushes over realtime too</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="11" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>/v1/conversations/{id}/messages/{messageId}/delivered</t>
+          <t>/v1/conversations/{id}/messages/{messageId}</t>
         </is>
       </c>
       <c r="C53" s="11" t="inlineStr">
@@ -6335,21 +6451,17 @@
           <t>Member</t>
         </is>
       </c>
-      <c r="E53" s="11" t="inlineStr">
-        <is>
-          <t>idempotent ack</t>
-        </is>
-      </c>
+      <c r="E53" s="11" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="11" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t>/v1/conversations/{id}/messages/{messageId}/reactions</t>
+          <t>/v1/conversations/{id}/messages/{messageId}/delivered</t>
         </is>
       </c>
       <c r="C54" s="11" t="inlineStr">
@@ -6362,12 +6474,16 @@
           <t>Member</t>
         </is>
       </c>
-      <c r="E54" s="11" t="inlineStr"/>
+      <c r="E54" s="11" t="inlineStr">
+        <is>
+          <t>idempotent ack</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="11" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B55" s="11" t="inlineStr">
@@ -6385,21 +6501,17 @@
           <t>Member</t>
         </is>
       </c>
-      <c r="E55" s="11" t="inlineStr">
-        <is>
-          <t>idempotent add</t>
-        </is>
-      </c>
+      <c r="E55" s="11" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="11" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t>/v1/conversations/{id}/messages/{messageId}/reactions/{type}</t>
+          <t>/v1/conversations/{id}/messages/{messageId}/reactions</t>
         </is>
       </c>
       <c r="C56" s="11" t="inlineStr">
@@ -6412,17 +6524,21 @@
           <t>Member</t>
         </is>
       </c>
-      <c r="E56" s="11" t="inlineStr"/>
+      <c r="E56" s="11" t="inlineStr">
+        <is>
+          <t>idempotent add</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="11" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>/v1/conversations/{id}/read/{userId}</t>
+          <t>/v1/conversations/{id}/messages/{messageId}/reactions/{type}</t>
         </is>
       </c>
       <c r="C57" s="11" t="inlineStr">
@@ -6440,12 +6556,12 @@
     <row r="58">
       <c r="A58" s="11" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t>/v1/conversations/{id}/read</t>
+          <t>/v1/conversations/{id}/read/{userId}</t>
         </is>
       </c>
       <c r="C58" s="11" t="inlineStr">
@@ -6463,22 +6579,22 @@
     <row r="59">
       <c r="A59" s="11" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>/v1/notifications</t>
+          <t>/v1/conversations/{id}/read</t>
         </is>
       </c>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>notifications</t>
+          <t>messaging</t>
         </is>
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>Authenticated (self)</t>
+          <t>Member</t>
         </is>
       </c>
       <c r="E59" s="11" t="inlineStr"/>
@@ -6486,7 +6602,7 @@
     <row r="60">
       <c r="A60" s="11" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B60" s="11" t="inlineStr">
@@ -6501,24 +6617,20 @@
       </c>
       <c r="D60" s="11" t="inlineStr">
         <is>
-          <t>Self or platform.admin</t>
-        </is>
-      </c>
-      <c r="E60" s="11" t="inlineStr">
-        <is>
-          <t>send</t>
-        </is>
-      </c>
+          <t>Authenticated (self)</t>
+        </is>
+      </c>
+      <c r="E60" s="11" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="11" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>/v1/notifications/{id}</t>
+          <t>/v1/notifications</t>
         </is>
       </c>
       <c r="C61" s="11" t="inlineStr">
@@ -6531,7 +6643,11 @@
           <t>Self or platform.admin</t>
         </is>
       </c>
-      <c r="E61" s="11" t="inlineStr"/>
+      <c r="E61" s="11" t="inlineStr">
+        <is>
+          <t>send</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="11" t="inlineStr">
@@ -6541,7 +6657,7 @@
       </c>
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t>/v1/notifications/{id}/deliveries</t>
+          <t>/v1/notifications/{id}</t>
         </is>
       </c>
       <c r="C62" s="11" t="inlineStr">
@@ -6559,12 +6675,12 @@
     <row r="63">
       <c r="A63" s="11" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>/v1/notifications/{id}/deliveries/{deliveryId}/retry</t>
+          <t>/v1/notifications/{id}/deliveries</t>
         </is>
       </c>
       <c r="C63" s="11" t="inlineStr">
@@ -6582,12 +6698,12 @@
     <row r="64">
       <c r="A64" s="11" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t>/v1/notification-preferences</t>
+          <t>/v1/notifications/{id}/deliveries/{deliveryId}/retry</t>
         </is>
       </c>
       <c r="C64" s="11" t="inlineStr">
@@ -6597,7 +6713,7 @@
       </c>
       <c r="D64" s="11" t="inlineStr">
         <is>
-          <t>Authenticated (self)</t>
+          <t>Self or platform.admin</t>
         </is>
       </c>
       <c r="E64" s="11" t="inlineStr"/>
@@ -6605,7 +6721,7 @@
     <row r="65">
       <c r="A65" s="11" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B65" s="11" t="inlineStr">
@@ -6623,21 +6739,17 @@
           <t>Authenticated (self)</t>
         </is>
       </c>
-      <c r="E65" s="11" t="inlineStr">
-        <is>
-          <t>category opt-outs</t>
-        </is>
-      </c>
+      <c r="E65" s="11" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="11" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B66" s="11" t="inlineStr">
         <is>
-          <t>/v1/notification-preferences/quiet-hours</t>
+          <t>/v1/notification-preferences</t>
         </is>
       </c>
       <c r="C66" s="11" t="inlineStr">
@@ -6650,12 +6762,16 @@
           <t>Authenticated (self)</t>
         </is>
       </c>
-      <c r="E66" s="11" t="inlineStr"/>
+      <c r="E66" s="11" t="inlineStr">
+        <is>
+          <t>category opt-outs</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="11" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B67" s="11" t="inlineStr">
@@ -6678,12 +6794,12 @@
     <row r="68">
       <c r="A68" s="11" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B68" s="11" t="inlineStr">
         <is>
-          <t>/v1/notification-templates</t>
+          <t>/v1/notification-preferences/quiet-hours</t>
         </is>
       </c>
       <c r="C68" s="11" t="inlineStr">
@@ -6693,7 +6809,7 @@
       </c>
       <c r="D68" s="11" t="inlineStr">
         <is>
-          <t>platform.admin</t>
+          <t>Authenticated (self)</t>
         </is>
       </c>
       <c r="E68" s="11" t="inlineStr"/>
@@ -6701,12 +6817,12 @@
     <row r="69">
       <c r="A69" s="11" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>/v1/notification-templates/{appId}/{key}</t>
+          <t>/v1/notification-templates</t>
         </is>
       </c>
       <c r="C69" s="11" t="inlineStr">
@@ -6724,7 +6840,7 @@
     <row r="70">
       <c r="A70" s="11" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B70" s="11" t="inlineStr">
@@ -6747,22 +6863,22 @@
     <row r="71">
       <c r="A71" s="11" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>/v1/files</t>
+          <t>/v1/notification-templates/{appId}/{key}</t>
         </is>
       </c>
       <c r="C71" s="11" t="inlineStr">
         <is>
-          <t>files</t>
+          <t>notifications</t>
         </is>
       </c>
       <c r="D71" s="11" t="inlineStr">
         <is>
-          <t>Owner or platform.admin</t>
+          <t>platform.admin</t>
         </is>
       </c>
       <c r="E71" s="11" t="inlineStr"/>
@@ -6770,7 +6886,7 @@
     <row r="72">
       <c r="A72" s="11" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B72" s="11" t="inlineStr">
@@ -6785,14 +6901,10 @@
       </c>
       <c r="D72" s="11" t="inlineStr">
         <is>
-          <t>Authenticated</t>
-        </is>
-      </c>
-      <c r="E72" s="11" t="inlineStr">
-        <is>
-          <t>requests a presigned upload URL</t>
-        </is>
-      </c>
+          <t>Owner or platform.admin</t>
+        </is>
+      </c>
+      <c r="E72" s="11" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="11" t="inlineStr">
@@ -6802,7 +6914,7 @@
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>/v1/files/{id}/confirm</t>
+          <t>/v1/files</t>
         </is>
       </c>
       <c r="C73" s="11" t="inlineStr">
@@ -6812,24 +6924,24 @@
       </c>
       <c r="D73" s="11" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Authenticated</t>
         </is>
       </c>
       <c r="E73" s="11" t="inlineStr">
         <is>
-          <t>verifies real size + MD5 checksum</t>
+          <t>requests a presigned upload URL</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="11" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t>/v1/files/{id}</t>
+          <t>/v1/files/{id}/confirm</t>
         </is>
       </c>
       <c r="C74" s="11" t="inlineStr">
@@ -6839,10 +6951,14 @@
       </c>
       <c r="D74" s="11" t="inlineStr">
         <is>
-          <t>Owner, or public if visibility allows</t>
-        </is>
-      </c>
-      <c r="E74" s="11" t="inlineStr"/>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="E74" s="11" t="inlineStr">
+        <is>
+          <t>verifies real size + MD5 checksum</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="11" t="inlineStr">
@@ -6852,7 +6968,7 @@
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>/v1/files/{id}/download</t>
+          <t>/v1/files/{id}</t>
         </is>
       </c>
       <c r="C75" s="11" t="inlineStr">
@@ -6865,21 +6981,17 @@
           <t>Owner, or public if visibility allows</t>
         </is>
       </c>
-      <c r="E75" s="11" t="inlineStr">
-        <is>
-          <t>presigned GET</t>
-        </is>
-      </c>
+      <c r="E75" s="11" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="11" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B76" s="11" t="inlineStr">
         <is>
-          <t>/v1/files/{id}</t>
+          <t>/v1/files/{id}/download</t>
         </is>
       </c>
       <c r="C76" s="11" t="inlineStr">
@@ -6889,24 +7001,24 @@
       </c>
       <c r="D76" s="11" t="inlineStr">
         <is>
-          <t>Owner or platform.admin</t>
+          <t>Owner, or public if visibility allows</t>
         </is>
       </c>
       <c r="E76" s="11" t="inlineStr">
         <is>
-          <t>also deletes from storage</t>
+          <t>presigned GET</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="11" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t>/v1/files/purge-expired</t>
+          <t>/v1/files/{id}</t>
         </is>
       </c>
       <c r="C77" s="11" t="inlineStr">
@@ -6916,30 +7028,34 @@
       </c>
       <c r="D77" s="11" t="inlineStr">
         <is>
-          <t>platform.admin</t>
-        </is>
-      </c>
-      <c r="E77" s="11" t="inlineStr"/>
+          <t>Owner or platform.admin</t>
+        </is>
+      </c>
+      <c r="E77" s="11" t="inlineStr">
+        <is>
+          <t>also deletes from storage</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="11" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B78" s="11" t="inlineStr">
         <is>
-          <t>/v1/search</t>
+          <t>/v1/files/purge-expired</t>
         </is>
       </c>
       <c r="C78" s="11" t="inlineStr">
         <is>
-          <t>search</t>
+          <t>files</t>
         </is>
       </c>
       <c r="D78" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>platform.admin</t>
         </is>
       </c>
       <c r="E78" s="11" t="inlineStr"/>
@@ -6947,12 +7063,12 @@
     <row r="79">
       <c r="A79" s="11" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>/v1/search/index</t>
+          <t>/v1/search</t>
         </is>
       </c>
       <c r="C79" s="11" t="inlineStr">
@@ -6962,24 +7078,20 @@
       </c>
       <c r="D79" s="11" t="inlineStr">
         <is>
-          <t>platform.admin</t>
-        </is>
-      </c>
-      <c r="E79" s="11" t="inlineStr">
-        <is>
-          <t>manual index (normally event-driven)</t>
-        </is>
-      </c>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E79" s="11" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="11" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B80" s="11" t="inlineStr">
         <is>
-          <t>/v1/search/index/{type}/{id}</t>
+          <t>/v1/search/index</t>
         </is>
       </c>
       <c r="C80" s="11" t="inlineStr">
@@ -6992,27 +7104,31 @@
           <t>platform.admin</t>
         </is>
       </c>
-      <c r="E80" s="11" t="inlineStr"/>
+      <c r="E80" s="11" t="inlineStr">
+        <is>
+          <t>manual index (normally event-driven)</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="11" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t>/v1/jobs</t>
+          <t>/v1/search/index/{type}/{id}</t>
         </is>
       </c>
       <c r="C81" s="11" t="inlineStr">
         <is>
-          <t>jobs</t>
+          <t>search</t>
         </is>
       </c>
       <c r="D81" s="11" t="inlineStr">
         <is>
-          <t>Owner or platform.admin</t>
+          <t>platform.admin</t>
         </is>
       </c>
       <c r="E81" s="11" t="inlineStr"/>
@@ -7020,7 +7136,7 @@
     <row r="82">
       <c r="A82" s="11" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B82" s="11" t="inlineStr">
@@ -7035,24 +7151,20 @@
       </c>
       <c r="D82" s="11" t="inlineStr">
         <is>
-          <t>Authenticated</t>
-        </is>
-      </c>
-      <c r="E82" s="11" t="inlineStr">
-        <is>
-          <t>enqueue only - never runs inline</t>
-        </is>
-      </c>
+          <t>Owner or platform.admin</t>
+        </is>
+      </c>
+      <c r="E82" s="11" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="11" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t>/v1/jobs/{id}</t>
+          <t>/v1/jobs</t>
         </is>
       </c>
       <c r="C83" s="11" t="inlineStr">
@@ -7062,10 +7174,14 @@
       </c>
       <c r="D83" s="11" t="inlineStr">
         <is>
-          <t>Owner or platform.admin</t>
-        </is>
-      </c>
-      <c r="E83" s="11" t="inlineStr"/>
+          <t>Authenticated</t>
+        </is>
+      </c>
+      <c r="E83" s="11" t="inlineStr">
+        <is>
+          <t>enqueue only - never runs inline</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="11" t="inlineStr">
@@ -7075,7 +7191,7 @@
       </c>
       <c r="B84" s="11" t="inlineStr">
         <is>
-          <t>/v1/jobs/{id}/attempts</t>
+          <t>/v1/jobs/{id}</t>
         </is>
       </c>
       <c r="C84" s="11" t="inlineStr">
@@ -7093,39 +7209,35 @@
     <row r="85">
       <c r="A85" s="11" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>/v1/workflows</t>
+          <t>/v1/jobs/{id}/attempts</t>
         </is>
       </c>
       <c r="C85" s="11" t="inlineStr">
         <is>
-          <t>workflows</t>
+          <t>jobs</t>
         </is>
       </c>
       <c r="D85" s="11" t="inlineStr">
         <is>
-          <t>Authenticated</t>
-        </is>
-      </c>
-      <c r="E85" s="11" t="inlineStr">
-        <is>
-          <t>starts a Temporal workflow</t>
-        </is>
-      </c>
+          <t>Owner or platform.admin</t>
+        </is>
+      </c>
+      <c r="E85" s="11" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="11" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B86" s="11" t="inlineStr">
         <is>
-          <t>/v1/workflows/{id}</t>
+          <t>/v1/workflows</t>
         </is>
       </c>
       <c r="C86" s="11" t="inlineStr">
@@ -7135,24 +7247,24 @@
       </c>
       <c r="D86" s="11" t="inlineStr">
         <is>
-          <t>Owner or platform.admin</t>
+          <t>Authenticated</t>
         </is>
       </c>
       <c r="E86" s="11" t="inlineStr">
         <is>
-          <t>live-queried from Temporal</t>
+          <t>starts a Temporal workflow</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="11" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>/v1/workflows/{id}/signal</t>
+          <t>/v1/workflows/{id}</t>
         </is>
       </c>
       <c r="C87" s="11" t="inlineStr">
@@ -7165,27 +7277,31 @@
           <t>Owner or platform.admin</t>
         </is>
       </c>
-      <c r="E87" s="11" t="inlineStr"/>
+      <c r="E87" s="11" t="inlineStr">
+        <is>
+          <t>live-queried from Temporal</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="11" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t>/v1/features</t>
+          <t>/v1/workflows/{id}/signal</t>
         </is>
       </c>
       <c r="C88" s="11" t="inlineStr">
         <is>
-          <t>features</t>
+          <t>workflows</t>
         </is>
       </c>
       <c r="D88" s="11" t="inlineStr">
         <is>
-          <t>platform.admin</t>
+          <t>Owner or platform.admin</t>
         </is>
       </c>
       <c r="E88" s="11" t="inlineStr"/>
@@ -7193,7 +7309,7 @@
     <row r="89">
       <c r="A89" s="11" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B89" s="11" t="inlineStr">
@@ -7216,12 +7332,12 @@
     <row r="90">
       <c r="A90" s="11" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B90" s="11" t="inlineStr">
         <is>
-          <t>/v1/features/{appId}/{key}</t>
+          <t>/v1/features</t>
         </is>
       </c>
       <c r="C90" s="11" t="inlineStr">
@@ -7239,7 +7355,7 @@
     <row r="91">
       <c r="A91" s="11" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B91" s="11" t="inlineStr">
@@ -7257,21 +7373,17 @@
           <t>platform.admin</t>
         </is>
       </c>
-      <c r="E91" s="11" t="inlineStr">
-        <is>
-          <t>kill switch etc</t>
-        </is>
-      </c>
+      <c r="E91" s="11" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="11" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B92" s="11" t="inlineStr">
         <is>
-          <t>/v1/features/{appId}/{key}/evaluate</t>
+          <t>/v1/features/{appId}/{key}</t>
         </is>
       </c>
       <c r="C92" s="11" t="inlineStr">
@@ -7281,24 +7393,24 @@
       </c>
       <c r="D92" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>platform.admin</t>
         </is>
       </c>
       <c r="E92" s="11" t="inlineStr">
         <is>
-          <t>isEnabled(feature, context)</t>
+          <t>kill switch etc</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="11" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t>/v1/features/{appId}/{key}/rules</t>
+          <t>/v1/features/{appId}/{key}/evaluate</t>
         </is>
       </c>
       <c r="C93" s="11" t="inlineStr">
@@ -7308,15 +7420,19 @@
       </c>
       <c r="D93" s="11" t="inlineStr">
         <is>
-          <t>platform.admin</t>
-        </is>
-      </c>
-      <c r="E93" s="11" t="inlineStr"/>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E93" s="11" t="inlineStr">
+        <is>
+          <t>isEnabled(feature, context)</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="11" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B94" s="11" t="inlineStr">
@@ -7339,12 +7455,12 @@
     <row r="95">
       <c r="A95" s="11" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>/v1/features/{appId}/{key}/rules/{ruleId}</t>
+          <t>/v1/features/{appId}/{key}/rules</t>
         </is>
       </c>
       <c r="C95" s="11" t="inlineStr">
@@ -7362,7 +7478,7 @@
     <row r="96">
       <c r="A96" s="11" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B96" s="11" t="inlineStr">
@@ -7385,29 +7501,25 @@
     <row r="97">
       <c r="A97" s="11" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t>/v1/config</t>
+          <t>/v1/features/{appId}/{key}/rules/{ruleId}</t>
         </is>
       </c>
       <c r="C97" s="11" t="inlineStr">
         <is>
-          <t>remoteconfig</t>
+          <t>features</t>
         </is>
       </c>
       <c r="D97" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="E97" s="11" t="inlineStr">
-        <is>
-          <t>list entries</t>
-        </is>
-      </c>
+          <t>platform.admin</t>
+        </is>
+      </c>
+      <c r="E97" s="11" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="11" t="inlineStr">
@@ -7417,7 +7529,7 @@
       </c>
       <c r="B98" s="11" t="inlineStr">
         <is>
-          <t>/v1/config/{appId}/{environment}/{key}</t>
+          <t>/v1/config</t>
         </is>
       </c>
       <c r="C98" s="11" t="inlineStr">
@@ -7430,12 +7542,16 @@
           <t>Open</t>
         </is>
       </c>
-      <c r="E98" s="11" t="inlineStr"/>
+      <c r="E98" s="11" t="inlineStr">
+        <is>
+          <t>list entries</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="11" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B99" s="11" t="inlineStr">
@@ -7450,19 +7566,15 @@
       </c>
       <c r="D99" s="11" t="inlineStr">
         <is>
-          <t>platform.admin</t>
-        </is>
-      </c>
-      <c r="E99" s="11" t="inlineStr">
-        <is>
-          <t>writes an audited Change row</t>
-        </is>
-      </c>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E99" s="11" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="11" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B100" s="11" t="inlineStr">
@@ -7480,17 +7592,21 @@
           <t>platform.admin</t>
         </is>
       </c>
-      <c r="E100" s="11" t="inlineStr"/>
+      <c r="E100" s="11" t="inlineStr">
+        <is>
+          <t>writes an audited Change row</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="11" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
-          <t>/v1/config/{appId}/{environment}/{key}/history</t>
+          <t>/v1/config/{appId}/{environment}/{key}</t>
         </is>
       </c>
       <c r="C101" s="11" t="inlineStr">
@@ -7508,22 +7624,22 @@
     <row r="102">
       <c r="A102" s="11" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B102" s="11" t="inlineStr">
         <is>
-          <t>/v1/audit</t>
+          <t>/v1/config/{appId}/{environment}/{key}/history</t>
         </is>
       </c>
       <c r="C102" s="11" t="inlineStr">
         <is>
-          <t>audit</t>
+          <t>remoteconfig</t>
         </is>
       </c>
       <c r="D102" s="11" t="inlineStr">
         <is>
-          <t>Authenticated (actor forced server-side)</t>
+          <t>platform.admin</t>
         </is>
       </c>
       <c r="E102" s="11" t="inlineStr"/>
@@ -7531,7 +7647,7 @@
     <row r="103">
       <c r="A103" s="11" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B103" s="11" t="inlineStr">
@@ -7546,7 +7662,7 @@
       </c>
       <c r="D103" s="11" t="inlineStr">
         <is>
-          <t>platform.admin</t>
+          <t>Authenticated (actor forced server-side)</t>
         </is>
       </c>
       <c r="E103" s="11" t="inlineStr"/>
@@ -7559,7 +7675,7 @@
       </c>
       <c r="B104" s="11" t="inlineStr">
         <is>
-          <t>/v1/audit/{id}</t>
+          <t>/v1/audit</t>
         </is>
       </c>
       <c r="C104" s="11" t="inlineStr">
@@ -7577,34 +7693,30 @@
     <row r="105">
       <c r="A105" s="11" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B105" s="11" t="inlineStr">
         <is>
-          <t>/v1/privacy/consent</t>
+          <t>/v1/audit/{id}</t>
         </is>
       </c>
       <c r="C105" s="11" t="inlineStr">
         <is>
-          <t>privacy</t>
+          <t>audit</t>
         </is>
       </c>
       <c r="D105" s="11" t="inlineStr">
         <is>
-          <t>Authenticated (self)</t>
-        </is>
-      </c>
-      <c r="E105" s="11" t="inlineStr">
-        <is>
-          <t>append-only history</t>
-        </is>
-      </c>
+          <t>platform.admin</t>
+        </is>
+      </c>
+      <c r="E105" s="11" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="11" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B106" s="11" t="inlineStr">
@@ -7622,7 +7734,11 @@
           <t>Authenticated (self)</t>
         </is>
       </c>
-      <c r="E106" s="11" t="inlineStr"/>
+      <c r="E106" s="11" t="inlineStr">
+        <is>
+          <t>append-only history</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="11" t="inlineStr">
@@ -7632,7 +7748,7 @@
       </c>
       <c r="B107" s="11" t="inlineStr">
         <is>
-          <t>/v1/privacy/preferences</t>
+          <t>/v1/privacy/consent</t>
         </is>
       </c>
       <c r="C107" s="11" t="inlineStr">
@@ -7650,7 +7766,7 @@
     <row r="108">
       <c r="A108" s="11" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B108" s="11" t="inlineStr">
@@ -7673,12 +7789,12 @@
     <row r="109">
       <c r="A109" s="11" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B109" s="11" t="inlineStr">
         <is>
-          <t>/v1/privacy/retention-policies</t>
+          <t>/v1/privacy/preferences</t>
         </is>
       </c>
       <c r="C109" s="11" t="inlineStr">
@@ -7688,7 +7804,7 @@
       </c>
       <c r="D109" s="11" t="inlineStr">
         <is>
-          <t>platform.admin</t>
+          <t>Authenticated (self)</t>
         </is>
       </c>
       <c r="E109" s="11" t="inlineStr"/>
@@ -7696,7 +7812,7 @@
     <row r="110">
       <c r="A110" s="11" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B110" s="11" t="inlineStr">
@@ -7719,12 +7835,12 @@
     <row r="111">
       <c r="A111" s="11" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B111" s="11" t="inlineStr">
         <is>
-          <t>/v1/privacy/export</t>
+          <t>/v1/privacy/retention-policies</t>
         </is>
       </c>
       <c r="C111" s="11" t="inlineStr">
@@ -7734,24 +7850,20 @@
       </c>
       <c r="D111" s="11" t="inlineStr">
         <is>
-          <t>Authenticated (self)</t>
-        </is>
-      </c>
-      <c r="E111" s="11" t="inlineStr">
-        <is>
-          <t>starts a Temporal workflow</t>
-        </is>
-      </c>
+          <t>platform.admin</t>
+        </is>
+      </c>
+      <c r="E111" s="11" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="11" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B112" s="11" t="inlineStr">
         <is>
-          <t>/v1/privacy/export/{id}</t>
+          <t>/v1/privacy/export</t>
         </is>
       </c>
       <c r="C112" s="11" t="inlineStr">
@@ -7761,12 +7873,12 @@
       </c>
       <c r="D112" s="11" t="inlineStr">
         <is>
-          <t>Self or platform.admin</t>
+          <t>Authenticated (self)</t>
         </is>
       </c>
       <c r="E112" s="11" t="inlineStr">
         <is>
-          <t>status is read from Postgres, not Temporal</t>
+          <t>starts a Temporal workflow</t>
         </is>
       </c>
     </row>
@@ -7778,7 +7890,7 @@
       </c>
       <c r="B113" s="11" t="inlineStr">
         <is>
-          <t>/v1/privacy/export/{id}/download</t>
+          <t>/v1/privacy/export/{id}</t>
         </is>
       </c>
       <c r="C113" s="11" t="inlineStr">
@@ -7793,19 +7905,19 @@
       </c>
       <c r="E113" s="11" t="inlineStr">
         <is>
-          <t>presigned MinIO/S3 GET</t>
+          <t>status is read from Postgres, not Temporal</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="11" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B114" s="11" t="inlineStr">
         <is>
-          <t>/v1/privacy/delete</t>
+          <t>/v1/privacy/export/{id}/download</t>
         </is>
       </c>
       <c r="C114" s="11" t="inlineStr">
@@ -7815,24 +7927,24 @@
       </c>
       <c r="D114" s="11" t="inlineStr">
         <is>
-          <t>Authenticated (self)</t>
+          <t>Self or platform.admin</t>
         </is>
       </c>
       <c r="E114" s="11" t="inlineStr">
         <is>
-          <t>starts a Temporal workflow</t>
+          <t>presigned MinIO/S3 GET</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="11" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B115" s="11" t="inlineStr">
         <is>
-          <t>/v1/privacy/delete/{id}</t>
+          <t>/v1/privacy/delete</t>
         </is>
       </c>
       <c r="C115" s="11" t="inlineStr">
@@ -7842,46 +7954,46 @@
       </c>
       <c r="D115" s="11" t="inlineStr">
         <is>
-          <t>Self or platform.admin</t>
+          <t>Authenticated (self)</t>
         </is>
       </c>
       <c r="E115" s="11" t="inlineStr">
         <is>
-          <t>a self-deleted user must use an admin to check this</t>
+          <t>starts a Temporal workflow</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="11" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B116" s="11" t="inlineStr">
         <is>
-          <t>/v1/trustsafety/mutes</t>
+          <t>/v1/privacy/delete/{id}</t>
         </is>
       </c>
       <c r="C116" s="11" t="inlineStr">
         <is>
-          <t>trustsafety</t>
+          <t>privacy</t>
         </is>
       </c>
       <c r="D116" s="11" t="inlineStr">
         <is>
-          <t>Authenticated (self)</t>
+          <t>Self or platform.admin</t>
         </is>
       </c>
       <c r="E116" s="11" t="inlineStr">
         <is>
-          <t>one-directional, silent</t>
+          <t>a self-deleted user must use an admin to check this</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="11" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B117" s="11" t="inlineStr">
@@ -7901,19 +8013,19 @@
       </c>
       <c r="E117" s="11" t="inlineStr">
         <is>
-          <t>exempt from requireActive - always reachable</t>
+          <t>one-directional, silent</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="11" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B118" s="11" t="inlineStr">
         <is>
-          <t>/v1/trustsafety/mutes/{userId}</t>
+          <t>/v1/trustsafety/mutes</t>
         </is>
       </c>
       <c r="C118" s="11" t="inlineStr">
@@ -7926,17 +8038,21 @@
           <t>Authenticated (self)</t>
         </is>
       </c>
-      <c r="E118" s="11" t="inlineStr"/>
+      <c r="E118" s="11" t="inlineStr">
+        <is>
+          <t>exempt from requireActive - always reachable</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="11" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B119" s="11" t="inlineStr">
         <is>
-          <t>/v1/trustsafety/reports</t>
+          <t>/v1/trustsafety/mutes/{userId}</t>
         </is>
       </c>
       <c r="C119" s="11" t="inlineStr">
@@ -7949,21 +8065,17 @@
           <t>Authenticated (self)</t>
         </is>
       </c>
-      <c r="E119" s="11" t="inlineStr">
-        <is>
-          <t>rate-limited 5/hour; dedupes onto one case</t>
-        </is>
-      </c>
+      <c r="E119" s="11" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="11" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B120" s="11" t="inlineStr">
         <is>
-          <t>/v1/trustsafety/reports/{id}</t>
+          <t>/v1/trustsafety/reports</t>
         </is>
       </c>
       <c r="C120" s="11" t="inlineStr">
@@ -7973,10 +8085,14 @@
       </c>
       <c r="D120" s="11" t="inlineStr">
         <is>
-          <t>Reporter or moderator/admin</t>
-        </is>
-      </c>
-      <c r="E120" s="11" t="inlineStr"/>
+          <t>Authenticated (self)</t>
+        </is>
+      </c>
+      <c r="E120" s="11" t="inlineStr">
+        <is>
+          <t>rate-limited 5/hour; dedupes onto one case</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="11" t="inlineStr">
@@ -7986,7 +8102,7 @@
       </c>
       <c r="B121" s="11" t="inlineStr">
         <is>
-          <t>/v1/trustsafety/cases</t>
+          <t>/v1/trustsafety/reports/{id}</t>
         </is>
       </c>
       <c r="C121" s="11" t="inlineStr">
@@ -7996,14 +8112,10 @@
       </c>
       <c r="D121" s="11" t="inlineStr">
         <is>
-          <t>Moderator or platform.admin</t>
-        </is>
-      </c>
-      <c r="E121" s="11" t="inlineStr">
-        <is>
-          <t>?status=</t>
-        </is>
-      </c>
+          <t>Reporter or moderator/admin</t>
+        </is>
+      </c>
+      <c r="E121" s="11" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="11" t="inlineStr">
@@ -8013,7 +8125,7 @@
       </c>
       <c r="B122" s="11" t="inlineStr">
         <is>
-          <t>/v1/trustsafety/cases/{id}</t>
+          <t>/v1/trustsafety/cases</t>
         </is>
       </c>
       <c r="C122" s="11" t="inlineStr">
@@ -8026,7 +8138,11 @@
           <t>Moderator or platform.admin</t>
         </is>
       </c>
-      <c r="E122" s="11" t="inlineStr"/>
+      <c r="E122" s="11" t="inlineStr">
+        <is>
+          <t>?status=</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="11" t="inlineStr">
@@ -8036,7 +8152,7 @@
       </c>
       <c r="B123" s="11" t="inlineStr">
         <is>
-          <t>/v1/trustsafety/cases/{id}/reports</t>
+          <t>/v1/trustsafety/cases/{id}</t>
         </is>
       </c>
       <c r="C123" s="11" t="inlineStr">
@@ -8054,12 +8170,12 @@
     <row r="124">
       <c r="A124" s="11" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B124" s="11" t="inlineStr">
         <is>
-          <t>/v1/trustsafety/cases/{id}/assign</t>
+          <t>/v1/trustsafety/cases/{id}/reports</t>
         </is>
       </c>
       <c r="C124" s="11" t="inlineStr">
@@ -8082,7 +8198,7 @@
       </c>
       <c r="B125" s="11" t="inlineStr">
         <is>
-          <t>/v1/trustsafety/cases/{id}</t>
+          <t>/v1/trustsafety/cases/{id}/assign</t>
         </is>
       </c>
       <c r="C125" s="11" t="inlineStr">
@@ -8095,21 +8211,17 @@
           <t>Moderator or platform.admin</t>
         </is>
       </c>
-      <c r="E125" s="11" t="inlineStr">
-        <is>
-          <t>resolve/dismiss</t>
-        </is>
-      </c>
+      <c r="E125" s="11" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="11" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B126" s="11" t="inlineStr">
         <is>
-          <t>/v1/trustsafety/suspensions</t>
+          <t>/v1/trustsafety/cases/{id}</t>
         </is>
       </c>
       <c r="C126" s="11" t="inlineStr">
@@ -8124,14 +8236,14 @@
       </c>
       <c r="E126" s="11" t="inlineStr">
         <is>
-          <t>temporary, EndsAt required</t>
+          <t>resolve/dismiss</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="11" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B127" s="11" t="inlineStr">
@@ -8146,24 +8258,24 @@
       </c>
       <c r="D127" s="11" t="inlineStr">
         <is>
-          <t>Self or moderator/admin</t>
+          <t>Moderator or platform.admin</t>
         </is>
       </c>
       <c r="E127" s="11" t="inlineStr">
         <is>
-          <t>?userId=</t>
+          <t>temporary, EndsAt required</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="11" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B128" s="11" t="inlineStr">
         <is>
-          <t>/v1/trustsafety/suspensions/{id}/lift</t>
+          <t>/v1/trustsafety/suspensions</t>
         </is>
       </c>
       <c r="C128" s="11" t="inlineStr">
@@ -8173,10 +8285,14 @@
       </c>
       <c r="D128" s="11" t="inlineStr">
         <is>
-          <t>Moderator or platform.admin</t>
-        </is>
-      </c>
-      <c r="E128" s="11" t="inlineStr"/>
+          <t>Self or moderator/admin</t>
+        </is>
+      </c>
+      <c r="E128" s="11" t="inlineStr">
+        <is>
+          <t>?userId=</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="11" t="inlineStr">
@@ -8186,7 +8302,7 @@
       </c>
       <c r="B129" s="11" t="inlineStr">
         <is>
-          <t>/v1/trustsafety/bans</t>
+          <t>/v1/trustsafety/suspensions/{id}/lift</t>
         </is>
       </c>
       <c r="C129" s="11" t="inlineStr">
@@ -8199,16 +8315,12 @@
           <t>Moderator or platform.admin</t>
         </is>
       </c>
-      <c r="E129" s="11" t="inlineStr">
-        <is>
-          <t>permanent until lifted</t>
-        </is>
-      </c>
+      <c r="E129" s="11" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="11" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B130" s="11" t="inlineStr">
@@ -8223,24 +8335,24 @@
       </c>
       <c r="D130" s="11" t="inlineStr">
         <is>
-          <t>Self or moderator/admin</t>
+          <t>Moderator or platform.admin</t>
         </is>
       </c>
       <c r="E130" s="11" t="inlineStr">
         <is>
-          <t>?userId=</t>
+          <t>permanent until lifted</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="11" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B131" s="11" t="inlineStr">
         <is>
-          <t>/v1/trustsafety/bans/{id}/lift</t>
+          <t>/v1/trustsafety/bans</t>
         </is>
       </c>
       <c r="C131" s="11" t="inlineStr">
@@ -8250,10 +8362,14 @@
       </c>
       <c r="D131" s="11" t="inlineStr">
         <is>
-          <t>Moderator or platform.admin</t>
-        </is>
-      </c>
-      <c r="E131" s="11" t="inlineStr"/>
+          <t>Self or moderator/admin</t>
+        </is>
+      </c>
+      <c r="E131" s="11" t="inlineStr">
+        <is>
+          <t>?userId=</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="11" t="inlineStr">
@@ -8263,7 +8379,7 @@
       </c>
       <c r="B132" s="11" t="inlineStr">
         <is>
-          <t>/v1/trustsafety/appeals</t>
+          <t>/v1/trustsafety/bans/{id}/lift</t>
         </is>
       </c>
       <c r="C132" s="11" t="inlineStr">
@@ -8273,19 +8389,15 @@
       </c>
       <c r="D132" s="11" t="inlineStr">
         <is>
-          <t>Authenticated (self, must own target)</t>
-        </is>
-      </c>
-      <c r="E132" s="11" t="inlineStr">
-        <is>
-          <t>exempt from requireActive - always reachable</t>
-        </is>
-      </c>
+          <t>Moderator or platform.admin</t>
+        </is>
+      </c>
+      <c r="E132" s="11" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="11" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B133" s="11" t="inlineStr">
@@ -8300,7 +8412,7 @@
       </c>
       <c r="D133" s="11" t="inlineStr">
         <is>
-          <t>Self or moderator/admin</t>
+          <t>Authenticated (self, must own target)</t>
         </is>
       </c>
       <c r="E133" s="11" t="inlineStr">
@@ -8312,12 +8424,12 @@
     <row r="134">
       <c r="A134" s="11" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B134" s="11" t="inlineStr">
         <is>
-          <t>/v1/trustsafety/appeals/{id}/review</t>
+          <t>/v1/trustsafety/appeals</t>
         </is>
       </c>
       <c r="C134" s="11" t="inlineStr">
@@ -8327,12 +8439,12 @@
       </c>
       <c r="D134" s="11" t="inlineStr">
         <is>
-          <t>Moderator or platform.admin</t>
+          <t>Self or moderator/admin</t>
         </is>
       </c>
       <c r="E134" s="11" t="inlineStr">
         <is>
-          <t>approving lifts the target restriction</t>
+          <t>exempt from requireActive - always reachable</t>
         </is>
       </c>
     </row>
@@ -8344,7 +8456,7 @@
       </c>
       <c r="B135" s="11" t="inlineStr">
         <is>
-          <t>/v1/trustsafety/signals</t>
+          <t>/v1/trustsafety/appeals/{id}/review</t>
         </is>
       </c>
       <c r="C135" s="11" t="inlineStr">
@@ -8354,19 +8466,19 @@
       </c>
       <c r="D135" s="11" t="inlineStr">
         <is>
-          <t>Authenticated</t>
+          <t>Moderator or platform.admin</t>
         </is>
       </c>
       <c r="E135" s="11" t="inlineStr">
         <is>
-          <t>critical severity auto-opens a case</t>
+          <t>approving lifts the target restriction</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="11" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B136" s="11" t="inlineStr">
@@ -8381,12 +8493,12 @@
       </c>
       <c r="D136" s="11" t="inlineStr">
         <is>
-          <t>Moderator or platform.admin</t>
+          <t>Authenticated</t>
         </is>
       </c>
       <c r="E136" s="11" t="inlineStr">
         <is>
-          <t>?resourceType=&amp;resourceId=</t>
+          <t>critical severity auto-opens a case</t>
         </is>
       </c>
     </row>
@@ -8398,22 +8510,22 @@
       </c>
       <c r="B137" s="11" t="inlineStr">
         <is>
-          <t>/v1/billing/entitlements</t>
+          <t>/v1/trustsafety/signals</t>
         </is>
       </c>
       <c r="C137" s="11" t="inlineStr">
         <is>
-          <t>billing</t>
+          <t>trustsafety</t>
         </is>
       </c>
       <c r="D137" s="11" t="inlineStr">
         <is>
-          <t>Self or platform.admin</t>
+          <t>Moderator or platform.admin</t>
         </is>
       </c>
       <c r="E137" s="11" t="inlineStr">
         <is>
-          <t>?userId=</t>
+          <t>?resourceType=&amp;resourceId=</t>
         </is>
       </c>
     </row>
@@ -8425,7 +8537,7 @@
       </c>
       <c r="B138" s="11" t="inlineStr">
         <is>
-          <t>/v1/billing/entitlements/check/{key}</t>
+          <t>/v1/billing/entitlements</t>
         </is>
       </c>
       <c r="C138" s="11" t="inlineStr">
@@ -8435,24 +8547,24 @@
       </c>
       <c r="D138" s="11" t="inlineStr">
         <is>
-          <t>Authenticated (self)</t>
+          <t>Self or platform.admin</t>
         </is>
       </c>
       <c r="E138" s="11" t="inlineStr">
         <is>
-          <t>the literal 'do I have entitlement X' check</t>
+          <t>?userId=</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="11" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B139" s="11" t="inlineStr">
         <is>
-          <t>/v1/billing/entitlements</t>
+          <t>/v1/billing/entitlements/check/{key}</t>
         </is>
       </c>
       <c r="C139" s="11" t="inlineStr">
@@ -8462,12 +8574,12 @@
       </c>
       <c r="D139" s="11" t="inlineStr">
         <is>
-          <t>platform.admin</t>
+          <t>Authenticated (self)</t>
         </is>
       </c>
       <c r="E139" s="11" t="inlineStr">
         <is>
-          <t>manual grant; source always "manual:&lt;adminId&gt;"</t>
+          <t>the literal 'do I have entitlement X' check</t>
         </is>
       </c>
     </row>
@@ -8479,7 +8591,7 @@
       </c>
       <c r="B140" s="11" t="inlineStr">
         <is>
-          <t>/v1/billing/entitlements/{id}/revoke</t>
+          <t>/v1/billing/entitlements</t>
         </is>
       </c>
       <c r="C140" s="11" t="inlineStr">
@@ -8492,17 +8604,21 @@
           <t>platform.admin</t>
         </is>
       </c>
-      <c r="E140" s="11" t="inlineStr"/>
+      <c r="E140" s="11" t="inlineStr">
+        <is>
+          <t>manual grant; source always "manual:&lt;adminId&gt;"</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="11" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B141" s="11" t="inlineStr">
         <is>
-          <t>/v1/billing/payments</t>
+          <t>/v1/billing/entitlements/{id}/revoke</t>
         </is>
       </c>
       <c r="C141" s="11" t="inlineStr">
@@ -8512,24 +8628,20 @@
       </c>
       <c r="D141" s="11" t="inlineStr">
         <is>
-          <t>Self or platform.admin</t>
-        </is>
-      </c>
-      <c r="E141" s="11" t="inlineStr">
-        <is>
-          <t>?userId=</t>
-        </is>
-      </c>
+          <t>platform.admin</t>
+        </is>
+      </c>
+      <c r="E141" s="11" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="11" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B142" s="11" t="inlineStr">
         <is>
-          <t>/v1/billing/webhooks/{provider}</t>
+          <t>/v1/billing/payments</t>
         </is>
       </c>
       <c r="C142" s="11" t="inlineStr">
@@ -8539,12 +8651,12 @@
       </c>
       <c r="D142" s="11" t="inlineStr">
         <is>
-          <t>Provider webhook signature (no Bearer token)</t>
+          <t>Self or platform.admin</t>
         </is>
       </c>
       <c r="E142" s="11" t="inlineStr">
         <is>
-          <t>the one route on this platform with no requireUser/requireActive</t>
+          <t>?userId=</t>
         </is>
       </c>
     </row>
@@ -8556,29 +8668,29 @@
       </c>
       <c r="B143" s="11" t="inlineStr">
         <is>
-          <t>/v1/analytics/events</t>
+          <t>/v1/billing/webhooks/{provider}</t>
         </is>
       </c>
       <c r="C143" s="11" t="inlineStr">
         <is>
-          <t>analytics</t>
+          <t>billing</t>
         </is>
       </c>
       <c r="D143" s="11" t="inlineStr">
         <is>
-          <t>Open (IP-rate-limited, no Bearer token)</t>
+          <t>Provider webhook signature (no Bearer token)</t>
         </is>
       </c>
       <c r="E143" s="11" t="inlineStr">
         <is>
-          <t>the platform's one deliberately unauthenticated write endpoint</t>
+          <t>the one route on this platform with no requireUser/requireActive</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="11" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B144" s="11" t="inlineStr">
@@ -8593,51 +8705,51 @@
       </c>
       <c r="D144" s="11" t="inlineStr">
         <is>
-          <t>platform.admin</t>
+          <t>Open (IP-rate-limited, no Bearer token)</t>
         </is>
       </c>
       <c r="E144" s="11" t="inlineStr">
         <is>
-          <t>operational debug view only, not for analytical queries</t>
+          <t>the platform's one deliberately unauthenticated write endpoint</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="11" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B145" s="11" t="inlineStr">
         <is>
-          <t>/v1/ai/completions</t>
+          <t>/v1/analytics/events</t>
         </is>
       </c>
       <c r="C145" s="11" t="inlineStr">
         <is>
-          <t>aigateway</t>
+          <t>analytics</t>
         </is>
       </c>
       <c r="D145" s="11" t="inlineStr">
         <is>
-          <t>Authenticated (quota-limited)</t>
+          <t>platform.admin</t>
         </is>
       </c>
       <c r="E145" s="11" t="inlineStr">
         <is>
-          <t>real local inference via Ollama; never call a vendor model name directly</t>
+          <t>operational debug view only, not for analytical queries</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="11" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B146" s="11" t="inlineStr">
         <is>
-          <t>/v1/ai/usage</t>
+          <t>/v1/ai/completions</t>
         </is>
       </c>
       <c r="C146" s="11" t="inlineStr">
@@ -8647,12 +8759,12 @@
       </c>
       <c r="D146" s="11" t="inlineStr">
         <is>
-          <t>Self or platform.admin</t>
+          <t>Authenticated (quota-limited)</t>
         </is>
       </c>
       <c r="E146" s="11" t="inlineStr">
         <is>
-          <t>?userId=; tokens/cost/latency, never prompt or response text</t>
+          <t>real local inference via Ollama; never call a vendor model name directly</t>
         </is>
       </c>
     </row>
@@ -8664,20 +8776,47 @@
       </c>
       <c r="B147" s="11" t="inlineStr">
         <is>
+          <t>/v1/ai/usage</t>
+        </is>
+      </c>
+      <c r="C147" s="11" t="inlineStr">
+        <is>
+          <t>aigateway</t>
+        </is>
+      </c>
+      <c r="D147" s="11" t="inlineStr">
+        <is>
+          <t>Self or platform.admin</t>
+        </is>
+      </c>
+      <c r="E147" s="11" t="inlineStr">
+        <is>
+          <t>?userId=; tokens/cost/latency, never prompt or response text</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="11" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="B148" s="11" t="inlineStr">
+        <is>
           <t>/v1/ai/models</t>
         </is>
       </c>
-      <c r="C147" s="11" t="inlineStr">
+      <c r="C148" s="11" t="inlineStr">
         <is>
           <t>aigateway</t>
         </is>
       </c>
-      <c r="D147" s="11" t="inlineStr">
+      <c r="D148" s="11" t="inlineStr">
         <is>
           <t>Authenticated</t>
         </is>
       </c>
-      <c r="E147" s="11" t="inlineStr">
+      <c r="E148" s="11" t="inlineStr">
         <is>
           <t>lists registered model aliases, never vendor model names</t>
         </is>
@@ -8697,7 +8836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -9231,6 +9370,28 @@
       <c r="D24" s="11" t="inlineStr">
         <is>
           <t>13 unit tests against a real dart:io HttpServer. apps/mobile depends on this package via a path: dependency in its pubspec.yaml.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="48" customHeight="1">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t>Look at real dashboards, metrics, logs, traces, and alerts</t>
+        </is>
+      </c>
+      <c r="C25" s="11" t="inlineStr">
+        <is>
+          <t>Open http://localhost:3000 (admin/admin) -&gt; Core Platform folder -&gt; Core Platform Overview</t>
+        </is>
+      </c>
+      <c r="D25" s="11" t="inlineStr">
+        <is>
+          <t>Needs core-api/realtime-gateway/worker actually running (steps 5-7). Every panel is real data (Phase 28) - API latency, error rate, requests/sec, DB connections, WebSocket connections, Redis latency, notification/job failures. Prometheus alerts: http://localhost:9090/alerts. Loki/Tempo: query via Grafana's Explore tab.</t>
         </is>
       </c>
     </row>
@@ -9248,7 +9409,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -9666,25 +9827,133 @@
     <row r="16" ht="32" customHeight="1">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>OTel Collector / Tempo / Prometheus / Grafana / Loki</t>
+          <t>Prometheus</t>
         </is>
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>Docker containers</t>
+          <t>Docker container</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>see infra/docker/docker-compose.yml</t>
+          <t>http://localhost:9090</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>Full observability stack - traces, metrics, logs, dashboards.</t>
+          <t>Scrapes a real GET /metrics on core-api/realtime-gateway/worker (Phase 28) and evaluates alerts.yml's 6 real alerting rules - api/v1/targets and api/v1/rules are both genuinely populated, not just running empty.</t>
         </is>
       </c>
       <c r="E16" s="11" t="inlineStr">
+        <is>
+          <t>no auth locally</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="32" customHeight="1">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>Grafana</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>Docker container</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>http://localhost:3000</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="inlineStr">
+        <is>
+          <t>Provisioned (Phase 28) - Prometheus/Tempo/Loki datasources and the real 'Core Platform Overview' dashboard auto-load on container start, previously mounted nowhere.</t>
+        </is>
+      </c>
+      <c r="E17" s="11" t="inlineStr">
+        <is>
+          <t>admin/admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="32" customHeight="1">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>Loki</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>Docker container</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>http://localhost:3100</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="inlineStr">
+        <is>
+          <t>Receives structured logs pushed directly by logging.NewWithLoki (Phase 28) - no log-shipping agent, since these services run as bare host processes Promtail-style container-log-tailing would never see.</t>
+        </is>
+      </c>
+      <c r="E18" s="11" t="inlineStr">
+        <is>
+          <t>no auth locally</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="32" customHeight="1">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>Tempo</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>Docker container</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>http://localhost:3200</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="inlineStr">
+        <is>
+          <t>Receives real traces via otel-collector (Phase 1).</t>
+        </is>
+      </c>
+      <c r="E19" s="11" t="inlineStr">
+        <is>
+          <t>no auth locally</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="32" customHeight="1">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>OTel Collector</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>Docker container</t>
+        </is>
+      </c>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>http://localhost:4318 (OTLP/HTTP)</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="inlineStr">
+        <is>
+          <t>Traces only - relays to Tempo. Logs bypass it entirely (Loki's native push API instead); no metrics pipeline (Prometheus scrapes services directly).</t>
+        </is>
+      </c>
+      <c r="E20" s="11" t="inlineStr">
         <is>
           <t>no auth locally</t>
         </is>

--- a/docs/control/data.xlsx
+++ b/docs/control/data.xlsx
@@ -239,8 +239,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="TodoChecklist" displayName="TodoChecklist" ref="A1:D135" headerRowCount="1">
-  <autoFilter ref="A1:D135"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="TodoChecklist" displayName="TodoChecklist" ref="A1:D143" headerRowCount="1">
+  <autoFilter ref="A1:D143"/>
   <tableColumns count="4">
     <tableColumn id="1" name="Phase"/>
     <tableColumn id="2" name="Status"/>
@@ -281,8 +281,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="HowToTest" displayName="HowToTest" ref="A1:D25" headerRowCount="1">
-  <autoFilter ref="A1:D25"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="HowToTest" displayName="HowToTest" ref="A1:D26" headerRowCount="1">
+  <autoFilter ref="A1:D26"/>
   <tableColumns count="4">
     <tableColumn id="1" name="Step"/>
     <tableColumn id="2" name="What"/>
@@ -633,12 +633,12 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>28 / 30</t>
+          <t>29 / 30</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>93%</t>
+          <t>97%</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>apps/admin (Next.js 15 App Router)</t>
+          <t>apps/admin (Next.js 15 App Router) - now includes /control-plane, Phase 29</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>42</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -1622,9 +1622,9 @@
       <c r="A30" s="9" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="12" t="inlineStr">
-        <is>
-          <t>Next up</t>
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C30" s="11" t="inlineStr">
@@ -1634,12 +1634,12 @@
       </c>
       <c r="D30" s="11" t="inlineStr">
         <is>
-          <t>One view of applications/services/versions/environments/dependencies/deployments/DB ownership/events/API contracts/health/alerts/recent changes - every module discoverable from one place.</t>
+          <t>New apps/admin/control-plane page - all 12 roadmap-named dimensions, real: applications/health (existing), real per-service versions (new config.Version - the actual git SHA, wired through health.Live/Health on all 3 services), real environment (from GET /v1/platform), the real dependency graph and DB ownership (docs/control/platform.json, a new machine-readable export from build_workbook.py's own data + catalog/system.yaml), real events (contracts/asyncapi), real live Prometheus alerts, a real git log for recent changes, and an honest Deployments placeholder (no CI/CD exists yet).</t>
         </is>
       </c>
       <c r="E30" s="11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>f0d1cc3</t>
         </is>
       </c>
     </row>
@@ -1647,9 +1647,9 @@
       <c r="A31" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B31" s="12" t="inlineStr">
+        <is>
+          <t>Next up</t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr">
@@ -1682,7 +1682,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D135"/>
+  <dimension ref="A1:D143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2163,7 +2163,7 @@
     </row>
     <row r="30">
       <c r="A30" s="9" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
@@ -2172,14 +2172,14 @@
       </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t>Repo health baseline (make doctor / validate-all / go test / go build) run and passed</t>
+          <t>Phase 29: Platform Control Plane implemented, unit-tested, live-validated, documented, committed</t>
         </is>
       </c>
       <c r="D30" s="11" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
@@ -2188,18 +2188,14 @@
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>Environment / ApplicationVersion / ApplicationConfiguration</t>
-        </is>
-      </c>
-      <c r="D31" s="11" t="inlineStr">
-        <is>
-          <t>Deferred - no consumer needs them yet, documented as intentional in applications/README.md</t>
-        </is>
-      </c>
+          <t>Repo health baseline (make doctor / validate-all / go test / go build) run and passed</t>
+        </is>
+      </c>
+      <c r="D31" s="11" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
@@ -2208,32 +2204,32 @@
       </c>
       <c r="C32" s="11" t="inlineStr">
         <is>
-          <t>Separate Session table</t>
+          <t>Environment / ApplicationVersion / ApplicationConfiguration</t>
         </is>
       </c>
       <c r="D32" s="11" t="inlineStr">
         <is>
-          <t>Deferred - Device.SessionStatus covers today's single-session-per-device need, documented in devices/README.md</t>
+          <t>Deferred - no consumer needs them yet, documented as intentional in applications/README.md</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="B33" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+        <v>5</v>
+      </c>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>UserPreferences (named in Phase 4, no fields ever specified)</t>
+          <t>Separate Session table</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>Deferred to Phase 12+; notification preferences shipped, a generic preferences bag did not</t>
+          <t>Deferred - Device.SessionStatus covers today's single-session-per-device need, documented in devices/README.md</t>
         </is>
       </c>
     </row>
@@ -2248,12 +2244,12 @@
       </c>
       <c r="C34" s="11" t="inlineStr">
         <is>
-          <t>apps/mobile test/ directory (make flutter-test currently fails)</t>
+          <t>UserPreferences (named in Phase 4, no fields ever specified)</t>
         </is>
       </c>
       <c r="D34" s="11" t="inlineStr">
         <is>
-          <t>Known gap since Phase 9's audit, not yet picked up</t>
+          <t>Deferred to Phase 12+; notification preferences shipped, a generic preferences bag did not</t>
         </is>
       </c>
     </row>
@@ -2268,30 +2264,34 @@
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>apps/admin next@15 / sharp transitive advisories</t>
+          <t>apps/mobile test/ directory (make flutter-test currently fails)</t>
         </is>
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>Fix is a Next.js major-version bump - separate, reviewable change</t>
+          <t>Known gap since Phase 9's audit, not yet picked up</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="9" t="n">
-        <v>20</v>
-      </c>
-      <c r="B36" s="10" t="inlineStr">
-        <is>
-          <t>Done</t>
+        <v>9</v>
+      </c>
+      <c r="B36" s="13" t="inlineStr">
+        <is>
+          <t>Pending</t>
         </is>
       </c>
       <c r="C36" s="11" t="inlineStr">
         <is>
-          <t>Privacy: consent (append-only history)</t>
-        </is>
-      </c>
-      <c r="D36" s="11" t="inlineStr"/>
+          <t>apps/admin next@15 / sharp transitive advisories</t>
+        </is>
+      </c>
+      <c r="D36" s="11" t="inlineStr">
+        <is>
+          <t>Fix is a Next.js major-version bump - separate, reviewable change</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="9" t="n">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>Privacy: user data export (ExportUserData registry - users/devices/files/audit)</t>
+          <t>Privacy: consent (append-only history)</t>
         </is>
       </c>
       <c r="D37" s="11" t="inlineStr"/>
@@ -2320,7 +2320,7 @@
       </c>
       <c r="C38" s="11" t="inlineStr">
         <is>
-          <t>Privacy: user deletion (DeleteUserData registry - users/devices/files; audit deliberately excluded)</t>
+          <t>Privacy: user data export (ExportUserData registry - users/devices/files/audit)</t>
         </is>
       </c>
       <c r="D38" s="11" t="inlineStr"/>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>Privacy: retention policy (declared, not scheduled - same documented gap as Phase 13's PurgeExpired)</t>
+          <t>Privacy: user deletion (DeleteUserData registry - users/devices/files; audit deliberately excluded)</t>
         </is>
       </c>
       <c r="D39" s="11" t="inlineStr"/>
@@ -2352,7 +2352,7 @@
       </c>
       <c r="C40" s="11" t="inlineStr">
         <is>
-          <t>Privacy: privacy preferences</t>
+          <t>Privacy: retention policy (declared, not scheduled - same documented gap as Phase 13's PurgeExpired)</t>
         </is>
       </c>
       <c r="D40" s="11" t="inlineStr"/>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>Privacy: coordinate deletion through workflows/events - core-api's own embedded Temporal worker</t>
+          <t>Privacy: privacy preferences</t>
         </is>
       </c>
       <c r="D41" s="11" t="inlineStr"/>
@@ -2377,21 +2377,17 @@
       <c r="A42" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="B42" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B42" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C42" s="11" t="inlineStr">
         <is>
-          <t>Privacy: notifications module as an Export/Delete participant</t>
-        </is>
-      </c>
-      <c r="D42" s="11" t="inlineStr">
-        <is>
-          <t>Deliberately deferred to prove the registry makes this a 2-line addition later, not a framework change</t>
-        </is>
-      </c>
+          <t>Privacy: coordinate deletion through workflows/events - core-api's own embedded Temporal worker</t>
+        </is>
+      </c>
+      <c r="D42" s="11" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="9" t="n">
@@ -2404,32 +2400,32 @@
       </c>
       <c r="C43" s="11" t="inlineStr">
         <is>
-          <t>Privacy: relationships/groups/messaging as participants</t>
+          <t>Privacy: notifications module as an Export/Delete participant</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>Deferred - shared multi-user data needs a redaction strategy this phase's per-user-in-isolation registry doesn't fit</t>
+          <t>Deliberately deferred to prove the registry makes this a 2-line addition later, not a framework change</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="9" t="n">
-        <v>21</v>
-      </c>
-      <c r="B44" s="10" t="inlineStr">
-        <is>
-          <t>Done</t>
+        <v>20</v>
+      </c>
+      <c r="B44" s="13" t="inlineStr">
+        <is>
+          <t>Pending</t>
         </is>
       </c>
       <c r="C44" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: Block</t>
+          <t>Privacy: relationships/groups/messaging as participants</t>
         </is>
       </c>
       <c r="D44" s="11" t="inlineStr">
         <is>
-          <t>Reused Phase 8's relationships (Status='blocked'), deliberately not duplicated</t>
+          <t>Deferred - shared multi-user data needs a redaction strategy this phase's per-user-in-isolation registry doesn't fit</t>
         </is>
       </c>
     </row>
@@ -2444,10 +2440,14 @@
       </c>
       <c r="C45" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: Mute</t>
-        </is>
-      </c>
-      <c r="D45" s="11" t="inlineStr"/>
+          <t>Trust &amp; Safety: Block</t>
+        </is>
+      </c>
+      <c r="D45" s="11" t="inlineStr">
+        <is>
+          <t>Reused Phase 8's relationships (Status='blocked'), deliberately not duplicated</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="9" t="n">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="C46" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: Report -&gt; ModerationCase (deduplicated via partial unique index)</t>
+          <t>Trust &amp; Safety: Mute</t>
         </is>
       </c>
       <c r="D46" s="11" t="inlineStr"/>
@@ -2476,7 +2476,7 @@
       </c>
       <c r="C47" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: Suspension</t>
+          <t>Trust &amp; Safety: Report -&gt; ModerationCase (deduplicated via partial unique index)</t>
         </is>
       </c>
       <c r="D47" s="11" t="inlineStr"/>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="C48" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: Ban</t>
+          <t>Trust &amp; Safety: Suspension</t>
         </is>
       </c>
       <c r="D48" s="11" t="inlineStr"/>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C49" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: Appeal (approving lifts the target restriction)</t>
+          <t>Trust &amp; Safety: Ban</t>
         </is>
       </c>
       <c r="D49" s="11" t="inlineStr"/>
@@ -2524,7 +2524,7 @@
       </c>
       <c r="C50" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: rate limiting (new platformkit/ratelimit, Valkey-backed)</t>
+          <t>Trust &amp; Safety: Appeal (approving lifts the target restriction)</t>
         </is>
       </c>
       <c r="D50" s="11" t="inlineStr"/>
@@ -2540,7 +2540,7 @@
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: spam protection (5 reports/hour per reporter)</t>
+          <t>Trust &amp; Safety: rate limiting (new platformkit/ratelimit, Valkey-backed)</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr"/>
@@ -2556,7 +2556,7 @@
       </c>
       <c r="C52" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: abuse signals (critical severity auto-opens a case)</t>
+          <t>Trust &amp; Safety: spam protection (5 reports/hour per reporter)</t>
         </is>
       </c>
       <c r="D52" s="11" t="inlineStr"/>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="C53" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: pluggable product-specific report reasons (free-form Reason field)</t>
+          <t>Trust &amp; Safety: abuse signals (critical severity auto-opens a case)</t>
         </is>
       </c>
       <c r="D53" s="11" t="inlineStr"/>
@@ -2588,7 +2588,7 @@
       </c>
       <c r="C54" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: Suspension/Ban actually restrict access (new requireActive middleware, one entry point)</t>
+          <t>Trust &amp; Safety: pluggable product-specific report reasons (free-form Reason field)</t>
         </is>
       </c>
       <c r="D54" s="11" t="inlineStr"/>
@@ -2597,21 +2597,17 @@
       <c r="A55" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="B55" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B55" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: WebSocket disconnect on suspension/ban</t>
-        </is>
-      </c>
-      <c r="D55" s="11" t="inlineStr">
-        <is>
-          <t>Deferred - only HTTP access is gated; an existing realtime-gateway connection isn't forcibly closed</t>
-        </is>
-      </c>
+          <t>Trust &amp; Safety: Suspension/Ban actually restrict access (new requireActive middleware, one entry point)</t>
+        </is>
+      </c>
+      <c r="D55" s="11" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="9" t="n">
@@ -2624,30 +2620,34 @@
       </c>
       <c r="C56" s="11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety: aggregating lower-severity signals over a time window</t>
+          <t>Trust &amp; Safety: WebSocket disconnect on suspension/ban</t>
         </is>
       </c>
       <c r="D56" s="11" t="inlineStr">
         <is>
-          <t>Deferred - a real abuse-detection engine is out of this phase's scope; only single-critical-signal escalation is implemented</t>
+          <t>Deferred - only HTTP access is gated; an existing realtime-gateway connection isn't forcibly closed</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="9" t="n">
-        <v>22</v>
-      </c>
-      <c r="B57" s="10" t="inlineStr">
-        <is>
-          <t>Done</t>
+        <v>21</v>
+      </c>
+      <c r="B57" s="13" t="inlineStr">
+        <is>
+          <t>Pending</t>
         </is>
       </c>
       <c r="C57" s="11" t="inlineStr">
         <is>
-          <t>Billing: Payment model (provider-specific transaction record)</t>
-        </is>
-      </c>
-      <c r="D57" s="11" t="inlineStr"/>
+          <t>Trust &amp; Safety: aggregating lower-severity signals over a time window</t>
+        </is>
+      </c>
+      <c r="D57" s="11" t="inlineStr">
+        <is>
+          <t>Deferred - a real abuse-detection engine is out of this phase's scope; only single-critical-signal escalation is implemented</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="9" t="n">
@@ -2660,7 +2660,7 @@
       </c>
       <c r="C58" s="11" t="inlineStr">
         <is>
-          <t>Billing: Entitlement model (platform-facing truth, kept separate from Payment)</t>
+          <t>Billing: Payment model (provider-specific transaction record)</t>
         </is>
       </c>
       <c r="D58" s="11" t="inlineStr"/>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>Billing: provider abstraction (PaymentProvider interface + registry, implemented first)</t>
+          <t>Billing: Entitlement model (platform-facing truth, kept separate from Payment)</t>
         </is>
       </c>
       <c r="D59" s="11" t="inlineStr"/>
@@ -2692,32 +2692,28 @@
       </c>
       <c r="C60" s="11" t="inlineStr">
         <is>
-          <t>Billing: Stripe adapter</t>
-        </is>
-      </c>
-      <c r="D60" s="11" t="inlineStr">
-        <is>
-          <t>Real HMAC-SHA256 webhook signature verification, live-validated without a Stripe account via self-signed test payloads</t>
-        </is>
-      </c>
+          <t>Billing: provider abstraction (PaymentProvider interface + registry, implemented first)</t>
+        </is>
+      </c>
+      <c r="D60" s="11" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="B61" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B61" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>Billing: Apple IAP adapter</t>
+          <t>Billing: Stripe adapter</t>
         </is>
       </c>
       <c r="D61" s="11" t="inlineStr">
         <is>
-          <t>Deferred - needs real App Store Server API credentials this environment doesn't have</t>
+          <t>Real HMAC-SHA256 webhook signature verification, live-validated without a Stripe account via self-signed test payloads</t>
         </is>
       </c>
     </row>
@@ -2732,30 +2728,34 @@
       </c>
       <c r="C62" s="11" t="inlineStr">
         <is>
-          <t>Billing: Google Play adapter</t>
+          <t>Billing: Apple IAP adapter</t>
         </is>
       </c>
       <c r="D62" s="11" t="inlineStr">
         <is>
-          <t>Deferred - needs real Play Developer API credentials this environment doesn't have</t>
+          <t>Deferred - needs real App Store Server API credentials this environment doesn't have</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="9" t="n">
-        <v>23</v>
-      </c>
-      <c r="B63" s="10" t="inlineStr">
-        <is>
-          <t>Done</t>
+        <v>22</v>
+      </c>
+      <c r="B63" s="13" t="inlineStr">
+        <is>
+          <t>Pending</t>
         </is>
       </c>
       <c r="C63" s="11" t="inlineStr">
         <is>
-          <t>Analytics: generic event envelope (event_name/user_id/anonymous_id/app_id/session_id/timestamp/properties/context)</t>
-        </is>
-      </c>
-      <c r="D63" s="11" t="inlineStr"/>
+          <t>Billing: Google Play adapter</t>
+        </is>
+      </c>
+      <c r="D63" s="11" t="inlineStr">
+        <is>
+          <t>Deferred - needs real Play Developer API credentials this environment doesn't have</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="9" t="n">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="C64" s="11" t="inlineStr">
         <is>
-          <t>Analytics: keep operational DBs out of the analytics path (analytics_events is a landing buffer, never queried for analytics)</t>
+          <t>Analytics: generic event envelope (event_name/user_id/anonymous_id/app_id/session_id/timestamp/properties/context)</t>
         </is>
       </c>
       <c r="D64" s="11" t="inlineStr"/>
@@ -2784,7 +2784,7 @@
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
-          <t>Analytics: pipeline foundation for ClickHouse/warehouse/data lake (worker batches NDJSON into MinIO/S3)</t>
+          <t>Analytics: keep operational DBs out of the analytics path (analytics_events is a landing buffer, never queried for analytics)</t>
         </is>
       </c>
       <c r="D65" s="11" t="inlineStr"/>
@@ -2793,37 +2793,37 @@
       <c r="A66" s="9" t="n">
         <v>23</v>
       </c>
-      <c r="B66" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B66" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C66" s="11" t="inlineStr">
         <is>
-          <t>Analytics: an actual ClickHouse/warehouse/data-lake query layer</t>
-        </is>
-      </c>
-      <c r="D66" s="11" t="inlineStr">
-        <is>
-          <t>Out of scope - this phase builds the landing pipeline only; no real destination system exists in this environment to integrate against honestly</t>
-        </is>
-      </c>
+          <t>Analytics: pipeline foundation for ClickHouse/warehouse/data lake (worker batches NDJSON into MinIO/S3)</t>
+        </is>
+      </c>
+      <c r="D66" s="11" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="9" t="n">
-        <v>24</v>
-      </c>
-      <c r="B67" s="10" t="inlineStr">
-        <is>
-          <t>Done</t>
+        <v>23</v>
+      </c>
+      <c r="B67" s="13" t="inlineStr">
+        <is>
+          <t>Pending</t>
         </is>
       </c>
       <c r="C67" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: provider-neutral interface (Provider: Name + Complete)</t>
-        </is>
-      </c>
-      <c r="D67" s="11" t="inlineStr"/>
+          <t>Analytics: an actual ClickHouse/warehouse/data-lake query layer</t>
+        </is>
+      </c>
+      <c r="D67" s="11" t="inlineStr">
+        <is>
+          <t>Out of scope - this phase builds the landing pipeline only; no real destination system exists in this environment to integrate against honestly</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="9" t="n">
@@ -2836,32 +2836,28 @@
       </c>
       <c r="C68" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: local models / Ollama adapter</t>
-        </is>
-      </c>
-      <c r="D68" s="11" t="inlineStr">
-        <is>
-          <t>Real local inference via a new Ollama container, auto-pulled model, no vendor API key - the one live-testable provider</t>
-        </is>
-      </c>
+          <t>AI Gateway: provider-neutral interface (Provider: Name + Complete)</t>
+        </is>
+      </c>
+      <c r="D68" s="11" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="9" t="n">
         <v>24</v>
       </c>
-      <c r="B69" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B69" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C69" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: OpenAI adapter</t>
+          <t>AI Gateway: local models / Ollama adapter</t>
         </is>
       </c>
       <c r="D69" s="11" t="inlineStr">
         <is>
-          <t>Deferred - no real API key in this environment to validate against honestly</t>
+          <t>Real local inference via a new Ollama container, auto-pulled model, no vendor API key - the one live-testable provider</t>
         </is>
       </c>
     </row>
@@ -2876,7 +2872,7 @@
       </c>
       <c r="C70" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: Anthropic adapter</t>
+          <t>AI Gateway: OpenAI adapter</t>
         </is>
       </c>
       <c r="D70" s="11" t="inlineStr">
@@ -2896,7 +2892,7 @@
       </c>
       <c r="C71" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: Google adapter</t>
+          <t>AI Gateway: Anthropic adapter</t>
         </is>
       </c>
       <c r="D71" s="11" t="inlineStr">
@@ -2909,17 +2905,21 @@
       <c r="A72" s="9" t="n">
         <v>24</v>
       </c>
-      <c r="B72" s="10" t="inlineStr">
-        <is>
-          <t>Done</t>
+      <c r="B72" s="13" t="inlineStr">
+        <is>
+          <t>Pending</t>
         </is>
       </c>
       <c r="C72" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: model routing (product-facing ModelAlias, never a vendor model name)</t>
-        </is>
-      </c>
-      <c r="D72" s="11" t="inlineStr"/>
+          <t>AI Gateway: Google adapter</t>
+        </is>
+      </c>
+      <c r="D72" s="11" t="inlineStr">
+        <is>
+          <t>Deferred - no real API key in this environment to validate against honestly</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="9" t="n">
@@ -2932,7 +2932,7 @@
       </c>
       <c r="C73" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: quotas (ratelimit.Limiter reused a third time, 60/min/caller)</t>
+          <t>AI Gateway: model routing (product-facing ModelAlias, never a vendor model name)</t>
         </is>
       </c>
       <c r="D73" s="11" t="inlineStr"/>
@@ -2948,7 +2948,7 @@
       </c>
       <c r="C74" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: token usage tracking</t>
+          <t>AI Gateway: quotas (ratelimit.Limiter reused a third time, 60/min/caller)</t>
         </is>
       </c>
       <c r="D74" s="11" t="inlineStr"/>
@@ -2964,7 +2964,7 @@
       </c>
       <c r="C75" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: cost tracking (real per-route price table; Ollama honestly priced at 0)</t>
+          <t>AI Gateway: token usage tracking</t>
         </is>
       </c>
       <c r="D75" s="11" t="inlineStr"/>
@@ -2980,7 +2980,7 @@
       </c>
       <c r="C76" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: audit integration (new AIGatewayAuditRecorder, a genuine audit.Record per call)</t>
+          <t>AI Gateway: cost tracking (real per-route price table; Ollama honestly priced at 0)</t>
         </is>
       </c>
       <c r="D76" s="11" t="inlineStr"/>
@@ -2996,7 +2996,7 @@
       </c>
       <c r="C77" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: prompt/version metadata (free-form PromptKey/PromptVersion)</t>
+          <t>AI Gateway: audit integration (new AIGatewayAuditRecorder, a genuine audit.Record per call)</t>
         </is>
       </c>
       <c r="D77" s="11" t="inlineStr"/>
@@ -3012,7 +3012,7 @@
       </c>
       <c r="C78" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: timeouts (context.WithTimeout per provider call)</t>
+          <t>AI Gateway: prompt/version metadata (free-form PromptKey/PromptVersion)</t>
         </is>
       </c>
       <c r="D78" s="11" t="inlineStr"/>
@@ -3028,7 +3028,7 @@
       </c>
       <c r="C79" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: fallback (ordered provider/model chain, first success wins)</t>
+          <t>AI Gateway: timeouts (context.WithTimeout per provider call)</t>
         </is>
       </c>
       <c r="D79" s="11" t="inlineStr"/>
@@ -3037,37 +3037,37 @@
       <c r="A80" s="9" t="n">
         <v>24</v>
       </c>
-      <c r="B80" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B80" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C80" s="11" t="inlineStr">
         <is>
-          <t>AI Gateway: live token-quantity quota (as opposed to today's call-count quota)</t>
-        </is>
-      </c>
-      <c r="D80" s="11" t="inlineStr">
-        <is>
-          <t>Deferred - Repository already has the data (Completion.TotalTokens); not wired as a live gate yet</t>
-        </is>
-      </c>
+          <t>AI Gateway: fallback (ordered provider/model chain, first success wins)</t>
+        </is>
+      </c>
+      <c r="D80" s="11" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="9" t="n">
-        <v>25</v>
-      </c>
-      <c r="B81" s="10" t="inlineStr">
-        <is>
-          <t>Done</t>
+        <v>24</v>
+      </c>
+      <c r="B81" s="13" t="inlineStr">
+        <is>
+          <t>Pending</t>
         </is>
       </c>
       <c r="C81" s="11" t="inlineStr">
         <is>
-          <t>Admin Portal: real Keycloak-authenticated session (Resource Owner Password Credentials grant), httpOnly session cookie</t>
-        </is>
-      </c>
-      <c r="D81" s="11" t="inlineStr"/>
+          <t>AI Gateway: live token-quantity quota (as opposed to today's call-count quota)</t>
+        </is>
+      </c>
+      <c r="D81" s="11" t="inlineStr">
+        <is>
+          <t>Deferred - Repository already has the data (Completion.TotalTokens); not wired as a live gate yet</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="9" t="n">
@@ -3080,14 +3080,10 @@
       </c>
       <c r="C82" s="11" t="inlineStr">
         <is>
-          <t>Admin Portal: visibility - Applications</t>
-        </is>
-      </c>
-      <c r="D82" s="11" t="inlineStr">
-        <is>
-          <t>Real GET /v1/apps table</t>
-        </is>
-      </c>
+          <t>Admin Portal: real Keycloak-authenticated session (Resource Owner Password Credentials grant), httpOnly session cookie</t>
+        </is>
+      </c>
+      <c r="D82" s="11" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="9" t="n">
@@ -3100,12 +3096,12 @@
       </c>
       <c r="C83" s="11" t="inlineStr">
         <is>
-          <t>Admin Portal: visibility - Users (list + detail)</t>
+          <t>Admin Portal: visibility - Applications</t>
         </is>
       </c>
       <c r="D83" s="11" t="inlineStr">
         <is>
-          <t>New admin-wide GET /v1/users (cursor-paginated, platform.admin-gated)</t>
+          <t>Real GET /v1/apps table</t>
         </is>
       </c>
     </row>
@@ -3120,12 +3116,12 @@
       </c>
       <c r="C84" s="11" t="inlineStr">
         <is>
-          <t>Admin Portal: visibility - Roles/Permissions</t>
+          <t>Admin Portal: visibility - Users (list + detail)</t>
         </is>
       </c>
       <c r="D84" s="11" t="inlineStr">
         <is>
-          <t>New authz HTTP surface (GET/POST /v1/authz/roles, POST /v1/authz/roles/revoke) with a full grant/revoke UI</t>
+          <t>New admin-wide GET /v1/users (cursor-paginated, platform.admin-gated)</t>
         </is>
       </c>
     </row>
@@ -3140,10 +3136,14 @@
       </c>
       <c r="C85" s="11" t="inlineStr">
         <is>
-          <t>Admin Portal: visibility - Feature Flags, Configuration, Jobs</t>
-        </is>
-      </c>
-      <c r="D85" s="11" t="inlineStr"/>
+          <t>Admin Portal: visibility - Roles/Permissions</t>
+        </is>
+      </c>
+      <c r="D85" s="11" t="inlineStr">
+        <is>
+          <t>New authz HTTP surface (GET/POST /v1/authz/roles, POST /v1/authz/roles/revoke) with a full grant/revoke UI</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="9" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="C86" s="11" t="inlineStr">
         <is>
-          <t>Admin Portal: visibility - Moderation, Audit</t>
+          <t>Admin Portal: visibility - Feature Flags, Configuration, Jobs</t>
         </is>
       </c>
       <c r="D86" s="11" t="inlineStr"/>
@@ -3172,14 +3172,10 @@
       </c>
       <c r="C87" s="11" t="inlineStr">
         <is>
-          <t>Admin Portal: visibility - System Health</t>
-        </is>
-      </c>
-      <c r="D87" s="11" t="inlineStr">
-        <is>
-          <t>Live GET /healthz against core-api/realtime-gateway/worker</t>
-        </is>
-      </c>
+          <t>Admin Portal: visibility - Moderation, Audit</t>
+        </is>
+      </c>
+      <c r="D87" s="11" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="9" t="n">
@@ -3192,30 +3188,30 @@
       </c>
       <c r="C88" s="11" t="inlineStr">
         <is>
-          <t>Admin Portal: visibility - Billing, AI Gateway usage (bonus, not roadmap-named)</t>
-        </is>
-      </c>
-      <c r="D88" s="11" t="inlineStr"/>
+          <t>Admin Portal: visibility - System Health</t>
+        </is>
+      </c>
+      <c r="D88" s="11" t="inlineStr">
+        <is>
+          <t>Live GET /healthz against core-api/realtime-gateway/worker</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="B89" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B89" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C89" s="11" t="inlineStr">
         <is>
-          <t>Admin Portal: visibility - Sessions/Devices, Tenants, Relationships, Messages, Notifications, Files</t>
-        </is>
-      </c>
-      <c r="D89" s="11" t="inlineStr">
-        <is>
-          <t>Deferred - each backing module only exposes a listMine-style self-scoped endpoint, not an admin-wide one; honest ComingSoon reasoning shown per area instead of fake rows</t>
-        </is>
-      </c>
+          <t>Admin Portal: visibility - Billing, AI Gateway usage (bonus, not roadmap-named)</t>
+        </is>
+      </c>
+      <c r="D89" s="11" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="9" t="n">
@@ -3228,32 +3224,32 @@
       </c>
       <c r="C90" s="11" t="inlineStr">
         <is>
-          <t>Admin Portal: visibility - Deployments</t>
+          <t>Admin Portal: visibility - Sessions/Devices, Tenants, Relationships, Messages, Notifications, Files</t>
         </is>
       </c>
       <c r="D90" s="11" t="inlineStr">
         <is>
-          <t>Deferred to Phase 29 - nothing in the platform tracks deployments as data yet</t>
+          <t>Deferred - each backing module only exposes a listMine-style self-scoped endpoint, not an admin-wide one; honest ComingSoon reasoning shown per area instead of fake rows</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="9" t="n">
-        <v>26</v>
-      </c>
-      <c r="B91" s="10" t="inlineStr">
-        <is>
-          <t>Done</t>
+        <v>25</v>
+      </c>
+      <c r="B91" s="13" t="inlineStr">
+        <is>
+          <t>Pending</t>
         </is>
       </c>
       <c r="C91" s="11" t="inlineStr">
         <is>
-          <t>Backstage: integrate Backstage as developer portal</t>
+          <t>Admin Portal: visibility - Deployments</t>
         </is>
       </c>
       <c r="D91" s="11" t="inlineStr">
         <is>
-          <t>Real @backstage/create-app instance at platform/backstage, catalog wired to real catalog/*.yaml + contracts/*/catalog-info.yaml, live-validated via the real catalog API (21 Components, 2 APIs, 1 System, 1 Group, 0 processing errors)</t>
+          <t>Deferred to Phase 29 - nothing in the platform tracks deployments as data yet</t>
         </is>
       </c>
     </row>
@@ -3268,12 +3264,12 @@
       </c>
       <c r="C92" s="11" t="inlineStr">
         <is>
-          <t>Backstage: per-module metadata - name/description/owner/lifecycle</t>
+          <t>Backstage: integrate Backstage as developer portal</t>
         </is>
       </c>
       <c r="D92" s="11" t="inlineStr">
         <is>
-          <t>All 16 modules/*/module.yaml + README.md real (11 were still stub text before this phase)</t>
+          <t>Real @backstage/create-app instance at platform/backstage, catalog wired to real catalog/*.yaml + contracts/*/catalog-info.yaml, live-validated via the real catalog API (21 Components, 2 APIs, 1 System, 1 Group, 0 processing errors)</t>
         </is>
       </c>
     </row>
@@ -3288,12 +3284,12 @@
       </c>
       <c r="C93" s="11" t="inlineStr">
         <is>
-          <t>Backstage: per-module metadata - repository/documentation</t>
+          <t>Backstage: per-module metadata - name/description/owner/lifecycle</t>
         </is>
       </c>
       <c r="D93" s="11" t="inlineStr">
         <is>
-          <t>Every Component links its module README; the System entity links VALIDATION.md and the new docs/RUNBOOKS.md</t>
+          <t>All 16 modules/*/module.yaml + README.md real (11 were still stub text before this phase)</t>
         </is>
       </c>
     </row>
@@ -3308,12 +3304,12 @@
       </c>
       <c r="C94" s="11" t="inlineStr">
         <is>
-          <t>Backstage: per-module metadata - dependencies</t>
+          <t>Backstage: per-module metadata - repository/documentation</t>
         </is>
       </c>
       <c r="D94" s="11" t="inlineStr">
         <is>
-          <t>Component dependsOn mirrors modules/*/module.yaml's real dependency graph; Backstage computes reverse dependencyOf relations automatically, confirmed live</t>
+          <t>Every Component links its module README; the System entity links VALIDATION.md and the new docs/RUNBOOKS.md</t>
         </is>
       </c>
     </row>
@@ -3328,12 +3324,12 @@
       </c>
       <c r="C95" s="11" t="inlineStr">
         <is>
-          <t>Backstage: per-module metadata - APIs</t>
+          <t>Backstage: per-module metadata - dependencies</t>
         </is>
       </c>
       <c r="D95" s="11" t="inlineStr">
         <is>
-          <t>2 API entities (OpenAPI, AsyncAPI), both with their full real spec embedded and live-loaded</t>
+          <t>Component dependsOn mirrors modules/*/module.yaml's real dependency graph; Backstage computes reverse dependencyOf relations automatically, confirmed live</t>
         </is>
       </c>
     </row>
@@ -3348,12 +3344,12 @@
       </c>
       <c r="C96" s="11" t="inlineStr">
         <is>
-          <t>Backstage: per-module metadata - events</t>
+          <t>Backstage: per-module metadata - APIs</t>
         </is>
       </c>
       <c r="D96" s="11" t="inlineStr">
         <is>
-          <t>providesApis set only on the components whose code actually calls outbox.Record, cross-checked against the real Go source</t>
+          <t>2 API entities (OpenAPI, AsyncAPI), both with their full real spec embedded and live-loaded</t>
         </is>
       </c>
     </row>
@@ -3361,19 +3357,19 @@
       <c r="A97" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="B97" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B97" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C97" s="11" t="inlineStr">
         <is>
-          <t>Backstage: per-module metadata - database ownership</t>
+          <t>Backstage: per-module metadata - events</t>
         </is>
       </c>
       <c r="D97" s="11" t="inlineStr">
         <is>
-          <t>Deferred - no per-module DB-ownership annotation convention chosen yet; docs/control's Modules sheet tracks this today at a finer grain than catalog/system.yaml's 16 domains</t>
+          <t>providesApis set only on the components whose code actually calls outbox.Record, cross-checked against the real Go source</t>
         </is>
       </c>
     </row>
@@ -3381,19 +3377,19 @@
       <c r="A98" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="B98" s="10" t="inlineStr">
-        <is>
-          <t>Done</t>
+      <c r="B98" s="13" t="inlineStr">
+        <is>
+          <t>Pending</t>
         </is>
       </c>
       <c r="C98" s="11" t="inlineStr">
         <is>
-          <t>Backstage: per-module metadata - dashboards</t>
+          <t>Backstage: per-module metadata - database ownership</t>
         </is>
       </c>
       <c r="D98" s="11" t="inlineStr">
         <is>
-          <t>core-platform.io/dashboard annotation on each service pointing at the real local Grafana instance - no per-service dashboard exists yet (that's Phase 28), so it points at the shared instance, documented as such</t>
+          <t>Deferred - no per-module DB-ownership annotation convention chosen yet; docs/control's Modules sheet tracks this today at a finer grain than catalog/system.yaml's 16 domains</t>
         </is>
       </c>
     </row>
@@ -3408,18 +3404,18 @@
       </c>
       <c r="C99" s="11" t="inlineStr">
         <is>
-          <t>Backstage: per-module metadata - runbooks</t>
+          <t>Backstage: per-module metadata - dashboards</t>
         </is>
       </c>
       <c r="D99" s="11" t="inlineStr">
         <is>
-          <t>New docs/RUNBOOKS.md, linked from the System entity</t>
+          <t>core-platform.io/dashboard annotation on each service pointing at the real local Grafana instance - no per-service dashboard exists yet (that's Phase 28), so it points at the shared instance, documented as such</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B100" s="10" t="inlineStr">
         <is>
@@ -3428,12 +3424,12 @@
       </c>
       <c r="C100" s="11" t="inlineStr">
         <is>
-          <t>SDKs: Go SDK</t>
+          <t>Backstage: per-module metadata - runbooks</t>
         </is>
       </c>
       <c r="D100" s="11" t="inlineStr">
         <is>
-          <t>packages/go/coresdk - 12 unit tests (httptest.Server), live-validated against real Keycloak/core-api/realtime-gateway</t>
+          <t>New docs/RUNBOOKS.md, linked from the System entity</t>
         </is>
       </c>
     </row>
@@ -3448,12 +3444,12 @@
       </c>
       <c r="C101" s="11" t="inlineStr">
         <is>
-          <t>SDKs: TypeScript SDK</t>
+          <t>SDKs: Go SDK</t>
         </is>
       </c>
       <c r="D101" s="11" t="inlineStr">
         <is>
-          <t>packages/typescript/core-sdk - 13 unit tests (node:http), real consumer: apps/admin's entire lib/api.ts migrated to it</t>
+          <t>packages/go/coresdk - 12 unit tests (httptest.Server), live-validated against real Keycloak/core-api/realtime-gateway</t>
         </is>
       </c>
     </row>
@@ -3468,12 +3464,12 @@
       </c>
       <c r="C102" s="11" t="inlineStr">
         <is>
-          <t>SDKs: Dart SDK</t>
+          <t>SDKs: TypeScript SDK</t>
         </is>
       </c>
       <c r="D102" s="11" t="inlineStr">
         <is>
-          <t>packages/flutter/core_sdk (pure Dart, no Flutter dependency) - 13 unit tests (dart:io HttpServer), real consumer: apps/mobile's login/profile flow</t>
+          <t>packages/typescript/core-sdk - 13 unit tests (node:http), real consumer: apps/admin's entire lib/api.ts migrated to it</t>
         </is>
       </c>
     </row>
@@ -3488,12 +3484,12 @@
       </c>
       <c r="C103" s="11" t="inlineStr">
         <is>
-          <t>SDKs: auth + token refresh in each SDK</t>
+          <t>SDKs: Dart SDK</t>
         </is>
       </c>
       <c r="D103" s="11" t="inlineStr">
         <is>
-          <t>TokenSource (static + real Keycloak password-grant with skew-aware, concurrency-coalesced refresh) in all three</t>
+          <t>packages/flutter/core_sdk (pure Dart, no Flutter dependency) - 13 unit tests (dart:io HttpServer), real consumer: apps/mobile's login/profile flow</t>
         </is>
       </c>
     </row>
@@ -3508,12 +3504,12 @@
       </c>
       <c r="C104" s="11" t="inlineStr">
         <is>
-          <t>SDKs: pagination + safe retries</t>
+          <t>SDKs: auth + token refresh in each SDK</t>
         </is>
       </c>
       <c r="D104" s="11" t="inlineStr">
         <is>
-          <t>Page/paginate/collectAll over the real {items,nextCursor} shape; GET-only retries by default on transient statuses, in all three</t>
+          <t>TokenSource (static + real Keycloak password-grant with skew-aware, concurrency-coalesced refresh) in all three</t>
         </is>
       </c>
     </row>
@@ -3528,12 +3524,12 @@
       </c>
       <c r="C105" s="11" t="inlineStr">
         <is>
-          <t>SDKs: realtime connection helper</t>
+          <t>SDKs: pagination + safe retries</t>
         </is>
       </c>
       <c r="D105" s="11" t="inlineStr">
         <is>
-          <t>Reproduces realtime-gateway's real ws://.../ws?access_token=&amp;deviceId= protocol and message shapes exactly, in all three - live-validated with real cross-connection fan-out</t>
+          <t>Page/paginate/collectAll over the real {items,nextCursor} shape; GET-only retries by default on transient statuses, in all three</t>
         </is>
       </c>
     </row>
@@ -3548,12 +3544,12 @@
       </c>
       <c r="C106" s="11" t="inlineStr">
         <is>
-          <t>SDKs: correlation ID propagation</t>
+          <t>SDKs: realtime connection helper</t>
         </is>
       </c>
       <c r="D106" s="11" t="inlineStr">
         <is>
-          <t>X-Correlation-ID on every call, matching platformkit/correlation's real header name, in all three</t>
+          <t>Reproduces realtime-gateway's real ws://.../ws?access_token=&amp;deviceId= protocol and message shapes exactly, in all three - live-validated with real cross-connection fan-out</t>
         </is>
       </c>
     </row>
@@ -3568,12 +3564,12 @@
       </c>
       <c r="C107" s="11" t="inlineStr">
         <is>
-          <t>SDKs: device registration helper</t>
+          <t>SDKs: correlation ID propagation</t>
         </is>
       </c>
       <c r="D107" s="11" t="inlineStr">
         <is>
-          <t>DevicesRegister/devicesRegister in all three - realtime dial requires a real registered device id</t>
+          <t>X-Correlation-ID on every call, matching platformkit/correlation's real header name, in all three</t>
         </is>
       </c>
     </row>
@@ -3588,12 +3584,12 @@
       </c>
       <c r="C108" s="11" t="inlineStr">
         <is>
-          <t>SDKs: apps/mobile test/ directory (make flutter-test currently fails)</t>
+          <t>SDKs: device registration helper</t>
         </is>
       </c>
       <c r="D108" s="11" t="inlineStr">
         <is>
-          <t>Closed as a side effect - real widget tests added, discovered and worked around Flutter's TestWidgetsFlutterBinding network-mocking constraint live. Was pending since Phase 9.</t>
+          <t>DevicesRegister/devicesRegister in all three - realtime dial requires a real registered device id</t>
         </is>
       </c>
     </row>
@@ -3601,39 +3597,39 @@
       <c r="A109" s="9" t="n">
         <v>27</v>
       </c>
-      <c r="B109" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B109" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C109" s="11" t="inlineStr">
         <is>
-          <t>SDKs: full API coverage (all 146 endpoints typed) in each SDK</t>
+          <t>SDKs: apps/mobile test/ directory (make flutter-test currently fails)</t>
         </is>
       </c>
       <c r="D109" s="11" t="inlineStr">
         <is>
-          <t>Deferred - each SDK covers a representative 'core identity' slice (platform/identity/users/devices/applications) plus what its real consumer needs; the untyped request()/Do() escape hatch reaches everything else. Broader coverage is real, additive work, not a framework limitation.</t>
+          <t>Closed as a side effect - real widget tests added, discovered and worked around Flutter's TestWidgetsFlutterBinding network-mocking constraint live. Was pending since Phase 9.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="9" t="n">
-        <v>28</v>
-      </c>
-      <c r="B110" s="10" t="inlineStr">
-        <is>
-          <t>Done</t>
+        <v>27</v>
+      </c>
+      <c r="B110" s="13" t="inlineStr">
+        <is>
+          <t>Pending</t>
         </is>
       </c>
       <c r="C110" s="11" t="inlineStr">
         <is>
-          <t>Observability: structured logs everywhere</t>
+          <t>SDKs: full API coverage (all 146 endpoints typed) in each SDK</t>
         </is>
       </c>
       <c r="D110" s="11" t="inlineStr">
         <is>
-          <t>logging.NewWithLoki ships every record to Loki's real push API directly; on by default locally (LOKI_PUSH_URL)</t>
+          <t>Deferred - each SDK covers a representative 'core identity' slice (platform/identity/users/devices/applications) plus what its real consumer needs; the untyped request()/Do() escape hatch reaches everything else. Broader coverage is real, additive work, not a framework limitation.</t>
         </is>
       </c>
     </row>
@@ -3648,12 +3644,12 @@
       </c>
       <c r="C111" s="11" t="inlineStr">
         <is>
-          <t>Observability: metrics everywhere</t>
+          <t>Observability: structured logs everywhere</t>
         </is>
       </c>
       <c r="D111" s="11" t="inlineStr">
         <is>
-          <t>New packages/go/platformkit/metrics - real GET /metrics (Prometheus exposition) on core-api, realtime-gateway, and worker</t>
+          <t>logging.NewWithLoki ships every record to Loki's real push API directly; on by default locally (LOKI_PUSH_URL)</t>
         </is>
       </c>
     </row>
@@ -3668,12 +3664,12 @@
       </c>
       <c r="C112" s="11" t="inlineStr">
         <is>
-          <t>Observability: distributed traces everywhere</t>
+          <t>Observability: metrics everywhere</t>
         </is>
       </c>
       <c r="D112" s="11" t="inlineStr">
         <is>
-          <t>Already real since Phase 1 (otelx) - confirmed still working live this phase</t>
+          <t>New packages/go/platformkit/metrics - real GET /metrics (Prometheus exposition) on core-api, realtime-gateway, and worker</t>
         </is>
       </c>
     </row>
@@ -3688,12 +3684,12 @@
       </c>
       <c r="C113" s="11" t="inlineStr">
         <is>
-          <t>Observability: health checks everywhere</t>
+          <t>Observability: distributed traces everywhere</t>
         </is>
       </c>
       <c r="D113" s="11" t="inlineStr">
         <is>
-          <t>Already real since Phase 1 (/livez /readyz /healthz) - confirmed still working live this phase</t>
+          <t>Already real since Phase 1 (otelx) - confirmed still working live this phase</t>
         </is>
       </c>
     </row>
@@ -3708,12 +3704,12 @@
       </c>
       <c r="C114" s="11" t="inlineStr">
         <is>
-          <t>Observability: dashboard - API latency</t>
+          <t>Observability: health checks everywhere</t>
         </is>
       </c>
       <c r="D114" s="11" t="inlineStr">
         <is>
-          <t>http_request_duration_seconds, labeled by route pattern (not raw path) to keep cardinality bounded</t>
+          <t>Already real since Phase 1 (/livez /readyz /healthz) - confirmed still working live this phase</t>
         </is>
       </c>
     </row>
@@ -3728,12 +3724,12 @@
       </c>
       <c r="C115" s="11" t="inlineStr">
         <is>
-          <t>Observability: dashboard - error rate</t>
+          <t>Observability: dashboard - API latency</t>
         </is>
       </c>
       <c r="D115" s="11" t="inlineStr">
         <is>
-          <t>http_requests_total{status=~"5.."} / http_requests_total</t>
+          <t>http_request_duration_seconds, labeled by route pattern (not raw path) to keep cardinality bounded</t>
         </is>
       </c>
     </row>
@@ -3748,12 +3744,12 @@
       </c>
       <c r="C116" s="11" t="inlineStr">
         <is>
-          <t>Observability: dashboard - requests/sec</t>
+          <t>Observability: dashboard - error rate</t>
         </is>
       </c>
       <c r="D116" s="11" t="inlineStr">
         <is>
-          <t>rate(http_requests_total[5m])</t>
+          <t>http_requests_total{status=~"5.."} / http_requests_total</t>
         </is>
       </c>
     </row>
@@ -3768,12 +3764,12 @@
       </c>
       <c r="C117" s="11" t="inlineStr">
         <is>
-          <t>Observability: dashboard - DB connections</t>
+          <t>Observability: dashboard - requests/sec</t>
         </is>
       </c>
       <c r="D117" s="11" t="inlineStr">
         <is>
-          <t>db_pool_connections, real pgxpool.Stat() polled on a ticker (pg.ReportStats) on all 3 services</t>
+          <t>rate(http_requests_total[5m])</t>
         </is>
       </c>
     </row>
@@ -3781,19 +3777,19 @@
       <c r="A118" s="9" t="n">
         <v>28</v>
       </c>
-      <c r="B118" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B118" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C118" s="11" t="inlineStr">
         <is>
-          <t>Observability: dashboard - Kafka lag</t>
+          <t>Observability: dashboard - DB connections</t>
         </is>
       </c>
       <c r="D118" s="11" t="inlineStr">
         <is>
-          <t>Deliberately not implemented - no real Kafka/Redpanda producer or consumer exists in this codebase yet (documented since Phase 14); an honest placeholder panel explains this instead of a fabricated metric</t>
+          <t>db_pool_connections, real pgxpool.Stat() polled on a ticker (pg.ReportStats) on all 3 services</t>
         </is>
       </c>
     </row>
@@ -3801,19 +3797,19 @@
       <c r="A119" s="9" t="n">
         <v>28</v>
       </c>
-      <c r="B119" s="10" t="inlineStr">
-        <is>
-          <t>Done</t>
+      <c r="B119" s="13" t="inlineStr">
+        <is>
+          <t>Pending</t>
         </is>
       </c>
       <c r="C119" s="11" t="inlineStr">
         <is>
-          <t>Observability: dashboard - WebSocket connections</t>
+          <t>Observability: dashboard - Kafka lag</t>
         </is>
       </c>
       <c r="D119" s="11" t="inlineStr">
         <is>
-          <t>realtime_ws_connections, live-validated going 0 -&gt; 1 -&gt; 0 across a real connect/hold/disconnect cycle against the running service</t>
+          <t>Deliberately not implemented - no real Kafka/Redpanda producer or consumer exists in this codebase yet (documented since Phase 14); an honest placeholder panel explains this instead of a fabricated metric</t>
         </is>
       </c>
     </row>
@@ -3828,12 +3824,12 @@
       </c>
       <c r="C120" s="11" t="inlineStr">
         <is>
-          <t>Observability: dashboard - Redis latency</t>
+          <t>Observability: dashboard - WebSocket connections</t>
         </is>
       </c>
       <c r="D120" s="11" t="inlineStr">
         <is>
-          <t>redis_command_duration_seconds via a real go-redis v9 Hook, InstrumentRedis</t>
+          <t>realtime_ws_connections, live-validated going 0 -&gt; 1 -&gt; 0 across a real connect/hold/disconnect cycle against the running service</t>
         </is>
       </c>
     </row>
@@ -3848,12 +3844,12 @@
       </c>
       <c r="C121" s="11" t="inlineStr">
         <is>
-          <t>Observability: dashboard - notification failures</t>
+          <t>Observability: dashboard - Redis latency</t>
         </is>
       </c>
       <c r="D121" s="11" t="inlineStr">
         <is>
-          <t>notification_delivery_failures_total, incremented at notifications.Service.dispatch's two real failure paths</t>
+          <t>redis_command_duration_seconds via a real go-redis v9 Hook, InstrumentRedis</t>
         </is>
       </c>
     </row>
@@ -3868,12 +3864,12 @@
       </c>
       <c r="C122" s="11" t="inlineStr">
         <is>
-          <t>Observability: dashboard - background job failures</t>
+          <t>Observability: dashboard - notification failures</t>
         </is>
       </c>
       <c r="D122" s="11" t="inlineStr">
         <is>
-          <t>job_failures_total, incremented only on jobrunner's real dead_letter transition (not every retryable attempt)</t>
+          <t>notification_delivery_failures_total, incremented at notifications.Service.dispatch's two real failure paths</t>
         </is>
       </c>
     </row>
@@ -3888,12 +3884,12 @@
       </c>
       <c r="C123" s="11" t="inlineStr">
         <is>
-          <t>Observability: alerting rules</t>
+          <t>Observability: dashboard - background job failures</t>
         </is>
       </c>
       <c r="D123" s="11" t="inlineStr">
         <is>
-          <t>6 real, live-evaluated Prometheus rules (infra/observability/alerts.yml) - ServiceDown live-confirmed firing then clearing on the real service lifecycle</t>
+          <t>job_failures_total, incremented only on jobrunner's real dead_letter transition (not every retryable attempt)</t>
         </is>
       </c>
     </row>
@@ -3901,19 +3897,19 @@
       <c r="A124" s="9" t="n">
         <v>28</v>
       </c>
-      <c r="B124" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B124" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C124" s="11" t="inlineStr">
         <is>
-          <t>Observability: Alertmanager routing (Slack/PagerDuty/email)</t>
+          <t>Observability: alerting rules</t>
         </is>
       </c>
       <c r="D124" s="11" t="inlineStr">
         <is>
-          <t>Deferred - no real notification-channel credentials in this environment, the same reasoning Stripe/AI vendor adapters have documented; Prometheus's own rule evaluation and API are real regardless</t>
+          <t>6 real, live-evaluated Prometheus rules (infra/observability/alerts.yml) - ServiceDown live-confirmed firing then clearing on the real service lifecycle</t>
         </is>
       </c>
     </row>
@@ -3928,18 +3924,18 @@
       </c>
       <c r="C125" s="11" t="inlineStr">
         <is>
-          <t>Observability: per-service (not shared) Grafana dashboards</t>
+          <t>Observability: Alertmanager routing (Slack/PagerDuty/email)</t>
         </is>
       </c>
       <c r="D125" s="11" t="inlineStr">
         <is>
-          <t>Deferred - one shared 'Core Platform Overview' dashboard covers all 3 services today, not 9 separate roadmap-named dashboards</t>
+          <t>Deferred - no real notification-channel credentials in this environment, the same reasoning Stripe/AI vendor adapters have documented; Prometheus's own rule evaluation and API are real regardless</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B126" s="13" t="inlineStr">
         <is>
@@ -3948,78 +3944,98 @@
       </c>
       <c r="C126" s="11" t="inlineStr">
         <is>
-          <t>Platform Control Plane: one view: applications/services/versions</t>
-        </is>
-      </c>
-      <c r="D126" s="11" t="inlineStr"/>
+          <t>Observability: per-service (not shared) Grafana dashboards</t>
+        </is>
+      </c>
+      <c r="D126" s="11" t="inlineStr">
+        <is>
+          <t>Deferred - one shared 'Core Platform Overview' dashboard covers all 3 services today, not 9 separate roadmap-named dashboards</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="9" t="n">
         <v>29</v>
       </c>
-      <c r="B127" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B127" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C127" s="11" t="inlineStr">
         <is>
-          <t>Platform Control Plane: one view: environments/dependencies/deployments</t>
-        </is>
-      </c>
-      <c r="D127" s="11" t="inlineStr"/>
+          <t>Control Plane: one view - applications/services</t>
+        </is>
+      </c>
+      <c r="D127" s="11" t="inlineStr">
+        <is>
+          <t>New apps/admin/control-plane page, real GET /v1/apps + per-service health</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="9" t="n">
         <v>29</v>
       </c>
-      <c r="B128" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B128" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C128" s="11" t="inlineStr">
         <is>
-          <t>Platform Control Plane: one view: DB ownership/events/API contracts</t>
-        </is>
-      </c>
-      <c r="D128" s="11" t="inlineStr"/>
+          <t>Control Plane: one view - versions</t>
+        </is>
+      </c>
+      <c r="D128" s="11" t="inlineStr">
+        <is>
+          <t>New config.Version (real git SHA via `git rev-parse --short HEAD`, BUILD_VERSION override) wired through health.Live/Health on all 3 services</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="9" t="n">
         <v>29</v>
       </c>
-      <c r="B129" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B129" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C129" s="11" t="inlineStr">
         <is>
-          <t>Platform Control Plane: one view: health/alerts/recent changes</t>
-        </is>
-      </c>
-      <c r="D129" s="11" t="inlineStr"/>
+          <t>Control Plane: one view - environments</t>
+        </is>
+      </c>
+      <c r="D129" s="11" t="inlineStr">
+        <is>
+          <t>Read live from GET /v1/platform's environment field - one real entry, not a fabricated multi-env list</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="9" t="n">
-        <v>30</v>
-      </c>
-      <c r="B130" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+        <v>29</v>
+      </c>
+      <c r="B130" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C130" s="11" t="inlineStr">
         <is>
-          <t>AI Development Context: every module: README</t>
-        </is>
-      </c>
-      <c r="D130" s="11" t="inlineStr"/>
+          <t>Control Plane: one view - dependencies</t>
+        </is>
+      </c>
+      <c r="D130" s="11" t="inlineStr">
+        <is>
+          <t>New docs/control/platform.json (build_workbook.py export) parses catalog/system.yaml's real dependsOn graph - 23 components</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="9" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B131" s="13" t="inlineStr">
         <is>
@@ -4028,74 +4044,230 @@
       </c>
       <c r="C131" s="11" t="inlineStr">
         <is>
-          <t>AI Development Context: every module: ownership metadata</t>
-        </is>
-      </c>
-      <c r="D131" s="11" t="inlineStr"/>
+          <t>Control Plane: one view - deployments</t>
+        </is>
+      </c>
+      <c r="D131" s="11" t="inlineStr">
+        <is>
+          <t>Honest placeholder - no CI/CD pipeline or deployment tracking exists in this environment; real per-service version is the closest honest signal today</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="9" t="n">
-        <v>30</v>
-      </c>
-      <c r="B132" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+        <v>29</v>
+      </c>
+      <c r="B132" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C132" s="11" t="inlineStr">
         <is>
-          <t>AI Development Context: every module: dependencies</t>
-        </is>
-      </c>
-      <c r="D132" s="11" t="inlineStr"/>
+          <t>Control Plane: one view - DB ownership</t>
+        </is>
+      </c>
+      <c r="D132" s="11" t="inlineStr">
+        <is>
+          <t>platform.json exports the same module/storage data docs/control's Modules sheet tracks - one source, not a third copy</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="9" t="n">
-        <v>30</v>
-      </c>
-      <c r="B133" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+        <v>29</v>
+      </c>
+      <c r="B133" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C133" s="11" t="inlineStr">
         <is>
-          <t>AI Development Context: every module: API contract</t>
-        </is>
-      </c>
-      <c r="D133" s="11" t="inlineStr"/>
+          <t>Control Plane: one view - events</t>
+        </is>
+      </c>
+      <c r="D133" s="11" t="inlineStr">
+        <is>
+          <t>platform.json parses contracts/asyncapi/events.yaml's real channels</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="9" t="n">
-        <v>30</v>
-      </c>
-      <c r="B134" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+        <v>29</v>
+      </c>
+      <c r="B134" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C134" s="11" t="inlineStr">
         <is>
-          <t>AI Development Context: every module: event contracts</t>
-        </is>
-      </c>
-      <c r="D134" s="11" t="inlineStr"/>
+          <t>Control Plane: one view - API contracts</t>
+        </is>
+      </c>
+      <c r="D134" s="11" t="inlineStr">
+        <is>
+          <t>Links to the real OpenAPI/AsyncAPI files and the Backstage catalog (Phase 26)</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="9" t="n">
+        <v>29</v>
+      </c>
+      <c r="B135" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="C135" s="11" t="inlineStr">
+        <is>
+          <t>Control Plane: one view - health</t>
+        </is>
+      </c>
+      <c r="D135" s="11" t="inlineStr">
+        <is>
+          <t>Reuses the existing real getSystemHealth() live /healthz calls</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="9" t="n">
+        <v>29</v>
+      </c>
+      <c r="B136" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="C136" s="11" t="inlineStr">
+        <is>
+          <t>Control Plane: one view - alerts</t>
+        </is>
+      </c>
+      <c r="D136" s="11" t="inlineStr">
+        <is>
+          <t>New live fetch of Prometheus's real GET /api/v1/alerts (Phase 28's rules) - cross-checked live against a direct curl to the same endpoint</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="9" t="n">
+        <v>29</v>
+      </c>
+      <c r="B137" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="C137" s="11" t="inlineStr">
+        <is>
+          <t>Control Plane: one view - recent changes</t>
+        </is>
+      </c>
+      <c r="D137" s="11" t="inlineStr">
+        <is>
+          <t>New real `git log` of the checkout, run server-side - not a hand-maintained changelog</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="B135" s="13" t="inlineStr">
+      <c r="B138" s="13" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="C135" s="11" t="inlineStr">
+      <c r="C138" s="11" t="inlineStr">
+        <is>
+          <t>AI Development Context: every module: README</t>
+        </is>
+      </c>
+      <c r="D138" s="11" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="B139" s="13" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="C139" s="11" t="inlineStr">
+        <is>
+          <t>AI Development Context: every module: ownership metadata</t>
+        </is>
+      </c>
+      <c r="D139" s="11" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="B140" s="13" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="C140" s="11" t="inlineStr">
+        <is>
+          <t>AI Development Context: every module: dependencies</t>
+        </is>
+      </c>
+      <c r="D140" s="11" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="B141" s="13" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="C141" s="11" t="inlineStr">
+        <is>
+          <t>AI Development Context: every module: API contract</t>
+        </is>
+      </c>
+      <c r="D141" s="11" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="B142" s="13" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="C142" s="11" t="inlineStr">
+        <is>
+          <t>AI Development Context: every module: event contracts</t>
+        </is>
+      </c>
+      <c r="D142" s="11" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="B143" s="13" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="C143" s="11" t="inlineStr">
         <is>
           <t>AI Development Context: every module: DB ownership</t>
         </is>
       </c>
-      <c r="D135" s="11" t="inlineStr"/>
+      <c r="D143" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8836,7 +9008,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -9392,6 +9564,28 @@
       <c r="D25" s="11" t="inlineStr">
         <is>
           <t>Needs core-api/realtime-gateway/worker actually running (steps 5-7). Every panel is real data (Phase 28) - API latency, error rate, requests/sec, DB connections, WebSocket connections, Redis latency, notification/job failures. Prometheus alerts: http://localhost:9090/alerts. Loki/Tempo: query via Grafana's Explore tab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="48" customHeight="1">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="inlineStr">
+        <is>
+          <t>See the whole platform in one view</t>
+        </is>
+      </c>
+      <c r="C26" s="11" t="inlineStr">
+        <is>
+          <t>Sign into the Admin Portal (step 19), then Overview -&gt; Control Plane</t>
+        </is>
+      </c>
+      <c r="D26" s="11" t="inlineStr">
+        <is>
+          <t>Phase 29 - applications, per-service health/real versions (git SHA), environment, the real dependency graph, database ownership, events, API contract links, live Prometheus alerts, and a real git log, all on one real page. Prometheus (step 24's stack) must be running for the Alerts section to show live data - it degrades to an honest empty list otherwise, not an error.</t>
         </is>
       </c>
     </row>

--- a/docs/control/data.xlsx
+++ b/docs/control/data.xlsx
@@ -63,7 +63,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -78,11 +78,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D1FAE5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00DBEAFE"/>
       </patternFill>
     </fill>
     <fill>
@@ -117,7 +112,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -143,9 +138,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -239,8 +231,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="TodoChecklist" displayName="TodoChecklist" ref="A1:D143" headerRowCount="1">
-  <autoFilter ref="A1:D143"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="TodoChecklist" displayName="TodoChecklist" ref="A1:D146" headerRowCount="1">
+  <autoFilter ref="A1:D146"/>
   <tableColumns count="4">
     <tableColumn id="1" name="Phase"/>
     <tableColumn id="2" name="Status"/>
@@ -633,12 +625,12 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>29 / 30</t>
+          <t>30 / 30</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>97%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
@@ -803,7 +795,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>45</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -1647,9 +1639,9 @@
       <c r="A31" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="12" t="inlineStr">
-        <is>
-          <t>Next up</t>
+      <c r="B31" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr">
@@ -1659,7 +1651,7 @@
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>Machine-readable context for AI agents - every module carries README, ownership metadata, dependencies, API contract, event contracts, DB ownership, so an agent (like this one) can safely work on any part of the platform.</t>
+          <t>Audited and confirmed real per-module README/ownership/dependencies/API+event contracts/DB ownership already existed (Phases 26/29); closed the one genuine gap - 12 of 22 core-api modules had no handler-level (http_test.go) coverage - with real tests reading each module's actual source, never assumed. Rewrote docs/AI_CONTEXT.md and docs/architecture/overview.md from stale initial-commit stubs into a real description of the module pattern, testing convention, real-infra-only validation philosophy, and the phase loop this whole build actually followed.</t>
         </is>
       </c>
       <c r="E31" s="11" t="inlineStr">
@@ -1682,7 +1674,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D143"/>
+  <dimension ref="A1:D146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2237,7 +2229,7 @@
       <c r="A34" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="B34" s="13" t="inlineStr">
+      <c r="B34" s="12" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -2257,7 +2249,7 @@
       <c r="A35" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="B35" s="13" t="inlineStr">
+      <c r="B35" s="12" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -2277,7 +2269,7 @@
       <c r="A36" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="B36" s="13" t="inlineStr">
+      <c r="B36" s="12" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -2393,7 +2385,7 @@
       <c r="A43" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="B43" s="13" t="inlineStr">
+      <c r="B43" s="12" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -2413,7 +2405,7 @@
       <c r="A44" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="B44" s="13" t="inlineStr">
+      <c r="B44" s="12" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -2613,7 +2605,7 @@
       <c r="A56" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="B56" s="13" t="inlineStr">
+      <c r="B56" s="12" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -2633,7 +2625,7 @@
       <c r="A57" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="B57" s="13" t="inlineStr">
+      <c r="B57" s="12" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -2721,7 +2713,7 @@
       <c r="A62" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="B62" s="13" t="inlineStr">
+      <c r="B62" s="12" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -2741,7 +2733,7 @@
       <c r="A63" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="B63" s="13" t="inlineStr">
+      <c r="B63" s="12" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -2809,7 +2801,7 @@
       <c r="A67" s="9" t="n">
         <v>23</v>
       </c>
-      <c r="B67" s="13" t="inlineStr">
+      <c r="B67" s="12" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -2865,7 +2857,7 @@
       <c r="A70" s="9" t="n">
         <v>24</v>
       </c>
-      <c r="B70" s="13" t="inlineStr">
+      <c r="B70" s="12" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -2885,7 +2877,7 @@
       <c r="A71" s="9" t="n">
         <v>24</v>
       </c>
-      <c r="B71" s="13" t="inlineStr">
+      <c r="B71" s="12" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -2905,7 +2897,7 @@
       <c r="A72" s="9" t="n">
         <v>24</v>
       </c>
-      <c r="B72" s="13" t="inlineStr">
+      <c r="B72" s="12" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -3053,7 +3045,7 @@
       <c r="A81" s="9" t="n">
         <v>24</v>
       </c>
-      <c r="B81" s="13" t="inlineStr">
+      <c r="B81" s="12" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -3217,7 +3209,7 @@
       <c r="A90" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="B90" s="13" t="inlineStr">
+      <c r="B90" s="12" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -3237,7 +3229,7 @@
       <c r="A91" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="B91" s="13" t="inlineStr">
+      <c r="B91" s="12" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -3377,7 +3369,7 @@
       <c r="A98" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="B98" s="13" t="inlineStr">
+      <c r="B98" s="12" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -3617,7 +3609,7 @@
       <c r="A110" s="9" t="n">
         <v>27</v>
       </c>
-      <c r="B110" s="13" t="inlineStr">
+      <c r="B110" s="12" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -3797,7 +3789,7 @@
       <c r="A119" s="9" t="n">
         <v>28</v>
       </c>
-      <c r="B119" s="13" t="inlineStr">
+      <c r="B119" s="12" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -3917,7 +3909,7 @@
       <c r="A125" s="9" t="n">
         <v>28</v>
       </c>
-      <c r="B125" s="13" t="inlineStr">
+      <c r="B125" s="12" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -3937,7 +3929,7 @@
       <c r="A126" s="9" t="n">
         <v>28</v>
       </c>
-      <c r="B126" s="13" t="inlineStr">
+      <c r="B126" s="12" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -4037,7 +4029,7 @@
       <c r="A131" s="9" t="n">
         <v>29</v>
       </c>
-      <c r="B131" s="13" t="inlineStr">
+      <c r="B131" s="12" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -4177,97 +4169,181 @@
       <c r="A138" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="B138" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B138" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C138" s="11" t="inlineStr">
         <is>
-          <t>AI Development Context: every module: README</t>
-        </is>
-      </c>
-      <c r="D138" s="11" t="inlineStr"/>
+          <t>AI Development Context: every module - README</t>
+        </is>
+      </c>
+      <c r="D138" s="11" t="inlineStr">
+        <is>
+          <t>backend/core-api/internal/&lt;module&gt;/README.md - real Responsibilities/Non-responsibilities/Layout/Storage sections, the actual architecture notes (already real since early phases, confirmed this phase)</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="B139" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B139" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C139" s="11" t="inlineStr">
         <is>
-          <t>AI Development Context: every module: ownership metadata</t>
-        </is>
-      </c>
-      <c r="D139" s="11" t="inlineStr"/>
+          <t>AI Development Context: every module - ownership metadata</t>
+        </is>
+      </c>
+      <c r="D139" s="11" t="inlineStr">
+        <is>
+          <t>modules/*/module.yaml (owner/lifecycle) - real since Phase 26</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="B140" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B140" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C140" s="11" t="inlineStr">
         <is>
-          <t>AI Development Context: every module: dependencies</t>
-        </is>
-      </c>
-      <c r="D140" s="11" t="inlineStr"/>
+          <t>AI Development Context: every module - dependencies</t>
+        </is>
+      </c>
+      <c r="D140" s="11" t="inlineStr">
+        <is>
+          <t>modules/*/module.yaml + catalog/system.yaml's dependsOn graph - real since Phase 26</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="B141" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B141" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C141" s="11" t="inlineStr">
         <is>
-          <t>AI Development Context: every module: API contract</t>
-        </is>
-      </c>
-      <c r="D141" s="11" t="inlineStr"/>
+          <t>AI Development Context: every module - API contract</t>
+        </is>
+      </c>
+      <c r="D141" s="11" t="inlineStr">
+        <is>
+          <t>contracts/openapi/core-api.yaml, module-prefixed operationIds - real since Phase 26</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="B142" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B142" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C142" s="11" t="inlineStr">
         <is>
-          <t>AI Development Context: every module: event contracts</t>
-        </is>
-      </c>
-      <c r="D142" s="11" t="inlineStr"/>
+          <t>AI Development Context: every module - event contracts</t>
+        </is>
+      </c>
+      <c r="D142" s="11" t="inlineStr">
+        <is>
+          <t>contracts/asyncapi/events.yaml, cross-checked against real outbox.Record call sites - real since Phase 26</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="B143" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="B143" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C143" s="11" t="inlineStr">
         <is>
-          <t>AI Development Context: every module: DB ownership</t>
-        </is>
-      </c>
-      <c r="D143" s="11" t="inlineStr"/>
+          <t>AI Development Context: every module - DB ownership</t>
+        </is>
+      </c>
+      <c r="D143" s="11" t="inlineStr">
+        <is>
+          <t>docs/control/platform.json's Modules export - real since Phase 29</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="B144" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="C144" s="11" t="inlineStr">
+        <is>
+          <t>AI Development Context: every module - tests</t>
+        </is>
+      </c>
+      <c r="D144" s="11" t="inlineStr">
+        <is>
+          <t>Service-layer tests were already real everywhere; closed the real gap this phase found - 12 of 22 core-api modules (aigateway, analytics, audit, authz, billing, features, jobs, privacy, remoteconfig, search, trustsafety, workflows) had no http_test.go handler-layer coverage. All 12 now have 3-5 tests each against the real router, reading actual source rather than assumed shapes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="B145" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="C145" s="11" t="inlineStr">
+        <is>
+          <t>AI Development Context: docs/AI_CONTEXT.md reflects real architecture rules</t>
+        </is>
+      </c>
+      <c r="D145" s="11" t="inlineStr">
+        <is>
+          <t>Rewritten from a 26-line initial-commit stub into a real description of the layered module pattern, consumer-defined interfaces, two-phase wiring, the testing convention, real-infra-only validation, the catalog/SDK/observability stack, and the Inspect-Design-Implement-Test-Validate-Document-Commit phase loop this whole build followed</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="B146" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="C146" s="11" t="inlineStr">
+        <is>
+          <t>AI Development Context: docs/architecture/overview.md kept current</t>
+        </is>
+      </c>
+      <c r="D146" s="11" t="inlineStr">
+        <is>
+          <t>Diagram and principles updated to include Keycloak/OpenFGA, the 3 SDKs, Backstage, the observability stack, and the Admin Portal - all previously entirely absent from the diagram</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
